--- a/excel/Pliki+Mistrz+Excela/początkowe/Rozdział 09 - Formatowanie warunkowe.xlsx
+++ b/excel/Pliki+Mistrz+Excela/początkowe/Rozdział 09 - Formatowanie warunkowe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huber\Desktop\portf\kursy\learning-practice-path\excel\Pliki+Mistrz+Excela\początkowe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6E0C02-1A56-47C8-B529-57C72944E146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D821D1D0-5C08-45F5-A8D3-CB8E4D47B11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="777" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="777" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExceliAdam" sheetId="44" r:id="rId1"/>
@@ -11121,49 +11121,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="34" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="36" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="34" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="37" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="35" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="36" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="36" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="35" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
@@ -11174,6 +11142,38 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="36" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="37" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="34" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="34" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="38">
@@ -11216,7 +11216,35 @@
     <cellStyle name="Wrap Text" xfId="29" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="ziel" xfId="30" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -11225,37 +11253,44 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <numFmt numFmtId="171" formatCode="#,##0\ &quot;zł&quot;"/>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="#,##0.00\ &quot;zł&quot;"/>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="-0.24994659260841701"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11317,51 +11352,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -12447,10 +12442,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="G1:G11" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16" dataCellStyle="Normalny 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="G1:G11" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18" dataCellStyle="Normalny 2">
   <autoFilter ref="G1:G11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Punkty" dataDxfId="15" dataCellStyle="Normalny 2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Punkty" dataDxfId="17" dataCellStyle="Normalny 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12851,38 +12846,38 @@
       <c r="W2" s="35"/>
       <c r="X2" s="35"/>
       <c r="Y2" s="35"/>
-      <c r="Z2" s="68" t="s">
+      <c r="Z2" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="AA2" s="68"/>
-      <c r="AB2" s="68"/>
-      <c r="AC2" s="68"/>
-      <c r="AD2" s="68"/>
-      <c r="AE2" s="68"/>
-      <c r="AF2" s="68"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="68"/>
-      <c r="AI2" s="68"/>
-      <c r="AJ2" s="68"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="68"/>
-      <c r="AM2" s="68"/>
-      <c r="AN2" s="68"/>
-      <c r="AO2" s="68"/>
-      <c r="AP2" s="68"/>
-      <c r="AQ2" s="68"/>
-      <c r="AR2" s="68"/>
-      <c r="AS2" s="68"/>
-      <c r="AT2" s="68"/>
-      <c r="AU2" s="68"/>
-      <c r="AV2" s="68"/>
-      <c r="AW2" s="68"/>
-      <c r="AX2" s="68"/>
-      <c r="AY2" s="68"/>
-      <c r="AZ2" s="68"/>
-      <c r="BA2" s="68"/>
-      <c r="BB2" s="68"/>
-      <c r="BC2" s="68"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="55"/>
+      <c r="AR2" s="55"/>
+      <c r="AS2" s="55"/>
+      <c r="AT2" s="55"/>
+      <c r="AU2" s="55"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="55"/>
+      <c r="BB2" s="55"/>
+      <c r="BC2" s="55"/>
       <c r="BD2" s="36"/>
       <c r="BE2" s="35"/>
       <c r="BF2" s="35"/>
@@ -12937,36 +12932,36 @@
       <c r="W3" s="35"/>
       <c r="X3" s="35"/>
       <c r="Y3" s="35"/>
-      <c r="Z3" s="68"/>
-      <c r="AA3" s="68"/>
-      <c r="AB3" s="68"/>
-      <c r="AC3" s="68"/>
-      <c r="AD3" s="68"/>
-      <c r="AE3" s="68"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
-      <c r="AM3" s="68"/>
-      <c r="AN3" s="68"/>
-      <c r="AO3" s="68"/>
-      <c r="AP3" s="68"/>
-      <c r="AQ3" s="68"/>
-      <c r="AR3" s="68"/>
-      <c r="AS3" s="68"/>
-      <c r="AT3" s="68"/>
-      <c r="AU3" s="68"/>
-      <c r="AV3" s="68"/>
-      <c r="AW3" s="68"/>
-      <c r="AX3" s="68"/>
-      <c r="AY3" s="68"/>
-      <c r="AZ3" s="68"/>
-      <c r="BA3" s="68"/>
-      <c r="BB3" s="68"/>
-      <c r="BC3" s="68"/>
+      <c r="Z3" s="55"/>
+      <c r="AA3" s="55"/>
+      <c r="AB3" s="55"/>
+      <c r="AC3" s="55"/>
+      <c r="AD3" s="55"/>
+      <c r="AE3" s="55"/>
+      <c r="AF3" s="55"/>
+      <c r="AG3" s="55"/>
+      <c r="AH3" s="55"/>
+      <c r="AI3" s="55"/>
+      <c r="AJ3" s="55"/>
+      <c r="AK3" s="55"/>
+      <c r="AL3" s="55"/>
+      <c r="AM3" s="55"/>
+      <c r="AN3" s="55"/>
+      <c r="AO3" s="55"/>
+      <c r="AP3" s="55"/>
+      <c r="AQ3" s="55"/>
+      <c r="AR3" s="55"/>
+      <c r="AS3" s="55"/>
+      <c r="AT3" s="55"/>
+      <c r="AU3" s="55"/>
+      <c r="AV3" s="55"/>
+      <c r="AW3" s="55"/>
+      <c r="AX3" s="55"/>
+      <c r="AY3" s="55"/>
+      <c r="AZ3" s="55"/>
+      <c r="BA3" s="55"/>
+      <c r="BB3" s="55"/>
+      <c r="BC3" s="55"/>
       <c r="BD3" s="36"/>
       <c r="BE3" s="35"/>
       <c r="BF3" s="35"/>
@@ -13021,38 +13016,38 @@
       <c r="W4" s="35"/>
       <c r="X4" s="35"/>
       <c r="Y4" s="35"/>
-      <c r="Z4" s="63" t="s">
+      <c r="Z4" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="AA4" s="63"/>
-      <c r="AB4" s="63"/>
-      <c r="AC4" s="63"/>
-      <c r="AD4" s="63"/>
-      <c r="AE4" s="63"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="63"/>
-      <c r="AH4" s="63"/>
-      <c r="AI4" s="63"/>
-      <c r="AJ4" s="63"/>
-      <c r="AK4" s="63"/>
-      <c r="AL4" s="63"/>
-      <c r="AM4" s="63"/>
-      <c r="AN4" s="63"/>
-      <c r="AO4" s="63"/>
-      <c r="AP4" s="63"/>
-      <c r="AQ4" s="63"/>
-      <c r="AR4" s="63"/>
-      <c r="AS4" s="63"/>
-      <c r="AT4" s="63"/>
-      <c r="AU4" s="63"/>
-      <c r="AV4" s="63"/>
-      <c r="AW4" s="63"/>
-      <c r="AX4" s="63"/>
-      <c r="AY4" s="63"/>
-      <c r="AZ4" s="63"/>
-      <c r="BA4" s="63"/>
-      <c r="BB4" s="63"/>
-      <c r="BC4" s="63"/>
+      <c r="AA4" s="56"/>
+      <c r="AB4" s="56"/>
+      <c r="AC4" s="56"/>
+      <c r="AD4" s="56"/>
+      <c r="AE4" s="56"/>
+      <c r="AF4" s="56"/>
+      <c r="AG4" s="56"/>
+      <c r="AH4" s="56"/>
+      <c r="AI4" s="56"/>
+      <c r="AJ4" s="56"/>
+      <c r="AK4" s="56"/>
+      <c r="AL4" s="56"/>
+      <c r="AM4" s="56"/>
+      <c r="AN4" s="56"/>
+      <c r="AO4" s="56"/>
+      <c r="AP4" s="56"/>
+      <c r="AQ4" s="56"/>
+      <c r="AR4" s="56"/>
+      <c r="AS4" s="56"/>
+      <c r="AT4" s="56"/>
+      <c r="AU4" s="56"/>
+      <c r="AV4" s="56"/>
+      <c r="AW4" s="56"/>
+      <c r="AX4" s="56"/>
+      <c r="AY4" s="56"/>
+      <c r="AZ4" s="56"/>
+      <c r="BA4" s="56"/>
+      <c r="BB4" s="56"/>
+      <c r="BC4" s="56"/>
       <c r="BD4" s="37"/>
       <c r="BE4" s="35"/>
       <c r="BF4" s="35"/>
@@ -13099,56 +13094,56 @@
       <c r="CU4" s="35"/>
     </row>
     <row r="5" spans="18:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="R5" s="69" t="s">
+      <c r="R5" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="S5" s="69"/>
-      <c r="T5" s="69"/>
-      <c r="U5" s="69"/>
-      <c r="V5" s="69"/>
-      <c r="W5" s="69"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="57"/>
       <c r="X5" s="35"/>
       <c r="Y5" s="35"/>
-      <c r="Z5" s="63"/>
-      <c r="AA5" s="63"/>
-      <c r="AB5" s="63"/>
-      <c r="AC5" s="63"/>
-      <c r="AD5" s="63"/>
-      <c r="AE5" s="63"/>
-      <c r="AF5" s="63"/>
-      <c r="AG5" s="63"/>
-      <c r="AH5" s="63"/>
-      <c r="AI5" s="63"/>
-      <c r="AJ5" s="63"/>
-      <c r="AK5" s="63"/>
-      <c r="AL5" s="63"/>
-      <c r="AM5" s="63"/>
-      <c r="AN5" s="63"/>
-      <c r="AO5" s="63"/>
-      <c r="AP5" s="63"/>
-      <c r="AQ5" s="63"/>
-      <c r="AR5" s="63"/>
-      <c r="AS5" s="63"/>
-      <c r="AT5" s="63"/>
-      <c r="AU5" s="63"/>
-      <c r="AV5" s="63"/>
-      <c r="AW5" s="63"/>
-      <c r="AX5" s="63"/>
-      <c r="AY5" s="63"/>
-      <c r="AZ5" s="63"/>
-      <c r="BA5" s="63"/>
-      <c r="BB5" s="63"/>
-      <c r="BC5" s="63"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="56"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="56"/>
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="56"/>
+      <c r="AH5" s="56"/>
+      <c r="AI5" s="56"/>
+      <c r="AJ5" s="56"/>
+      <c r="AK5" s="56"/>
+      <c r="AL5" s="56"/>
+      <c r="AM5" s="56"/>
+      <c r="AN5" s="56"/>
+      <c r="AO5" s="56"/>
+      <c r="AP5" s="56"/>
+      <c r="AQ5" s="56"/>
+      <c r="AR5" s="56"/>
+      <c r="AS5" s="56"/>
+      <c r="AT5" s="56"/>
+      <c r="AU5" s="56"/>
+      <c r="AV5" s="56"/>
+      <c r="AW5" s="56"/>
+      <c r="AX5" s="56"/>
+      <c r="AY5" s="56"/>
+      <c r="AZ5" s="56"/>
+      <c r="BA5" s="56"/>
+      <c r="BB5" s="56"/>
+      <c r="BC5" s="56"/>
       <c r="BD5" s="37"/>
       <c r="BE5" s="35"/>
-      <c r="BF5" s="69" t="s">
+      <c r="BF5" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="BG5" s="69"/>
-      <c r="BH5" s="69"/>
-      <c r="BI5" s="69"/>
-      <c r="BJ5" s="69"/>
-      <c r="BK5" s="69"/>
+      <c r="BG5" s="57"/>
+      <c r="BH5" s="57"/>
+      <c r="BI5" s="57"/>
+      <c r="BJ5" s="57"/>
+      <c r="BK5" s="57"/>
       <c r="BL5" s="35"/>
       <c r="BM5" s="35"/>
       <c r="BN5" s="35"/>
@@ -13187,52 +13182,52 @@
       <c r="CU5" s="35"/>
     </row>
     <row r="6" spans="18:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="R6" s="69"/>
-      <c r="S6" s="69"/>
-      <c r="T6" s="69"/>
-      <c r="U6" s="69"/>
-      <c r="V6" s="69"/>
-      <c r="W6" s="69"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="57"/>
+      <c r="U6" s="57"/>
+      <c r="V6" s="57"/>
+      <c r="W6" s="57"/>
       <c r="X6" s="35"/>
       <c r="Y6" s="35"/>
-      <c r="Z6" s="63"/>
-      <c r="AA6" s="63"/>
-      <c r="AB6" s="63"/>
-      <c r="AC6" s="63"/>
-      <c r="AD6" s="63"/>
-      <c r="AE6" s="63"/>
-      <c r="AF6" s="63"/>
-      <c r="AG6" s="63"/>
-      <c r="AH6" s="63"/>
-      <c r="AI6" s="63"/>
-      <c r="AJ6" s="63"/>
-      <c r="AK6" s="63"/>
-      <c r="AL6" s="63"/>
-      <c r="AM6" s="63"/>
-      <c r="AN6" s="63"/>
-      <c r="AO6" s="63"/>
-      <c r="AP6" s="63"/>
-      <c r="AQ6" s="63"/>
-      <c r="AR6" s="63"/>
-      <c r="AS6" s="63"/>
-      <c r="AT6" s="63"/>
-      <c r="AU6" s="63"/>
-      <c r="AV6" s="63"/>
-      <c r="AW6" s="63"/>
-      <c r="AX6" s="63"/>
-      <c r="AY6" s="63"/>
-      <c r="AZ6" s="63"/>
-      <c r="BA6" s="63"/>
-      <c r="BB6" s="63"/>
-      <c r="BC6" s="63"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="56"/>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="56"/>
+      <c r="AF6" s="56"/>
+      <c r="AG6" s="56"/>
+      <c r="AH6" s="56"/>
+      <c r="AI6" s="56"/>
+      <c r="AJ6" s="56"/>
+      <c r="AK6" s="56"/>
+      <c r="AL6" s="56"/>
+      <c r="AM6" s="56"/>
+      <c r="AN6" s="56"/>
+      <c r="AO6" s="56"/>
+      <c r="AP6" s="56"/>
+      <c r="AQ6" s="56"/>
+      <c r="AR6" s="56"/>
+      <c r="AS6" s="56"/>
+      <c r="AT6" s="56"/>
+      <c r="AU6" s="56"/>
+      <c r="AV6" s="56"/>
+      <c r="AW6" s="56"/>
+      <c r="AX6" s="56"/>
+      <c r="AY6" s="56"/>
+      <c r="AZ6" s="56"/>
+      <c r="BA6" s="56"/>
+      <c r="BB6" s="56"/>
+      <c r="BC6" s="56"/>
       <c r="BD6" s="37"/>
       <c r="BE6" s="35"/>
-      <c r="BF6" s="69"/>
-      <c r="BG6" s="69"/>
-      <c r="BH6" s="69"/>
-      <c r="BI6" s="69"/>
-      <c r="BJ6" s="69"/>
-      <c r="BK6" s="69"/>
+      <c r="BF6" s="57"/>
+      <c r="BG6" s="57"/>
+      <c r="BH6" s="57"/>
+      <c r="BI6" s="57"/>
+      <c r="BJ6" s="57"/>
+      <c r="BK6" s="57"/>
       <c r="BL6" s="35"/>
       <c r="BM6" s="35"/>
       <c r="BN6" s="35"/>
@@ -13271,12 +13266,12 @@
       <c r="CU6" s="35"/>
     </row>
     <row r="7" spans="18:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="R7" s="69"/>
-      <c r="S7" s="69"/>
-      <c r="T7" s="69"/>
-      <c r="U7" s="69"/>
-      <c r="V7" s="69"/>
-      <c r="W7" s="69"/>
+      <c r="R7" s="57"/>
+      <c r="S7" s="57"/>
+      <c r="T7" s="57"/>
+      <c r="U7" s="57"/>
+      <c r="V7" s="57"/>
+      <c r="W7" s="57"/>
       <c r="X7" s="38"/>
       <c r="Y7" s="35"/>
       <c r="Z7" s="35"/>
@@ -13311,12 +13306,12 @@
       <c r="BC7" s="35"/>
       <c r="BD7" s="35"/>
       <c r="BE7" s="35"/>
-      <c r="BF7" s="69"/>
-      <c r="BG7" s="69"/>
-      <c r="BH7" s="69"/>
-      <c r="BI7" s="69"/>
-      <c r="BJ7" s="69"/>
-      <c r="BK7" s="69"/>
+      <c r="BF7" s="57"/>
+      <c r="BG7" s="57"/>
+      <c r="BH7" s="57"/>
+      <c r="BI7" s="57"/>
+      <c r="BJ7" s="57"/>
+      <c r="BK7" s="57"/>
       <c r="BL7" s="35"/>
       <c r="BM7" s="35"/>
       <c r="BN7" s="35"/>
@@ -13447,38 +13442,38 @@
       <c r="W9" s="39"/>
       <c r="X9" s="39"/>
       <c r="Y9" s="39"/>
-      <c r="Z9" s="70" t="s">
+      <c r="Z9" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="AA9" s="70"/>
-      <c r="AB9" s="70"/>
-      <c r="AC9" s="70"/>
-      <c r="AD9" s="70"/>
-      <c r="AE9" s="70"/>
-      <c r="AF9" s="70"/>
-      <c r="AG9" s="70"/>
-      <c r="AH9" s="70"/>
-      <c r="AI9" s="70"/>
-      <c r="AJ9" s="70"/>
-      <c r="AK9" s="70"/>
-      <c r="AL9" s="70"/>
-      <c r="AM9" s="70"/>
-      <c r="AN9" s="70"/>
-      <c r="AO9" s="70"/>
-      <c r="AP9" s="70"/>
-      <c r="AQ9" s="70"/>
-      <c r="AR9" s="70"/>
-      <c r="AS9" s="70"/>
-      <c r="AT9" s="70"/>
-      <c r="AU9" s="70"/>
-      <c r="AV9" s="70"/>
-      <c r="AW9" s="70"/>
-      <c r="AX9" s="70"/>
-      <c r="AY9" s="70"/>
-      <c r="AZ9" s="70"/>
-      <c r="BA9" s="70"/>
-      <c r="BB9" s="70"/>
-      <c r="BC9" s="70"/>
+      <c r="AA9" s="58"/>
+      <c r="AB9" s="58"/>
+      <c r="AC9" s="58"/>
+      <c r="AD9" s="58"/>
+      <c r="AE9" s="58"/>
+      <c r="AF9" s="58"/>
+      <c r="AG9" s="58"/>
+      <c r="AH9" s="58"/>
+      <c r="AI9" s="58"/>
+      <c r="AJ9" s="58"/>
+      <c r="AK9" s="58"/>
+      <c r="AL9" s="58"/>
+      <c r="AM9" s="58"/>
+      <c r="AN9" s="58"/>
+      <c r="AO9" s="58"/>
+      <c r="AP9" s="58"/>
+      <c r="AQ9" s="58"/>
+      <c r="AR9" s="58"/>
+      <c r="AS9" s="58"/>
+      <c r="AT9" s="58"/>
+      <c r="AU9" s="58"/>
+      <c r="AV9" s="58"/>
+      <c r="AW9" s="58"/>
+      <c r="AX9" s="58"/>
+      <c r="AY9" s="58"/>
+      <c r="AZ9" s="58"/>
+      <c r="BA9" s="58"/>
+      <c r="BB9" s="58"/>
+      <c r="BC9" s="58"/>
       <c r="BD9" s="40"/>
       <c r="BE9" s="35"/>
       <c r="BF9" s="39"/>
@@ -13489,38 +13484,38 @@
       <c r="BK9" s="39"/>
       <c r="BL9" s="39"/>
       <c r="BM9" s="39"/>
-      <c r="BN9" s="60" t="s">
+      <c r="BN9" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="BO9" s="60"/>
-      <c r="BP9" s="60"/>
-      <c r="BQ9" s="60"/>
-      <c r="BR9" s="60"/>
-      <c r="BS9" s="60"/>
-      <c r="BT9" s="60"/>
-      <c r="BU9" s="60"/>
-      <c r="BV9" s="60"/>
-      <c r="BW9" s="60"/>
-      <c r="BX9" s="60"/>
-      <c r="BY9" s="60"/>
-      <c r="BZ9" s="60"/>
-      <c r="CA9" s="60"/>
-      <c r="CB9" s="60"/>
-      <c r="CC9" s="60"/>
-      <c r="CD9" s="60"/>
-      <c r="CE9" s="60"/>
-      <c r="CF9" s="60"/>
-      <c r="CG9" s="60"/>
-      <c r="CH9" s="60"/>
-      <c r="CI9" s="60"/>
-      <c r="CJ9" s="60"/>
-      <c r="CK9" s="60"/>
-      <c r="CL9" s="60"/>
-      <c r="CM9" s="60"/>
-      <c r="CN9" s="60"/>
-      <c r="CO9" s="60"/>
-      <c r="CP9" s="60"/>
-      <c r="CQ9" s="60"/>
+      <c r="BO9" s="52"/>
+      <c r="BP9" s="52"/>
+      <c r="BQ9" s="52"/>
+      <c r="BR9" s="52"/>
+      <c r="BS9" s="52"/>
+      <c r="BT9" s="52"/>
+      <c r="BU9" s="52"/>
+      <c r="BV9" s="52"/>
+      <c r="BW9" s="52"/>
+      <c r="BX9" s="52"/>
+      <c r="BY9" s="52"/>
+      <c r="BZ9" s="52"/>
+      <c r="CA9" s="52"/>
+      <c r="CB9" s="52"/>
+      <c r="CC9" s="52"/>
+      <c r="CD9" s="52"/>
+      <c r="CE9" s="52"/>
+      <c r="CF9" s="52"/>
+      <c r="CG9" s="52"/>
+      <c r="CH9" s="52"/>
+      <c r="CI9" s="52"/>
+      <c r="CJ9" s="52"/>
+      <c r="CK9" s="52"/>
+      <c r="CL9" s="52"/>
+      <c r="CM9" s="52"/>
+      <c r="CN9" s="52"/>
+      <c r="CO9" s="52"/>
+      <c r="CP9" s="52"/>
+      <c r="CQ9" s="52"/>
       <c r="CR9" s="41"/>
       <c r="CS9" s="41"/>
       <c r="CT9" s="41"/>
@@ -13535,36 +13530,36 @@
       <c r="W10" s="35"/>
       <c r="X10" s="35"/>
       <c r="Y10" s="35"/>
-      <c r="Z10" s="71"/>
-      <c r="AA10" s="71"/>
-      <c r="AB10" s="71"/>
-      <c r="AC10" s="71"/>
-      <c r="AD10" s="71"/>
-      <c r="AE10" s="71"/>
-      <c r="AF10" s="71"/>
-      <c r="AG10" s="71"/>
-      <c r="AH10" s="71"/>
-      <c r="AI10" s="71"/>
-      <c r="AJ10" s="71"/>
-      <c r="AK10" s="71"/>
-      <c r="AL10" s="71"/>
-      <c r="AM10" s="71"/>
-      <c r="AN10" s="71"/>
-      <c r="AO10" s="71"/>
-      <c r="AP10" s="71"/>
-      <c r="AQ10" s="71"/>
-      <c r="AR10" s="71"/>
-      <c r="AS10" s="71"/>
-      <c r="AT10" s="71"/>
-      <c r="AU10" s="71"/>
-      <c r="AV10" s="71"/>
-      <c r="AW10" s="71"/>
-      <c r="AX10" s="71"/>
-      <c r="AY10" s="71"/>
-      <c r="AZ10" s="71"/>
-      <c r="BA10" s="71"/>
-      <c r="BB10" s="71"/>
-      <c r="BC10" s="71"/>
+      <c r="Z10" s="59"/>
+      <c r="AA10" s="59"/>
+      <c r="AB10" s="59"/>
+      <c r="AC10" s="59"/>
+      <c r="AD10" s="59"/>
+      <c r="AE10" s="59"/>
+      <c r="AF10" s="59"/>
+      <c r="AG10" s="59"/>
+      <c r="AH10" s="59"/>
+      <c r="AI10" s="59"/>
+      <c r="AJ10" s="59"/>
+      <c r="AK10" s="59"/>
+      <c r="AL10" s="59"/>
+      <c r="AM10" s="59"/>
+      <c r="AN10" s="59"/>
+      <c r="AO10" s="59"/>
+      <c r="AP10" s="59"/>
+      <c r="AQ10" s="59"/>
+      <c r="AR10" s="59"/>
+      <c r="AS10" s="59"/>
+      <c r="AT10" s="59"/>
+      <c r="AU10" s="59"/>
+      <c r="AV10" s="59"/>
+      <c r="AW10" s="59"/>
+      <c r="AX10" s="59"/>
+      <c r="AY10" s="59"/>
+      <c r="AZ10" s="59"/>
+      <c r="BA10" s="59"/>
+      <c r="BB10" s="59"/>
+      <c r="BC10" s="59"/>
       <c r="BD10" s="40"/>
       <c r="BE10" s="35"/>
       <c r="BF10" s="35"/>
@@ -13575,36 +13570,36 @@
       <c r="BK10" s="35"/>
       <c r="BL10" s="35"/>
       <c r="BM10" s="35"/>
-      <c r="BN10" s="55"/>
-      <c r="BO10" s="55"/>
-      <c r="BP10" s="55"/>
-      <c r="BQ10" s="55"/>
-      <c r="BR10" s="55"/>
-      <c r="BS10" s="55"/>
-      <c r="BT10" s="55"/>
-      <c r="BU10" s="55"/>
-      <c r="BV10" s="55"/>
-      <c r="BW10" s="55"/>
-      <c r="BX10" s="55"/>
-      <c r="BY10" s="55"/>
-      <c r="BZ10" s="55"/>
-      <c r="CA10" s="55"/>
-      <c r="CB10" s="55"/>
-      <c r="CC10" s="55"/>
-      <c r="CD10" s="55"/>
-      <c r="CE10" s="55"/>
-      <c r="CF10" s="55"/>
-      <c r="CG10" s="55"/>
-      <c r="CH10" s="55"/>
-      <c r="CI10" s="55"/>
-      <c r="CJ10" s="55"/>
-      <c r="CK10" s="55"/>
-      <c r="CL10" s="55"/>
-      <c r="CM10" s="55"/>
-      <c r="CN10" s="55"/>
-      <c r="CO10" s="55"/>
-      <c r="CP10" s="55"/>
-      <c r="CQ10" s="55"/>
+      <c r="BN10" s="53"/>
+      <c r="BO10" s="53"/>
+      <c r="BP10" s="53"/>
+      <c r="BQ10" s="53"/>
+      <c r="BR10" s="53"/>
+      <c r="BS10" s="53"/>
+      <c r="BT10" s="53"/>
+      <c r="BU10" s="53"/>
+      <c r="BV10" s="53"/>
+      <c r="BW10" s="53"/>
+      <c r="BX10" s="53"/>
+      <c r="BY10" s="53"/>
+      <c r="BZ10" s="53"/>
+      <c r="CA10" s="53"/>
+      <c r="CB10" s="53"/>
+      <c r="CC10" s="53"/>
+      <c r="CD10" s="53"/>
+      <c r="CE10" s="53"/>
+      <c r="CF10" s="53"/>
+      <c r="CG10" s="53"/>
+      <c r="CH10" s="53"/>
+      <c r="CI10" s="53"/>
+      <c r="CJ10" s="53"/>
+      <c r="CK10" s="53"/>
+      <c r="CL10" s="53"/>
+      <c r="CM10" s="53"/>
+      <c r="CN10" s="53"/>
+      <c r="CO10" s="53"/>
+      <c r="CP10" s="53"/>
+      <c r="CQ10" s="53"/>
       <c r="CR10" s="41"/>
       <c r="CS10" s="41"/>
       <c r="CT10" s="41"/>
@@ -13619,36 +13614,36 @@
       <c r="W11" s="35"/>
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
-      <c r="Z11" s="71"/>
-      <c r="AA11" s="71"/>
-      <c r="AB11" s="71"/>
-      <c r="AC11" s="71"/>
-      <c r="AD11" s="71"/>
-      <c r="AE11" s="71"/>
-      <c r="AF11" s="71"/>
-      <c r="AG11" s="71"/>
-      <c r="AH11" s="71"/>
-      <c r="AI11" s="71"/>
-      <c r="AJ11" s="71"/>
-      <c r="AK11" s="71"/>
-      <c r="AL11" s="71"/>
-      <c r="AM11" s="71"/>
-      <c r="AN11" s="71"/>
-      <c r="AO11" s="71"/>
-      <c r="AP11" s="71"/>
-      <c r="AQ11" s="71"/>
-      <c r="AR11" s="71"/>
-      <c r="AS11" s="71"/>
-      <c r="AT11" s="71"/>
-      <c r="AU11" s="71"/>
-      <c r="AV11" s="71"/>
-      <c r="AW11" s="71"/>
-      <c r="AX11" s="71"/>
-      <c r="AY11" s="71"/>
-      <c r="AZ11" s="71"/>
-      <c r="BA11" s="71"/>
-      <c r="BB11" s="71"/>
-      <c r="BC11" s="71"/>
+      <c r="Z11" s="59"/>
+      <c r="AA11" s="59"/>
+      <c r="AB11" s="59"/>
+      <c r="AC11" s="59"/>
+      <c r="AD11" s="59"/>
+      <c r="AE11" s="59"/>
+      <c r="AF11" s="59"/>
+      <c r="AG11" s="59"/>
+      <c r="AH11" s="59"/>
+      <c r="AI11" s="59"/>
+      <c r="AJ11" s="59"/>
+      <c r="AK11" s="59"/>
+      <c r="AL11" s="59"/>
+      <c r="AM11" s="59"/>
+      <c r="AN11" s="59"/>
+      <c r="AO11" s="59"/>
+      <c r="AP11" s="59"/>
+      <c r="AQ11" s="59"/>
+      <c r="AR11" s="59"/>
+      <c r="AS11" s="59"/>
+      <c r="AT11" s="59"/>
+      <c r="AU11" s="59"/>
+      <c r="AV11" s="59"/>
+      <c r="AW11" s="59"/>
+      <c r="AX11" s="59"/>
+      <c r="AY11" s="59"/>
+      <c r="AZ11" s="59"/>
+      <c r="BA11" s="59"/>
+      <c r="BB11" s="59"/>
+      <c r="BC11" s="59"/>
       <c r="BD11" s="40"/>
       <c r="BE11" s="35"/>
       <c r="BF11" s="35"/>
@@ -13659,36 +13654,36 @@
       <c r="BK11" s="35"/>
       <c r="BL11" s="35"/>
       <c r="BM11" s="35"/>
-      <c r="BN11" s="55"/>
-      <c r="BO11" s="55"/>
-      <c r="BP11" s="55"/>
-      <c r="BQ11" s="55"/>
-      <c r="BR11" s="55"/>
-      <c r="BS11" s="55"/>
-      <c r="BT11" s="55"/>
-      <c r="BU11" s="55"/>
-      <c r="BV11" s="55"/>
-      <c r="BW11" s="55"/>
-      <c r="BX11" s="55"/>
-      <c r="BY11" s="55"/>
-      <c r="BZ11" s="55"/>
-      <c r="CA11" s="55"/>
-      <c r="CB11" s="55"/>
-      <c r="CC11" s="55"/>
-      <c r="CD11" s="55"/>
-      <c r="CE11" s="55"/>
-      <c r="CF11" s="55"/>
-      <c r="CG11" s="55"/>
-      <c r="CH11" s="55"/>
-      <c r="CI11" s="55"/>
-      <c r="CJ11" s="55"/>
-      <c r="CK11" s="55"/>
-      <c r="CL11" s="55"/>
-      <c r="CM11" s="55"/>
-      <c r="CN11" s="55"/>
-      <c r="CO11" s="55"/>
-      <c r="CP11" s="55"/>
-      <c r="CQ11" s="55"/>
+      <c r="BN11" s="53"/>
+      <c r="BO11" s="53"/>
+      <c r="BP11" s="53"/>
+      <c r="BQ11" s="53"/>
+      <c r="BR11" s="53"/>
+      <c r="BS11" s="53"/>
+      <c r="BT11" s="53"/>
+      <c r="BU11" s="53"/>
+      <c r="BV11" s="53"/>
+      <c r="BW11" s="53"/>
+      <c r="BX11" s="53"/>
+      <c r="BY11" s="53"/>
+      <c r="BZ11" s="53"/>
+      <c r="CA11" s="53"/>
+      <c r="CB11" s="53"/>
+      <c r="CC11" s="53"/>
+      <c r="CD11" s="53"/>
+      <c r="CE11" s="53"/>
+      <c r="CF11" s="53"/>
+      <c r="CG11" s="53"/>
+      <c r="CH11" s="53"/>
+      <c r="CI11" s="53"/>
+      <c r="CJ11" s="53"/>
+      <c r="CK11" s="53"/>
+      <c r="CL11" s="53"/>
+      <c r="CM11" s="53"/>
+      <c r="CN11" s="53"/>
+      <c r="CO11" s="53"/>
+      <c r="CP11" s="53"/>
+      <c r="CQ11" s="53"/>
       <c r="CR11" s="41"/>
       <c r="CS11" s="41"/>
       <c r="CT11" s="41"/>
@@ -13703,36 +13698,36 @@
       <c r="W12" s="35"/>
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
-      <c r="Z12" s="71"/>
-      <c r="AA12" s="71"/>
-      <c r="AB12" s="71"/>
-      <c r="AC12" s="71"/>
-      <c r="AD12" s="71"/>
-      <c r="AE12" s="71"/>
-      <c r="AF12" s="71"/>
-      <c r="AG12" s="71"/>
-      <c r="AH12" s="71"/>
-      <c r="AI12" s="71"/>
-      <c r="AJ12" s="71"/>
-      <c r="AK12" s="71"/>
-      <c r="AL12" s="71"/>
-      <c r="AM12" s="71"/>
-      <c r="AN12" s="71"/>
-      <c r="AO12" s="71"/>
-      <c r="AP12" s="71"/>
-      <c r="AQ12" s="71"/>
-      <c r="AR12" s="71"/>
-      <c r="AS12" s="71"/>
-      <c r="AT12" s="71"/>
-      <c r="AU12" s="71"/>
-      <c r="AV12" s="71"/>
-      <c r="AW12" s="71"/>
-      <c r="AX12" s="71"/>
-      <c r="AY12" s="71"/>
-      <c r="AZ12" s="71"/>
-      <c r="BA12" s="71"/>
-      <c r="BB12" s="71"/>
-      <c r="BC12" s="71"/>
+      <c r="Z12" s="59"/>
+      <c r="AA12" s="59"/>
+      <c r="AB12" s="59"/>
+      <c r="AC12" s="59"/>
+      <c r="AD12" s="59"/>
+      <c r="AE12" s="59"/>
+      <c r="AF12" s="59"/>
+      <c r="AG12" s="59"/>
+      <c r="AH12" s="59"/>
+      <c r="AI12" s="59"/>
+      <c r="AJ12" s="59"/>
+      <c r="AK12" s="59"/>
+      <c r="AL12" s="59"/>
+      <c r="AM12" s="59"/>
+      <c r="AN12" s="59"/>
+      <c r="AO12" s="59"/>
+      <c r="AP12" s="59"/>
+      <c r="AQ12" s="59"/>
+      <c r="AR12" s="59"/>
+      <c r="AS12" s="59"/>
+      <c r="AT12" s="59"/>
+      <c r="AU12" s="59"/>
+      <c r="AV12" s="59"/>
+      <c r="AW12" s="59"/>
+      <c r="AX12" s="59"/>
+      <c r="AY12" s="59"/>
+      <c r="AZ12" s="59"/>
+      <c r="BA12" s="59"/>
+      <c r="BB12" s="59"/>
+      <c r="BC12" s="59"/>
       <c r="BD12" s="40"/>
       <c r="BE12" s="35"/>
       <c r="BF12" s="35"/>
@@ -13743,38 +13738,38 @@
       <c r="BK12" s="35"/>
       <c r="BL12" s="35"/>
       <c r="BM12" s="35"/>
-      <c r="BN12" s="56" t="s">
+      <c r="BN12" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="BO12" s="56"/>
-      <c r="BP12" s="56"/>
-      <c r="BQ12" s="56"/>
-      <c r="BR12" s="56"/>
-      <c r="BS12" s="56"/>
-      <c r="BT12" s="56"/>
-      <c r="BU12" s="56"/>
-      <c r="BV12" s="56"/>
-      <c r="BW12" s="56"/>
-      <c r="BX12" s="56"/>
-      <c r="BY12" s="56"/>
-      <c r="BZ12" s="56"/>
-      <c r="CA12" s="56"/>
-      <c r="CB12" s="56"/>
-      <c r="CC12" s="56"/>
-      <c r="CD12" s="56"/>
-      <c r="CE12" s="56"/>
-      <c r="CF12" s="56"/>
-      <c r="CG12" s="56"/>
-      <c r="CH12" s="56"/>
-      <c r="CI12" s="56"/>
-      <c r="CJ12" s="56"/>
-      <c r="CK12" s="56"/>
-      <c r="CL12" s="56"/>
-      <c r="CM12" s="56"/>
-      <c r="CN12" s="56"/>
-      <c r="CO12" s="56"/>
-      <c r="CP12" s="56"/>
-      <c r="CQ12" s="56"/>
+      <c r="BO12" s="54"/>
+      <c r="BP12" s="54"/>
+      <c r="BQ12" s="54"/>
+      <c r="BR12" s="54"/>
+      <c r="BS12" s="54"/>
+      <c r="BT12" s="54"/>
+      <c r="BU12" s="54"/>
+      <c r="BV12" s="54"/>
+      <c r="BW12" s="54"/>
+      <c r="BX12" s="54"/>
+      <c r="BY12" s="54"/>
+      <c r="BZ12" s="54"/>
+      <c r="CA12" s="54"/>
+      <c r="CB12" s="54"/>
+      <c r="CC12" s="54"/>
+      <c r="CD12" s="54"/>
+      <c r="CE12" s="54"/>
+      <c r="CF12" s="54"/>
+      <c r="CG12" s="54"/>
+      <c r="CH12" s="54"/>
+      <c r="CI12" s="54"/>
+      <c r="CJ12" s="54"/>
+      <c r="CK12" s="54"/>
+      <c r="CL12" s="54"/>
+      <c r="CM12" s="54"/>
+      <c r="CN12" s="54"/>
+      <c r="CO12" s="54"/>
+      <c r="CP12" s="54"/>
+      <c r="CQ12" s="54"/>
       <c r="CR12" s="42"/>
       <c r="CS12" s="42"/>
       <c r="CT12" s="42"/>
@@ -13789,36 +13784,36 @@
       <c r="W13" s="35"/>
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
-      <c r="Z13" s="71"/>
-      <c r="AA13" s="71"/>
-      <c r="AB13" s="71"/>
-      <c r="AC13" s="71"/>
-      <c r="AD13" s="71"/>
-      <c r="AE13" s="71"/>
-      <c r="AF13" s="71"/>
-      <c r="AG13" s="71"/>
-      <c r="AH13" s="71"/>
-      <c r="AI13" s="71"/>
-      <c r="AJ13" s="71"/>
-      <c r="AK13" s="71"/>
-      <c r="AL13" s="71"/>
-      <c r="AM13" s="71"/>
-      <c r="AN13" s="71"/>
-      <c r="AO13" s="71"/>
-      <c r="AP13" s="71"/>
-      <c r="AQ13" s="71"/>
-      <c r="AR13" s="71"/>
-      <c r="AS13" s="71"/>
-      <c r="AT13" s="71"/>
-      <c r="AU13" s="71"/>
-      <c r="AV13" s="71"/>
-      <c r="AW13" s="71"/>
-      <c r="AX13" s="71"/>
-      <c r="AY13" s="71"/>
-      <c r="AZ13" s="71"/>
-      <c r="BA13" s="71"/>
-      <c r="BB13" s="71"/>
-      <c r="BC13" s="71"/>
+      <c r="Z13" s="59"/>
+      <c r="AA13" s="59"/>
+      <c r="AB13" s="59"/>
+      <c r="AC13" s="59"/>
+      <c r="AD13" s="59"/>
+      <c r="AE13" s="59"/>
+      <c r="AF13" s="59"/>
+      <c r="AG13" s="59"/>
+      <c r="AH13" s="59"/>
+      <c r="AI13" s="59"/>
+      <c r="AJ13" s="59"/>
+      <c r="AK13" s="59"/>
+      <c r="AL13" s="59"/>
+      <c r="AM13" s="59"/>
+      <c r="AN13" s="59"/>
+      <c r="AO13" s="59"/>
+      <c r="AP13" s="59"/>
+      <c r="AQ13" s="59"/>
+      <c r="AR13" s="59"/>
+      <c r="AS13" s="59"/>
+      <c r="AT13" s="59"/>
+      <c r="AU13" s="59"/>
+      <c r="AV13" s="59"/>
+      <c r="AW13" s="59"/>
+      <c r="AX13" s="59"/>
+      <c r="AY13" s="59"/>
+      <c r="AZ13" s="59"/>
+      <c r="BA13" s="59"/>
+      <c r="BB13" s="59"/>
+      <c r="BC13" s="59"/>
       <c r="BD13" s="40"/>
       <c r="BE13" s="35"/>
       <c r="BF13" s="35"/>
@@ -13829,36 +13824,36 @@
       <c r="BK13" s="35"/>
       <c r="BL13" s="35"/>
       <c r="BM13" s="35"/>
-      <c r="BN13" s="56"/>
-      <c r="BO13" s="56"/>
-      <c r="BP13" s="56"/>
-      <c r="BQ13" s="56"/>
-      <c r="BR13" s="56"/>
-      <c r="BS13" s="56"/>
-      <c r="BT13" s="56"/>
-      <c r="BU13" s="56"/>
-      <c r="BV13" s="56"/>
-      <c r="BW13" s="56"/>
-      <c r="BX13" s="56"/>
-      <c r="BY13" s="56"/>
-      <c r="BZ13" s="56"/>
-      <c r="CA13" s="56"/>
-      <c r="CB13" s="56"/>
-      <c r="CC13" s="56"/>
-      <c r="CD13" s="56"/>
-      <c r="CE13" s="56"/>
-      <c r="CF13" s="56"/>
-      <c r="CG13" s="56"/>
-      <c r="CH13" s="56"/>
-      <c r="CI13" s="56"/>
-      <c r="CJ13" s="56"/>
-      <c r="CK13" s="56"/>
-      <c r="CL13" s="56"/>
-      <c r="CM13" s="56"/>
-      <c r="CN13" s="56"/>
-      <c r="CO13" s="56"/>
-      <c r="CP13" s="56"/>
-      <c r="CQ13" s="56"/>
+      <c r="BN13" s="54"/>
+      <c r="BO13" s="54"/>
+      <c r="BP13" s="54"/>
+      <c r="BQ13" s="54"/>
+      <c r="BR13" s="54"/>
+      <c r="BS13" s="54"/>
+      <c r="BT13" s="54"/>
+      <c r="BU13" s="54"/>
+      <c r="BV13" s="54"/>
+      <c r="BW13" s="54"/>
+      <c r="BX13" s="54"/>
+      <c r="BY13" s="54"/>
+      <c r="BZ13" s="54"/>
+      <c r="CA13" s="54"/>
+      <c r="CB13" s="54"/>
+      <c r="CC13" s="54"/>
+      <c r="CD13" s="54"/>
+      <c r="CE13" s="54"/>
+      <c r="CF13" s="54"/>
+      <c r="CG13" s="54"/>
+      <c r="CH13" s="54"/>
+      <c r="CI13" s="54"/>
+      <c r="CJ13" s="54"/>
+      <c r="CK13" s="54"/>
+      <c r="CL13" s="54"/>
+      <c r="CM13" s="54"/>
+      <c r="CN13" s="54"/>
+      <c r="CO13" s="54"/>
+      <c r="CP13" s="54"/>
+      <c r="CQ13" s="54"/>
       <c r="CR13" s="42"/>
       <c r="CS13" s="42"/>
       <c r="CT13" s="42"/>
@@ -13873,38 +13868,38 @@
       <c r="W14" s="35"/>
       <c r="X14" s="35"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="59" t="s">
+      <c r="Z14" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="AA14" s="59"/>
-      <c r="AB14" s="59"/>
-      <c r="AC14" s="59"/>
-      <c r="AD14" s="59"/>
-      <c r="AE14" s="59"/>
-      <c r="AF14" s="59"/>
-      <c r="AG14" s="59"/>
-      <c r="AH14" s="59"/>
-      <c r="AI14" s="59"/>
-      <c r="AJ14" s="59"/>
-      <c r="AK14" s="59"/>
-      <c r="AL14" s="59"/>
-      <c r="AM14" s="59"/>
-      <c r="AN14" s="59"/>
-      <c r="AO14" s="59"/>
-      <c r="AP14" s="59"/>
-      <c r="AQ14" s="59"/>
-      <c r="AR14" s="59"/>
-      <c r="AS14" s="59"/>
-      <c r="AT14" s="59"/>
-      <c r="AU14" s="59"/>
-      <c r="AV14" s="59"/>
-      <c r="AW14" s="59"/>
-      <c r="AX14" s="59"/>
-      <c r="AY14" s="59"/>
-      <c r="AZ14" s="59"/>
-      <c r="BA14" s="59"/>
-      <c r="BB14" s="59"/>
-      <c r="BC14" s="59"/>
+      <c r="AA14" s="62"/>
+      <c r="AB14" s="62"/>
+      <c r="AC14" s="62"/>
+      <c r="AD14" s="62"/>
+      <c r="AE14" s="62"/>
+      <c r="AF14" s="62"/>
+      <c r="AG14" s="62"/>
+      <c r="AH14" s="62"/>
+      <c r="AI14" s="62"/>
+      <c r="AJ14" s="62"/>
+      <c r="AK14" s="62"/>
+      <c r="AL14" s="62"/>
+      <c r="AM14" s="62"/>
+      <c r="AN14" s="62"/>
+      <c r="AO14" s="62"/>
+      <c r="AP14" s="62"/>
+      <c r="AQ14" s="62"/>
+      <c r="AR14" s="62"/>
+      <c r="AS14" s="62"/>
+      <c r="AT14" s="62"/>
+      <c r="AU14" s="62"/>
+      <c r="AV14" s="62"/>
+      <c r="AW14" s="62"/>
+      <c r="AX14" s="62"/>
+      <c r="AY14" s="62"/>
+      <c r="AZ14" s="62"/>
+      <c r="BA14" s="62"/>
+      <c r="BB14" s="62"/>
+      <c r="BC14" s="62"/>
       <c r="BD14" s="43"/>
       <c r="BE14" s="35"/>
       <c r="BF14" s="35"/>
@@ -13959,36 +13954,36 @@
       <c r="W15" s="35"/>
       <c r="X15" s="35"/>
       <c r="Y15" s="35"/>
-      <c r="Z15" s="59"/>
-      <c r="AA15" s="59"/>
-      <c r="AB15" s="59"/>
-      <c r="AC15" s="59"/>
-      <c r="AD15" s="59"/>
-      <c r="AE15" s="59"/>
-      <c r="AF15" s="59"/>
-      <c r="AG15" s="59"/>
-      <c r="AH15" s="59"/>
-      <c r="AI15" s="59"/>
-      <c r="AJ15" s="59"/>
-      <c r="AK15" s="59"/>
-      <c r="AL15" s="59"/>
-      <c r="AM15" s="59"/>
-      <c r="AN15" s="59"/>
-      <c r="AO15" s="59"/>
-      <c r="AP15" s="59"/>
-      <c r="AQ15" s="59"/>
-      <c r="AR15" s="59"/>
-      <c r="AS15" s="59"/>
-      <c r="AT15" s="59"/>
-      <c r="AU15" s="59"/>
-      <c r="AV15" s="59"/>
-      <c r="AW15" s="59"/>
-      <c r="AX15" s="59"/>
-      <c r="AY15" s="59"/>
-      <c r="AZ15" s="59"/>
-      <c r="BA15" s="59"/>
-      <c r="BB15" s="59"/>
-      <c r="BC15" s="59"/>
+      <c r="Z15" s="62"/>
+      <c r="AA15" s="62"/>
+      <c r="AB15" s="62"/>
+      <c r="AC15" s="62"/>
+      <c r="AD15" s="62"/>
+      <c r="AE15" s="62"/>
+      <c r="AF15" s="62"/>
+      <c r="AG15" s="62"/>
+      <c r="AH15" s="62"/>
+      <c r="AI15" s="62"/>
+      <c r="AJ15" s="62"/>
+      <c r="AK15" s="62"/>
+      <c r="AL15" s="62"/>
+      <c r="AM15" s="62"/>
+      <c r="AN15" s="62"/>
+      <c r="AO15" s="62"/>
+      <c r="AP15" s="62"/>
+      <c r="AQ15" s="62"/>
+      <c r="AR15" s="62"/>
+      <c r="AS15" s="62"/>
+      <c r="AT15" s="62"/>
+      <c r="AU15" s="62"/>
+      <c r="AV15" s="62"/>
+      <c r="AW15" s="62"/>
+      <c r="AX15" s="62"/>
+      <c r="AY15" s="62"/>
+      <c r="AZ15" s="62"/>
+      <c r="BA15" s="62"/>
+      <c r="BB15" s="62"/>
+      <c r="BC15" s="62"/>
       <c r="BD15" s="43"/>
       <c r="BE15" s="35"/>
       <c r="BF15" s="35"/>
@@ -14043,36 +14038,36 @@
       <c r="W16" s="35"/>
       <c r="X16" s="35"/>
       <c r="Y16" s="35"/>
-      <c r="Z16" s="59"/>
-      <c r="AA16" s="59"/>
-      <c r="AB16" s="59"/>
-      <c r="AC16" s="59"/>
-      <c r="AD16" s="59"/>
-      <c r="AE16" s="59"/>
-      <c r="AF16" s="59"/>
-      <c r="AG16" s="59"/>
-      <c r="AH16" s="59"/>
-      <c r="AI16" s="59"/>
-      <c r="AJ16" s="59"/>
-      <c r="AK16" s="59"/>
-      <c r="AL16" s="59"/>
-      <c r="AM16" s="59"/>
-      <c r="AN16" s="59"/>
-      <c r="AO16" s="59"/>
-      <c r="AP16" s="59"/>
-      <c r="AQ16" s="59"/>
-      <c r="AR16" s="59"/>
-      <c r="AS16" s="59"/>
-      <c r="AT16" s="59"/>
-      <c r="AU16" s="59"/>
-      <c r="AV16" s="59"/>
-      <c r="AW16" s="59"/>
-      <c r="AX16" s="59"/>
-      <c r="AY16" s="59"/>
-      <c r="AZ16" s="59"/>
-      <c r="BA16" s="59"/>
-      <c r="BB16" s="59"/>
-      <c r="BC16" s="59"/>
+      <c r="Z16" s="62"/>
+      <c r="AA16" s="62"/>
+      <c r="AB16" s="62"/>
+      <c r="AC16" s="62"/>
+      <c r="AD16" s="62"/>
+      <c r="AE16" s="62"/>
+      <c r="AF16" s="62"/>
+      <c r="AG16" s="62"/>
+      <c r="AH16" s="62"/>
+      <c r="AI16" s="62"/>
+      <c r="AJ16" s="62"/>
+      <c r="AK16" s="62"/>
+      <c r="AL16" s="62"/>
+      <c r="AM16" s="62"/>
+      <c r="AN16" s="62"/>
+      <c r="AO16" s="62"/>
+      <c r="AP16" s="62"/>
+      <c r="AQ16" s="62"/>
+      <c r="AR16" s="62"/>
+      <c r="AS16" s="62"/>
+      <c r="AT16" s="62"/>
+      <c r="AU16" s="62"/>
+      <c r="AV16" s="62"/>
+      <c r="AW16" s="62"/>
+      <c r="AX16" s="62"/>
+      <c r="AY16" s="62"/>
+      <c r="AZ16" s="62"/>
+      <c r="BA16" s="62"/>
+      <c r="BB16" s="62"/>
+      <c r="BC16" s="62"/>
       <c r="BD16" s="43"/>
       <c r="BE16" s="35"/>
       <c r="BF16" s="35"/>
@@ -14119,71 +14114,71 @@
       <c r="CU16" s="35"/>
     </row>
     <row r="17" spans="18:56" ht="6" customHeight="1">
-      <c r="Z17" s="57" t="s">
+      <c r="Z17" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="AA17" s="57"/>
-      <c r="AB17" s="57"/>
-      <c r="AC17" s="57"/>
-      <c r="AD17" s="57"/>
-      <c r="AE17" s="57"/>
-      <c r="AF17" s="57"/>
-      <c r="AG17" s="57"/>
-      <c r="AH17" s="57"/>
-      <c r="AI17" s="57"/>
-      <c r="AJ17" s="57"/>
-      <c r="AK17" s="57"/>
-      <c r="AL17" s="57"/>
-      <c r="AM17" s="57"/>
-      <c r="AN17" s="57"/>
-      <c r="AO17" s="57"/>
-      <c r="AP17" s="57"/>
-      <c r="AQ17" s="57"/>
-      <c r="AR17" s="57"/>
-      <c r="AS17" s="57"/>
-      <c r="AT17" s="57"/>
-      <c r="AU17" s="57"/>
-      <c r="AV17" s="57"/>
-      <c r="AW17" s="57"/>
-      <c r="AX17" s="57"/>
-      <c r="AY17" s="57"/>
-      <c r="AZ17" s="57"/>
-      <c r="BA17" s="57"/>
-      <c r="BB17" s="57"/>
-      <c r="BC17" s="57"/>
+      <c r="AA17" s="63"/>
+      <c r="AB17" s="63"/>
+      <c r="AC17" s="63"/>
+      <c r="AD17" s="63"/>
+      <c r="AE17" s="63"/>
+      <c r="AF17" s="63"/>
+      <c r="AG17" s="63"/>
+      <c r="AH17" s="63"/>
+      <c r="AI17" s="63"/>
+      <c r="AJ17" s="63"/>
+      <c r="AK17" s="63"/>
+      <c r="AL17" s="63"/>
+      <c r="AM17" s="63"/>
+      <c r="AN17" s="63"/>
+      <c r="AO17" s="63"/>
+      <c r="AP17" s="63"/>
+      <c r="AQ17" s="63"/>
+      <c r="AR17" s="63"/>
+      <c r="AS17" s="63"/>
+      <c r="AT17" s="63"/>
+      <c r="AU17" s="63"/>
+      <c r="AV17" s="63"/>
+      <c r="AW17" s="63"/>
+      <c r="AX17" s="63"/>
+      <c r="AY17" s="63"/>
+      <c r="AZ17" s="63"/>
+      <c r="BA17" s="63"/>
+      <c r="BB17" s="63"/>
+      <c r="BC17" s="63"/>
       <c r="BD17" s="44"/>
     </row>
     <row r="18" spans="18:56" ht="6" customHeight="1">
-      <c r="Z18" s="57"/>
-      <c r="AA18" s="57"/>
-      <c r="AB18" s="57"/>
-      <c r="AC18" s="57"/>
-      <c r="AD18" s="57"/>
-      <c r="AE18" s="57"/>
-      <c r="AF18" s="57"/>
-      <c r="AG18" s="57"/>
-      <c r="AH18" s="57"/>
-      <c r="AI18" s="57"/>
-      <c r="AJ18" s="57"/>
-      <c r="AK18" s="57"/>
-      <c r="AL18" s="57"/>
-      <c r="AM18" s="57"/>
-      <c r="AN18" s="57"/>
-      <c r="AO18" s="57"/>
-      <c r="AP18" s="57"/>
-      <c r="AQ18" s="57"/>
-      <c r="AR18" s="57"/>
-      <c r="AS18" s="57"/>
-      <c r="AT18" s="57"/>
-      <c r="AU18" s="57"/>
-      <c r="AV18" s="57"/>
-      <c r="AW18" s="57"/>
-      <c r="AX18" s="57"/>
-      <c r="AY18" s="57"/>
-      <c r="AZ18" s="57"/>
-      <c r="BA18" s="57"/>
-      <c r="BB18" s="57"/>
-      <c r="BC18" s="57"/>
+      <c r="Z18" s="63"/>
+      <c r="AA18" s="63"/>
+      <c r="AB18" s="63"/>
+      <c r="AC18" s="63"/>
+      <c r="AD18" s="63"/>
+      <c r="AE18" s="63"/>
+      <c r="AF18" s="63"/>
+      <c r="AG18" s="63"/>
+      <c r="AH18" s="63"/>
+      <c r="AI18" s="63"/>
+      <c r="AJ18" s="63"/>
+      <c r="AK18" s="63"/>
+      <c r="AL18" s="63"/>
+      <c r="AM18" s="63"/>
+      <c r="AN18" s="63"/>
+      <c r="AO18" s="63"/>
+      <c r="AP18" s="63"/>
+      <c r="AQ18" s="63"/>
+      <c r="AR18" s="63"/>
+      <c r="AS18" s="63"/>
+      <c r="AT18" s="63"/>
+      <c r="AU18" s="63"/>
+      <c r="AV18" s="63"/>
+      <c r="AW18" s="63"/>
+      <c r="AX18" s="63"/>
+      <c r="AY18" s="63"/>
+      <c r="AZ18" s="63"/>
+      <c r="BA18" s="63"/>
+      <c r="BB18" s="63"/>
+      <c r="BC18" s="63"/>
       <c r="BD18" s="44"/>
     </row>
     <row r="19" spans="18:56" ht="6" customHeight="1"/>
@@ -14197,208 +14192,208 @@
       <c r="W21" s="39"/>
       <c r="X21" s="39"/>
       <c r="Y21" s="39"/>
-      <c r="Z21" s="65" t="s">
+      <c r="Z21" s="64" t="s">
         <v>102</v>
       </c>
-      <c r="AA21" s="65"/>
-      <c r="AB21" s="65"/>
-      <c r="AC21" s="65"/>
-      <c r="AD21" s="65"/>
-      <c r="AE21" s="65"/>
-      <c r="AF21" s="65"/>
-      <c r="AG21" s="65"/>
-      <c r="AH21" s="65"/>
-      <c r="AI21" s="65"/>
-      <c r="AJ21" s="65"/>
-      <c r="AK21" s="65"/>
-      <c r="AL21" s="65"/>
-      <c r="AM21" s="65"/>
-      <c r="AN21" s="65"/>
-      <c r="AO21" s="65"/>
-      <c r="AP21" s="65"/>
-      <c r="AQ21" s="65"/>
-      <c r="AR21" s="65"/>
-      <c r="AS21" s="65"/>
-      <c r="AT21" s="65"/>
-      <c r="AU21" s="65"/>
-      <c r="AV21" s="65"/>
-      <c r="AW21" s="65"/>
-      <c r="AX21" s="65"/>
-      <c r="AY21" s="65"/>
-      <c r="AZ21" s="65"/>
-      <c r="BA21" s="65"/>
-      <c r="BB21" s="65"/>
-      <c r="BC21" s="65"/>
+      <c r="AA21" s="64"/>
+      <c r="AB21" s="64"/>
+      <c r="AC21" s="64"/>
+      <c r="AD21" s="64"/>
+      <c r="AE21" s="64"/>
+      <c r="AF21" s="64"/>
+      <c r="AG21" s="64"/>
+      <c r="AH21" s="64"/>
+      <c r="AI21" s="64"/>
+      <c r="AJ21" s="64"/>
+      <c r="AK21" s="64"/>
+      <c r="AL21" s="64"/>
+      <c r="AM21" s="64"/>
+      <c r="AN21" s="64"/>
+      <c r="AO21" s="64"/>
+      <c r="AP21" s="64"/>
+      <c r="AQ21" s="64"/>
+      <c r="AR21" s="64"/>
+      <c r="AS21" s="64"/>
+      <c r="AT21" s="64"/>
+      <c r="AU21" s="64"/>
+      <c r="AV21" s="64"/>
+      <c r="AW21" s="64"/>
+      <c r="AX21" s="64"/>
+      <c r="AY21" s="64"/>
+      <c r="AZ21" s="64"/>
+      <c r="BA21" s="64"/>
+      <c r="BB21" s="64"/>
+      <c r="BC21" s="64"/>
       <c r="BD21" s="45"/>
     </row>
     <row r="22" spans="18:56" ht="6" customHeight="1">
-      <c r="Z22" s="66"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="66"/>
-      <c r="AC22" s="66"/>
-      <c r="AD22" s="66"/>
-      <c r="AE22" s="66"/>
-      <c r="AF22" s="66"/>
-      <c r="AG22" s="66"/>
-      <c r="AH22" s="66"/>
-      <c r="AI22" s="66"/>
-      <c r="AJ22" s="66"/>
-      <c r="AK22" s="66"/>
-      <c r="AL22" s="66"/>
-      <c r="AM22" s="66"/>
-      <c r="AN22" s="66"/>
-      <c r="AO22" s="66"/>
-      <c r="AP22" s="66"/>
-      <c r="AQ22" s="66"/>
-      <c r="AR22" s="66"/>
-      <c r="AS22" s="66"/>
-      <c r="AT22" s="66"/>
-      <c r="AU22" s="66"/>
-      <c r="AV22" s="66"/>
-      <c r="AW22" s="66"/>
-      <c r="AX22" s="66"/>
-      <c r="AY22" s="66"/>
-      <c r="AZ22" s="66"/>
-      <c r="BA22" s="66"/>
-      <c r="BB22" s="66"/>
-      <c r="BC22" s="66"/>
+      <c r="Z22" s="65"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="65"/>
+      <c r="AE22" s="65"/>
+      <c r="AF22" s="65"/>
+      <c r="AG22" s="65"/>
+      <c r="AH22" s="65"/>
+      <c r="AI22" s="65"/>
+      <c r="AJ22" s="65"/>
+      <c r="AK22" s="65"/>
+      <c r="AL22" s="65"/>
+      <c r="AM22" s="65"/>
+      <c r="AN22" s="65"/>
+      <c r="AO22" s="65"/>
+      <c r="AP22" s="65"/>
+      <c r="AQ22" s="65"/>
+      <c r="AR22" s="65"/>
+      <c r="AS22" s="65"/>
+      <c r="AT22" s="65"/>
+      <c r="AU22" s="65"/>
+      <c r="AV22" s="65"/>
+      <c r="AW22" s="65"/>
+      <c r="AX22" s="65"/>
+      <c r="AY22" s="65"/>
+      <c r="AZ22" s="65"/>
+      <c r="BA22" s="65"/>
+      <c r="BB22" s="65"/>
+      <c r="BC22" s="65"/>
       <c r="BD22" s="45"/>
     </row>
     <row r="23" spans="18:56" ht="6" customHeight="1">
-      <c r="Z23" s="67" t="s">
+      <c r="Z23" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="AA23" s="67"/>
-      <c r="AB23" s="67"/>
-      <c r="AC23" s="67"/>
-      <c r="AD23" s="67"/>
-      <c r="AE23" s="67"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="67"/>
-      <c r="AH23" s="67"/>
-      <c r="AI23" s="67"/>
-      <c r="AJ23" s="67"/>
-      <c r="AK23" s="67"/>
-      <c r="AL23" s="67"/>
-      <c r="AM23" s="67"/>
-      <c r="AN23" s="67"/>
-      <c r="AO23" s="67"/>
-      <c r="AP23" s="67"/>
-      <c r="AQ23" s="67"/>
-      <c r="AR23" s="67"/>
-      <c r="AS23" s="67"/>
-      <c r="AT23" s="67"/>
-      <c r="AU23" s="67"/>
-      <c r="AV23" s="67"/>
-      <c r="AW23" s="67"/>
-      <c r="AX23" s="67"/>
-      <c r="AY23" s="67"/>
-      <c r="AZ23" s="67"/>
-      <c r="BA23" s="67"/>
-      <c r="BB23" s="67"/>
-      <c r="BC23" s="67"/>
+      <c r="AA23" s="66"/>
+      <c r="AB23" s="66"/>
+      <c r="AC23" s="66"/>
+      <c r="AD23" s="66"/>
+      <c r="AE23" s="66"/>
+      <c r="AF23" s="66"/>
+      <c r="AG23" s="66"/>
+      <c r="AH23" s="66"/>
+      <c r="AI23" s="66"/>
+      <c r="AJ23" s="66"/>
+      <c r="AK23" s="66"/>
+      <c r="AL23" s="66"/>
+      <c r="AM23" s="66"/>
+      <c r="AN23" s="66"/>
+      <c r="AO23" s="66"/>
+      <c r="AP23" s="66"/>
+      <c r="AQ23" s="66"/>
+      <c r="AR23" s="66"/>
+      <c r="AS23" s="66"/>
+      <c r="AT23" s="66"/>
+      <c r="AU23" s="66"/>
+      <c r="AV23" s="66"/>
+      <c r="AW23" s="66"/>
+      <c r="AX23" s="66"/>
+      <c r="AY23" s="66"/>
+      <c r="AZ23" s="66"/>
+      <c r="BA23" s="66"/>
+      <c r="BB23" s="66"/>
+      <c r="BC23" s="66"/>
       <c r="BD23" s="46"/>
     </row>
     <row r="24" spans="18:56" ht="6" customHeight="1">
-      <c r="Z24" s="67"/>
-      <c r="AA24" s="67"/>
-      <c r="AB24" s="67"/>
-      <c r="AC24" s="67"/>
-      <c r="AD24" s="67"/>
-      <c r="AE24" s="67"/>
-      <c r="AF24" s="67"/>
-      <c r="AG24" s="67"/>
-      <c r="AH24" s="67"/>
-      <c r="AI24" s="67"/>
-      <c r="AJ24" s="67"/>
-      <c r="AK24" s="67"/>
-      <c r="AL24" s="67"/>
-      <c r="AM24" s="67"/>
-      <c r="AN24" s="67"/>
-      <c r="AO24" s="67"/>
-      <c r="AP24" s="67"/>
-      <c r="AQ24" s="67"/>
-      <c r="AR24" s="67"/>
-      <c r="AS24" s="67"/>
-      <c r="AT24" s="67"/>
-      <c r="AU24" s="67"/>
-      <c r="AV24" s="67"/>
-      <c r="AW24" s="67"/>
-      <c r="AX24" s="67"/>
-      <c r="AY24" s="67"/>
-      <c r="AZ24" s="67"/>
-      <c r="BA24" s="67"/>
-      <c r="BB24" s="67"/>
-      <c r="BC24" s="67"/>
+      <c r="Z24" s="66"/>
+      <c r="AA24" s="66"/>
+      <c r="AB24" s="66"/>
+      <c r="AC24" s="66"/>
+      <c r="AD24" s="66"/>
+      <c r="AE24" s="66"/>
+      <c r="AF24" s="66"/>
+      <c r="AG24" s="66"/>
+      <c r="AH24" s="66"/>
+      <c r="AI24" s="66"/>
+      <c r="AJ24" s="66"/>
+      <c r="AK24" s="66"/>
+      <c r="AL24" s="66"/>
+      <c r="AM24" s="66"/>
+      <c r="AN24" s="66"/>
+      <c r="AO24" s="66"/>
+      <c r="AP24" s="66"/>
+      <c r="AQ24" s="66"/>
+      <c r="AR24" s="66"/>
+      <c r="AS24" s="66"/>
+      <c r="AT24" s="66"/>
+      <c r="AU24" s="66"/>
+      <c r="AV24" s="66"/>
+      <c r="AW24" s="66"/>
+      <c r="AX24" s="66"/>
+      <c r="AY24" s="66"/>
+      <c r="AZ24" s="66"/>
+      <c r="BA24" s="66"/>
+      <c r="BB24" s="66"/>
+      <c r="BC24" s="66"/>
       <c r="BD24" s="46"/>
     </row>
     <row r="25" spans="18:56" ht="6" customHeight="1"/>
     <row r="26" spans="18:56" ht="6" customHeight="1">
-      <c r="Z26" s="57" t="s">
+      <c r="Z26" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="AA26" s="57"/>
-      <c r="AB26" s="57"/>
-      <c r="AC26" s="57"/>
-      <c r="AD26" s="57"/>
-      <c r="AE26" s="57"/>
-      <c r="AF26" s="57"/>
-      <c r="AG26" s="57"/>
-      <c r="AH26" s="57"/>
-      <c r="AI26" s="57"/>
-      <c r="AJ26" s="57"/>
-      <c r="AK26" s="57"/>
-      <c r="AL26" s="57"/>
-      <c r="AM26" s="57"/>
-      <c r="AN26" s="57"/>
-      <c r="AO26" s="57"/>
-      <c r="AP26" s="57"/>
-      <c r="AQ26" s="57"/>
-      <c r="AR26" s="57"/>
-      <c r="AS26" s="57"/>
-      <c r="AT26" s="57"/>
-      <c r="AU26" s="57"/>
-      <c r="AV26" s="57"/>
-      <c r="AW26" s="57"/>
-      <c r="AX26" s="57"/>
-      <c r="AY26" s="57"/>
-      <c r="AZ26" s="57"/>
-      <c r="BA26" s="57"/>
-      <c r="BB26" s="57"/>
-      <c r="BC26" s="57"/>
+      <c r="AA26" s="63"/>
+      <c r="AB26" s="63"/>
+      <c r="AC26" s="63"/>
+      <c r="AD26" s="63"/>
+      <c r="AE26" s="63"/>
+      <c r="AF26" s="63"/>
+      <c r="AG26" s="63"/>
+      <c r="AH26" s="63"/>
+      <c r="AI26" s="63"/>
+      <c r="AJ26" s="63"/>
+      <c r="AK26" s="63"/>
+      <c r="AL26" s="63"/>
+      <c r="AM26" s="63"/>
+      <c r="AN26" s="63"/>
+      <c r="AO26" s="63"/>
+      <c r="AP26" s="63"/>
+      <c r="AQ26" s="63"/>
+      <c r="AR26" s="63"/>
+      <c r="AS26" s="63"/>
+      <c r="AT26" s="63"/>
+      <c r="AU26" s="63"/>
+      <c r="AV26" s="63"/>
+      <c r="AW26" s="63"/>
+      <c r="AX26" s="63"/>
+      <c r="AY26" s="63"/>
+      <c r="AZ26" s="63"/>
+      <c r="BA26" s="63"/>
+      <c r="BB26" s="63"/>
+      <c r="BC26" s="63"/>
       <c r="BD26" s="44"/>
     </row>
     <row r="27" spans="18:56" ht="6" customHeight="1">
-      <c r="Z27" s="57"/>
-      <c r="AA27" s="57"/>
-      <c r="AB27" s="57"/>
-      <c r="AC27" s="57"/>
-      <c r="AD27" s="57"/>
-      <c r="AE27" s="57"/>
-      <c r="AF27" s="57"/>
-      <c r="AG27" s="57"/>
-      <c r="AH27" s="57"/>
-      <c r="AI27" s="57"/>
-      <c r="AJ27" s="57"/>
-      <c r="AK27" s="57"/>
-      <c r="AL27" s="57"/>
-      <c r="AM27" s="57"/>
-      <c r="AN27" s="57"/>
-      <c r="AO27" s="57"/>
-      <c r="AP27" s="57"/>
-      <c r="AQ27" s="57"/>
-      <c r="AR27" s="57"/>
-      <c r="AS27" s="57"/>
-      <c r="AT27" s="57"/>
-      <c r="AU27" s="57"/>
-      <c r="AV27" s="57"/>
-      <c r="AW27" s="57"/>
-      <c r="AX27" s="57"/>
-      <c r="AY27" s="57"/>
-      <c r="AZ27" s="57"/>
-      <c r="BA27" s="57"/>
-      <c r="BB27" s="57"/>
-      <c r="BC27" s="57"/>
+      <c r="Z27" s="63"/>
+      <c r="AA27" s="63"/>
+      <c r="AB27" s="63"/>
+      <c r="AC27" s="63"/>
+      <c r="AD27" s="63"/>
+      <c r="AE27" s="63"/>
+      <c r="AF27" s="63"/>
+      <c r="AG27" s="63"/>
+      <c r="AH27" s="63"/>
+      <c r="AI27" s="63"/>
+      <c r="AJ27" s="63"/>
+      <c r="AK27" s="63"/>
+      <c r="AL27" s="63"/>
+      <c r="AM27" s="63"/>
+      <c r="AN27" s="63"/>
+      <c r="AO27" s="63"/>
+      <c r="AP27" s="63"/>
+      <c r="AQ27" s="63"/>
+      <c r="AR27" s="63"/>
+      <c r="AS27" s="63"/>
+      <c r="AT27" s="63"/>
+      <c r="AU27" s="63"/>
+      <c r="AV27" s="63"/>
+      <c r="AW27" s="63"/>
+      <c r="AX27" s="63"/>
+      <c r="AY27" s="63"/>
+      <c r="AZ27" s="63"/>
+      <c r="BA27" s="63"/>
+      <c r="BB27" s="63"/>
+      <c r="BC27" s="63"/>
       <c r="BD27" s="44"/>
     </row>
     <row r="28" spans="18:56" ht="6" customHeight="1">
@@ -14446,38 +14441,38 @@
       <c r="W32" s="39"/>
       <c r="X32" s="39"/>
       <c r="Y32" s="39"/>
-      <c r="Z32" s="53" t="s">
+      <c r="Z32" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="AA32" s="53"/>
-      <c r="AB32" s="53"/>
-      <c r="AC32" s="53"/>
-      <c r="AD32" s="53"/>
-      <c r="AE32" s="53"/>
-      <c r="AF32" s="53"/>
-      <c r="AG32" s="53"/>
-      <c r="AH32" s="53"/>
-      <c r="AI32" s="53"/>
-      <c r="AJ32" s="53"/>
-      <c r="AK32" s="53"/>
-      <c r="AL32" s="53"/>
-      <c r="AM32" s="53"/>
-      <c r="AN32" s="53"/>
-      <c r="AO32" s="53"/>
-      <c r="AP32" s="53"/>
-      <c r="AQ32" s="53"/>
-      <c r="AR32" s="53"/>
-      <c r="AS32" s="53"/>
-      <c r="AT32" s="53"/>
-      <c r="AU32" s="53"/>
-      <c r="AV32" s="53"/>
-      <c r="AW32" s="53"/>
-      <c r="AX32" s="53"/>
-      <c r="AY32" s="53"/>
-      <c r="AZ32" s="53"/>
-      <c r="BA32" s="53"/>
-      <c r="BB32" s="53"/>
-      <c r="BC32" s="53"/>
+      <c r="AA32" s="60"/>
+      <c r="AB32" s="60"/>
+      <c r="AC32" s="60"/>
+      <c r="AD32" s="60"/>
+      <c r="AE32" s="60"/>
+      <c r="AF32" s="60"/>
+      <c r="AG32" s="60"/>
+      <c r="AH32" s="60"/>
+      <c r="AI32" s="60"/>
+      <c r="AJ32" s="60"/>
+      <c r="AK32" s="60"/>
+      <c r="AL32" s="60"/>
+      <c r="AM32" s="60"/>
+      <c r="AN32" s="60"/>
+      <c r="AO32" s="60"/>
+      <c r="AP32" s="60"/>
+      <c r="AQ32" s="60"/>
+      <c r="AR32" s="60"/>
+      <c r="AS32" s="60"/>
+      <c r="AT32" s="60"/>
+      <c r="AU32" s="60"/>
+      <c r="AV32" s="60"/>
+      <c r="AW32" s="60"/>
+      <c r="AX32" s="60"/>
+      <c r="AY32" s="60"/>
+      <c r="AZ32" s="60"/>
+      <c r="BA32" s="60"/>
+      <c r="BB32" s="60"/>
+      <c r="BC32" s="60"/>
       <c r="BD32" s="48"/>
     </row>
     <row r="33" spans="18:99" s="1" customFormat="1" ht="6" customHeight="1">
@@ -14489,36 +14484,36 @@
       <c r="W33" s="35"/>
       <c r="X33" s="35"/>
       <c r="Y33" s="35"/>
-      <c r="Z33" s="54"/>
-      <c r="AA33" s="54"/>
-      <c r="AB33" s="54"/>
-      <c r="AC33" s="54"/>
-      <c r="AD33" s="54"/>
-      <c r="AE33" s="54"/>
-      <c r="AF33" s="54"/>
-      <c r="AG33" s="54"/>
-      <c r="AH33" s="54"/>
-      <c r="AI33" s="54"/>
-      <c r="AJ33" s="54"/>
-      <c r="AK33" s="54"/>
-      <c r="AL33" s="54"/>
-      <c r="AM33" s="54"/>
-      <c r="AN33" s="54"/>
-      <c r="AO33" s="54"/>
-      <c r="AP33" s="54"/>
-      <c r="AQ33" s="54"/>
-      <c r="AR33" s="54"/>
-      <c r="AS33" s="54"/>
-      <c r="AT33" s="54"/>
-      <c r="AU33" s="54"/>
-      <c r="AV33" s="54"/>
-      <c r="AW33" s="54"/>
-      <c r="AX33" s="54"/>
-      <c r="AY33" s="54"/>
-      <c r="AZ33" s="54"/>
-      <c r="BA33" s="54"/>
-      <c r="BB33" s="54"/>
-      <c r="BC33" s="54"/>
+      <c r="Z33" s="61"/>
+      <c r="AA33" s="61"/>
+      <c r="AB33" s="61"/>
+      <c r="AC33" s="61"/>
+      <c r="AD33" s="61"/>
+      <c r="AE33" s="61"/>
+      <c r="AF33" s="61"/>
+      <c r="AG33" s="61"/>
+      <c r="AH33" s="61"/>
+      <c r="AI33" s="61"/>
+      <c r="AJ33" s="61"/>
+      <c r="AK33" s="61"/>
+      <c r="AL33" s="61"/>
+      <c r="AM33" s="61"/>
+      <c r="AN33" s="61"/>
+      <c r="AO33" s="61"/>
+      <c r="AP33" s="61"/>
+      <c r="AQ33" s="61"/>
+      <c r="AR33" s="61"/>
+      <c r="AS33" s="61"/>
+      <c r="AT33" s="61"/>
+      <c r="AU33" s="61"/>
+      <c r="AV33" s="61"/>
+      <c r="AW33" s="61"/>
+      <c r="AX33" s="61"/>
+      <c r="AY33" s="61"/>
+      <c r="AZ33" s="61"/>
+      <c r="BA33" s="61"/>
+      <c r="BB33" s="61"/>
+      <c r="BC33" s="61"/>
       <c r="BD33" s="48"/>
       <c r="BE33" s="35"/>
       <c r="BF33" s="35"/>
@@ -14573,36 +14568,36 @@
       <c r="W34" s="35"/>
       <c r="X34" s="35"/>
       <c r="Y34" s="35"/>
-      <c r="Z34" s="54"/>
-      <c r="AA34" s="54"/>
-      <c r="AB34" s="54"/>
-      <c r="AC34" s="54"/>
-      <c r="AD34" s="54"/>
-      <c r="AE34" s="54"/>
-      <c r="AF34" s="54"/>
-      <c r="AG34" s="54"/>
-      <c r="AH34" s="54"/>
-      <c r="AI34" s="54"/>
-      <c r="AJ34" s="54"/>
-      <c r="AK34" s="54"/>
-      <c r="AL34" s="54"/>
-      <c r="AM34" s="54"/>
-      <c r="AN34" s="54"/>
-      <c r="AO34" s="54"/>
-      <c r="AP34" s="54"/>
-      <c r="AQ34" s="54"/>
-      <c r="AR34" s="54"/>
-      <c r="AS34" s="54"/>
-      <c r="AT34" s="54"/>
-      <c r="AU34" s="54"/>
-      <c r="AV34" s="54"/>
-      <c r="AW34" s="54"/>
-      <c r="AX34" s="54"/>
-      <c r="AY34" s="54"/>
-      <c r="AZ34" s="54"/>
-      <c r="BA34" s="54"/>
-      <c r="BB34" s="54"/>
-      <c r="BC34" s="54"/>
+      <c r="Z34" s="61"/>
+      <c r="AA34" s="61"/>
+      <c r="AB34" s="61"/>
+      <c r="AC34" s="61"/>
+      <c r="AD34" s="61"/>
+      <c r="AE34" s="61"/>
+      <c r="AF34" s="61"/>
+      <c r="AG34" s="61"/>
+      <c r="AH34" s="61"/>
+      <c r="AI34" s="61"/>
+      <c r="AJ34" s="61"/>
+      <c r="AK34" s="61"/>
+      <c r="AL34" s="61"/>
+      <c r="AM34" s="61"/>
+      <c r="AN34" s="61"/>
+      <c r="AO34" s="61"/>
+      <c r="AP34" s="61"/>
+      <c r="AQ34" s="61"/>
+      <c r="AR34" s="61"/>
+      <c r="AS34" s="61"/>
+      <c r="AT34" s="61"/>
+      <c r="AU34" s="61"/>
+      <c r="AV34" s="61"/>
+      <c r="AW34" s="61"/>
+      <c r="AX34" s="61"/>
+      <c r="AY34" s="61"/>
+      <c r="AZ34" s="61"/>
+      <c r="BA34" s="61"/>
+      <c r="BB34" s="61"/>
+      <c r="BC34" s="61"/>
       <c r="BD34" s="48"/>
       <c r="BE34" s="35"/>
       <c r="BF34" s="39"/>
@@ -14613,38 +14608,38 @@
       <c r="BK34" s="39"/>
       <c r="BL34" s="39"/>
       <c r="BM34" s="39"/>
-      <c r="BN34" s="60" t="s">
+      <c r="BN34" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="BO34" s="60"/>
-      <c r="BP34" s="60"/>
-      <c r="BQ34" s="60"/>
-      <c r="BR34" s="60"/>
-      <c r="BS34" s="60"/>
-      <c r="BT34" s="60"/>
-      <c r="BU34" s="60"/>
-      <c r="BV34" s="60"/>
-      <c r="BW34" s="60"/>
-      <c r="BX34" s="60"/>
-      <c r="BY34" s="60"/>
-      <c r="BZ34" s="60"/>
-      <c r="CA34" s="60"/>
-      <c r="CB34" s="60"/>
-      <c r="CC34" s="60"/>
-      <c r="CD34" s="60"/>
-      <c r="CE34" s="60"/>
-      <c r="CF34" s="60"/>
-      <c r="CG34" s="60"/>
-      <c r="CH34" s="60"/>
-      <c r="CI34" s="60"/>
-      <c r="CJ34" s="60"/>
-      <c r="CK34" s="60"/>
-      <c r="CL34" s="60"/>
-      <c r="CM34" s="60"/>
-      <c r="CN34" s="60"/>
-      <c r="CO34" s="60"/>
-      <c r="CP34" s="60"/>
-      <c r="CQ34" s="60"/>
+      <c r="BO34" s="52"/>
+      <c r="BP34" s="52"/>
+      <c r="BQ34" s="52"/>
+      <c r="BR34" s="52"/>
+      <c r="BS34" s="52"/>
+      <c r="BT34" s="52"/>
+      <c r="BU34" s="52"/>
+      <c r="BV34" s="52"/>
+      <c r="BW34" s="52"/>
+      <c r="BX34" s="52"/>
+      <c r="BY34" s="52"/>
+      <c r="BZ34" s="52"/>
+      <c r="CA34" s="52"/>
+      <c r="CB34" s="52"/>
+      <c r="CC34" s="52"/>
+      <c r="CD34" s="52"/>
+      <c r="CE34" s="52"/>
+      <c r="CF34" s="52"/>
+      <c r="CG34" s="52"/>
+      <c r="CH34" s="52"/>
+      <c r="CI34" s="52"/>
+      <c r="CJ34" s="52"/>
+      <c r="CK34" s="52"/>
+      <c r="CL34" s="52"/>
+      <c r="CM34" s="52"/>
+      <c r="CN34" s="52"/>
+      <c r="CO34" s="52"/>
+      <c r="CP34" s="52"/>
+      <c r="CQ34" s="52"/>
       <c r="CR34" s="41"/>
       <c r="CS34" s="41"/>
       <c r="CT34" s="41"/>
@@ -14659,36 +14654,36 @@
       <c r="W35" s="35"/>
       <c r="X35" s="35"/>
       <c r="Y35" s="35"/>
-      <c r="Z35" s="54"/>
-      <c r="AA35" s="54"/>
-      <c r="AB35" s="54"/>
-      <c r="AC35" s="54"/>
-      <c r="AD35" s="54"/>
-      <c r="AE35" s="54"/>
-      <c r="AF35" s="54"/>
-      <c r="AG35" s="54"/>
-      <c r="AH35" s="54"/>
-      <c r="AI35" s="54"/>
-      <c r="AJ35" s="54"/>
-      <c r="AK35" s="54"/>
-      <c r="AL35" s="54"/>
-      <c r="AM35" s="54"/>
-      <c r="AN35" s="54"/>
-      <c r="AO35" s="54"/>
-      <c r="AP35" s="54"/>
-      <c r="AQ35" s="54"/>
-      <c r="AR35" s="54"/>
-      <c r="AS35" s="54"/>
-      <c r="AT35" s="54"/>
-      <c r="AU35" s="54"/>
-      <c r="AV35" s="54"/>
-      <c r="AW35" s="54"/>
-      <c r="AX35" s="54"/>
-      <c r="AY35" s="54"/>
-      <c r="AZ35" s="54"/>
-      <c r="BA35" s="54"/>
-      <c r="BB35" s="54"/>
-      <c r="BC35" s="54"/>
+      <c r="Z35" s="61"/>
+      <c r="AA35" s="61"/>
+      <c r="AB35" s="61"/>
+      <c r="AC35" s="61"/>
+      <c r="AD35" s="61"/>
+      <c r="AE35" s="61"/>
+      <c r="AF35" s="61"/>
+      <c r="AG35" s="61"/>
+      <c r="AH35" s="61"/>
+      <c r="AI35" s="61"/>
+      <c r="AJ35" s="61"/>
+      <c r="AK35" s="61"/>
+      <c r="AL35" s="61"/>
+      <c r="AM35" s="61"/>
+      <c r="AN35" s="61"/>
+      <c r="AO35" s="61"/>
+      <c r="AP35" s="61"/>
+      <c r="AQ35" s="61"/>
+      <c r="AR35" s="61"/>
+      <c r="AS35" s="61"/>
+      <c r="AT35" s="61"/>
+      <c r="AU35" s="61"/>
+      <c r="AV35" s="61"/>
+      <c r="AW35" s="61"/>
+      <c r="AX35" s="61"/>
+      <c r="AY35" s="61"/>
+      <c r="AZ35" s="61"/>
+      <c r="BA35" s="61"/>
+      <c r="BB35" s="61"/>
+      <c r="BC35" s="61"/>
       <c r="BD35" s="48"/>
       <c r="BE35" s="35"/>
       <c r="BF35" s="35"/>
@@ -14699,36 +14694,36 @@
       <c r="BK35" s="35"/>
       <c r="BL35" s="35"/>
       <c r="BM35" s="35"/>
-      <c r="BN35" s="55"/>
-      <c r="BO35" s="55"/>
-      <c r="BP35" s="55"/>
-      <c r="BQ35" s="55"/>
-      <c r="BR35" s="55"/>
-      <c r="BS35" s="55"/>
-      <c r="BT35" s="55"/>
-      <c r="BU35" s="55"/>
-      <c r="BV35" s="55"/>
-      <c r="BW35" s="55"/>
-      <c r="BX35" s="55"/>
-      <c r="BY35" s="55"/>
-      <c r="BZ35" s="55"/>
-      <c r="CA35" s="55"/>
-      <c r="CB35" s="55"/>
-      <c r="CC35" s="55"/>
-      <c r="CD35" s="55"/>
-      <c r="CE35" s="55"/>
-      <c r="CF35" s="55"/>
-      <c r="CG35" s="55"/>
-      <c r="CH35" s="55"/>
-      <c r="CI35" s="55"/>
-      <c r="CJ35" s="55"/>
-      <c r="CK35" s="55"/>
-      <c r="CL35" s="55"/>
-      <c r="CM35" s="55"/>
-      <c r="CN35" s="55"/>
-      <c r="CO35" s="55"/>
-      <c r="CP35" s="55"/>
-      <c r="CQ35" s="55"/>
+      <c r="BN35" s="53"/>
+      <c r="BO35" s="53"/>
+      <c r="BP35" s="53"/>
+      <c r="BQ35" s="53"/>
+      <c r="BR35" s="53"/>
+      <c r="BS35" s="53"/>
+      <c r="BT35" s="53"/>
+      <c r="BU35" s="53"/>
+      <c r="BV35" s="53"/>
+      <c r="BW35" s="53"/>
+      <c r="BX35" s="53"/>
+      <c r="BY35" s="53"/>
+      <c r="BZ35" s="53"/>
+      <c r="CA35" s="53"/>
+      <c r="CB35" s="53"/>
+      <c r="CC35" s="53"/>
+      <c r="CD35" s="53"/>
+      <c r="CE35" s="53"/>
+      <c r="CF35" s="53"/>
+      <c r="CG35" s="53"/>
+      <c r="CH35" s="53"/>
+      <c r="CI35" s="53"/>
+      <c r="CJ35" s="53"/>
+      <c r="CK35" s="53"/>
+      <c r="CL35" s="53"/>
+      <c r="CM35" s="53"/>
+      <c r="CN35" s="53"/>
+      <c r="CO35" s="53"/>
+      <c r="CP35" s="53"/>
+      <c r="CQ35" s="53"/>
       <c r="CR35" s="41"/>
       <c r="CS35" s="41"/>
       <c r="CT35" s="41"/>
@@ -14743,36 +14738,36 @@
       <c r="W36" s="35"/>
       <c r="X36" s="35"/>
       <c r="Y36" s="35"/>
-      <c r="Z36" s="54"/>
-      <c r="AA36" s="54"/>
-      <c r="AB36" s="54"/>
-      <c r="AC36" s="54"/>
-      <c r="AD36" s="54"/>
-      <c r="AE36" s="54"/>
-      <c r="AF36" s="54"/>
-      <c r="AG36" s="54"/>
-      <c r="AH36" s="54"/>
-      <c r="AI36" s="54"/>
-      <c r="AJ36" s="54"/>
-      <c r="AK36" s="54"/>
-      <c r="AL36" s="54"/>
-      <c r="AM36" s="54"/>
-      <c r="AN36" s="54"/>
-      <c r="AO36" s="54"/>
-      <c r="AP36" s="54"/>
-      <c r="AQ36" s="54"/>
-      <c r="AR36" s="54"/>
-      <c r="AS36" s="54"/>
-      <c r="AT36" s="54"/>
-      <c r="AU36" s="54"/>
-      <c r="AV36" s="54"/>
-      <c r="AW36" s="54"/>
-      <c r="AX36" s="54"/>
-      <c r="AY36" s="54"/>
-      <c r="AZ36" s="54"/>
-      <c r="BA36" s="54"/>
-      <c r="BB36" s="54"/>
-      <c r="BC36" s="54"/>
+      <c r="Z36" s="61"/>
+      <c r="AA36" s="61"/>
+      <c r="AB36" s="61"/>
+      <c r="AC36" s="61"/>
+      <c r="AD36" s="61"/>
+      <c r="AE36" s="61"/>
+      <c r="AF36" s="61"/>
+      <c r="AG36" s="61"/>
+      <c r="AH36" s="61"/>
+      <c r="AI36" s="61"/>
+      <c r="AJ36" s="61"/>
+      <c r="AK36" s="61"/>
+      <c r="AL36" s="61"/>
+      <c r="AM36" s="61"/>
+      <c r="AN36" s="61"/>
+      <c r="AO36" s="61"/>
+      <c r="AP36" s="61"/>
+      <c r="AQ36" s="61"/>
+      <c r="AR36" s="61"/>
+      <c r="AS36" s="61"/>
+      <c r="AT36" s="61"/>
+      <c r="AU36" s="61"/>
+      <c r="AV36" s="61"/>
+      <c r="AW36" s="61"/>
+      <c r="AX36" s="61"/>
+      <c r="AY36" s="61"/>
+      <c r="AZ36" s="61"/>
+      <c r="BA36" s="61"/>
+      <c r="BB36" s="61"/>
+      <c r="BC36" s="61"/>
       <c r="BD36" s="48"/>
       <c r="BE36" s="35"/>
       <c r="BF36" s="35"/>
@@ -14783,36 +14778,36 @@
       <c r="BK36" s="35"/>
       <c r="BL36" s="35"/>
       <c r="BM36" s="35"/>
-      <c r="BN36" s="55"/>
-      <c r="BO36" s="55"/>
-      <c r="BP36" s="55"/>
-      <c r="BQ36" s="55"/>
-      <c r="BR36" s="55"/>
-      <c r="BS36" s="55"/>
-      <c r="BT36" s="55"/>
-      <c r="BU36" s="55"/>
-      <c r="BV36" s="55"/>
-      <c r="BW36" s="55"/>
-      <c r="BX36" s="55"/>
-      <c r="BY36" s="55"/>
-      <c r="BZ36" s="55"/>
-      <c r="CA36" s="55"/>
-      <c r="CB36" s="55"/>
-      <c r="CC36" s="55"/>
-      <c r="CD36" s="55"/>
-      <c r="CE36" s="55"/>
-      <c r="CF36" s="55"/>
-      <c r="CG36" s="55"/>
-      <c r="CH36" s="55"/>
-      <c r="CI36" s="55"/>
-      <c r="CJ36" s="55"/>
-      <c r="CK36" s="55"/>
-      <c r="CL36" s="55"/>
-      <c r="CM36" s="55"/>
-      <c r="CN36" s="55"/>
-      <c r="CO36" s="55"/>
-      <c r="CP36" s="55"/>
-      <c r="CQ36" s="55"/>
+      <c r="BN36" s="53"/>
+      <c r="BO36" s="53"/>
+      <c r="BP36" s="53"/>
+      <c r="BQ36" s="53"/>
+      <c r="BR36" s="53"/>
+      <c r="BS36" s="53"/>
+      <c r="BT36" s="53"/>
+      <c r="BU36" s="53"/>
+      <c r="BV36" s="53"/>
+      <c r="BW36" s="53"/>
+      <c r="BX36" s="53"/>
+      <c r="BY36" s="53"/>
+      <c r="BZ36" s="53"/>
+      <c r="CA36" s="53"/>
+      <c r="CB36" s="53"/>
+      <c r="CC36" s="53"/>
+      <c r="CD36" s="53"/>
+      <c r="CE36" s="53"/>
+      <c r="CF36" s="53"/>
+      <c r="CG36" s="53"/>
+      <c r="CH36" s="53"/>
+      <c r="CI36" s="53"/>
+      <c r="CJ36" s="53"/>
+      <c r="CK36" s="53"/>
+      <c r="CL36" s="53"/>
+      <c r="CM36" s="53"/>
+      <c r="CN36" s="53"/>
+      <c r="CO36" s="53"/>
+      <c r="CP36" s="53"/>
+      <c r="CQ36" s="53"/>
       <c r="CR36" s="41"/>
       <c r="CS36" s="41"/>
       <c r="CT36" s="41"/>
@@ -14827,38 +14822,38 @@
       <c r="W37" s="35"/>
       <c r="X37" s="35"/>
       <c r="Y37" s="35"/>
-      <c r="Z37" s="59" t="s">
+      <c r="Z37" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="AA37" s="59"/>
-      <c r="AB37" s="59"/>
-      <c r="AC37" s="59"/>
-      <c r="AD37" s="59"/>
-      <c r="AE37" s="59"/>
-      <c r="AF37" s="59"/>
-      <c r="AG37" s="59"/>
-      <c r="AH37" s="59"/>
-      <c r="AI37" s="59"/>
-      <c r="AJ37" s="59"/>
-      <c r="AK37" s="59"/>
-      <c r="AL37" s="59"/>
-      <c r="AM37" s="59"/>
-      <c r="AN37" s="59"/>
-      <c r="AO37" s="59"/>
-      <c r="AP37" s="59"/>
-      <c r="AQ37" s="59"/>
-      <c r="AR37" s="59"/>
-      <c r="AS37" s="59"/>
-      <c r="AT37" s="59"/>
-      <c r="AU37" s="59"/>
-      <c r="AV37" s="59"/>
-      <c r="AW37" s="59"/>
-      <c r="AX37" s="59"/>
-      <c r="AY37" s="59"/>
-      <c r="AZ37" s="59"/>
-      <c r="BA37" s="59"/>
-      <c r="BB37" s="59"/>
-      <c r="BC37" s="59"/>
+      <c r="AA37" s="62"/>
+      <c r="AB37" s="62"/>
+      <c r="AC37" s="62"/>
+      <c r="AD37" s="62"/>
+      <c r="AE37" s="62"/>
+      <c r="AF37" s="62"/>
+      <c r="AG37" s="62"/>
+      <c r="AH37" s="62"/>
+      <c r="AI37" s="62"/>
+      <c r="AJ37" s="62"/>
+      <c r="AK37" s="62"/>
+      <c r="AL37" s="62"/>
+      <c r="AM37" s="62"/>
+      <c r="AN37" s="62"/>
+      <c r="AO37" s="62"/>
+      <c r="AP37" s="62"/>
+      <c r="AQ37" s="62"/>
+      <c r="AR37" s="62"/>
+      <c r="AS37" s="62"/>
+      <c r="AT37" s="62"/>
+      <c r="AU37" s="62"/>
+      <c r="AV37" s="62"/>
+      <c r="AW37" s="62"/>
+      <c r="AX37" s="62"/>
+      <c r="AY37" s="62"/>
+      <c r="AZ37" s="62"/>
+      <c r="BA37" s="62"/>
+      <c r="BB37" s="62"/>
+      <c r="BC37" s="62"/>
       <c r="BD37" s="43"/>
       <c r="BE37" s="35"/>
       <c r="BF37" s="35"/>
@@ -14869,38 +14864,38 @@
       <c r="BK37" s="35"/>
       <c r="BL37" s="35"/>
       <c r="BM37" s="35"/>
-      <c r="BN37" s="56" t="s">
+      <c r="BN37" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="BO37" s="56"/>
-      <c r="BP37" s="56"/>
-      <c r="BQ37" s="56"/>
-      <c r="BR37" s="56"/>
-      <c r="BS37" s="56"/>
-      <c r="BT37" s="56"/>
-      <c r="BU37" s="56"/>
-      <c r="BV37" s="56"/>
-      <c r="BW37" s="56"/>
-      <c r="BX37" s="56"/>
-      <c r="BY37" s="56"/>
-      <c r="BZ37" s="56"/>
-      <c r="CA37" s="56"/>
-      <c r="CB37" s="56"/>
-      <c r="CC37" s="56"/>
-      <c r="CD37" s="56"/>
-      <c r="CE37" s="56"/>
-      <c r="CF37" s="56"/>
-      <c r="CG37" s="56"/>
-      <c r="CH37" s="56"/>
-      <c r="CI37" s="56"/>
-      <c r="CJ37" s="56"/>
-      <c r="CK37" s="56"/>
-      <c r="CL37" s="56"/>
-      <c r="CM37" s="56"/>
-      <c r="CN37" s="56"/>
-      <c r="CO37" s="56"/>
-      <c r="CP37" s="56"/>
-      <c r="CQ37" s="56"/>
+      <c r="BO37" s="54"/>
+      <c r="BP37" s="54"/>
+      <c r="BQ37" s="54"/>
+      <c r="BR37" s="54"/>
+      <c r="BS37" s="54"/>
+      <c r="BT37" s="54"/>
+      <c r="BU37" s="54"/>
+      <c r="BV37" s="54"/>
+      <c r="BW37" s="54"/>
+      <c r="BX37" s="54"/>
+      <c r="BY37" s="54"/>
+      <c r="BZ37" s="54"/>
+      <c r="CA37" s="54"/>
+      <c r="CB37" s="54"/>
+      <c r="CC37" s="54"/>
+      <c r="CD37" s="54"/>
+      <c r="CE37" s="54"/>
+      <c r="CF37" s="54"/>
+      <c r="CG37" s="54"/>
+      <c r="CH37" s="54"/>
+      <c r="CI37" s="54"/>
+      <c r="CJ37" s="54"/>
+      <c r="CK37" s="54"/>
+      <c r="CL37" s="54"/>
+      <c r="CM37" s="54"/>
+      <c r="CN37" s="54"/>
+      <c r="CO37" s="54"/>
+      <c r="CP37" s="54"/>
+      <c r="CQ37" s="54"/>
       <c r="CR37" s="42"/>
       <c r="CS37" s="42"/>
       <c r="CT37" s="42"/>
@@ -14915,36 +14910,36 @@
       <c r="W38" s="35"/>
       <c r="X38" s="35"/>
       <c r="Y38" s="35"/>
-      <c r="Z38" s="59"/>
-      <c r="AA38" s="59"/>
-      <c r="AB38" s="59"/>
-      <c r="AC38" s="59"/>
-      <c r="AD38" s="59"/>
-      <c r="AE38" s="59"/>
-      <c r="AF38" s="59"/>
-      <c r="AG38" s="59"/>
-      <c r="AH38" s="59"/>
-      <c r="AI38" s="59"/>
-      <c r="AJ38" s="59"/>
-      <c r="AK38" s="59"/>
-      <c r="AL38" s="59"/>
-      <c r="AM38" s="59"/>
-      <c r="AN38" s="59"/>
-      <c r="AO38" s="59"/>
-      <c r="AP38" s="59"/>
-      <c r="AQ38" s="59"/>
-      <c r="AR38" s="59"/>
-      <c r="AS38" s="59"/>
-      <c r="AT38" s="59"/>
-      <c r="AU38" s="59"/>
-      <c r="AV38" s="59"/>
-      <c r="AW38" s="59"/>
-      <c r="AX38" s="59"/>
-      <c r="AY38" s="59"/>
-      <c r="AZ38" s="59"/>
-      <c r="BA38" s="59"/>
-      <c r="BB38" s="59"/>
-      <c r="BC38" s="59"/>
+      <c r="Z38" s="62"/>
+      <c r="AA38" s="62"/>
+      <c r="AB38" s="62"/>
+      <c r="AC38" s="62"/>
+      <c r="AD38" s="62"/>
+      <c r="AE38" s="62"/>
+      <c r="AF38" s="62"/>
+      <c r="AG38" s="62"/>
+      <c r="AH38" s="62"/>
+      <c r="AI38" s="62"/>
+      <c r="AJ38" s="62"/>
+      <c r="AK38" s="62"/>
+      <c r="AL38" s="62"/>
+      <c r="AM38" s="62"/>
+      <c r="AN38" s="62"/>
+      <c r="AO38" s="62"/>
+      <c r="AP38" s="62"/>
+      <c r="AQ38" s="62"/>
+      <c r="AR38" s="62"/>
+      <c r="AS38" s="62"/>
+      <c r="AT38" s="62"/>
+      <c r="AU38" s="62"/>
+      <c r="AV38" s="62"/>
+      <c r="AW38" s="62"/>
+      <c r="AX38" s="62"/>
+      <c r="AY38" s="62"/>
+      <c r="AZ38" s="62"/>
+      <c r="BA38" s="62"/>
+      <c r="BB38" s="62"/>
+      <c r="BC38" s="62"/>
       <c r="BD38" s="43"/>
       <c r="BE38" s="35"/>
       <c r="BF38" s="35"/>
@@ -14955,36 +14950,36 @@
       <c r="BK38" s="35"/>
       <c r="BL38" s="35"/>
       <c r="BM38" s="35"/>
-      <c r="BN38" s="56"/>
-      <c r="BO38" s="56"/>
-      <c r="BP38" s="56"/>
-      <c r="BQ38" s="56"/>
-      <c r="BR38" s="56"/>
-      <c r="BS38" s="56"/>
-      <c r="BT38" s="56"/>
-      <c r="BU38" s="56"/>
-      <c r="BV38" s="56"/>
-      <c r="BW38" s="56"/>
-      <c r="BX38" s="56"/>
-      <c r="BY38" s="56"/>
-      <c r="BZ38" s="56"/>
-      <c r="CA38" s="56"/>
-      <c r="CB38" s="56"/>
-      <c r="CC38" s="56"/>
-      <c r="CD38" s="56"/>
-      <c r="CE38" s="56"/>
-      <c r="CF38" s="56"/>
-      <c r="CG38" s="56"/>
-      <c r="CH38" s="56"/>
-      <c r="CI38" s="56"/>
-      <c r="CJ38" s="56"/>
-      <c r="CK38" s="56"/>
-      <c r="CL38" s="56"/>
-      <c r="CM38" s="56"/>
-      <c r="CN38" s="56"/>
-      <c r="CO38" s="56"/>
-      <c r="CP38" s="56"/>
-      <c r="CQ38" s="56"/>
+      <c r="BN38" s="54"/>
+      <c r="BO38" s="54"/>
+      <c r="BP38" s="54"/>
+      <c r="BQ38" s="54"/>
+      <c r="BR38" s="54"/>
+      <c r="BS38" s="54"/>
+      <c r="BT38" s="54"/>
+      <c r="BU38" s="54"/>
+      <c r="BV38" s="54"/>
+      <c r="BW38" s="54"/>
+      <c r="BX38" s="54"/>
+      <c r="BY38" s="54"/>
+      <c r="BZ38" s="54"/>
+      <c r="CA38" s="54"/>
+      <c r="CB38" s="54"/>
+      <c r="CC38" s="54"/>
+      <c r="CD38" s="54"/>
+      <c r="CE38" s="54"/>
+      <c r="CF38" s="54"/>
+      <c r="CG38" s="54"/>
+      <c r="CH38" s="54"/>
+      <c r="CI38" s="54"/>
+      <c r="CJ38" s="54"/>
+      <c r="CK38" s="54"/>
+      <c r="CL38" s="54"/>
+      <c r="CM38" s="54"/>
+      <c r="CN38" s="54"/>
+      <c r="CO38" s="54"/>
+      <c r="CP38" s="54"/>
+      <c r="CQ38" s="54"/>
       <c r="CR38" s="42"/>
       <c r="CS38" s="42"/>
       <c r="CT38" s="42"/>
@@ -14999,36 +14994,36 @@
       <c r="W39" s="35"/>
       <c r="X39" s="35"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="59"/>
-      <c r="AA39" s="59"/>
-      <c r="AB39" s="59"/>
-      <c r="AC39" s="59"/>
-      <c r="AD39" s="59"/>
-      <c r="AE39" s="59"/>
-      <c r="AF39" s="59"/>
-      <c r="AG39" s="59"/>
-      <c r="AH39" s="59"/>
-      <c r="AI39" s="59"/>
-      <c r="AJ39" s="59"/>
-      <c r="AK39" s="59"/>
-      <c r="AL39" s="59"/>
-      <c r="AM39" s="59"/>
-      <c r="AN39" s="59"/>
-      <c r="AO39" s="59"/>
-      <c r="AP39" s="59"/>
-      <c r="AQ39" s="59"/>
-      <c r="AR39" s="59"/>
-      <c r="AS39" s="59"/>
-      <c r="AT39" s="59"/>
-      <c r="AU39" s="59"/>
-      <c r="AV39" s="59"/>
-      <c r="AW39" s="59"/>
-      <c r="AX39" s="59"/>
-      <c r="AY39" s="59"/>
-      <c r="AZ39" s="59"/>
-      <c r="BA39" s="59"/>
-      <c r="BB39" s="59"/>
-      <c r="BC39" s="59"/>
+      <c r="Z39" s="62"/>
+      <c r="AA39" s="62"/>
+      <c r="AB39" s="62"/>
+      <c r="AC39" s="62"/>
+      <c r="AD39" s="62"/>
+      <c r="AE39" s="62"/>
+      <c r="AF39" s="62"/>
+      <c r="AG39" s="62"/>
+      <c r="AH39" s="62"/>
+      <c r="AI39" s="62"/>
+      <c r="AJ39" s="62"/>
+      <c r="AK39" s="62"/>
+      <c r="AL39" s="62"/>
+      <c r="AM39" s="62"/>
+      <c r="AN39" s="62"/>
+      <c r="AO39" s="62"/>
+      <c r="AP39" s="62"/>
+      <c r="AQ39" s="62"/>
+      <c r="AR39" s="62"/>
+      <c r="AS39" s="62"/>
+      <c r="AT39" s="62"/>
+      <c r="AU39" s="62"/>
+      <c r="AV39" s="62"/>
+      <c r="AW39" s="62"/>
+      <c r="AX39" s="62"/>
+      <c r="AY39" s="62"/>
+      <c r="AZ39" s="62"/>
+      <c r="BA39" s="62"/>
+      <c r="BB39" s="62"/>
+      <c r="BC39" s="62"/>
       <c r="BD39" s="43"/>
       <c r="BE39" s="35"/>
       <c r="BF39" s="35"/>
@@ -15083,38 +15078,38 @@
       <c r="W40" s="35"/>
       <c r="X40" s="35"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="57" t="s">
+      <c r="Z40" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="AA40" s="57"/>
-      <c r="AB40" s="57"/>
-      <c r="AC40" s="57"/>
-      <c r="AD40" s="57"/>
-      <c r="AE40" s="57"/>
-      <c r="AF40" s="57"/>
-      <c r="AG40" s="57"/>
-      <c r="AH40" s="57"/>
-      <c r="AI40" s="57"/>
-      <c r="AJ40" s="57"/>
-      <c r="AK40" s="57"/>
-      <c r="AL40" s="57"/>
-      <c r="AM40" s="57"/>
-      <c r="AN40" s="57"/>
-      <c r="AO40" s="57"/>
-      <c r="AP40" s="57"/>
-      <c r="AQ40" s="57"/>
-      <c r="AR40" s="57"/>
-      <c r="AS40" s="57"/>
-      <c r="AT40" s="57"/>
-      <c r="AU40" s="57"/>
-      <c r="AV40" s="57"/>
-      <c r="AW40" s="57"/>
-      <c r="AX40" s="57"/>
-      <c r="AY40" s="57"/>
-      <c r="AZ40" s="57"/>
-      <c r="BA40" s="57"/>
-      <c r="BB40" s="57"/>
-      <c r="BC40" s="57"/>
+      <c r="AA40" s="63"/>
+      <c r="AB40" s="63"/>
+      <c r="AC40" s="63"/>
+      <c r="AD40" s="63"/>
+      <c r="AE40" s="63"/>
+      <c r="AF40" s="63"/>
+      <c r="AG40" s="63"/>
+      <c r="AH40" s="63"/>
+      <c r="AI40" s="63"/>
+      <c r="AJ40" s="63"/>
+      <c r="AK40" s="63"/>
+      <c r="AL40" s="63"/>
+      <c r="AM40" s="63"/>
+      <c r="AN40" s="63"/>
+      <c r="AO40" s="63"/>
+      <c r="AP40" s="63"/>
+      <c r="AQ40" s="63"/>
+      <c r="AR40" s="63"/>
+      <c r="AS40" s="63"/>
+      <c r="AT40" s="63"/>
+      <c r="AU40" s="63"/>
+      <c r="AV40" s="63"/>
+      <c r="AW40" s="63"/>
+      <c r="AX40" s="63"/>
+      <c r="AY40" s="63"/>
+      <c r="AZ40" s="63"/>
+      <c r="BA40" s="63"/>
+      <c r="BB40" s="63"/>
+      <c r="BC40" s="63"/>
       <c r="BD40" s="44"/>
       <c r="BE40" s="35"/>
       <c r="BF40" s="35"/>
@@ -15125,38 +15120,38 @@
       <c r="BK40" s="35"/>
       <c r="BL40" s="35"/>
       <c r="BM40" s="35"/>
-      <c r="BN40" s="55" t="s">
+      <c r="BN40" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="BO40" s="55"/>
-      <c r="BP40" s="55"/>
-      <c r="BQ40" s="55"/>
-      <c r="BR40" s="55"/>
-      <c r="BS40" s="55"/>
-      <c r="BT40" s="55"/>
-      <c r="BU40" s="55"/>
-      <c r="BV40" s="55"/>
-      <c r="BW40" s="55"/>
-      <c r="BX40" s="55"/>
-      <c r="BY40" s="55"/>
-      <c r="BZ40" s="55"/>
-      <c r="CA40" s="55"/>
-      <c r="CB40" s="55"/>
-      <c r="CC40" s="55"/>
-      <c r="CD40" s="55"/>
-      <c r="CE40" s="55"/>
-      <c r="CF40" s="55"/>
-      <c r="CG40" s="55"/>
-      <c r="CH40" s="55"/>
-      <c r="CI40" s="55"/>
-      <c r="CJ40" s="55"/>
-      <c r="CK40" s="55"/>
-      <c r="CL40" s="55"/>
-      <c r="CM40" s="55"/>
-      <c r="CN40" s="55"/>
-      <c r="CO40" s="55"/>
-      <c r="CP40" s="55"/>
-      <c r="CQ40" s="55"/>
+      <c r="BO40" s="53"/>
+      <c r="BP40" s="53"/>
+      <c r="BQ40" s="53"/>
+      <c r="BR40" s="53"/>
+      <c r="BS40" s="53"/>
+      <c r="BT40" s="53"/>
+      <c r="BU40" s="53"/>
+      <c r="BV40" s="53"/>
+      <c r="BW40" s="53"/>
+      <c r="BX40" s="53"/>
+      <c r="BY40" s="53"/>
+      <c r="BZ40" s="53"/>
+      <c r="CA40" s="53"/>
+      <c r="CB40" s="53"/>
+      <c r="CC40" s="53"/>
+      <c r="CD40" s="53"/>
+      <c r="CE40" s="53"/>
+      <c r="CF40" s="53"/>
+      <c r="CG40" s="53"/>
+      <c r="CH40" s="53"/>
+      <c r="CI40" s="53"/>
+      <c r="CJ40" s="53"/>
+      <c r="CK40" s="53"/>
+      <c r="CL40" s="53"/>
+      <c r="CM40" s="53"/>
+      <c r="CN40" s="53"/>
+      <c r="CO40" s="53"/>
+      <c r="CP40" s="53"/>
+      <c r="CQ40" s="53"/>
       <c r="CR40" s="41"/>
       <c r="CS40" s="41"/>
       <c r="CT40" s="41"/>
@@ -15171,36 +15166,36 @@
       <c r="W41" s="35"/>
       <c r="X41" s="35"/>
       <c r="Y41" s="35"/>
-      <c r="Z41" s="57"/>
-      <c r="AA41" s="57"/>
-      <c r="AB41" s="57"/>
-      <c r="AC41" s="57"/>
-      <c r="AD41" s="57"/>
-      <c r="AE41" s="57"/>
-      <c r="AF41" s="57"/>
-      <c r="AG41" s="57"/>
-      <c r="AH41" s="57"/>
-      <c r="AI41" s="57"/>
-      <c r="AJ41" s="57"/>
-      <c r="AK41" s="57"/>
-      <c r="AL41" s="57"/>
-      <c r="AM41" s="57"/>
-      <c r="AN41" s="57"/>
-      <c r="AO41" s="57"/>
-      <c r="AP41" s="57"/>
-      <c r="AQ41" s="57"/>
-      <c r="AR41" s="57"/>
-      <c r="AS41" s="57"/>
-      <c r="AT41" s="57"/>
-      <c r="AU41" s="57"/>
-      <c r="AV41" s="57"/>
-      <c r="AW41" s="57"/>
-      <c r="AX41" s="57"/>
-      <c r="AY41" s="57"/>
-      <c r="AZ41" s="57"/>
-      <c r="BA41" s="57"/>
-      <c r="BB41" s="57"/>
-      <c r="BC41" s="57"/>
+      <c r="Z41" s="63"/>
+      <c r="AA41" s="63"/>
+      <c r="AB41" s="63"/>
+      <c r="AC41" s="63"/>
+      <c r="AD41" s="63"/>
+      <c r="AE41" s="63"/>
+      <c r="AF41" s="63"/>
+      <c r="AG41" s="63"/>
+      <c r="AH41" s="63"/>
+      <c r="AI41" s="63"/>
+      <c r="AJ41" s="63"/>
+      <c r="AK41" s="63"/>
+      <c r="AL41" s="63"/>
+      <c r="AM41" s="63"/>
+      <c r="AN41" s="63"/>
+      <c r="AO41" s="63"/>
+      <c r="AP41" s="63"/>
+      <c r="AQ41" s="63"/>
+      <c r="AR41" s="63"/>
+      <c r="AS41" s="63"/>
+      <c r="AT41" s="63"/>
+      <c r="AU41" s="63"/>
+      <c r="AV41" s="63"/>
+      <c r="AW41" s="63"/>
+      <c r="AX41" s="63"/>
+      <c r="AY41" s="63"/>
+      <c r="AZ41" s="63"/>
+      <c r="BA41" s="63"/>
+      <c r="BB41" s="63"/>
+      <c r="BC41" s="63"/>
       <c r="BD41" s="44"/>
       <c r="BE41" s="35"/>
       <c r="BF41" s="35"/>
@@ -15211,36 +15206,36 @@
       <c r="BK41" s="35"/>
       <c r="BL41" s="35"/>
       <c r="BM41" s="35"/>
-      <c r="BN41" s="55"/>
-      <c r="BO41" s="55"/>
-      <c r="BP41" s="55"/>
-      <c r="BQ41" s="55"/>
-      <c r="BR41" s="55"/>
-      <c r="BS41" s="55"/>
-      <c r="BT41" s="55"/>
-      <c r="BU41" s="55"/>
-      <c r="BV41" s="55"/>
-      <c r="BW41" s="55"/>
-      <c r="BX41" s="55"/>
-      <c r="BY41" s="55"/>
-      <c r="BZ41" s="55"/>
-      <c r="CA41" s="55"/>
-      <c r="CB41" s="55"/>
-      <c r="CC41" s="55"/>
-      <c r="CD41" s="55"/>
-      <c r="CE41" s="55"/>
-      <c r="CF41" s="55"/>
-      <c r="CG41" s="55"/>
-      <c r="CH41" s="55"/>
-      <c r="CI41" s="55"/>
-      <c r="CJ41" s="55"/>
-      <c r="CK41" s="55"/>
-      <c r="CL41" s="55"/>
-      <c r="CM41" s="55"/>
-      <c r="CN41" s="55"/>
-      <c r="CO41" s="55"/>
-      <c r="CP41" s="55"/>
-      <c r="CQ41" s="55"/>
+      <c r="BN41" s="53"/>
+      <c r="BO41" s="53"/>
+      <c r="BP41" s="53"/>
+      <c r="BQ41" s="53"/>
+      <c r="BR41" s="53"/>
+      <c r="BS41" s="53"/>
+      <c r="BT41" s="53"/>
+      <c r="BU41" s="53"/>
+      <c r="BV41" s="53"/>
+      <c r="BW41" s="53"/>
+      <c r="BX41" s="53"/>
+      <c r="BY41" s="53"/>
+      <c r="BZ41" s="53"/>
+      <c r="CA41" s="53"/>
+      <c r="CB41" s="53"/>
+      <c r="CC41" s="53"/>
+      <c r="CD41" s="53"/>
+      <c r="CE41" s="53"/>
+      <c r="CF41" s="53"/>
+      <c r="CG41" s="53"/>
+      <c r="CH41" s="53"/>
+      <c r="CI41" s="53"/>
+      <c r="CJ41" s="53"/>
+      <c r="CK41" s="53"/>
+      <c r="CL41" s="53"/>
+      <c r="CM41" s="53"/>
+      <c r="CN41" s="53"/>
+      <c r="CO41" s="53"/>
+      <c r="CP41" s="53"/>
+      <c r="CQ41" s="53"/>
       <c r="CR41" s="41"/>
       <c r="CS41" s="41"/>
       <c r="CT41" s="41"/>
@@ -15295,36 +15290,36 @@
       <c r="BK42" s="35"/>
       <c r="BL42" s="35"/>
       <c r="BM42" s="35"/>
-      <c r="BN42" s="55"/>
-      <c r="BO42" s="55"/>
-      <c r="BP42" s="55"/>
-      <c r="BQ42" s="55"/>
-      <c r="BR42" s="55"/>
-      <c r="BS42" s="55"/>
-      <c r="BT42" s="55"/>
-      <c r="BU42" s="55"/>
-      <c r="BV42" s="55"/>
-      <c r="BW42" s="55"/>
-      <c r="BX42" s="55"/>
-      <c r="BY42" s="55"/>
-      <c r="BZ42" s="55"/>
-      <c r="CA42" s="55"/>
-      <c r="CB42" s="55"/>
-      <c r="CC42" s="55"/>
-      <c r="CD42" s="55"/>
-      <c r="CE42" s="55"/>
-      <c r="CF42" s="55"/>
-      <c r="CG42" s="55"/>
-      <c r="CH42" s="55"/>
-      <c r="CI42" s="55"/>
-      <c r="CJ42" s="55"/>
-      <c r="CK42" s="55"/>
-      <c r="CL42" s="55"/>
-      <c r="CM42" s="55"/>
-      <c r="CN42" s="55"/>
-      <c r="CO42" s="55"/>
-      <c r="CP42" s="55"/>
-      <c r="CQ42" s="55"/>
+      <c r="BN42" s="53"/>
+      <c r="BO42" s="53"/>
+      <c r="BP42" s="53"/>
+      <c r="BQ42" s="53"/>
+      <c r="BR42" s="53"/>
+      <c r="BS42" s="53"/>
+      <c r="BT42" s="53"/>
+      <c r="BU42" s="53"/>
+      <c r="BV42" s="53"/>
+      <c r="BW42" s="53"/>
+      <c r="BX42" s="53"/>
+      <c r="BY42" s="53"/>
+      <c r="BZ42" s="53"/>
+      <c r="CA42" s="53"/>
+      <c r="CB42" s="53"/>
+      <c r="CC42" s="53"/>
+      <c r="CD42" s="53"/>
+      <c r="CE42" s="53"/>
+      <c r="CF42" s="53"/>
+      <c r="CG42" s="53"/>
+      <c r="CH42" s="53"/>
+      <c r="CI42" s="53"/>
+      <c r="CJ42" s="53"/>
+      <c r="CK42" s="53"/>
+      <c r="CL42" s="53"/>
+      <c r="CM42" s="53"/>
+      <c r="CN42" s="53"/>
+      <c r="CO42" s="53"/>
+      <c r="CP42" s="53"/>
+      <c r="CQ42" s="53"/>
       <c r="CR42" s="41"/>
       <c r="CS42" s="41"/>
       <c r="CT42" s="41"/>
@@ -15339,38 +15334,38 @@
       <c r="W43" s="39"/>
       <c r="X43" s="39"/>
       <c r="Y43" s="39"/>
-      <c r="Z43" s="53" t="s">
+      <c r="Z43" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="AA43" s="53"/>
-      <c r="AB43" s="53"/>
-      <c r="AC43" s="53"/>
-      <c r="AD43" s="53"/>
-      <c r="AE43" s="53"/>
-      <c r="AF43" s="53"/>
-      <c r="AG43" s="53"/>
-      <c r="AH43" s="53"/>
-      <c r="AI43" s="53"/>
-      <c r="AJ43" s="53"/>
-      <c r="AK43" s="53"/>
-      <c r="AL43" s="53"/>
-      <c r="AM43" s="53"/>
-      <c r="AN43" s="53"/>
-      <c r="AO43" s="53"/>
-      <c r="AP43" s="53"/>
-      <c r="AQ43" s="53"/>
-      <c r="AR43" s="53"/>
-      <c r="AS43" s="53"/>
-      <c r="AT43" s="53"/>
-      <c r="AU43" s="53"/>
-      <c r="AV43" s="53"/>
-      <c r="AW43" s="53"/>
-      <c r="AX43" s="53"/>
-      <c r="AY43" s="53"/>
-      <c r="AZ43" s="53"/>
-      <c r="BA43" s="53"/>
-      <c r="BB43" s="53"/>
-      <c r="BC43" s="53"/>
+      <c r="AA43" s="60"/>
+      <c r="AB43" s="60"/>
+      <c r="AC43" s="60"/>
+      <c r="AD43" s="60"/>
+      <c r="AE43" s="60"/>
+      <c r="AF43" s="60"/>
+      <c r="AG43" s="60"/>
+      <c r="AH43" s="60"/>
+      <c r="AI43" s="60"/>
+      <c r="AJ43" s="60"/>
+      <c r="AK43" s="60"/>
+      <c r="AL43" s="60"/>
+      <c r="AM43" s="60"/>
+      <c r="AN43" s="60"/>
+      <c r="AO43" s="60"/>
+      <c r="AP43" s="60"/>
+      <c r="AQ43" s="60"/>
+      <c r="AR43" s="60"/>
+      <c r="AS43" s="60"/>
+      <c r="AT43" s="60"/>
+      <c r="AU43" s="60"/>
+      <c r="AV43" s="60"/>
+      <c r="AW43" s="60"/>
+      <c r="AX43" s="60"/>
+      <c r="AY43" s="60"/>
+      <c r="AZ43" s="60"/>
+      <c r="BA43" s="60"/>
+      <c r="BB43" s="60"/>
+      <c r="BC43" s="60"/>
       <c r="BD43" s="48"/>
       <c r="BE43" s="35"/>
       <c r="BF43" s="35"/>
@@ -15381,38 +15376,38 @@
       <c r="BK43" s="35"/>
       <c r="BL43" s="35"/>
       <c r="BM43" s="35"/>
-      <c r="BN43" s="56" t="s">
+      <c r="BN43" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="BO43" s="56"/>
-      <c r="BP43" s="56"/>
-      <c r="BQ43" s="56"/>
-      <c r="BR43" s="56"/>
-      <c r="BS43" s="56"/>
-      <c r="BT43" s="56"/>
-      <c r="BU43" s="56"/>
-      <c r="BV43" s="56"/>
-      <c r="BW43" s="56"/>
-      <c r="BX43" s="56"/>
-      <c r="BY43" s="56"/>
-      <c r="BZ43" s="56"/>
-      <c r="CA43" s="56"/>
-      <c r="CB43" s="56"/>
-      <c r="CC43" s="56"/>
-      <c r="CD43" s="56"/>
-      <c r="CE43" s="56"/>
-      <c r="CF43" s="56"/>
-      <c r="CG43" s="56"/>
-      <c r="CH43" s="56"/>
-      <c r="CI43" s="56"/>
-      <c r="CJ43" s="56"/>
-      <c r="CK43" s="56"/>
-      <c r="CL43" s="56"/>
-      <c r="CM43" s="56"/>
-      <c r="CN43" s="56"/>
-      <c r="CO43" s="56"/>
-      <c r="CP43" s="56"/>
-      <c r="CQ43" s="56"/>
+      <c r="BO43" s="54"/>
+      <c r="BP43" s="54"/>
+      <c r="BQ43" s="54"/>
+      <c r="BR43" s="54"/>
+      <c r="BS43" s="54"/>
+      <c r="BT43" s="54"/>
+      <c r="BU43" s="54"/>
+      <c r="BV43" s="54"/>
+      <c r="BW43" s="54"/>
+      <c r="BX43" s="54"/>
+      <c r="BY43" s="54"/>
+      <c r="BZ43" s="54"/>
+      <c r="CA43" s="54"/>
+      <c r="CB43" s="54"/>
+      <c r="CC43" s="54"/>
+      <c r="CD43" s="54"/>
+      <c r="CE43" s="54"/>
+      <c r="CF43" s="54"/>
+      <c r="CG43" s="54"/>
+      <c r="CH43" s="54"/>
+      <c r="CI43" s="54"/>
+      <c r="CJ43" s="54"/>
+      <c r="CK43" s="54"/>
+      <c r="CL43" s="54"/>
+      <c r="CM43" s="54"/>
+      <c r="CN43" s="54"/>
+      <c r="CO43" s="54"/>
+      <c r="CP43" s="54"/>
+      <c r="CQ43" s="54"/>
       <c r="CR43" s="42"/>
       <c r="CS43" s="42"/>
       <c r="CT43" s="42"/>
@@ -15427,36 +15422,36 @@
       <c r="W44" s="35"/>
       <c r="X44" s="35"/>
       <c r="Y44" s="35"/>
-      <c r="Z44" s="54"/>
-      <c r="AA44" s="54"/>
-      <c r="AB44" s="54"/>
-      <c r="AC44" s="54"/>
-      <c r="AD44" s="54"/>
-      <c r="AE44" s="54"/>
-      <c r="AF44" s="54"/>
-      <c r="AG44" s="54"/>
-      <c r="AH44" s="54"/>
-      <c r="AI44" s="54"/>
-      <c r="AJ44" s="54"/>
-      <c r="AK44" s="54"/>
-      <c r="AL44" s="54"/>
-      <c r="AM44" s="54"/>
-      <c r="AN44" s="54"/>
-      <c r="AO44" s="54"/>
-      <c r="AP44" s="54"/>
-      <c r="AQ44" s="54"/>
-      <c r="AR44" s="54"/>
-      <c r="AS44" s="54"/>
-      <c r="AT44" s="54"/>
-      <c r="AU44" s="54"/>
-      <c r="AV44" s="54"/>
-      <c r="AW44" s="54"/>
-      <c r="AX44" s="54"/>
-      <c r="AY44" s="54"/>
-      <c r="AZ44" s="54"/>
-      <c r="BA44" s="54"/>
-      <c r="BB44" s="54"/>
-      <c r="BC44" s="54"/>
+      <c r="Z44" s="61"/>
+      <c r="AA44" s="61"/>
+      <c r="AB44" s="61"/>
+      <c r="AC44" s="61"/>
+      <c r="AD44" s="61"/>
+      <c r="AE44" s="61"/>
+      <c r="AF44" s="61"/>
+      <c r="AG44" s="61"/>
+      <c r="AH44" s="61"/>
+      <c r="AI44" s="61"/>
+      <c r="AJ44" s="61"/>
+      <c r="AK44" s="61"/>
+      <c r="AL44" s="61"/>
+      <c r="AM44" s="61"/>
+      <c r="AN44" s="61"/>
+      <c r="AO44" s="61"/>
+      <c r="AP44" s="61"/>
+      <c r="AQ44" s="61"/>
+      <c r="AR44" s="61"/>
+      <c r="AS44" s="61"/>
+      <c r="AT44" s="61"/>
+      <c r="AU44" s="61"/>
+      <c r="AV44" s="61"/>
+      <c r="AW44" s="61"/>
+      <c r="AX44" s="61"/>
+      <c r="AY44" s="61"/>
+      <c r="AZ44" s="61"/>
+      <c r="BA44" s="61"/>
+      <c r="BB44" s="61"/>
+      <c r="BC44" s="61"/>
       <c r="BD44" s="48"/>
       <c r="BE44" s="35"/>
       <c r="BF44" s="35"/>
@@ -15467,36 +15462,36 @@
       <c r="BK44" s="35"/>
       <c r="BL44" s="35"/>
       <c r="BM44" s="35"/>
-      <c r="BN44" s="56"/>
-      <c r="BO44" s="56"/>
-      <c r="BP44" s="56"/>
-      <c r="BQ44" s="56"/>
-      <c r="BR44" s="56"/>
-      <c r="BS44" s="56"/>
-      <c r="BT44" s="56"/>
-      <c r="BU44" s="56"/>
-      <c r="BV44" s="56"/>
-      <c r="BW44" s="56"/>
-      <c r="BX44" s="56"/>
-      <c r="BY44" s="56"/>
-      <c r="BZ44" s="56"/>
-      <c r="CA44" s="56"/>
-      <c r="CB44" s="56"/>
-      <c r="CC44" s="56"/>
-      <c r="CD44" s="56"/>
-      <c r="CE44" s="56"/>
-      <c r="CF44" s="56"/>
-      <c r="CG44" s="56"/>
-      <c r="CH44" s="56"/>
-      <c r="CI44" s="56"/>
-      <c r="CJ44" s="56"/>
-      <c r="CK44" s="56"/>
-      <c r="CL44" s="56"/>
-      <c r="CM44" s="56"/>
-      <c r="CN44" s="56"/>
-      <c r="CO44" s="56"/>
-      <c r="CP44" s="56"/>
-      <c r="CQ44" s="56"/>
+      <c r="BN44" s="54"/>
+      <c r="BO44" s="54"/>
+      <c r="BP44" s="54"/>
+      <c r="BQ44" s="54"/>
+      <c r="BR44" s="54"/>
+      <c r="BS44" s="54"/>
+      <c r="BT44" s="54"/>
+      <c r="BU44" s="54"/>
+      <c r="BV44" s="54"/>
+      <c r="BW44" s="54"/>
+      <c r="BX44" s="54"/>
+      <c r="BY44" s="54"/>
+      <c r="BZ44" s="54"/>
+      <c r="CA44" s="54"/>
+      <c r="CB44" s="54"/>
+      <c r="CC44" s="54"/>
+      <c r="CD44" s="54"/>
+      <c r="CE44" s="54"/>
+      <c r="CF44" s="54"/>
+      <c r="CG44" s="54"/>
+      <c r="CH44" s="54"/>
+      <c r="CI44" s="54"/>
+      <c r="CJ44" s="54"/>
+      <c r="CK44" s="54"/>
+      <c r="CL44" s="54"/>
+      <c r="CM44" s="54"/>
+      <c r="CN44" s="54"/>
+      <c r="CO44" s="54"/>
+      <c r="CP44" s="54"/>
+      <c r="CQ44" s="54"/>
       <c r="CR44" s="42"/>
       <c r="CS44" s="42"/>
       <c r="CT44" s="42"/>
@@ -15511,36 +15506,36 @@
       <c r="W45" s="35"/>
       <c r="X45" s="35"/>
       <c r="Y45" s="35"/>
-      <c r="Z45" s="54"/>
-      <c r="AA45" s="54"/>
-      <c r="AB45" s="54"/>
-      <c r="AC45" s="54"/>
-      <c r="AD45" s="54"/>
-      <c r="AE45" s="54"/>
-      <c r="AF45" s="54"/>
-      <c r="AG45" s="54"/>
-      <c r="AH45" s="54"/>
-      <c r="AI45" s="54"/>
-      <c r="AJ45" s="54"/>
-      <c r="AK45" s="54"/>
-      <c r="AL45" s="54"/>
-      <c r="AM45" s="54"/>
-      <c r="AN45" s="54"/>
-      <c r="AO45" s="54"/>
-      <c r="AP45" s="54"/>
-      <c r="AQ45" s="54"/>
-      <c r="AR45" s="54"/>
-      <c r="AS45" s="54"/>
-      <c r="AT45" s="54"/>
-      <c r="AU45" s="54"/>
-      <c r="AV45" s="54"/>
-      <c r="AW45" s="54"/>
-      <c r="AX45" s="54"/>
-      <c r="AY45" s="54"/>
-      <c r="AZ45" s="54"/>
-      <c r="BA45" s="54"/>
-      <c r="BB45" s="54"/>
-      <c r="BC45" s="54"/>
+      <c r="Z45" s="61"/>
+      <c r="AA45" s="61"/>
+      <c r="AB45" s="61"/>
+      <c r="AC45" s="61"/>
+      <c r="AD45" s="61"/>
+      <c r="AE45" s="61"/>
+      <c r="AF45" s="61"/>
+      <c r="AG45" s="61"/>
+      <c r="AH45" s="61"/>
+      <c r="AI45" s="61"/>
+      <c r="AJ45" s="61"/>
+      <c r="AK45" s="61"/>
+      <c r="AL45" s="61"/>
+      <c r="AM45" s="61"/>
+      <c r="AN45" s="61"/>
+      <c r="AO45" s="61"/>
+      <c r="AP45" s="61"/>
+      <c r="AQ45" s="61"/>
+      <c r="AR45" s="61"/>
+      <c r="AS45" s="61"/>
+      <c r="AT45" s="61"/>
+      <c r="AU45" s="61"/>
+      <c r="AV45" s="61"/>
+      <c r="AW45" s="61"/>
+      <c r="AX45" s="61"/>
+      <c r="AY45" s="61"/>
+      <c r="AZ45" s="61"/>
+      <c r="BA45" s="61"/>
+      <c r="BB45" s="61"/>
+      <c r="BC45" s="61"/>
       <c r="BD45" s="48"/>
       <c r="BE45" s="35"/>
       <c r="BF45" s="35"/>
@@ -15595,36 +15590,36 @@
       <c r="W46" s="35"/>
       <c r="X46" s="35"/>
       <c r="Y46" s="35"/>
-      <c r="Z46" s="54"/>
-      <c r="AA46" s="54"/>
-      <c r="AB46" s="54"/>
-      <c r="AC46" s="54"/>
-      <c r="AD46" s="54"/>
-      <c r="AE46" s="54"/>
-      <c r="AF46" s="54"/>
-      <c r="AG46" s="54"/>
-      <c r="AH46" s="54"/>
-      <c r="AI46" s="54"/>
-      <c r="AJ46" s="54"/>
-      <c r="AK46" s="54"/>
-      <c r="AL46" s="54"/>
-      <c r="AM46" s="54"/>
-      <c r="AN46" s="54"/>
-      <c r="AO46" s="54"/>
-      <c r="AP46" s="54"/>
-      <c r="AQ46" s="54"/>
-      <c r="AR46" s="54"/>
-      <c r="AS46" s="54"/>
-      <c r="AT46" s="54"/>
-      <c r="AU46" s="54"/>
-      <c r="AV46" s="54"/>
-      <c r="AW46" s="54"/>
-      <c r="AX46" s="54"/>
-      <c r="AY46" s="54"/>
-      <c r="AZ46" s="54"/>
-      <c r="BA46" s="54"/>
-      <c r="BB46" s="54"/>
-      <c r="BC46" s="54"/>
+      <c r="Z46" s="61"/>
+      <c r="AA46" s="61"/>
+      <c r="AB46" s="61"/>
+      <c r="AC46" s="61"/>
+      <c r="AD46" s="61"/>
+      <c r="AE46" s="61"/>
+      <c r="AF46" s="61"/>
+      <c r="AG46" s="61"/>
+      <c r="AH46" s="61"/>
+      <c r="AI46" s="61"/>
+      <c r="AJ46" s="61"/>
+      <c r="AK46" s="61"/>
+      <c r="AL46" s="61"/>
+      <c r="AM46" s="61"/>
+      <c r="AN46" s="61"/>
+      <c r="AO46" s="61"/>
+      <c r="AP46" s="61"/>
+      <c r="AQ46" s="61"/>
+      <c r="AR46" s="61"/>
+      <c r="AS46" s="61"/>
+      <c r="AT46" s="61"/>
+      <c r="AU46" s="61"/>
+      <c r="AV46" s="61"/>
+      <c r="AW46" s="61"/>
+      <c r="AX46" s="61"/>
+      <c r="AY46" s="61"/>
+      <c r="AZ46" s="61"/>
+      <c r="BA46" s="61"/>
+      <c r="BB46" s="61"/>
+      <c r="BC46" s="61"/>
       <c r="BD46" s="48"/>
       <c r="BE46" s="35"/>
       <c r="BF46" s="35"/>
@@ -15679,36 +15674,36 @@
       <c r="W47" s="35"/>
       <c r="X47" s="35"/>
       <c r="Y47" s="35"/>
-      <c r="Z47" s="54"/>
-      <c r="AA47" s="54"/>
-      <c r="AB47" s="54"/>
-      <c r="AC47" s="54"/>
-      <c r="AD47" s="54"/>
-      <c r="AE47" s="54"/>
-      <c r="AF47" s="54"/>
-      <c r="AG47" s="54"/>
-      <c r="AH47" s="54"/>
-      <c r="AI47" s="54"/>
-      <c r="AJ47" s="54"/>
-      <c r="AK47" s="54"/>
-      <c r="AL47" s="54"/>
-      <c r="AM47" s="54"/>
-      <c r="AN47" s="54"/>
-      <c r="AO47" s="54"/>
-      <c r="AP47" s="54"/>
-      <c r="AQ47" s="54"/>
-      <c r="AR47" s="54"/>
-      <c r="AS47" s="54"/>
-      <c r="AT47" s="54"/>
-      <c r="AU47" s="54"/>
-      <c r="AV47" s="54"/>
-      <c r="AW47" s="54"/>
-      <c r="AX47" s="54"/>
-      <c r="AY47" s="54"/>
-      <c r="AZ47" s="54"/>
-      <c r="BA47" s="54"/>
-      <c r="BB47" s="54"/>
-      <c r="BC47" s="54"/>
+      <c r="Z47" s="61"/>
+      <c r="AA47" s="61"/>
+      <c r="AB47" s="61"/>
+      <c r="AC47" s="61"/>
+      <c r="AD47" s="61"/>
+      <c r="AE47" s="61"/>
+      <c r="AF47" s="61"/>
+      <c r="AG47" s="61"/>
+      <c r="AH47" s="61"/>
+      <c r="AI47" s="61"/>
+      <c r="AJ47" s="61"/>
+      <c r="AK47" s="61"/>
+      <c r="AL47" s="61"/>
+      <c r="AM47" s="61"/>
+      <c r="AN47" s="61"/>
+      <c r="AO47" s="61"/>
+      <c r="AP47" s="61"/>
+      <c r="AQ47" s="61"/>
+      <c r="AR47" s="61"/>
+      <c r="AS47" s="61"/>
+      <c r="AT47" s="61"/>
+      <c r="AU47" s="61"/>
+      <c r="AV47" s="61"/>
+      <c r="AW47" s="61"/>
+      <c r="AX47" s="61"/>
+      <c r="AY47" s="61"/>
+      <c r="AZ47" s="61"/>
+      <c r="BA47" s="61"/>
+      <c r="BB47" s="61"/>
+      <c r="BC47" s="61"/>
       <c r="BD47" s="48"/>
       <c r="BE47" s="35"/>
       <c r="BF47" s="35"/>
@@ -15763,38 +15758,38 @@
       <c r="W48" s="35"/>
       <c r="X48" s="35"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="59" t="s">
+      <c r="Z48" s="62" t="s">
         <v>113</v>
       </c>
-      <c r="AA48" s="59"/>
-      <c r="AB48" s="59"/>
-      <c r="AC48" s="59"/>
-      <c r="AD48" s="59"/>
-      <c r="AE48" s="59"/>
-      <c r="AF48" s="59"/>
-      <c r="AG48" s="59"/>
-      <c r="AH48" s="59"/>
-      <c r="AI48" s="59"/>
-      <c r="AJ48" s="59"/>
-      <c r="AK48" s="59"/>
-      <c r="AL48" s="59"/>
-      <c r="AM48" s="59"/>
-      <c r="AN48" s="59"/>
-      <c r="AO48" s="59"/>
-      <c r="AP48" s="59"/>
-      <c r="AQ48" s="59"/>
-      <c r="AR48" s="59"/>
-      <c r="AS48" s="59"/>
-      <c r="AT48" s="59"/>
-      <c r="AU48" s="59"/>
-      <c r="AV48" s="59"/>
-      <c r="AW48" s="59"/>
-      <c r="AX48" s="59"/>
-      <c r="AY48" s="59"/>
-      <c r="AZ48" s="59"/>
-      <c r="BA48" s="59"/>
-      <c r="BB48" s="59"/>
-      <c r="BC48" s="59"/>
+      <c r="AA48" s="62"/>
+      <c r="AB48" s="62"/>
+      <c r="AC48" s="62"/>
+      <c r="AD48" s="62"/>
+      <c r="AE48" s="62"/>
+      <c r="AF48" s="62"/>
+      <c r="AG48" s="62"/>
+      <c r="AH48" s="62"/>
+      <c r="AI48" s="62"/>
+      <c r="AJ48" s="62"/>
+      <c r="AK48" s="62"/>
+      <c r="AL48" s="62"/>
+      <c r="AM48" s="62"/>
+      <c r="AN48" s="62"/>
+      <c r="AO48" s="62"/>
+      <c r="AP48" s="62"/>
+      <c r="AQ48" s="62"/>
+      <c r="AR48" s="62"/>
+      <c r="AS48" s="62"/>
+      <c r="AT48" s="62"/>
+      <c r="AU48" s="62"/>
+      <c r="AV48" s="62"/>
+      <c r="AW48" s="62"/>
+      <c r="AX48" s="62"/>
+      <c r="AY48" s="62"/>
+      <c r="AZ48" s="62"/>
+      <c r="BA48" s="62"/>
+      <c r="BB48" s="62"/>
+      <c r="BC48" s="62"/>
       <c r="BD48" s="43"/>
       <c r="BE48" s="35"/>
       <c r="BF48" s="35"/>
@@ -15865,36 +15860,36 @@
       <c r="W49" s="35"/>
       <c r="X49" s="35"/>
       <c r="Y49" s="35"/>
-      <c r="Z49" s="59"/>
-      <c r="AA49" s="59"/>
-      <c r="AB49" s="59"/>
-      <c r="AC49" s="59"/>
-      <c r="AD49" s="59"/>
-      <c r="AE49" s="59"/>
-      <c r="AF49" s="59"/>
-      <c r="AG49" s="59"/>
-      <c r="AH49" s="59"/>
-      <c r="AI49" s="59"/>
-      <c r="AJ49" s="59"/>
-      <c r="AK49" s="59"/>
-      <c r="AL49" s="59"/>
-      <c r="AM49" s="59"/>
-      <c r="AN49" s="59"/>
-      <c r="AO49" s="59"/>
-      <c r="AP49" s="59"/>
-      <c r="AQ49" s="59"/>
-      <c r="AR49" s="59"/>
-      <c r="AS49" s="59"/>
-      <c r="AT49" s="59"/>
-      <c r="AU49" s="59"/>
-      <c r="AV49" s="59"/>
-      <c r="AW49" s="59"/>
-      <c r="AX49" s="59"/>
-      <c r="AY49" s="59"/>
-      <c r="AZ49" s="59"/>
-      <c r="BA49" s="59"/>
-      <c r="BB49" s="59"/>
-      <c r="BC49" s="59"/>
+      <c r="Z49" s="62"/>
+      <c r="AA49" s="62"/>
+      <c r="AB49" s="62"/>
+      <c r="AC49" s="62"/>
+      <c r="AD49" s="62"/>
+      <c r="AE49" s="62"/>
+      <c r="AF49" s="62"/>
+      <c r="AG49" s="62"/>
+      <c r="AH49" s="62"/>
+      <c r="AI49" s="62"/>
+      <c r="AJ49" s="62"/>
+      <c r="AK49" s="62"/>
+      <c r="AL49" s="62"/>
+      <c r="AM49" s="62"/>
+      <c r="AN49" s="62"/>
+      <c r="AO49" s="62"/>
+      <c r="AP49" s="62"/>
+      <c r="AQ49" s="62"/>
+      <c r="AR49" s="62"/>
+      <c r="AS49" s="62"/>
+      <c r="AT49" s="62"/>
+      <c r="AU49" s="62"/>
+      <c r="AV49" s="62"/>
+      <c r="AW49" s="62"/>
+      <c r="AX49" s="62"/>
+      <c r="AY49" s="62"/>
+      <c r="AZ49" s="62"/>
+      <c r="BA49" s="62"/>
+      <c r="BB49" s="62"/>
+      <c r="BC49" s="62"/>
       <c r="BD49" s="43"/>
       <c r="BE49" s="35"/>
       <c r="BF49" s="35"/>
@@ -15965,36 +15960,36 @@
       <c r="W50" s="35"/>
       <c r="X50" s="35"/>
       <c r="Y50" s="35"/>
-      <c r="Z50" s="59"/>
-      <c r="AA50" s="59"/>
-      <c r="AB50" s="59"/>
-      <c r="AC50" s="59"/>
-      <c r="AD50" s="59"/>
-      <c r="AE50" s="59"/>
-      <c r="AF50" s="59"/>
-      <c r="AG50" s="59"/>
-      <c r="AH50" s="59"/>
-      <c r="AI50" s="59"/>
-      <c r="AJ50" s="59"/>
-      <c r="AK50" s="59"/>
-      <c r="AL50" s="59"/>
-      <c r="AM50" s="59"/>
-      <c r="AN50" s="59"/>
-      <c r="AO50" s="59"/>
-      <c r="AP50" s="59"/>
-      <c r="AQ50" s="59"/>
-      <c r="AR50" s="59"/>
-      <c r="AS50" s="59"/>
-      <c r="AT50" s="59"/>
-      <c r="AU50" s="59"/>
-      <c r="AV50" s="59"/>
-      <c r="AW50" s="59"/>
-      <c r="AX50" s="59"/>
-      <c r="AY50" s="59"/>
-      <c r="AZ50" s="59"/>
-      <c r="BA50" s="59"/>
-      <c r="BB50" s="59"/>
-      <c r="BC50" s="59"/>
+      <c r="Z50" s="62"/>
+      <c r="AA50" s="62"/>
+      <c r="AB50" s="62"/>
+      <c r="AC50" s="62"/>
+      <c r="AD50" s="62"/>
+      <c r="AE50" s="62"/>
+      <c r="AF50" s="62"/>
+      <c r="AG50" s="62"/>
+      <c r="AH50" s="62"/>
+      <c r="AI50" s="62"/>
+      <c r="AJ50" s="62"/>
+      <c r="AK50" s="62"/>
+      <c r="AL50" s="62"/>
+      <c r="AM50" s="62"/>
+      <c r="AN50" s="62"/>
+      <c r="AO50" s="62"/>
+      <c r="AP50" s="62"/>
+      <c r="AQ50" s="62"/>
+      <c r="AR50" s="62"/>
+      <c r="AS50" s="62"/>
+      <c r="AT50" s="62"/>
+      <c r="AU50" s="62"/>
+      <c r="AV50" s="62"/>
+      <c r="AW50" s="62"/>
+      <c r="AX50" s="62"/>
+      <c r="AY50" s="62"/>
+      <c r="AZ50" s="62"/>
+      <c r="BA50" s="62"/>
+      <c r="BB50" s="62"/>
+      <c r="BC50" s="62"/>
       <c r="BD50" s="43"/>
       <c r="BE50" s="35"/>
       <c r="BF50" s="35"/>
@@ -16041,23 +16036,23 @@
       <c r="CU50" s="35"/>
     </row>
     <row r="51" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B51" s="63" t="s">
+      <c r="B51" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="63"/>
-      <c r="D51" s="63"/>
-      <c r="E51" s="63"/>
-      <c r="F51" s="63"/>
-      <c r="G51" s="63"/>
-      <c r="H51" s="63"/>
-      <c r="I51" s="63"/>
-      <c r="J51" s="63"/>
-      <c r="K51" s="63"/>
-      <c r="L51" s="63"/>
-      <c r="M51" s="63"/>
-      <c r="N51" s="63"/>
-      <c r="O51" s="63"/>
-      <c r="P51" s="63"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="56"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="56"/>
+      <c r="K51" s="56"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="56"/>
+      <c r="N51" s="56"/>
+      <c r="O51" s="56"/>
+      <c r="P51" s="56"/>
       <c r="Q51" s="35"/>
       <c r="R51" s="35"/>
       <c r="S51" s="35"/>
@@ -16067,38 +16062,38 @@
       <c r="W51" s="35"/>
       <c r="X51" s="35"/>
       <c r="Y51" s="35"/>
-      <c r="Z51" s="57" t="s">
+      <c r="Z51" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="AA51" s="57"/>
-      <c r="AB51" s="57"/>
-      <c r="AC51" s="57"/>
-      <c r="AD51" s="57"/>
-      <c r="AE51" s="57"/>
-      <c r="AF51" s="57"/>
-      <c r="AG51" s="57"/>
-      <c r="AH51" s="57"/>
-      <c r="AI51" s="57"/>
-      <c r="AJ51" s="57"/>
-      <c r="AK51" s="57"/>
-      <c r="AL51" s="57"/>
-      <c r="AM51" s="57"/>
-      <c r="AN51" s="57"/>
-      <c r="AO51" s="57"/>
-      <c r="AP51" s="57"/>
-      <c r="AQ51" s="57"/>
-      <c r="AR51" s="57"/>
-      <c r="AS51" s="57"/>
-      <c r="AT51" s="57"/>
-      <c r="AU51" s="57"/>
-      <c r="AV51" s="57"/>
-      <c r="AW51" s="57"/>
-      <c r="AX51" s="57"/>
-      <c r="AY51" s="57"/>
-      <c r="AZ51" s="57"/>
-      <c r="BA51" s="57"/>
-      <c r="BB51" s="57"/>
-      <c r="BC51" s="57"/>
+      <c r="AA51" s="63"/>
+      <c r="AB51" s="63"/>
+      <c r="AC51" s="63"/>
+      <c r="AD51" s="63"/>
+      <c r="AE51" s="63"/>
+      <c r="AF51" s="63"/>
+      <c r="AG51" s="63"/>
+      <c r="AH51" s="63"/>
+      <c r="AI51" s="63"/>
+      <c r="AJ51" s="63"/>
+      <c r="AK51" s="63"/>
+      <c r="AL51" s="63"/>
+      <c r="AM51" s="63"/>
+      <c r="AN51" s="63"/>
+      <c r="AO51" s="63"/>
+      <c r="AP51" s="63"/>
+      <c r="AQ51" s="63"/>
+      <c r="AR51" s="63"/>
+      <c r="AS51" s="63"/>
+      <c r="AT51" s="63"/>
+      <c r="AU51" s="63"/>
+      <c r="AV51" s="63"/>
+      <c r="AW51" s="63"/>
+      <c r="AX51" s="63"/>
+      <c r="AY51" s="63"/>
+      <c r="AZ51" s="63"/>
+      <c r="BA51" s="63"/>
+      <c r="BB51" s="63"/>
+      <c r="BC51" s="63"/>
       <c r="BD51" s="44"/>
       <c r="BE51" s="35"/>
       <c r="BF51" s="35"/>
@@ -16145,21 +16140,21 @@
       <c r="CU51" s="35"/>
     </row>
     <row r="52" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B52" s="63"/>
-      <c r="C52" s="63"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
-      <c r="F52" s="63"/>
-      <c r="G52" s="63"/>
-      <c r="H52" s="63"/>
-      <c r="I52" s="63"/>
-      <c r="J52" s="63"/>
-      <c r="K52" s="63"/>
-      <c r="L52" s="63"/>
-      <c r="M52" s="63"/>
-      <c r="N52" s="63"/>
-      <c r="O52" s="63"/>
-      <c r="P52" s="63"/>
+      <c r="B52" s="56"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="56"/>
+      <c r="G52" s="56"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="56"/>
+      <c r="K52" s="56"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="56"/>
+      <c r="N52" s="56"/>
+      <c r="O52" s="56"/>
+      <c r="P52" s="56"/>
       <c r="Q52" s="35"/>
       <c r="R52" s="35"/>
       <c r="S52" s="35"/>
@@ -16169,36 +16164,36 @@
       <c r="W52" s="35"/>
       <c r="X52" s="35"/>
       <c r="Y52" s="35"/>
-      <c r="Z52" s="57"/>
-      <c r="AA52" s="57"/>
-      <c r="AB52" s="57"/>
-      <c r="AC52" s="57"/>
-      <c r="AD52" s="57"/>
-      <c r="AE52" s="57"/>
-      <c r="AF52" s="57"/>
-      <c r="AG52" s="57"/>
-      <c r="AH52" s="57"/>
-      <c r="AI52" s="57"/>
-      <c r="AJ52" s="57"/>
-      <c r="AK52" s="57"/>
-      <c r="AL52" s="57"/>
-      <c r="AM52" s="57"/>
-      <c r="AN52" s="57"/>
-      <c r="AO52" s="57"/>
-      <c r="AP52" s="57"/>
-      <c r="AQ52" s="57"/>
-      <c r="AR52" s="57"/>
-      <c r="AS52" s="57"/>
-      <c r="AT52" s="57"/>
-      <c r="AU52" s="57"/>
-      <c r="AV52" s="57"/>
-      <c r="AW52" s="57"/>
-      <c r="AX52" s="57"/>
-      <c r="AY52" s="57"/>
-      <c r="AZ52" s="57"/>
-      <c r="BA52" s="57"/>
-      <c r="BB52" s="57"/>
-      <c r="BC52" s="57"/>
+      <c r="Z52" s="63"/>
+      <c r="AA52" s="63"/>
+      <c r="AB52" s="63"/>
+      <c r="AC52" s="63"/>
+      <c r="AD52" s="63"/>
+      <c r="AE52" s="63"/>
+      <c r="AF52" s="63"/>
+      <c r="AG52" s="63"/>
+      <c r="AH52" s="63"/>
+      <c r="AI52" s="63"/>
+      <c r="AJ52" s="63"/>
+      <c r="AK52" s="63"/>
+      <c r="AL52" s="63"/>
+      <c r="AM52" s="63"/>
+      <c r="AN52" s="63"/>
+      <c r="AO52" s="63"/>
+      <c r="AP52" s="63"/>
+      <c r="AQ52" s="63"/>
+      <c r="AR52" s="63"/>
+      <c r="AS52" s="63"/>
+      <c r="AT52" s="63"/>
+      <c r="AU52" s="63"/>
+      <c r="AV52" s="63"/>
+      <c r="AW52" s="63"/>
+      <c r="AX52" s="63"/>
+      <c r="AY52" s="63"/>
+      <c r="AZ52" s="63"/>
+      <c r="BA52" s="63"/>
+      <c r="BB52" s="63"/>
+      <c r="BC52" s="63"/>
       <c r="BD52" s="44"/>
       <c r="BE52" s="35"/>
       <c r="BF52" s="35"/>
@@ -16345,23 +16340,23 @@
       <c r="CU53" s="35"/>
     </row>
     <row r="54" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B54" s="61" t="s">
+      <c r="B54" s="67" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="61"/>
-      <c r="D54" s="61"/>
-      <c r="E54" s="61"/>
-      <c r="F54" s="61"/>
-      <c r="G54" s="61"/>
-      <c r="H54" s="61"/>
-      <c r="I54" s="61"/>
-      <c r="J54" s="61"/>
-      <c r="K54" s="61"/>
-      <c r="L54" s="61"/>
-      <c r="M54" s="61"/>
-      <c r="N54" s="61"/>
-      <c r="O54" s="61"/>
-      <c r="P54" s="61"/>
+      <c r="C54" s="67"/>
+      <c r="D54" s="67"/>
+      <c r="E54" s="67"/>
+      <c r="F54" s="67"/>
+      <c r="G54" s="67"/>
+      <c r="H54" s="67"/>
+      <c r="I54" s="67"/>
+      <c r="J54" s="67"/>
+      <c r="K54" s="67"/>
+      <c r="L54" s="67"/>
+      <c r="M54" s="67"/>
+      <c r="N54" s="67"/>
+      <c r="O54" s="67"/>
+      <c r="P54" s="67"/>
       <c r="Q54" s="35"/>
       <c r="R54" s="39"/>
       <c r="S54" s="39"/>
@@ -16371,38 +16366,38 @@
       <c r="W54" s="39"/>
       <c r="X54" s="39"/>
       <c r="Y54" s="39"/>
-      <c r="Z54" s="53" t="s">
+      <c r="Z54" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="AA54" s="53"/>
-      <c r="AB54" s="53"/>
-      <c r="AC54" s="53"/>
-      <c r="AD54" s="53"/>
-      <c r="AE54" s="53"/>
-      <c r="AF54" s="53"/>
-      <c r="AG54" s="53"/>
-      <c r="AH54" s="53"/>
-      <c r="AI54" s="53"/>
-      <c r="AJ54" s="53"/>
-      <c r="AK54" s="53"/>
-      <c r="AL54" s="53"/>
-      <c r="AM54" s="53"/>
-      <c r="AN54" s="53"/>
-      <c r="AO54" s="53"/>
-      <c r="AP54" s="53"/>
-      <c r="AQ54" s="53"/>
-      <c r="AR54" s="53"/>
-      <c r="AS54" s="53"/>
-      <c r="AT54" s="53"/>
-      <c r="AU54" s="53"/>
-      <c r="AV54" s="53"/>
-      <c r="AW54" s="53"/>
-      <c r="AX54" s="53"/>
-      <c r="AY54" s="53"/>
-      <c r="AZ54" s="53"/>
-      <c r="BA54" s="53"/>
-      <c r="BB54" s="53"/>
-      <c r="BC54" s="53"/>
+      <c r="AA54" s="60"/>
+      <c r="AB54" s="60"/>
+      <c r="AC54" s="60"/>
+      <c r="AD54" s="60"/>
+      <c r="AE54" s="60"/>
+      <c r="AF54" s="60"/>
+      <c r="AG54" s="60"/>
+      <c r="AH54" s="60"/>
+      <c r="AI54" s="60"/>
+      <c r="AJ54" s="60"/>
+      <c r="AK54" s="60"/>
+      <c r="AL54" s="60"/>
+      <c r="AM54" s="60"/>
+      <c r="AN54" s="60"/>
+      <c r="AO54" s="60"/>
+      <c r="AP54" s="60"/>
+      <c r="AQ54" s="60"/>
+      <c r="AR54" s="60"/>
+      <c r="AS54" s="60"/>
+      <c r="AT54" s="60"/>
+      <c r="AU54" s="60"/>
+      <c r="AV54" s="60"/>
+      <c r="AW54" s="60"/>
+      <c r="AX54" s="60"/>
+      <c r="AY54" s="60"/>
+      <c r="AZ54" s="60"/>
+      <c r="BA54" s="60"/>
+      <c r="BB54" s="60"/>
+      <c r="BC54" s="60"/>
       <c r="BD54" s="48"/>
       <c r="BE54" s="35"/>
       <c r="BF54" s="35"/>
@@ -16449,21 +16444,21 @@
       <c r="CU54" s="35"/>
     </row>
     <row r="55" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B55" s="61"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="61"/>
-      <c r="G55" s="61"/>
-      <c r="H55" s="61"/>
-      <c r="I55" s="61"/>
-      <c r="J55" s="61"/>
-      <c r="K55" s="61"/>
-      <c r="L55" s="61"/>
-      <c r="M55" s="61"/>
-      <c r="N55" s="61"/>
-      <c r="O55" s="61"/>
-      <c r="P55" s="61"/>
+      <c r="B55" s="67"/>
+      <c r="C55" s="67"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="67"/>
+      <c r="F55" s="67"/>
+      <c r="G55" s="67"/>
+      <c r="H55" s="67"/>
+      <c r="I55" s="67"/>
+      <c r="J55" s="67"/>
+      <c r="K55" s="67"/>
+      <c r="L55" s="67"/>
+      <c r="M55" s="67"/>
+      <c r="N55" s="67"/>
+      <c r="O55" s="67"/>
+      <c r="P55" s="67"/>
       <c r="Q55" s="35"/>
       <c r="R55" s="35"/>
       <c r="S55" s="35"/>
@@ -16473,36 +16468,36 @@
       <c r="W55" s="35"/>
       <c r="X55" s="35"/>
       <c r="Y55" s="35"/>
-      <c r="Z55" s="54"/>
-      <c r="AA55" s="54"/>
-      <c r="AB55" s="54"/>
-      <c r="AC55" s="54"/>
-      <c r="AD55" s="54"/>
-      <c r="AE55" s="54"/>
-      <c r="AF55" s="54"/>
-      <c r="AG55" s="54"/>
-      <c r="AH55" s="54"/>
-      <c r="AI55" s="54"/>
-      <c r="AJ55" s="54"/>
-      <c r="AK55" s="54"/>
-      <c r="AL55" s="54"/>
-      <c r="AM55" s="54"/>
-      <c r="AN55" s="54"/>
-      <c r="AO55" s="54"/>
-      <c r="AP55" s="54"/>
-      <c r="AQ55" s="54"/>
-      <c r="AR55" s="54"/>
-      <c r="AS55" s="54"/>
-      <c r="AT55" s="54"/>
-      <c r="AU55" s="54"/>
-      <c r="AV55" s="54"/>
-      <c r="AW55" s="54"/>
-      <c r="AX55" s="54"/>
-      <c r="AY55" s="54"/>
-      <c r="AZ55" s="54"/>
-      <c r="BA55" s="54"/>
-      <c r="BB55" s="54"/>
-      <c r="BC55" s="54"/>
+      <c r="Z55" s="61"/>
+      <c r="AA55" s="61"/>
+      <c r="AB55" s="61"/>
+      <c r="AC55" s="61"/>
+      <c r="AD55" s="61"/>
+      <c r="AE55" s="61"/>
+      <c r="AF55" s="61"/>
+      <c r="AG55" s="61"/>
+      <c r="AH55" s="61"/>
+      <c r="AI55" s="61"/>
+      <c r="AJ55" s="61"/>
+      <c r="AK55" s="61"/>
+      <c r="AL55" s="61"/>
+      <c r="AM55" s="61"/>
+      <c r="AN55" s="61"/>
+      <c r="AO55" s="61"/>
+      <c r="AP55" s="61"/>
+      <c r="AQ55" s="61"/>
+      <c r="AR55" s="61"/>
+      <c r="AS55" s="61"/>
+      <c r="AT55" s="61"/>
+      <c r="AU55" s="61"/>
+      <c r="AV55" s="61"/>
+      <c r="AW55" s="61"/>
+      <c r="AX55" s="61"/>
+      <c r="AY55" s="61"/>
+      <c r="AZ55" s="61"/>
+      <c r="BA55" s="61"/>
+      <c r="BB55" s="61"/>
+      <c r="BC55" s="61"/>
       <c r="BD55" s="48"/>
       <c r="BE55" s="35"/>
       <c r="BF55" s="35"/>
@@ -16549,21 +16544,21 @@
       <c r="CU55" s="35"/>
     </row>
     <row r="56" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="61"/>
-      <c r="F56" s="61"/>
-      <c r="G56" s="61"/>
-      <c r="H56" s="61"/>
-      <c r="I56" s="61"/>
-      <c r="J56" s="61"/>
-      <c r="K56" s="61"/>
-      <c r="L56" s="61"/>
-      <c r="M56" s="61"/>
-      <c r="N56" s="61"/>
-      <c r="O56" s="61"/>
-      <c r="P56" s="61"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="67"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="67"/>
+      <c r="H56" s="67"/>
+      <c r="I56" s="67"/>
+      <c r="J56" s="67"/>
+      <c r="K56" s="67"/>
+      <c r="L56" s="67"/>
+      <c r="M56" s="67"/>
+      <c r="N56" s="67"/>
+      <c r="O56" s="67"/>
+      <c r="P56" s="67"/>
       <c r="Q56" s="35"/>
       <c r="R56" s="35"/>
       <c r="S56" s="35"/>
@@ -16573,36 +16568,36 @@
       <c r="W56" s="35"/>
       <c r="X56" s="35"/>
       <c r="Y56" s="35"/>
-      <c r="Z56" s="54"/>
-      <c r="AA56" s="54"/>
-      <c r="AB56" s="54"/>
-      <c r="AC56" s="54"/>
-      <c r="AD56" s="54"/>
-      <c r="AE56" s="54"/>
-      <c r="AF56" s="54"/>
-      <c r="AG56" s="54"/>
-      <c r="AH56" s="54"/>
-      <c r="AI56" s="54"/>
-      <c r="AJ56" s="54"/>
-      <c r="AK56" s="54"/>
-      <c r="AL56" s="54"/>
-      <c r="AM56" s="54"/>
-      <c r="AN56" s="54"/>
-      <c r="AO56" s="54"/>
-      <c r="AP56" s="54"/>
-      <c r="AQ56" s="54"/>
-      <c r="AR56" s="54"/>
-      <c r="AS56" s="54"/>
-      <c r="AT56" s="54"/>
-      <c r="AU56" s="54"/>
-      <c r="AV56" s="54"/>
-      <c r="AW56" s="54"/>
-      <c r="AX56" s="54"/>
-      <c r="AY56" s="54"/>
-      <c r="AZ56" s="54"/>
-      <c r="BA56" s="54"/>
-      <c r="BB56" s="54"/>
-      <c r="BC56" s="54"/>
+      <c r="Z56" s="61"/>
+      <c r="AA56" s="61"/>
+      <c r="AB56" s="61"/>
+      <c r="AC56" s="61"/>
+      <c r="AD56" s="61"/>
+      <c r="AE56" s="61"/>
+      <c r="AF56" s="61"/>
+      <c r="AG56" s="61"/>
+      <c r="AH56" s="61"/>
+      <c r="AI56" s="61"/>
+      <c r="AJ56" s="61"/>
+      <c r="AK56" s="61"/>
+      <c r="AL56" s="61"/>
+      <c r="AM56" s="61"/>
+      <c r="AN56" s="61"/>
+      <c r="AO56" s="61"/>
+      <c r="AP56" s="61"/>
+      <c r="AQ56" s="61"/>
+      <c r="AR56" s="61"/>
+      <c r="AS56" s="61"/>
+      <c r="AT56" s="61"/>
+      <c r="AU56" s="61"/>
+      <c r="AV56" s="61"/>
+      <c r="AW56" s="61"/>
+      <c r="AX56" s="61"/>
+      <c r="AY56" s="61"/>
+      <c r="AZ56" s="61"/>
+      <c r="BA56" s="61"/>
+      <c r="BB56" s="61"/>
+      <c r="BC56" s="61"/>
       <c r="BD56" s="48"/>
       <c r="BE56" s="35"/>
       <c r="BF56" s="35"/>
@@ -16649,23 +16644,23 @@
       <c r="CU56" s="35"/>
     </row>
     <row r="57" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B57" s="64" t="s">
+      <c r="B57" s="68" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="64"/>
-      <c r="D57" s="64"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
-      <c r="H57" s="64"/>
-      <c r="I57" s="64"/>
-      <c r="J57" s="64"/>
-      <c r="K57" s="64"/>
-      <c r="L57" s="64"/>
-      <c r="M57" s="64"/>
-      <c r="N57" s="64"/>
-      <c r="O57" s="64"/>
-      <c r="P57" s="64"/>
+      <c r="C57" s="68"/>
+      <c r="D57" s="68"/>
+      <c r="E57" s="68"/>
+      <c r="F57" s="68"/>
+      <c r="G57" s="68"/>
+      <c r="H57" s="68"/>
+      <c r="I57" s="68"/>
+      <c r="J57" s="68"/>
+      <c r="K57" s="68"/>
+      <c r="L57" s="68"/>
+      <c r="M57" s="68"/>
+      <c r="N57" s="68"/>
+      <c r="O57" s="68"/>
+      <c r="P57" s="68"/>
       <c r="Q57" s="35"/>
       <c r="R57" s="35"/>
       <c r="S57" s="35"/>
@@ -16675,36 +16670,36 @@
       <c r="W57" s="35"/>
       <c r="X57" s="35"/>
       <c r="Y57" s="35"/>
-      <c r="Z57" s="54"/>
-      <c r="AA57" s="54"/>
-      <c r="AB57" s="54"/>
-      <c r="AC57" s="54"/>
-      <c r="AD57" s="54"/>
-      <c r="AE57" s="54"/>
-      <c r="AF57" s="54"/>
-      <c r="AG57" s="54"/>
-      <c r="AH57" s="54"/>
-      <c r="AI57" s="54"/>
-      <c r="AJ57" s="54"/>
-      <c r="AK57" s="54"/>
-      <c r="AL57" s="54"/>
-      <c r="AM57" s="54"/>
-      <c r="AN57" s="54"/>
-      <c r="AO57" s="54"/>
-      <c r="AP57" s="54"/>
-      <c r="AQ57" s="54"/>
-      <c r="AR57" s="54"/>
-      <c r="AS57" s="54"/>
-      <c r="AT57" s="54"/>
-      <c r="AU57" s="54"/>
-      <c r="AV57" s="54"/>
-      <c r="AW57" s="54"/>
-      <c r="AX57" s="54"/>
-      <c r="AY57" s="54"/>
-      <c r="AZ57" s="54"/>
-      <c r="BA57" s="54"/>
-      <c r="BB57" s="54"/>
-      <c r="BC57" s="54"/>
+      <c r="Z57" s="61"/>
+      <c r="AA57" s="61"/>
+      <c r="AB57" s="61"/>
+      <c r="AC57" s="61"/>
+      <c r="AD57" s="61"/>
+      <c r="AE57" s="61"/>
+      <c r="AF57" s="61"/>
+      <c r="AG57" s="61"/>
+      <c r="AH57" s="61"/>
+      <c r="AI57" s="61"/>
+      <c r="AJ57" s="61"/>
+      <c r="AK57" s="61"/>
+      <c r="AL57" s="61"/>
+      <c r="AM57" s="61"/>
+      <c r="AN57" s="61"/>
+      <c r="AO57" s="61"/>
+      <c r="AP57" s="61"/>
+      <c r="AQ57" s="61"/>
+      <c r="AR57" s="61"/>
+      <c r="AS57" s="61"/>
+      <c r="AT57" s="61"/>
+      <c r="AU57" s="61"/>
+      <c r="AV57" s="61"/>
+      <c r="AW57" s="61"/>
+      <c r="AX57" s="61"/>
+      <c r="AY57" s="61"/>
+      <c r="AZ57" s="61"/>
+      <c r="BA57" s="61"/>
+      <c r="BB57" s="61"/>
+      <c r="BC57" s="61"/>
       <c r="BD57" s="48"/>
       <c r="BE57" s="35"/>
       <c r="BF57" s="35"/>
@@ -16751,21 +16746,21 @@
       <c r="CU57" s="35"/>
     </row>
     <row r="58" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B58" s="64"/>
-      <c r="C58" s="64"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="64"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="64"/>
-      <c r="J58" s="64"/>
-      <c r="K58" s="64"/>
-      <c r="L58" s="64"/>
-      <c r="M58" s="64"/>
-      <c r="N58" s="64"/>
-      <c r="O58" s="64"/>
-      <c r="P58" s="64"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="68"/>
+      <c r="D58" s="68"/>
+      <c r="E58" s="68"/>
+      <c r="F58" s="68"/>
+      <c r="G58" s="68"/>
+      <c r="H58" s="68"/>
+      <c r="I58" s="68"/>
+      <c r="J58" s="68"/>
+      <c r="K58" s="68"/>
+      <c r="L58" s="68"/>
+      <c r="M58" s="68"/>
+      <c r="N58" s="68"/>
+      <c r="O58" s="68"/>
+      <c r="P58" s="68"/>
       <c r="Q58" s="35"/>
       <c r="R58" s="35"/>
       <c r="S58" s="35"/>
@@ -16775,36 +16770,36 @@
       <c r="W58" s="35"/>
       <c r="X58" s="35"/>
       <c r="Y58" s="35"/>
-      <c r="Z58" s="54"/>
-      <c r="AA58" s="54"/>
-      <c r="AB58" s="54"/>
-      <c r="AC58" s="54"/>
-      <c r="AD58" s="54"/>
-      <c r="AE58" s="54"/>
-      <c r="AF58" s="54"/>
-      <c r="AG58" s="54"/>
-      <c r="AH58" s="54"/>
-      <c r="AI58" s="54"/>
-      <c r="AJ58" s="54"/>
-      <c r="AK58" s="54"/>
-      <c r="AL58" s="54"/>
-      <c r="AM58" s="54"/>
-      <c r="AN58" s="54"/>
-      <c r="AO58" s="54"/>
-      <c r="AP58" s="54"/>
-      <c r="AQ58" s="54"/>
-      <c r="AR58" s="54"/>
-      <c r="AS58" s="54"/>
-      <c r="AT58" s="54"/>
-      <c r="AU58" s="54"/>
-      <c r="AV58" s="54"/>
-      <c r="AW58" s="54"/>
-      <c r="AX58" s="54"/>
-      <c r="AY58" s="54"/>
-      <c r="AZ58" s="54"/>
-      <c r="BA58" s="54"/>
-      <c r="BB58" s="54"/>
-      <c r="BC58" s="54"/>
+      <c r="Z58" s="61"/>
+      <c r="AA58" s="61"/>
+      <c r="AB58" s="61"/>
+      <c r="AC58" s="61"/>
+      <c r="AD58" s="61"/>
+      <c r="AE58" s="61"/>
+      <c r="AF58" s="61"/>
+      <c r="AG58" s="61"/>
+      <c r="AH58" s="61"/>
+      <c r="AI58" s="61"/>
+      <c r="AJ58" s="61"/>
+      <c r="AK58" s="61"/>
+      <c r="AL58" s="61"/>
+      <c r="AM58" s="61"/>
+      <c r="AN58" s="61"/>
+      <c r="AO58" s="61"/>
+      <c r="AP58" s="61"/>
+      <c r="AQ58" s="61"/>
+      <c r="AR58" s="61"/>
+      <c r="AS58" s="61"/>
+      <c r="AT58" s="61"/>
+      <c r="AU58" s="61"/>
+      <c r="AV58" s="61"/>
+      <c r="AW58" s="61"/>
+      <c r="AX58" s="61"/>
+      <c r="AY58" s="61"/>
+      <c r="AZ58" s="61"/>
+      <c r="BA58" s="61"/>
+      <c r="BB58" s="61"/>
+      <c r="BC58" s="61"/>
       <c r="BD58" s="48"/>
       <c r="BE58" s="35"/>
       <c r="BF58" s="35"/>
@@ -16875,38 +16870,38 @@
       <c r="W59" s="35"/>
       <c r="X59" s="35"/>
       <c r="Y59" s="35"/>
-      <c r="Z59" s="59" t="s">
+      <c r="Z59" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="AA59" s="59"/>
-      <c r="AB59" s="59"/>
-      <c r="AC59" s="59"/>
-      <c r="AD59" s="59"/>
-      <c r="AE59" s="59"/>
-      <c r="AF59" s="59"/>
-      <c r="AG59" s="59"/>
-      <c r="AH59" s="59"/>
-      <c r="AI59" s="59"/>
-      <c r="AJ59" s="59"/>
-      <c r="AK59" s="59"/>
-      <c r="AL59" s="59"/>
-      <c r="AM59" s="59"/>
-      <c r="AN59" s="59"/>
-      <c r="AO59" s="59"/>
-      <c r="AP59" s="59"/>
-      <c r="AQ59" s="59"/>
-      <c r="AR59" s="59"/>
-      <c r="AS59" s="59"/>
-      <c r="AT59" s="59"/>
-      <c r="AU59" s="59"/>
-      <c r="AV59" s="59"/>
-      <c r="AW59" s="59"/>
-      <c r="AX59" s="59"/>
-      <c r="AY59" s="59"/>
-      <c r="AZ59" s="59"/>
-      <c r="BA59" s="59"/>
-      <c r="BB59" s="59"/>
-      <c r="BC59" s="59"/>
+      <c r="AA59" s="62"/>
+      <c r="AB59" s="62"/>
+      <c r="AC59" s="62"/>
+      <c r="AD59" s="62"/>
+      <c r="AE59" s="62"/>
+      <c r="AF59" s="62"/>
+      <c r="AG59" s="62"/>
+      <c r="AH59" s="62"/>
+      <c r="AI59" s="62"/>
+      <c r="AJ59" s="62"/>
+      <c r="AK59" s="62"/>
+      <c r="AL59" s="62"/>
+      <c r="AM59" s="62"/>
+      <c r="AN59" s="62"/>
+      <c r="AO59" s="62"/>
+      <c r="AP59" s="62"/>
+      <c r="AQ59" s="62"/>
+      <c r="AR59" s="62"/>
+      <c r="AS59" s="62"/>
+      <c r="AT59" s="62"/>
+      <c r="AU59" s="62"/>
+      <c r="AV59" s="62"/>
+      <c r="AW59" s="62"/>
+      <c r="AX59" s="62"/>
+      <c r="AY59" s="62"/>
+      <c r="AZ59" s="62"/>
+      <c r="BA59" s="62"/>
+      <c r="BB59" s="62"/>
+      <c r="BC59" s="62"/>
       <c r="BD59" s="43"/>
       <c r="BE59" s="35"/>
       <c r="BF59" s="39"/>
@@ -16917,61 +16912,61 @@
       <c r="BK59" s="39"/>
       <c r="BL59" s="39"/>
       <c r="BM59" s="39"/>
-      <c r="BN59" s="60" t="s">
+      <c r="BN59" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="BO59" s="60"/>
-      <c r="BP59" s="60"/>
-      <c r="BQ59" s="60"/>
-      <c r="BR59" s="60"/>
-      <c r="BS59" s="60"/>
-      <c r="BT59" s="60"/>
-      <c r="BU59" s="60"/>
-      <c r="BV59" s="60"/>
-      <c r="BW59" s="60"/>
-      <c r="BX59" s="60"/>
-      <c r="BY59" s="60"/>
-      <c r="BZ59" s="60"/>
-      <c r="CA59" s="60"/>
-      <c r="CB59" s="60"/>
-      <c r="CC59" s="60"/>
-      <c r="CD59" s="60"/>
-      <c r="CE59" s="60"/>
-      <c r="CF59" s="60"/>
-      <c r="CG59" s="60"/>
-      <c r="CH59" s="60"/>
-      <c r="CI59" s="60"/>
-      <c r="CJ59" s="60"/>
-      <c r="CK59" s="60"/>
-      <c r="CL59" s="60"/>
-      <c r="CM59" s="60"/>
-      <c r="CN59" s="60"/>
-      <c r="CO59" s="60"/>
-      <c r="CP59" s="60"/>
-      <c r="CQ59" s="60"/>
+      <c r="BO59" s="52"/>
+      <c r="BP59" s="52"/>
+      <c r="BQ59" s="52"/>
+      <c r="BR59" s="52"/>
+      <c r="BS59" s="52"/>
+      <c r="BT59" s="52"/>
+      <c r="BU59" s="52"/>
+      <c r="BV59" s="52"/>
+      <c r="BW59" s="52"/>
+      <c r="BX59" s="52"/>
+      <c r="BY59" s="52"/>
+      <c r="BZ59" s="52"/>
+      <c r="CA59" s="52"/>
+      <c r="CB59" s="52"/>
+      <c r="CC59" s="52"/>
+      <c r="CD59" s="52"/>
+      <c r="CE59" s="52"/>
+      <c r="CF59" s="52"/>
+      <c r="CG59" s="52"/>
+      <c r="CH59" s="52"/>
+      <c r="CI59" s="52"/>
+      <c r="CJ59" s="52"/>
+      <c r="CK59" s="52"/>
+      <c r="CL59" s="52"/>
+      <c r="CM59" s="52"/>
+      <c r="CN59" s="52"/>
+      <c r="CO59" s="52"/>
+      <c r="CP59" s="52"/>
+      <c r="CQ59" s="52"/>
       <c r="CR59" s="41"/>
       <c r="CS59" s="41"/>
       <c r="CT59" s="41"/>
       <c r="CU59" s="41"/>
     </row>
     <row r="60" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B60" s="61" t="s">
+      <c r="B60" s="67" t="s">
         <v>120</v>
       </c>
-      <c r="C60" s="61"/>
-      <c r="D60" s="61"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="61"/>
-      <c r="J60" s="61"/>
-      <c r="K60" s="61"/>
-      <c r="L60" s="61"/>
-      <c r="M60" s="61"/>
-      <c r="N60" s="61"/>
-      <c r="O60" s="61"/>
-      <c r="P60" s="61"/>
+      <c r="C60" s="67"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="F60" s="67"/>
+      <c r="G60" s="67"/>
+      <c r="H60" s="67"/>
+      <c r="I60" s="67"/>
+      <c r="J60" s="67"/>
+      <c r="K60" s="67"/>
+      <c r="L60" s="67"/>
+      <c r="M60" s="67"/>
+      <c r="N60" s="67"/>
+      <c r="O60" s="67"/>
+      <c r="P60" s="67"/>
       <c r="Q60" s="35"/>
       <c r="R60" s="35"/>
       <c r="S60" s="35"/>
@@ -16981,36 +16976,36 @@
       <c r="W60" s="35"/>
       <c r="X60" s="35"/>
       <c r="Y60" s="35"/>
-      <c r="Z60" s="59"/>
-      <c r="AA60" s="59"/>
-      <c r="AB60" s="59"/>
-      <c r="AC60" s="59"/>
-      <c r="AD60" s="59"/>
-      <c r="AE60" s="59"/>
-      <c r="AF60" s="59"/>
-      <c r="AG60" s="59"/>
-      <c r="AH60" s="59"/>
-      <c r="AI60" s="59"/>
-      <c r="AJ60" s="59"/>
-      <c r="AK60" s="59"/>
-      <c r="AL60" s="59"/>
-      <c r="AM60" s="59"/>
-      <c r="AN60" s="59"/>
-      <c r="AO60" s="59"/>
-      <c r="AP60" s="59"/>
-      <c r="AQ60" s="59"/>
-      <c r="AR60" s="59"/>
-      <c r="AS60" s="59"/>
-      <c r="AT60" s="59"/>
-      <c r="AU60" s="59"/>
-      <c r="AV60" s="59"/>
-      <c r="AW60" s="59"/>
-      <c r="AX60" s="59"/>
-      <c r="AY60" s="59"/>
-      <c r="AZ60" s="59"/>
-      <c r="BA60" s="59"/>
-      <c r="BB60" s="59"/>
-      <c r="BC60" s="59"/>
+      <c r="Z60" s="62"/>
+      <c r="AA60" s="62"/>
+      <c r="AB60" s="62"/>
+      <c r="AC60" s="62"/>
+      <c r="AD60" s="62"/>
+      <c r="AE60" s="62"/>
+      <c r="AF60" s="62"/>
+      <c r="AG60" s="62"/>
+      <c r="AH60" s="62"/>
+      <c r="AI60" s="62"/>
+      <c r="AJ60" s="62"/>
+      <c r="AK60" s="62"/>
+      <c r="AL60" s="62"/>
+      <c r="AM60" s="62"/>
+      <c r="AN60" s="62"/>
+      <c r="AO60" s="62"/>
+      <c r="AP60" s="62"/>
+      <c r="AQ60" s="62"/>
+      <c r="AR60" s="62"/>
+      <c r="AS60" s="62"/>
+      <c r="AT60" s="62"/>
+      <c r="AU60" s="62"/>
+      <c r="AV60" s="62"/>
+      <c r="AW60" s="62"/>
+      <c r="AX60" s="62"/>
+      <c r="AY60" s="62"/>
+      <c r="AZ60" s="62"/>
+      <c r="BA60" s="62"/>
+      <c r="BB60" s="62"/>
+      <c r="BC60" s="62"/>
       <c r="BD60" s="43"/>
       <c r="BE60" s="35"/>
       <c r="BF60" s="35"/>
@@ -17021,57 +17016,57 @@
       <c r="BK60" s="35"/>
       <c r="BL60" s="35"/>
       <c r="BM60" s="35"/>
-      <c r="BN60" s="55"/>
-      <c r="BO60" s="55"/>
-      <c r="BP60" s="55"/>
-      <c r="BQ60" s="55"/>
-      <c r="BR60" s="55"/>
-      <c r="BS60" s="55"/>
-      <c r="BT60" s="55"/>
-      <c r="BU60" s="55"/>
-      <c r="BV60" s="55"/>
-      <c r="BW60" s="55"/>
-      <c r="BX60" s="55"/>
-      <c r="BY60" s="55"/>
-      <c r="BZ60" s="55"/>
-      <c r="CA60" s="55"/>
-      <c r="CB60" s="55"/>
-      <c r="CC60" s="55"/>
-      <c r="CD60" s="55"/>
-      <c r="CE60" s="55"/>
-      <c r="CF60" s="55"/>
-      <c r="CG60" s="55"/>
-      <c r="CH60" s="55"/>
-      <c r="CI60" s="55"/>
-      <c r="CJ60" s="55"/>
-      <c r="CK60" s="55"/>
-      <c r="CL60" s="55"/>
-      <c r="CM60" s="55"/>
-      <c r="CN60" s="55"/>
-      <c r="CO60" s="55"/>
-      <c r="CP60" s="55"/>
-      <c r="CQ60" s="55"/>
+      <c r="BN60" s="53"/>
+      <c r="BO60" s="53"/>
+      <c r="BP60" s="53"/>
+      <c r="BQ60" s="53"/>
+      <c r="BR60" s="53"/>
+      <c r="BS60" s="53"/>
+      <c r="BT60" s="53"/>
+      <c r="BU60" s="53"/>
+      <c r="BV60" s="53"/>
+      <c r="BW60" s="53"/>
+      <c r="BX60" s="53"/>
+      <c r="BY60" s="53"/>
+      <c r="BZ60" s="53"/>
+      <c r="CA60" s="53"/>
+      <c r="CB60" s="53"/>
+      <c r="CC60" s="53"/>
+      <c r="CD60" s="53"/>
+      <c r="CE60" s="53"/>
+      <c r="CF60" s="53"/>
+      <c r="CG60" s="53"/>
+      <c r="CH60" s="53"/>
+      <c r="CI60" s="53"/>
+      <c r="CJ60" s="53"/>
+      <c r="CK60" s="53"/>
+      <c r="CL60" s="53"/>
+      <c r="CM60" s="53"/>
+      <c r="CN60" s="53"/>
+      <c r="CO60" s="53"/>
+      <c r="CP60" s="53"/>
+      <c r="CQ60" s="53"/>
       <c r="CR60" s="41"/>
       <c r="CS60" s="41"/>
       <c r="CT60" s="41"/>
       <c r="CU60" s="41"/>
     </row>
     <row r="61" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B61" s="61"/>
-      <c r="C61" s="61"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61"/>
-      <c r="J61" s="61"/>
-      <c r="K61" s="61"/>
-      <c r="L61" s="61"/>
-      <c r="M61" s="61"/>
-      <c r="N61" s="61"/>
-      <c r="O61" s="61"/>
-      <c r="P61" s="61"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="67"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="67"/>
+      <c r="I61" s="67"/>
+      <c r="J61" s="67"/>
+      <c r="K61" s="67"/>
+      <c r="L61" s="67"/>
+      <c r="M61" s="67"/>
+      <c r="N61" s="67"/>
+      <c r="O61" s="67"/>
+      <c r="P61" s="67"/>
       <c r="Q61" s="35"/>
       <c r="R61" s="35"/>
       <c r="S61" s="35"/>
@@ -17081,36 +17076,36 @@
       <c r="W61" s="35"/>
       <c r="X61" s="35"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="59"/>
-      <c r="AA61" s="59"/>
-      <c r="AB61" s="59"/>
-      <c r="AC61" s="59"/>
-      <c r="AD61" s="59"/>
-      <c r="AE61" s="59"/>
-      <c r="AF61" s="59"/>
-      <c r="AG61" s="59"/>
-      <c r="AH61" s="59"/>
-      <c r="AI61" s="59"/>
-      <c r="AJ61" s="59"/>
-      <c r="AK61" s="59"/>
-      <c r="AL61" s="59"/>
-      <c r="AM61" s="59"/>
-      <c r="AN61" s="59"/>
-      <c r="AO61" s="59"/>
-      <c r="AP61" s="59"/>
-      <c r="AQ61" s="59"/>
-      <c r="AR61" s="59"/>
-      <c r="AS61" s="59"/>
-      <c r="AT61" s="59"/>
-      <c r="AU61" s="59"/>
-      <c r="AV61" s="59"/>
-      <c r="AW61" s="59"/>
-      <c r="AX61" s="59"/>
-      <c r="AY61" s="59"/>
-      <c r="AZ61" s="59"/>
-      <c r="BA61" s="59"/>
-      <c r="BB61" s="59"/>
-      <c r="BC61" s="59"/>
+      <c r="Z61" s="62"/>
+      <c r="AA61" s="62"/>
+      <c r="AB61" s="62"/>
+      <c r="AC61" s="62"/>
+      <c r="AD61" s="62"/>
+      <c r="AE61" s="62"/>
+      <c r="AF61" s="62"/>
+      <c r="AG61" s="62"/>
+      <c r="AH61" s="62"/>
+      <c r="AI61" s="62"/>
+      <c r="AJ61" s="62"/>
+      <c r="AK61" s="62"/>
+      <c r="AL61" s="62"/>
+      <c r="AM61" s="62"/>
+      <c r="AN61" s="62"/>
+      <c r="AO61" s="62"/>
+      <c r="AP61" s="62"/>
+      <c r="AQ61" s="62"/>
+      <c r="AR61" s="62"/>
+      <c r="AS61" s="62"/>
+      <c r="AT61" s="62"/>
+      <c r="AU61" s="62"/>
+      <c r="AV61" s="62"/>
+      <c r="AW61" s="62"/>
+      <c r="AX61" s="62"/>
+      <c r="AY61" s="62"/>
+      <c r="AZ61" s="62"/>
+      <c r="BA61" s="62"/>
+      <c r="BB61" s="62"/>
+      <c r="BC61" s="62"/>
       <c r="BD61" s="43"/>
       <c r="BE61" s="35"/>
       <c r="BF61" s="35"/>
@@ -17121,57 +17116,57 @@
       <c r="BK61" s="35"/>
       <c r="BL61" s="35"/>
       <c r="BM61" s="35"/>
-      <c r="BN61" s="55"/>
-      <c r="BO61" s="55"/>
-      <c r="BP61" s="55"/>
-      <c r="BQ61" s="55"/>
-      <c r="BR61" s="55"/>
-      <c r="BS61" s="55"/>
-      <c r="BT61" s="55"/>
-      <c r="BU61" s="55"/>
-      <c r="BV61" s="55"/>
-      <c r="BW61" s="55"/>
-      <c r="BX61" s="55"/>
-      <c r="BY61" s="55"/>
-      <c r="BZ61" s="55"/>
-      <c r="CA61" s="55"/>
-      <c r="CB61" s="55"/>
-      <c r="CC61" s="55"/>
-      <c r="CD61" s="55"/>
-      <c r="CE61" s="55"/>
-      <c r="CF61" s="55"/>
-      <c r="CG61" s="55"/>
-      <c r="CH61" s="55"/>
-      <c r="CI61" s="55"/>
-      <c r="CJ61" s="55"/>
-      <c r="CK61" s="55"/>
-      <c r="CL61" s="55"/>
-      <c r="CM61" s="55"/>
-      <c r="CN61" s="55"/>
-      <c r="CO61" s="55"/>
-      <c r="CP61" s="55"/>
-      <c r="CQ61" s="55"/>
+      <c r="BN61" s="53"/>
+      <c r="BO61" s="53"/>
+      <c r="BP61" s="53"/>
+      <c r="BQ61" s="53"/>
+      <c r="BR61" s="53"/>
+      <c r="BS61" s="53"/>
+      <c r="BT61" s="53"/>
+      <c r="BU61" s="53"/>
+      <c r="BV61" s="53"/>
+      <c r="BW61" s="53"/>
+      <c r="BX61" s="53"/>
+      <c r="BY61" s="53"/>
+      <c r="BZ61" s="53"/>
+      <c r="CA61" s="53"/>
+      <c r="CB61" s="53"/>
+      <c r="CC61" s="53"/>
+      <c r="CD61" s="53"/>
+      <c r="CE61" s="53"/>
+      <c r="CF61" s="53"/>
+      <c r="CG61" s="53"/>
+      <c r="CH61" s="53"/>
+      <c r="CI61" s="53"/>
+      <c r="CJ61" s="53"/>
+      <c r="CK61" s="53"/>
+      <c r="CL61" s="53"/>
+      <c r="CM61" s="53"/>
+      <c r="CN61" s="53"/>
+      <c r="CO61" s="53"/>
+      <c r="CP61" s="53"/>
+      <c r="CQ61" s="53"/>
       <c r="CR61" s="41"/>
       <c r="CS61" s="41"/>
       <c r="CT61" s="41"/>
       <c r="CU61" s="41"/>
     </row>
     <row r="62" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B62" s="61"/>
-      <c r="C62" s="61"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="61"/>
-      <c r="I62" s="61"/>
-      <c r="J62" s="61"/>
-      <c r="K62" s="61"/>
-      <c r="L62" s="61"/>
-      <c r="M62" s="61"/>
-      <c r="N62" s="61"/>
-      <c r="O62" s="61"/>
-      <c r="P62" s="61"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="67"/>
+      <c r="D62" s="67"/>
+      <c r="E62" s="67"/>
+      <c r="F62" s="67"/>
+      <c r="G62" s="67"/>
+      <c r="H62" s="67"/>
+      <c r="I62" s="67"/>
+      <c r="J62" s="67"/>
+      <c r="K62" s="67"/>
+      <c r="L62" s="67"/>
+      <c r="M62" s="67"/>
+      <c r="N62" s="67"/>
+      <c r="O62" s="67"/>
+      <c r="P62" s="67"/>
       <c r="Q62" s="35"/>
       <c r="R62" s="35"/>
       <c r="S62" s="35"/>
@@ -17181,38 +17176,38 @@
       <c r="W62" s="35"/>
       <c r="X62" s="35"/>
       <c r="Y62" s="35"/>
-      <c r="Z62" s="57" t="s">
+      <c r="Z62" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="AA62" s="57"/>
-      <c r="AB62" s="57"/>
-      <c r="AC62" s="57"/>
-      <c r="AD62" s="57"/>
-      <c r="AE62" s="57"/>
-      <c r="AF62" s="57"/>
-      <c r="AG62" s="57"/>
-      <c r="AH62" s="57"/>
-      <c r="AI62" s="57"/>
-      <c r="AJ62" s="57"/>
-      <c r="AK62" s="57"/>
-      <c r="AL62" s="57"/>
-      <c r="AM62" s="57"/>
-      <c r="AN62" s="57"/>
-      <c r="AO62" s="57"/>
-      <c r="AP62" s="57"/>
-      <c r="AQ62" s="57"/>
-      <c r="AR62" s="57"/>
-      <c r="AS62" s="57"/>
-      <c r="AT62" s="57"/>
-      <c r="AU62" s="57"/>
-      <c r="AV62" s="57"/>
-      <c r="AW62" s="57"/>
-      <c r="AX62" s="57"/>
-      <c r="AY62" s="57"/>
-      <c r="AZ62" s="57"/>
-      <c r="BA62" s="57"/>
-      <c r="BB62" s="57"/>
-      <c r="BC62" s="57"/>
+      <c r="AA62" s="63"/>
+      <c r="AB62" s="63"/>
+      <c r="AC62" s="63"/>
+      <c r="AD62" s="63"/>
+      <c r="AE62" s="63"/>
+      <c r="AF62" s="63"/>
+      <c r="AG62" s="63"/>
+      <c r="AH62" s="63"/>
+      <c r="AI62" s="63"/>
+      <c r="AJ62" s="63"/>
+      <c r="AK62" s="63"/>
+      <c r="AL62" s="63"/>
+      <c r="AM62" s="63"/>
+      <c r="AN62" s="63"/>
+      <c r="AO62" s="63"/>
+      <c r="AP62" s="63"/>
+      <c r="AQ62" s="63"/>
+      <c r="AR62" s="63"/>
+      <c r="AS62" s="63"/>
+      <c r="AT62" s="63"/>
+      <c r="AU62" s="63"/>
+      <c r="AV62" s="63"/>
+      <c r="AW62" s="63"/>
+      <c r="AX62" s="63"/>
+      <c r="AY62" s="63"/>
+      <c r="AZ62" s="63"/>
+      <c r="BA62" s="63"/>
+      <c r="BB62" s="63"/>
+      <c r="BC62" s="63"/>
       <c r="BD62" s="44"/>
       <c r="BE62" s="35"/>
       <c r="BF62" s="35"/>
@@ -17223,61 +17218,61 @@
       <c r="BK62" s="35"/>
       <c r="BL62" s="35"/>
       <c r="BM62" s="35"/>
-      <c r="BN62" s="56" t="s">
+      <c r="BN62" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="BO62" s="56"/>
-      <c r="BP62" s="56"/>
-      <c r="BQ62" s="56"/>
-      <c r="BR62" s="56"/>
-      <c r="BS62" s="56"/>
-      <c r="BT62" s="56"/>
-      <c r="BU62" s="56"/>
-      <c r="BV62" s="56"/>
-      <c r="BW62" s="56"/>
-      <c r="BX62" s="56"/>
-      <c r="BY62" s="56"/>
-      <c r="BZ62" s="56"/>
-      <c r="CA62" s="56"/>
-      <c r="CB62" s="56"/>
-      <c r="CC62" s="56"/>
-      <c r="CD62" s="56"/>
-      <c r="CE62" s="56"/>
-      <c r="CF62" s="56"/>
-      <c r="CG62" s="56"/>
-      <c r="CH62" s="56"/>
-      <c r="CI62" s="56"/>
-      <c r="CJ62" s="56"/>
-      <c r="CK62" s="56"/>
-      <c r="CL62" s="56"/>
-      <c r="CM62" s="56"/>
-      <c r="CN62" s="56"/>
-      <c r="CO62" s="56"/>
-      <c r="CP62" s="56"/>
-      <c r="CQ62" s="56"/>
+      <c r="BO62" s="54"/>
+      <c r="BP62" s="54"/>
+      <c r="BQ62" s="54"/>
+      <c r="BR62" s="54"/>
+      <c r="BS62" s="54"/>
+      <c r="BT62" s="54"/>
+      <c r="BU62" s="54"/>
+      <c r="BV62" s="54"/>
+      <c r="BW62" s="54"/>
+      <c r="BX62" s="54"/>
+      <c r="BY62" s="54"/>
+      <c r="BZ62" s="54"/>
+      <c r="CA62" s="54"/>
+      <c r="CB62" s="54"/>
+      <c r="CC62" s="54"/>
+      <c r="CD62" s="54"/>
+      <c r="CE62" s="54"/>
+      <c r="CF62" s="54"/>
+      <c r="CG62" s="54"/>
+      <c r="CH62" s="54"/>
+      <c r="CI62" s="54"/>
+      <c r="CJ62" s="54"/>
+      <c r="CK62" s="54"/>
+      <c r="CL62" s="54"/>
+      <c r="CM62" s="54"/>
+      <c r="CN62" s="54"/>
+      <c r="CO62" s="54"/>
+      <c r="CP62" s="54"/>
+      <c r="CQ62" s="54"/>
       <c r="CR62" s="42"/>
       <c r="CS62" s="42"/>
       <c r="CT62" s="42"/>
       <c r="CU62" s="42"/>
     </row>
     <row r="63" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B63" s="62" t="s">
+      <c r="B63" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="62"/>
-      <c r="D63" s="62"/>
-      <c r="E63" s="62"/>
-      <c r="F63" s="62"/>
-      <c r="G63" s="62"/>
-      <c r="H63" s="62"/>
-      <c r="I63" s="62"/>
-      <c r="J63" s="62"/>
-      <c r="K63" s="62"/>
-      <c r="L63" s="62"/>
-      <c r="M63" s="62"/>
-      <c r="N63" s="62"/>
-      <c r="O63" s="62"/>
-      <c r="P63" s="62"/>
+      <c r="C63" s="69"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="69"/>
+      <c r="F63" s="69"/>
+      <c r="G63" s="69"/>
+      <c r="H63" s="69"/>
+      <c r="I63" s="69"/>
+      <c r="J63" s="69"/>
+      <c r="K63" s="69"/>
+      <c r="L63" s="69"/>
+      <c r="M63" s="69"/>
+      <c r="N63" s="69"/>
+      <c r="O63" s="69"/>
+      <c r="P63" s="69"/>
       <c r="Q63" s="35"/>
       <c r="R63" s="35"/>
       <c r="S63" s="35"/>
@@ -17287,36 +17282,36 @@
       <c r="W63" s="35"/>
       <c r="X63" s="35"/>
       <c r="Y63" s="35"/>
-      <c r="Z63" s="57"/>
-      <c r="AA63" s="57"/>
-      <c r="AB63" s="57"/>
-      <c r="AC63" s="57"/>
-      <c r="AD63" s="57"/>
-      <c r="AE63" s="57"/>
-      <c r="AF63" s="57"/>
-      <c r="AG63" s="57"/>
-      <c r="AH63" s="57"/>
-      <c r="AI63" s="57"/>
-      <c r="AJ63" s="57"/>
-      <c r="AK63" s="57"/>
-      <c r="AL63" s="57"/>
-      <c r="AM63" s="57"/>
-      <c r="AN63" s="57"/>
-      <c r="AO63" s="57"/>
-      <c r="AP63" s="57"/>
-      <c r="AQ63" s="57"/>
-      <c r="AR63" s="57"/>
-      <c r="AS63" s="57"/>
-      <c r="AT63" s="57"/>
-      <c r="AU63" s="57"/>
-      <c r="AV63" s="57"/>
-      <c r="AW63" s="57"/>
-      <c r="AX63" s="57"/>
-      <c r="AY63" s="57"/>
-      <c r="AZ63" s="57"/>
-      <c r="BA63" s="57"/>
-      <c r="BB63" s="57"/>
-      <c r="BC63" s="57"/>
+      <c r="Z63" s="63"/>
+      <c r="AA63" s="63"/>
+      <c r="AB63" s="63"/>
+      <c r="AC63" s="63"/>
+      <c r="AD63" s="63"/>
+      <c r="AE63" s="63"/>
+      <c r="AF63" s="63"/>
+      <c r="AG63" s="63"/>
+      <c r="AH63" s="63"/>
+      <c r="AI63" s="63"/>
+      <c r="AJ63" s="63"/>
+      <c r="AK63" s="63"/>
+      <c r="AL63" s="63"/>
+      <c r="AM63" s="63"/>
+      <c r="AN63" s="63"/>
+      <c r="AO63" s="63"/>
+      <c r="AP63" s="63"/>
+      <c r="AQ63" s="63"/>
+      <c r="AR63" s="63"/>
+      <c r="AS63" s="63"/>
+      <c r="AT63" s="63"/>
+      <c r="AU63" s="63"/>
+      <c r="AV63" s="63"/>
+      <c r="AW63" s="63"/>
+      <c r="AX63" s="63"/>
+      <c r="AY63" s="63"/>
+      <c r="AZ63" s="63"/>
+      <c r="BA63" s="63"/>
+      <c r="BB63" s="63"/>
+      <c r="BC63" s="63"/>
       <c r="BD63" s="44"/>
       <c r="BE63" s="35"/>
       <c r="BF63" s="35"/>
@@ -17327,57 +17322,57 @@
       <c r="BK63" s="35"/>
       <c r="BL63" s="35"/>
       <c r="BM63" s="35"/>
-      <c r="BN63" s="56"/>
-      <c r="BO63" s="56"/>
-      <c r="BP63" s="56"/>
-      <c r="BQ63" s="56"/>
-      <c r="BR63" s="56"/>
-      <c r="BS63" s="56"/>
-      <c r="BT63" s="56"/>
-      <c r="BU63" s="56"/>
-      <c r="BV63" s="56"/>
-      <c r="BW63" s="56"/>
-      <c r="BX63" s="56"/>
-      <c r="BY63" s="56"/>
-      <c r="BZ63" s="56"/>
-      <c r="CA63" s="56"/>
-      <c r="CB63" s="56"/>
-      <c r="CC63" s="56"/>
-      <c r="CD63" s="56"/>
-      <c r="CE63" s="56"/>
-      <c r="CF63" s="56"/>
-      <c r="CG63" s="56"/>
-      <c r="CH63" s="56"/>
-      <c r="CI63" s="56"/>
-      <c r="CJ63" s="56"/>
-      <c r="CK63" s="56"/>
-      <c r="CL63" s="56"/>
-      <c r="CM63" s="56"/>
-      <c r="CN63" s="56"/>
-      <c r="CO63" s="56"/>
-      <c r="CP63" s="56"/>
-      <c r="CQ63" s="56"/>
+      <c r="BN63" s="54"/>
+      <c r="BO63" s="54"/>
+      <c r="BP63" s="54"/>
+      <c r="BQ63" s="54"/>
+      <c r="BR63" s="54"/>
+      <c r="BS63" s="54"/>
+      <c r="BT63" s="54"/>
+      <c r="BU63" s="54"/>
+      <c r="BV63" s="54"/>
+      <c r="BW63" s="54"/>
+      <c r="BX63" s="54"/>
+      <c r="BY63" s="54"/>
+      <c r="BZ63" s="54"/>
+      <c r="CA63" s="54"/>
+      <c r="CB63" s="54"/>
+      <c r="CC63" s="54"/>
+      <c r="CD63" s="54"/>
+      <c r="CE63" s="54"/>
+      <c r="CF63" s="54"/>
+      <c r="CG63" s="54"/>
+      <c r="CH63" s="54"/>
+      <c r="CI63" s="54"/>
+      <c r="CJ63" s="54"/>
+      <c r="CK63" s="54"/>
+      <c r="CL63" s="54"/>
+      <c r="CM63" s="54"/>
+      <c r="CN63" s="54"/>
+      <c r="CO63" s="54"/>
+      <c r="CP63" s="54"/>
+      <c r="CQ63" s="54"/>
       <c r="CR63" s="42"/>
       <c r="CS63" s="42"/>
       <c r="CT63" s="42"/>
       <c r="CU63" s="42"/>
     </row>
     <row r="64" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B64" s="62"/>
-      <c r="C64" s="62"/>
-      <c r="D64" s="62"/>
-      <c r="E64" s="62"/>
-      <c r="F64" s="62"/>
-      <c r="G64" s="62"/>
-      <c r="H64" s="62"/>
-      <c r="I64" s="62"/>
-      <c r="J64" s="62"/>
-      <c r="K64" s="62"/>
-      <c r="L64" s="62"/>
-      <c r="M64" s="62"/>
-      <c r="N64" s="62"/>
-      <c r="O64" s="62"/>
-      <c r="P64" s="62"/>
+      <c r="B64" s="69"/>
+      <c r="C64" s="69"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="69"/>
+      <c r="F64" s="69"/>
+      <c r="G64" s="69"/>
+      <c r="H64" s="69"/>
+      <c r="I64" s="69"/>
+      <c r="J64" s="69"/>
+      <c r="K64" s="69"/>
+      <c r="L64" s="69"/>
+      <c r="M64" s="69"/>
+      <c r="N64" s="69"/>
+      <c r="O64" s="69"/>
+      <c r="P64" s="69"/>
       <c r="Q64" s="35"/>
       <c r="R64" s="35"/>
       <c r="S64" s="35"/>
@@ -17471,38 +17466,38 @@
       <c r="W65" s="39"/>
       <c r="X65" s="39"/>
       <c r="Y65" s="39"/>
-      <c r="Z65" s="53" t="s">
+      <c r="Z65" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="AA65" s="53"/>
-      <c r="AB65" s="53"/>
-      <c r="AC65" s="53"/>
-      <c r="AD65" s="53"/>
-      <c r="AE65" s="53"/>
-      <c r="AF65" s="53"/>
-      <c r="AG65" s="53"/>
-      <c r="AH65" s="53"/>
-      <c r="AI65" s="53"/>
-      <c r="AJ65" s="53"/>
-      <c r="AK65" s="53"/>
-      <c r="AL65" s="53"/>
-      <c r="AM65" s="53"/>
-      <c r="AN65" s="53"/>
-      <c r="AO65" s="53"/>
-      <c r="AP65" s="53"/>
-      <c r="AQ65" s="53"/>
-      <c r="AR65" s="53"/>
-      <c r="AS65" s="53"/>
-      <c r="AT65" s="53"/>
-      <c r="AU65" s="53"/>
-      <c r="AV65" s="53"/>
-      <c r="AW65" s="53"/>
-      <c r="AX65" s="53"/>
-      <c r="AY65" s="53"/>
-      <c r="AZ65" s="53"/>
-      <c r="BA65" s="53"/>
-      <c r="BB65" s="53"/>
-      <c r="BC65" s="53"/>
+      <c r="AA65" s="60"/>
+      <c r="AB65" s="60"/>
+      <c r="AC65" s="60"/>
+      <c r="AD65" s="60"/>
+      <c r="AE65" s="60"/>
+      <c r="AF65" s="60"/>
+      <c r="AG65" s="60"/>
+      <c r="AH65" s="60"/>
+      <c r="AI65" s="60"/>
+      <c r="AJ65" s="60"/>
+      <c r="AK65" s="60"/>
+      <c r="AL65" s="60"/>
+      <c r="AM65" s="60"/>
+      <c r="AN65" s="60"/>
+      <c r="AO65" s="60"/>
+      <c r="AP65" s="60"/>
+      <c r="AQ65" s="60"/>
+      <c r="AR65" s="60"/>
+      <c r="AS65" s="60"/>
+      <c r="AT65" s="60"/>
+      <c r="AU65" s="60"/>
+      <c r="AV65" s="60"/>
+      <c r="AW65" s="60"/>
+      <c r="AX65" s="60"/>
+      <c r="AY65" s="60"/>
+      <c r="AZ65" s="60"/>
+      <c r="BA65" s="60"/>
+      <c r="BB65" s="60"/>
+      <c r="BC65" s="60"/>
       <c r="BD65" s="48"/>
       <c r="BE65" s="35"/>
       <c r="BF65" s="35"/>
@@ -17513,38 +17508,38 @@
       <c r="BK65" s="35"/>
       <c r="BL65" s="35"/>
       <c r="BM65" s="35"/>
-      <c r="BN65" s="55" t="s">
+      <c r="BN65" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="BO65" s="55"/>
-      <c r="BP65" s="55"/>
-      <c r="BQ65" s="55"/>
-      <c r="BR65" s="55"/>
-      <c r="BS65" s="55"/>
-      <c r="BT65" s="55"/>
-      <c r="BU65" s="55"/>
-      <c r="BV65" s="55"/>
-      <c r="BW65" s="55"/>
-      <c r="BX65" s="55"/>
-      <c r="BY65" s="55"/>
-      <c r="BZ65" s="55"/>
-      <c r="CA65" s="55"/>
-      <c r="CB65" s="55"/>
-      <c r="CC65" s="55"/>
-      <c r="CD65" s="55"/>
-      <c r="CE65" s="55"/>
-      <c r="CF65" s="55"/>
-      <c r="CG65" s="55"/>
-      <c r="CH65" s="55"/>
-      <c r="CI65" s="55"/>
-      <c r="CJ65" s="55"/>
-      <c r="CK65" s="55"/>
-      <c r="CL65" s="55"/>
-      <c r="CM65" s="55"/>
-      <c r="CN65" s="55"/>
-      <c r="CO65" s="55"/>
-      <c r="CP65" s="55"/>
-      <c r="CQ65" s="55"/>
+      <c r="BO65" s="53"/>
+      <c r="BP65" s="53"/>
+      <c r="BQ65" s="53"/>
+      <c r="BR65" s="53"/>
+      <c r="BS65" s="53"/>
+      <c r="BT65" s="53"/>
+      <c r="BU65" s="53"/>
+      <c r="BV65" s="53"/>
+      <c r="BW65" s="53"/>
+      <c r="BX65" s="53"/>
+      <c r="BY65" s="53"/>
+      <c r="BZ65" s="53"/>
+      <c r="CA65" s="53"/>
+      <c r="CB65" s="53"/>
+      <c r="CC65" s="53"/>
+      <c r="CD65" s="53"/>
+      <c r="CE65" s="53"/>
+      <c r="CF65" s="53"/>
+      <c r="CG65" s="53"/>
+      <c r="CH65" s="53"/>
+      <c r="CI65" s="53"/>
+      <c r="CJ65" s="53"/>
+      <c r="CK65" s="53"/>
+      <c r="CL65" s="53"/>
+      <c r="CM65" s="53"/>
+      <c r="CN65" s="53"/>
+      <c r="CO65" s="53"/>
+      <c r="CP65" s="53"/>
+      <c r="CQ65" s="53"/>
       <c r="CR65" s="41"/>
       <c r="CS65" s="41"/>
       <c r="CT65" s="41"/>
@@ -17559,36 +17554,36 @@
       <c r="W66" s="35"/>
       <c r="X66" s="35"/>
       <c r="Y66" s="35"/>
-      <c r="Z66" s="54"/>
-      <c r="AA66" s="54"/>
-      <c r="AB66" s="54"/>
-      <c r="AC66" s="54"/>
-      <c r="AD66" s="54"/>
-      <c r="AE66" s="54"/>
-      <c r="AF66" s="54"/>
-      <c r="AG66" s="54"/>
-      <c r="AH66" s="54"/>
-      <c r="AI66" s="54"/>
-      <c r="AJ66" s="54"/>
-      <c r="AK66" s="54"/>
-      <c r="AL66" s="54"/>
-      <c r="AM66" s="54"/>
-      <c r="AN66" s="54"/>
-      <c r="AO66" s="54"/>
-      <c r="AP66" s="54"/>
-      <c r="AQ66" s="54"/>
-      <c r="AR66" s="54"/>
-      <c r="AS66" s="54"/>
-      <c r="AT66" s="54"/>
-      <c r="AU66" s="54"/>
-      <c r="AV66" s="54"/>
-      <c r="AW66" s="54"/>
-      <c r="AX66" s="54"/>
-      <c r="AY66" s="54"/>
-      <c r="AZ66" s="54"/>
-      <c r="BA66" s="54"/>
-      <c r="BB66" s="54"/>
-      <c r="BC66" s="54"/>
+      <c r="Z66" s="61"/>
+      <c r="AA66" s="61"/>
+      <c r="AB66" s="61"/>
+      <c r="AC66" s="61"/>
+      <c r="AD66" s="61"/>
+      <c r="AE66" s="61"/>
+      <c r="AF66" s="61"/>
+      <c r="AG66" s="61"/>
+      <c r="AH66" s="61"/>
+      <c r="AI66" s="61"/>
+      <c r="AJ66" s="61"/>
+      <c r="AK66" s="61"/>
+      <c r="AL66" s="61"/>
+      <c r="AM66" s="61"/>
+      <c r="AN66" s="61"/>
+      <c r="AO66" s="61"/>
+      <c r="AP66" s="61"/>
+      <c r="AQ66" s="61"/>
+      <c r="AR66" s="61"/>
+      <c r="AS66" s="61"/>
+      <c r="AT66" s="61"/>
+      <c r="AU66" s="61"/>
+      <c r="AV66" s="61"/>
+      <c r="AW66" s="61"/>
+      <c r="AX66" s="61"/>
+      <c r="AY66" s="61"/>
+      <c r="AZ66" s="61"/>
+      <c r="BA66" s="61"/>
+      <c r="BB66" s="61"/>
+      <c r="BC66" s="61"/>
       <c r="BD66" s="48"/>
       <c r="BE66" s="35"/>
       <c r="BF66" s="35"/>
@@ -17599,36 +17594,36 @@
       <c r="BK66" s="35"/>
       <c r="BL66" s="35"/>
       <c r="BM66" s="35"/>
-      <c r="BN66" s="55"/>
-      <c r="BO66" s="55"/>
-      <c r="BP66" s="55"/>
-      <c r="BQ66" s="55"/>
-      <c r="BR66" s="55"/>
-      <c r="BS66" s="55"/>
-      <c r="BT66" s="55"/>
-      <c r="BU66" s="55"/>
-      <c r="BV66" s="55"/>
-      <c r="BW66" s="55"/>
-      <c r="BX66" s="55"/>
-      <c r="BY66" s="55"/>
-      <c r="BZ66" s="55"/>
-      <c r="CA66" s="55"/>
-      <c r="CB66" s="55"/>
-      <c r="CC66" s="55"/>
-      <c r="CD66" s="55"/>
-      <c r="CE66" s="55"/>
-      <c r="CF66" s="55"/>
-      <c r="CG66" s="55"/>
-      <c r="CH66" s="55"/>
-      <c r="CI66" s="55"/>
-      <c r="CJ66" s="55"/>
-      <c r="CK66" s="55"/>
-      <c r="CL66" s="55"/>
-      <c r="CM66" s="55"/>
-      <c r="CN66" s="55"/>
-      <c r="CO66" s="55"/>
-      <c r="CP66" s="55"/>
-      <c r="CQ66" s="55"/>
+      <c r="BN66" s="53"/>
+      <c r="BO66" s="53"/>
+      <c r="BP66" s="53"/>
+      <c r="BQ66" s="53"/>
+      <c r="BR66" s="53"/>
+      <c r="BS66" s="53"/>
+      <c r="BT66" s="53"/>
+      <c r="BU66" s="53"/>
+      <c r="BV66" s="53"/>
+      <c r="BW66" s="53"/>
+      <c r="BX66" s="53"/>
+      <c r="BY66" s="53"/>
+      <c r="BZ66" s="53"/>
+      <c r="CA66" s="53"/>
+      <c r="CB66" s="53"/>
+      <c r="CC66" s="53"/>
+      <c r="CD66" s="53"/>
+      <c r="CE66" s="53"/>
+      <c r="CF66" s="53"/>
+      <c r="CG66" s="53"/>
+      <c r="CH66" s="53"/>
+      <c r="CI66" s="53"/>
+      <c r="CJ66" s="53"/>
+      <c r="CK66" s="53"/>
+      <c r="CL66" s="53"/>
+      <c r="CM66" s="53"/>
+      <c r="CN66" s="53"/>
+      <c r="CO66" s="53"/>
+      <c r="CP66" s="53"/>
+      <c r="CQ66" s="53"/>
       <c r="CR66" s="41"/>
       <c r="CS66" s="41"/>
       <c r="CT66" s="41"/>
@@ -17643,36 +17638,36 @@
       <c r="W67" s="35"/>
       <c r="X67" s="35"/>
       <c r="Y67" s="35"/>
-      <c r="Z67" s="54"/>
-      <c r="AA67" s="54"/>
-      <c r="AB67" s="54"/>
-      <c r="AC67" s="54"/>
-      <c r="AD67" s="54"/>
-      <c r="AE67" s="54"/>
-      <c r="AF67" s="54"/>
-      <c r="AG67" s="54"/>
-      <c r="AH67" s="54"/>
-      <c r="AI67" s="54"/>
-      <c r="AJ67" s="54"/>
-      <c r="AK67" s="54"/>
-      <c r="AL67" s="54"/>
-      <c r="AM67" s="54"/>
-      <c r="AN67" s="54"/>
-      <c r="AO67" s="54"/>
-      <c r="AP67" s="54"/>
-      <c r="AQ67" s="54"/>
-      <c r="AR67" s="54"/>
-      <c r="AS67" s="54"/>
-      <c r="AT67" s="54"/>
-      <c r="AU67" s="54"/>
-      <c r="AV67" s="54"/>
-      <c r="AW67" s="54"/>
-      <c r="AX67" s="54"/>
-      <c r="AY67" s="54"/>
-      <c r="AZ67" s="54"/>
-      <c r="BA67" s="54"/>
-      <c r="BB67" s="54"/>
-      <c r="BC67" s="54"/>
+      <c r="Z67" s="61"/>
+      <c r="AA67" s="61"/>
+      <c r="AB67" s="61"/>
+      <c r="AC67" s="61"/>
+      <c r="AD67" s="61"/>
+      <c r="AE67" s="61"/>
+      <c r="AF67" s="61"/>
+      <c r="AG67" s="61"/>
+      <c r="AH67" s="61"/>
+      <c r="AI67" s="61"/>
+      <c r="AJ67" s="61"/>
+      <c r="AK67" s="61"/>
+      <c r="AL67" s="61"/>
+      <c r="AM67" s="61"/>
+      <c r="AN67" s="61"/>
+      <c r="AO67" s="61"/>
+      <c r="AP67" s="61"/>
+      <c r="AQ67" s="61"/>
+      <c r="AR67" s="61"/>
+      <c r="AS67" s="61"/>
+      <c r="AT67" s="61"/>
+      <c r="AU67" s="61"/>
+      <c r="AV67" s="61"/>
+      <c r="AW67" s="61"/>
+      <c r="AX67" s="61"/>
+      <c r="AY67" s="61"/>
+      <c r="AZ67" s="61"/>
+      <c r="BA67" s="61"/>
+      <c r="BB67" s="61"/>
+      <c r="BC67" s="61"/>
       <c r="BD67" s="48"/>
       <c r="BE67" s="35"/>
       <c r="BF67" s="35"/>
@@ -17683,36 +17678,36 @@
       <c r="BK67" s="35"/>
       <c r="BL67" s="35"/>
       <c r="BM67" s="35"/>
-      <c r="BN67" s="55"/>
-      <c r="BO67" s="55"/>
-      <c r="BP67" s="55"/>
-      <c r="BQ67" s="55"/>
-      <c r="BR67" s="55"/>
-      <c r="BS67" s="55"/>
-      <c r="BT67" s="55"/>
-      <c r="BU67" s="55"/>
-      <c r="BV67" s="55"/>
-      <c r="BW67" s="55"/>
-      <c r="BX67" s="55"/>
-      <c r="BY67" s="55"/>
-      <c r="BZ67" s="55"/>
-      <c r="CA67" s="55"/>
-      <c r="CB67" s="55"/>
-      <c r="CC67" s="55"/>
-      <c r="CD67" s="55"/>
-      <c r="CE67" s="55"/>
-      <c r="CF67" s="55"/>
-      <c r="CG67" s="55"/>
-      <c r="CH67" s="55"/>
-      <c r="CI67" s="55"/>
-      <c r="CJ67" s="55"/>
-      <c r="CK67" s="55"/>
-      <c r="CL67" s="55"/>
-      <c r="CM67" s="55"/>
-      <c r="CN67" s="55"/>
-      <c r="CO67" s="55"/>
-      <c r="CP67" s="55"/>
-      <c r="CQ67" s="55"/>
+      <c r="BN67" s="53"/>
+      <c r="BO67" s="53"/>
+      <c r="BP67" s="53"/>
+      <c r="BQ67" s="53"/>
+      <c r="BR67" s="53"/>
+      <c r="BS67" s="53"/>
+      <c r="BT67" s="53"/>
+      <c r="BU67" s="53"/>
+      <c r="BV67" s="53"/>
+      <c r="BW67" s="53"/>
+      <c r="BX67" s="53"/>
+      <c r="BY67" s="53"/>
+      <c r="BZ67" s="53"/>
+      <c r="CA67" s="53"/>
+      <c r="CB67" s="53"/>
+      <c r="CC67" s="53"/>
+      <c r="CD67" s="53"/>
+      <c r="CE67" s="53"/>
+      <c r="CF67" s="53"/>
+      <c r="CG67" s="53"/>
+      <c r="CH67" s="53"/>
+      <c r="CI67" s="53"/>
+      <c r="CJ67" s="53"/>
+      <c r="CK67" s="53"/>
+      <c r="CL67" s="53"/>
+      <c r="CM67" s="53"/>
+      <c r="CN67" s="53"/>
+      <c r="CO67" s="53"/>
+      <c r="CP67" s="53"/>
+      <c r="CQ67" s="53"/>
       <c r="CR67" s="41"/>
       <c r="CS67" s="41"/>
       <c r="CT67" s="41"/>
@@ -17727,36 +17722,36 @@
       <c r="W68" s="35"/>
       <c r="X68" s="35"/>
       <c r="Y68" s="35"/>
-      <c r="Z68" s="54"/>
-      <c r="AA68" s="54"/>
-      <c r="AB68" s="54"/>
-      <c r="AC68" s="54"/>
-      <c r="AD68" s="54"/>
-      <c r="AE68" s="54"/>
-      <c r="AF68" s="54"/>
-      <c r="AG68" s="54"/>
-      <c r="AH68" s="54"/>
-      <c r="AI68" s="54"/>
-      <c r="AJ68" s="54"/>
-      <c r="AK68" s="54"/>
-      <c r="AL68" s="54"/>
-      <c r="AM68" s="54"/>
-      <c r="AN68" s="54"/>
-      <c r="AO68" s="54"/>
-      <c r="AP68" s="54"/>
-      <c r="AQ68" s="54"/>
-      <c r="AR68" s="54"/>
-      <c r="AS68" s="54"/>
-      <c r="AT68" s="54"/>
-      <c r="AU68" s="54"/>
-      <c r="AV68" s="54"/>
-      <c r="AW68" s="54"/>
-      <c r="AX68" s="54"/>
-      <c r="AY68" s="54"/>
-      <c r="AZ68" s="54"/>
-      <c r="BA68" s="54"/>
-      <c r="BB68" s="54"/>
-      <c r="BC68" s="54"/>
+      <c r="Z68" s="61"/>
+      <c r="AA68" s="61"/>
+      <c r="AB68" s="61"/>
+      <c r="AC68" s="61"/>
+      <c r="AD68" s="61"/>
+      <c r="AE68" s="61"/>
+      <c r="AF68" s="61"/>
+      <c r="AG68" s="61"/>
+      <c r="AH68" s="61"/>
+      <c r="AI68" s="61"/>
+      <c r="AJ68" s="61"/>
+      <c r="AK68" s="61"/>
+      <c r="AL68" s="61"/>
+      <c r="AM68" s="61"/>
+      <c r="AN68" s="61"/>
+      <c r="AO68" s="61"/>
+      <c r="AP68" s="61"/>
+      <c r="AQ68" s="61"/>
+      <c r="AR68" s="61"/>
+      <c r="AS68" s="61"/>
+      <c r="AT68" s="61"/>
+      <c r="AU68" s="61"/>
+      <c r="AV68" s="61"/>
+      <c r="AW68" s="61"/>
+      <c r="AX68" s="61"/>
+      <c r="AY68" s="61"/>
+      <c r="AZ68" s="61"/>
+      <c r="BA68" s="61"/>
+      <c r="BB68" s="61"/>
+      <c r="BC68" s="61"/>
       <c r="BD68" s="48"/>
       <c r="BE68" s="35"/>
       <c r="BF68" s="35"/>
@@ -17767,38 +17762,38 @@
       <c r="BK68" s="35"/>
       <c r="BL68" s="35"/>
       <c r="BM68" s="35"/>
-      <c r="BN68" s="56" t="s">
+      <c r="BN68" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="BO68" s="56"/>
-      <c r="BP68" s="56"/>
-      <c r="BQ68" s="56"/>
-      <c r="BR68" s="56"/>
-      <c r="BS68" s="56"/>
-      <c r="BT68" s="56"/>
-      <c r="BU68" s="56"/>
-      <c r="BV68" s="56"/>
-      <c r="BW68" s="56"/>
-      <c r="BX68" s="56"/>
-      <c r="BY68" s="56"/>
-      <c r="BZ68" s="56"/>
-      <c r="CA68" s="56"/>
-      <c r="CB68" s="56"/>
-      <c r="CC68" s="56"/>
-      <c r="CD68" s="56"/>
-      <c r="CE68" s="56"/>
-      <c r="CF68" s="56"/>
-      <c r="CG68" s="56"/>
-      <c r="CH68" s="56"/>
-      <c r="CI68" s="56"/>
-      <c r="CJ68" s="56"/>
-      <c r="CK68" s="56"/>
-      <c r="CL68" s="56"/>
-      <c r="CM68" s="56"/>
-      <c r="CN68" s="56"/>
-      <c r="CO68" s="56"/>
-      <c r="CP68" s="56"/>
-      <c r="CQ68" s="56"/>
+      <c r="BO68" s="54"/>
+      <c r="BP68" s="54"/>
+      <c r="BQ68" s="54"/>
+      <c r="BR68" s="54"/>
+      <c r="BS68" s="54"/>
+      <c r="BT68" s="54"/>
+      <c r="BU68" s="54"/>
+      <c r="BV68" s="54"/>
+      <c r="BW68" s="54"/>
+      <c r="BX68" s="54"/>
+      <c r="BY68" s="54"/>
+      <c r="BZ68" s="54"/>
+      <c r="CA68" s="54"/>
+      <c r="CB68" s="54"/>
+      <c r="CC68" s="54"/>
+      <c r="CD68" s="54"/>
+      <c r="CE68" s="54"/>
+      <c r="CF68" s="54"/>
+      <c r="CG68" s="54"/>
+      <c r="CH68" s="54"/>
+      <c r="CI68" s="54"/>
+      <c r="CJ68" s="54"/>
+      <c r="CK68" s="54"/>
+      <c r="CL68" s="54"/>
+      <c r="CM68" s="54"/>
+      <c r="CN68" s="54"/>
+      <c r="CO68" s="54"/>
+      <c r="CP68" s="54"/>
+      <c r="CQ68" s="54"/>
       <c r="CR68" s="42"/>
       <c r="CS68" s="42"/>
       <c r="CT68" s="42"/>
@@ -17813,36 +17808,36 @@
       <c r="W69" s="35"/>
       <c r="X69" s="35"/>
       <c r="Y69" s="35"/>
-      <c r="Z69" s="54"/>
-      <c r="AA69" s="54"/>
-      <c r="AB69" s="54"/>
-      <c r="AC69" s="54"/>
-      <c r="AD69" s="54"/>
-      <c r="AE69" s="54"/>
-      <c r="AF69" s="54"/>
-      <c r="AG69" s="54"/>
-      <c r="AH69" s="54"/>
-      <c r="AI69" s="54"/>
-      <c r="AJ69" s="54"/>
-      <c r="AK69" s="54"/>
-      <c r="AL69" s="54"/>
-      <c r="AM69" s="54"/>
-      <c r="AN69" s="54"/>
-      <c r="AO69" s="54"/>
-      <c r="AP69" s="54"/>
-      <c r="AQ69" s="54"/>
-      <c r="AR69" s="54"/>
-      <c r="AS69" s="54"/>
-      <c r="AT69" s="54"/>
-      <c r="AU69" s="54"/>
-      <c r="AV69" s="54"/>
-      <c r="AW69" s="54"/>
-      <c r="AX69" s="54"/>
-      <c r="AY69" s="54"/>
-      <c r="AZ69" s="54"/>
-      <c r="BA69" s="54"/>
-      <c r="BB69" s="54"/>
-      <c r="BC69" s="54"/>
+      <c r="Z69" s="61"/>
+      <c r="AA69" s="61"/>
+      <c r="AB69" s="61"/>
+      <c r="AC69" s="61"/>
+      <c r="AD69" s="61"/>
+      <c r="AE69" s="61"/>
+      <c r="AF69" s="61"/>
+      <c r="AG69" s="61"/>
+      <c r="AH69" s="61"/>
+      <c r="AI69" s="61"/>
+      <c r="AJ69" s="61"/>
+      <c r="AK69" s="61"/>
+      <c r="AL69" s="61"/>
+      <c r="AM69" s="61"/>
+      <c r="AN69" s="61"/>
+      <c r="AO69" s="61"/>
+      <c r="AP69" s="61"/>
+      <c r="AQ69" s="61"/>
+      <c r="AR69" s="61"/>
+      <c r="AS69" s="61"/>
+      <c r="AT69" s="61"/>
+      <c r="AU69" s="61"/>
+      <c r="AV69" s="61"/>
+      <c r="AW69" s="61"/>
+      <c r="AX69" s="61"/>
+      <c r="AY69" s="61"/>
+      <c r="AZ69" s="61"/>
+      <c r="BA69" s="61"/>
+      <c r="BB69" s="61"/>
+      <c r="BC69" s="61"/>
       <c r="BD69" s="48"/>
       <c r="BE69" s="35"/>
       <c r="BF69" s="35"/>
@@ -17853,36 +17848,36 @@
       <c r="BK69" s="35"/>
       <c r="BL69" s="35"/>
       <c r="BM69" s="35"/>
-      <c r="BN69" s="56"/>
-      <c r="BO69" s="56"/>
-      <c r="BP69" s="56"/>
-      <c r="BQ69" s="56"/>
-      <c r="BR69" s="56"/>
-      <c r="BS69" s="56"/>
-      <c r="BT69" s="56"/>
-      <c r="BU69" s="56"/>
-      <c r="BV69" s="56"/>
-      <c r="BW69" s="56"/>
-      <c r="BX69" s="56"/>
-      <c r="BY69" s="56"/>
-      <c r="BZ69" s="56"/>
-      <c r="CA69" s="56"/>
-      <c r="CB69" s="56"/>
-      <c r="CC69" s="56"/>
-      <c r="CD69" s="56"/>
-      <c r="CE69" s="56"/>
-      <c r="CF69" s="56"/>
-      <c r="CG69" s="56"/>
-      <c r="CH69" s="56"/>
-      <c r="CI69" s="56"/>
-      <c r="CJ69" s="56"/>
-      <c r="CK69" s="56"/>
-      <c r="CL69" s="56"/>
-      <c r="CM69" s="56"/>
-      <c r="CN69" s="56"/>
-      <c r="CO69" s="56"/>
-      <c r="CP69" s="56"/>
-      <c r="CQ69" s="56"/>
+      <c r="BN69" s="54"/>
+      <c r="BO69" s="54"/>
+      <c r="BP69" s="54"/>
+      <c r="BQ69" s="54"/>
+      <c r="BR69" s="54"/>
+      <c r="BS69" s="54"/>
+      <c r="BT69" s="54"/>
+      <c r="BU69" s="54"/>
+      <c r="BV69" s="54"/>
+      <c r="BW69" s="54"/>
+      <c r="BX69" s="54"/>
+      <c r="BY69" s="54"/>
+      <c r="BZ69" s="54"/>
+      <c r="CA69" s="54"/>
+      <c r="CB69" s="54"/>
+      <c r="CC69" s="54"/>
+      <c r="CD69" s="54"/>
+      <c r="CE69" s="54"/>
+      <c r="CF69" s="54"/>
+      <c r="CG69" s="54"/>
+      <c r="CH69" s="54"/>
+      <c r="CI69" s="54"/>
+      <c r="CJ69" s="54"/>
+      <c r="CK69" s="54"/>
+      <c r="CL69" s="54"/>
+      <c r="CM69" s="54"/>
+      <c r="CN69" s="54"/>
+      <c r="CO69" s="54"/>
+      <c r="CP69" s="54"/>
+      <c r="CQ69" s="54"/>
       <c r="CR69" s="42"/>
       <c r="CS69" s="42"/>
       <c r="CT69" s="42"/>
@@ -17981,38 +17976,38 @@
       <c r="W71" s="35"/>
       <c r="X71" s="35"/>
       <c r="Y71" s="35"/>
-      <c r="Z71" s="57" t="s">
+      <c r="Z71" s="63" t="s">
         <v>126</v>
       </c>
-      <c r="AA71" s="57"/>
-      <c r="AB71" s="57"/>
-      <c r="AC71" s="57"/>
-      <c r="AD71" s="57"/>
-      <c r="AE71" s="57"/>
-      <c r="AF71" s="57"/>
-      <c r="AG71" s="57"/>
-      <c r="AH71" s="57"/>
-      <c r="AI71" s="57"/>
-      <c r="AJ71" s="57"/>
-      <c r="AK71" s="57"/>
-      <c r="AL71" s="57"/>
-      <c r="AM71" s="57"/>
-      <c r="AN71" s="57"/>
-      <c r="AO71" s="57"/>
-      <c r="AP71" s="57"/>
-      <c r="AQ71" s="57"/>
-      <c r="AR71" s="57"/>
-      <c r="AS71" s="57"/>
-      <c r="AT71" s="57"/>
-      <c r="AU71" s="57"/>
-      <c r="AV71" s="57"/>
-      <c r="AW71" s="57"/>
-      <c r="AX71" s="57"/>
-      <c r="AY71" s="57"/>
-      <c r="AZ71" s="57"/>
-      <c r="BA71" s="57"/>
-      <c r="BB71" s="57"/>
-      <c r="BC71" s="57"/>
+      <c r="AA71" s="63"/>
+      <c r="AB71" s="63"/>
+      <c r="AC71" s="63"/>
+      <c r="AD71" s="63"/>
+      <c r="AE71" s="63"/>
+      <c r="AF71" s="63"/>
+      <c r="AG71" s="63"/>
+      <c r="AH71" s="63"/>
+      <c r="AI71" s="63"/>
+      <c r="AJ71" s="63"/>
+      <c r="AK71" s="63"/>
+      <c r="AL71" s="63"/>
+      <c r="AM71" s="63"/>
+      <c r="AN71" s="63"/>
+      <c r="AO71" s="63"/>
+      <c r="AP71" s="63"/>
+      <c r="AQ71" s="63"/>
+      <c r="AR71" s="63"/>
+      <c r="AS71" s="63"/>
+      <c r="AT71" s="63"/>
+      <c r="AU71" s="63"/>
+      <c r="AV71" s="63"/>
+      <c r="AW71" s="63"/>
+      <c r="AX71" s="63"/>
+      <c r="AY71" s="63"/>
+      <c r="AZ71" s="63"/>
+      <c r="BA71" s="63"/>
+      <c r="BB71" s="63"/>
+      <c r="BC71" s="63"/>
       <c r="BD71" s="47"/>
       <c r="BE71" s="35"/>
       <c r="BF71" s="35"/>
@@ -18067,36 +18062,36 @@
       <c r="W72" s="35"/>
       <c r="X72" s="35"/>
       <c r="Y72" s="35"/>
-      <c r="Z72" s="57"/>
-      <c r="AA72" s="57"/>
-      <c r="AB72" s="57"/>
-      <c r="AC72" s="57"/>
-      <c r="AD72" s="57"/>
-      <c r="AE72" s="57"/>
-      <c r="AF72" s="57"/>
-      <c r="AG72" s="57"/>
-      <c r="AH72" s="57"/>
-      <c r="AI72" s="57"/>
-      <c r="AJ72" s="57"/>
-      <c r="AK72" s="57"/>
-      <c r="AL72" s="57"/>
-      <c r="AM72" s="57"/>
-      <c r="AN72" s="57"/>
-      <c r="AO72" s="57"/>
-      <c r="AP72" s="57"/>
-      <c r="AQ72" s="57"/>
-      <c r="AR72" s="57"/>
-      <c r="AS72" s="57"/>
-      <c r="AT72" s="57"/>
-      <c r="AU72" s="57"/>
-      <c r="AV72" s="57"/>
-      <c r="AW72" s="57"/>
-      <c r="AX72" s="57"/>
-      <c r="AY72" s="57"/>
-      <c r="AZ72" s="57"/>
-      <c r="BA72" s="57"/>
-      <c r="BB72" s="57"/>
-      <c r="BC72" s="57"/>
+      <c r="Z72" s="63"/>
+      <c r="AA72" s="63"/>
+      <c r="AB72" s="63"/>
+      <c r="AC72" s="63"/>
+      <c r="AD72" s="63"/>
+      <c r="AE72" s="63"/>
+      <c r="AF72" s="63"/>
+      <c r="AG72" s="63"/>
+      <c r="AH72" s="63"/>
+      <c r="AI72" s="63"/>
+      <c r="AJ72" s="63"/>
+      <c r="AK72" s="63"/>
+      <c r="AL72" s="63"/>
+      <c r="AM72" s="63"/>
+      <c r="AN72" s="63"/>
+      <c r="AO72" s="63"/>
+      <c r="AP72" s="63"/>
+      <c r="AQ72" s="63"/>
+      <c r="AR72" s="63"/>
+      <c r="AS72" s="63"/>
+      <c r="AT72" s="63"/>
+      <c r="AU72" s="63"/>
+      <c r="AV72" s="63"/>
+      <c r="AW72" s="63"/>
+      <c r="AX72" s="63"/>
+      <c r="AY72" s="63"/>
+      <c r="AZ72" s="63"/>
+      <c r="BA72" s="63"/>
+      <c r="BB72" s="63"/>
+      <c r="BC72" s="63"/>
       <c r="BD72" s="47"/>
       <c r="BE72" s="35"/>
       <c r="BF72" s="35"/>
@@ -18487,38 +18482,38 @@
       <c r="W77" s="35"/>
       <c r="X77" s="35"/>
       <c r="Y77" s="35"/>
-      <c r="Z77" s="58" t="s">
+      <c r="Z77" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="AA77" s="58"/>
-      <c r="AB77" s="58"/>
-      <c r="AC77" s="58"/>
-      <c r="AD77" s="58"/>
-      <c r="AE77" s="58"/>
-      <c r="AF77" s="58"/>
-      <c r="AG77" s="58"/>
-      <c r="AH77" s="58"/>
-      <c r="AI77" s="58"/>
-      <c r="AJ77" s="58"/>
-      <c r="AK77" s="58"/>
-      <c r="AL77" s="58"/>
-      <c r="AM77" s="58"/>
-      <c r="AN77" s="58"/>
-      <c r="AO77" s="58"/>
-      <c r="AP77" s="58"/>
-      <c r="AQ77" s="58"/>
-      <c r="AR77" s="58"/>
-      <c r="AS77" s="58"/>
-      <c r="AT77" s="58"/>
-      <c r="AU77" s="58"/>
-      <c r="AV77" s="58"/>
-      <c r="AW77" s="58"/>
-      <c r="AX77" s="58"/>
-      <c r="AY77" s="58"/>
-      <c r="AZ77" s="58"/>
-      <c r="BA77" s="58"/>
-      <c r="BB77" s="58"/>
-      <c r="BC77" s="58"/>
+      <c r="AA77" s="71"/>
+      <c r="AB77" s="71"/>
+      <c r="AC77" s="71"/>
+      <c r="AD77" s="71"/>
+      <c r="AE77" s="71"/>
+      <c r="AF77" s="71"/>
+      <c r="AG77" s="71"/>
+      <c r="AH77" s="71"/>
+      <c r="AI77" s="71"/>
+      <c r="AJ77" s="71"/>
+      <c r="AK77" s="71"/>
+      <c r="AL77" s="71"/>
+      <c r="AM77" s="71"/>
+      <c r="AN77" s="71"/>
+      <c r="AO77" s="71"/>
+      <c r="AP77" s="71"/>
+      <c r="AQ77" s="71"/>
+      <c r="AR77" s="71"/>
+      <c r="AS77" s="71"/>
+      <c r="AT77" s="71"/>
+      <c r="AU77" s="71"/>
+      <c r="AV77" s="71"/>
+      <c r="AW77" s="71"/>
+      <c r="AX77" s="71"/>
+      <c r="AY77" s="71"/>
+      <c r="AZ77" s="71"/>
+      <c r="BA77" s="71"/>
+      <c r="BB77" s="71"/>
+      <c r="BC77" s="71"/>
       <c r="BD77" s="49"/>
       <c r="BE77" s="35"/>
       <c r="BF77" s="35"/>
@@ -18573,36 +18568,36 @@
       <c r="W78" s="35"/>
       <c r="X78" s="35"/>
       <c r="Y78" s="35"/>
-      <c r="Z78" s="58"/>
-      <c r="AA78" s="58"/>
-      <c r="AB78" s="58"/>
-      <c r="AC78" s="58"/>
-      <c r="AD78" s="58"/>
-      <c r="AE78" s="58"/>
-      <c r="AF78" s="58"/>
-      <c r="AG78" s="58"/>
-      <c r="AH78" s="58"/>
-      <c r="AI78" s="58"/>
-      <c r="AJ78" s="58"/>
-      <c r="AK78" s="58"/>
-      <c r="AL78" s="58"/>
-      <c r="AM78" s="58"/>
-      <c r="AN78" s="58"/>
-      <c r="AO78" s="58"/>
-      <c r="AP78" s="58"/>
-      <c r="AQ78" s="58"/>
-      <c r="AR78" s="58"/>
-      <c r="AS78" s="58"/>
-      <c r="AT78" s="58"/>
-      <c r="AU78" s="58"/>
-      <c r="AV78" s="58"/>
-      <c r="AW78" s="58"/>
-      <c r="AX78" s="58"/>
-      <c r="AY78" s="58"/>
-      <c r="AZ78" s="58"/>
-      <c r="BA78" s="58"/>
-      <c r="BB78" s="58"/>
-      <c r="BC78" s="58"/>
+      <c r="Z78" s="71"/>
+      <c r="AA78" s="71"/>
+      <c r="AB78" s="71"/>
+      <c r="AC78" s="71"/>
+      <c r="AD78" s="71"/>
+      <c r="AE78" s="71"/>
+      <c r="AF78" s="71"/>
+      <c r="AG78" s="71"/>
+      <c r="AH78" s="71"/>
+      <c r="AI78" s="71"/>
+      <c r="AJ78" s="71"/>
+      <c r="AK78" s="71"/>
+      <c r="AL78" s="71"/>
+      <c r="AM78" s="71"/>
+      <c r="AN78" s="71"/>
+      <c r="AO78" s="71"/>
+      <c r="AP78" s="71"/>
+      <c r="AQ78" s="71"/>
+      <c r="AR78" s="71"/>
+      <c r="AS78" s="71"/>
+      <c r="AT78" s="71"/>
+      <c r="AU78" s="71"/>
+      <c r="AV78" s="71"/>
+      <c r="AW78" s="71"/>
+      <c r="AX78" s="71"/>
+      <c r="AY78" s="71"/>
+      <c r="AZ78" s="71"/>
+      <c r="BA78" s="71"/>
+      <c r="BB78" s="71"/>
+      <c r="BC78" s="71"/>
       <c r="BD78" s="49"/>
       <c r="BE78" s="35"/>
       <c r="BF78" s="35"/>
@@ -18657,36 +18652,36 @@
       <c r="W79" s="35"/>
       <c r="X79" s="35"/>
       <c r="Y79" s="35"/>
-      <c r="Z79" s="58"/>
-      <c r="AA79" s="58"/>
-      <c r="AB79" s="58"/>
-      <c r="AC79" s="58"/>
-      <c r="AD79" s="58"/>
-      <c r="AE79" s="58"/>
-      <c r="AF79" s="58"/>
-      <c r="AG79" s="58"/>
-      <c r="AH79" s="58"/>
-      <c r="AI79" s="58"/>
-      <c r="AJ79" s="58"/>
-      <c r="AK79" s="58"/>
-      <c r="AL79" s="58"/>
-      <c r="AM79" s="58"/>
-      <c r="AN79" s="58"/>
-      <c r="AO79" s="58"/>
-      <c r="AP79" s="58"/>
-      <c r="AQ79" s="58"/>
-      <c r="AR79" s="58"/>
-      <c r="AS79" s="58"/>
-      <c r="AT79" s="58"/>
-      <c r="AU79" s="58"/>
-      <c r="AV79" s="58"/>
-      <c r="AW79" s="58"/>
-      <c r="AX79" s="58"/>
-      <c r="AY79" s="58"/>
-      <c r="AZ79" s="58"/>
-      <c r="BA79" s="58"/>
-      <c r="BB79" s="58"/>
-      <c r="BC79" s="58"/>
+      <c r="Z79" s="71"/>
+      <c r="AA79" s="71"/>
+      <c r="AB79" s="71"/>
+      <c r="AC79" s="71"/>
+      <c r="AD79" s="71"/>
+      <c r="AE79" s="71"/>
+      <c r="AF79" s="71"/>
+      <c r="AG79" s="71"/>
+      <c r="AH79" s="71"/>
+      <c r="AI79" s="71"/>
+      <c r="AJ79" s="71"/>
+      <c r="AK79" s="71"/>
+      <c r="AL79" s="71"/>
+      <c r="AM79" s="71"/>
+      <c r="AN79" s="71"/>
+      <c r="AO79" s="71"/>
+      <c r="AP79" s="71"/>
+      <c r="AQ79" s="71"/>
+      <c r="AR79" s="71"/>
+      <c r="AS79" s="71"/>
+      <c r="AT79" s="71"/>
+      <c r="AU79" s="71"/>
+      <c r="AV79" s="71"/>
+      <c r="AW79" s="71"/>
+      <c r="AX79" s="71"/>
+      <c r="AY79" s="71"/>
+      <c r="AZ79" s="71"/>
+      <c r="BA79" s="71"/>
+      <c r="BB79" s="71"/>
+      <c r="BC79" s="71"/>
       <c r="BD79" s="49"/>
       <c r="BE79" s="35"/>
       <c r="BF79" s="35"/>
@@ -18741,36 +18736,36 @@
       <c r="W80" s="35"/>
       <c r="X80" s="35"/>
       <c r="Y80" s="35"/>
-      <c r="Z80" s="58"/>
-      <c r="AA80" s="58"/>
-      <c r="AB80" s="58"/>
-      <c r="AC80" s="58"/>
-      <c r="AD80" s="58"/>
-      <c r="AE80" s="58"/>
-      <c r="AF80" s="58"/>
-      <c r="AG80" s="58"/>
-      <c r="AH80" s="58"/>
-      <c r="AI80" s="58"/>
-      <c r="AJ80" s="58"/>
-      <c r="AK80" s="58"/>
-      <c r="AL80" s="58"/>
-      <c r="AM80" s="58"/>
-      <c r="AN80" s="58"/>
-      <c r="AO80" s="58"/>
-      <c r="AP80" s="58"/>
-      <c r="AQ80" s="58"/>
-      <c r="AR80" s="58"/>
-      <c r="AS80" s="58"/>
-      <c r="AT80" s="58"/>
-      <c r="AU80" s="58"/>
-      <c r="AV80" s="58"/>
-      <c r="AW80" s="58"/>
-      <c r="AX80" s="58"/>
-      <c r="AY80" s="58"/>
-      <c r="AZ80" s="58"/>
-      <c r="BA80" s="58"/>
-      <c r="BB80" s="58"/>
-      <c r="BC80" s="58"/>
+      <c r="Z80" s="71"/>
+      <c r="AA80" s="71"/>
+      <c r="AB80" s="71"/>
+      <c r="AC80" s="71"/>
+      <c r="AD80" s="71"/>
+      <c r="AE80" s="71"/>
+      <c r="AF80" s="71"/>
+      <c r="AG80" s="71"/>
+      <c r="AH80" s="71"/>
+      <c r="AI80" s="71"/>
+      <c r="AJ80" s="71"/>
+      <c r="AK80" s="71"/>
+      <c r="AL80" s="71"/>
+      <c r="AM80" s="71"/>
+      <c r="AN80" s="71"/>
+      <c r="AO80" s="71"/>
+      <c r="AP80" s="71"/>
+      <c r="AQ80" s="71"/>
+      <c r="AR80" s="71"/>
+      <c r="AS80" s="71"/>
+      <c r="AT80" s="71"/>
+      <c r="AU80" s="71"/>
+      <c r="AV80" s="71"/>
+      <c r="AW80" s="71"/>
+      <c r="AX80" s="71"/>
+      <c r="AY80" s="71"/>
+      <c r="AZ80" s="71"/>
+      <c r="BA80" s="71"/>
+      <c r="BB80" s="71"/>
+      <c r="BC80" s="71"/>
       <c r="BD80" s="49"/>
       <c r="BE80" s="35"/>
       <c r="BF80" s="35"/>
@@ -18817,370 +18812,370 @@
       <c r="CU80" s="35"/>
     </row>
     <row r="81" spans="26:56" ht="6" customHeight="1">
-      <c r="Z81" s="58"/>
-      <c r="AA81" s="58"/>
-      <c r="AB81" s="58"/>
-      <c r="AC81" s="58"/>
-      <c r="AD81" s="58"/>
-      <c r="AE81" s="58"/>
-      <c r="AF81" s="58"/>
-      <c r="AG81" s="58"/>
-      <c r="AH81" s="58"/>
-      <c r="AI81" s="58"/>
-      <c r="AJ81" s="58"/>
-      <c r="AK81" s="58"/>
-      <c r="AL81" s="58"/>
-      <c r="AM81" s="58"/>
-      <c r="AN81" s="58"/>
-      <c r="AO81" s="58"/>
-      <c r="AP81" s="58"/>
-      <c r="AQ81" s="58"/>
-      <c r="AR81" s="58"/>
-      <c r="AS81" s="58"/>
-      <c r="AT81" s="58"/>
-      <c r="AU81" s="58"/>
-      <c r="AV81" s="58"/>
-      <c r="AW81" s="58"/>
-      <c r="AX81" s="58"/>
-      <c r="AY81" s="58"/>
-      <c r="AZ81" s="58"/>
-      <c r="BA81" s="58"/>
-      <c r="BB81" s="58"/>
-      <c r="BC81" s="58"/>
+      <c r="Z81" s="71"/>
+      <c r="AA81" s="71"/>
+      <c r="AB81" s="71"/>
+      <c r="AC81" s="71"/>
+      <c r="AD81" s="71"/>
+      <c r="AE81" s="71"/>
+      <c r="AF81" s="71"/>
+      <c r="AG81" s="71"/>
+      <c r="AH81" s="71"/>
+      <c r="AI81" s="71"/>
+      <c r="AJ81" s="71"/>
+      <c r="AK81" s="71"/>
+      <c r="AL81" s="71"/>
+      <c r="AM81" s="71"/>
+      <c r="AN81" s="71"/>
+      <c r="AO81" s="71"/>
+      <c r="AP81" s="71"/>
+      <c r="AQ81" s="71"/>
+      <c r="AR81" s="71"/>
+      <c r="AS81" s="71"/>
+      <c r="AT81" s="71"/>
+      <c r="AU81" s="71"/>
+      <c r="AV81" s="71"/>
+      <c r="AW81" s="71"/>
+      <c r="AX81" s="71"/>
+      <c r="AY81" s="71"/>
+      <c r="AZ81" s="71"/>
+      <c r="BA81" s="71"/>
+      <c r="BB81" s="71"/>
+      <c r="BC81" s="71"/>
       <c r="BD81" s="49"/>
     </row>
     <row r="82" spans="26:56" ht="6" customHeight="1">
-      <c r="Z82" s="58" t="s">
+      <c r="Z82" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="AA82" s="58"/>
-      <c r="AB82" s="58"/>
-      <c r="AC82" s="58"/>
-      <c r="AD82" s="58"/>
-      <c r="AE82" s="58"/>
-      <c r="AF82" s="58"/>
-      <c r="AG82" s="58"/>
-      <c r="AH82" s="58"/>
-      <c r="AI82" s="58"/>
-      <c r="AJ82" s="58"/>
-      <c r="AK82" s="58"/>
-      <c r="AL82" s="58"/>
-      <c r="AM82" s="58"/>
-      <c r="AN82" s="58"/>
-      <c r="AO82" s="58"/>
-      <c r="AP82" s="58"/>
-      <c r="AQ82" s="58"/>
-      <c r="AR82" s="58"/>
-      <c r="AS82" s="58"/>
-      <c r="AT82" s="58"/>
-      <c r="AU82" s="58"/>
-      <c r="AV82" s="58"/>
-      <c r="AW82" s="58"/>
-      <c r="AX82" s="58"/>
-      <c r="AY82" s="58"/>
-      <c r="AZ82" s="58"/>
-      <c r="BA82" s="58"/>
-      <c r="BB82" s="58"/>
-      <c r="BC82" s="58"/>
+      <c r="AA82" s="71"/>
+      <c r="AB82" s="71"/>
+      <c r="AC82" s="71"/>
+      <c r="AD82" s="71"/>
+      <c r="AE82" s="71"/>
+      <c r="AF82" s="71"/>
+      <c r="AG82" s="71"/>
+      <c r="AH82" s="71"/>
+      <c r="AI82" s="71"/>
+      <c r="AJ82" s="71"/>
+      <c r="AK82" s="71"/>
+      <c r="AL82" s="71"/>
+      <c r="AM82" s="71"/>
+      <c r="AN82" s="71"/>
+      <c r="AO82" s="71"/>
+      <c r="AP82" s="71"/>
+      <c r="AQ82" s="71"/>
+      <c r="AR82" s="71"/>
+      <c r="AS82" s="71"/>
+      <c r="AT82" s="71"/>
+      <c r="AU82" s="71"/>
+      <c r="AV82" s="71"/>
+      <c r="AW82" s="71"/>
+      <c r="AX82" s="71"/>
+      <c r="AY82" s="71"/>
+      <c r="AZ82" s="71"/>
+      <c r="BA82" s="71"/>
+      <c r="BB82" s="71"/>
+      <c r="BC82" s="71"/>
       <c r="BD82" s="49"/>
     </row>
     <row r="83" spans="26:56" ht="6" customHeight="1">
-      <c r="Z83" s="58"/>
-      <c r="AA83" s="58"/>
-      <c r="AB83" s="58"/>
-      <c r="AC83" s="58"/>
-      <c r="AD83" s="58"/>
-      <c r="AE83" s="58"/>
-      <c r="AF83" s="58"/>
-      <c r="AG83" s="58"/>
-      <c r="AH83" s="58"/>
-      <c r="AI83" s="58"/>
-      <c r="AJ83" s="58"/>
-      <c r="AK83" s="58"/>
-      <c r="AL83" s="58"/>
-      <c r="AM83" s="58"/>
-      <c r="AN83" s="58"/>
-      <c r="AO83" s="58"/>
-      <c r="AP83" s="58"/>
-      <c r="AQ83" s="58"/>
-      <c r="AR83" s="58"/>
-      <c r="AS83" s="58"/>
-      <c r="AT83" s="58"/>
-      <c r="AU83" s="58"/>
-      <c r="AV83" s="58"/>
-      <c r="AW83" s="58"/>
-      <c r="AX83" s="58"/>
-      <c r="AY83" s="58"/>
-      <c r="AZ83" s="58"/>
-      <c r="BA83" s="58"/>
-      <c r="BB83" s="58"/>
-      <c r="BC83" s="58"/>
+      <c r="Z83" s="71"/>
+      <c r="AA83" s="71"/>
+      <c r="AB83" s="71"/>
+      <c r="AC83" s="71"/>
+      <c r="AD83" s="71"/>
+      <c r="AE83" s="71"/>
+      <c r="AF83" s="71"/>
+      <c r="AG83" s="71"/>
+      <c r="AH83" s="71"/>
+      <c r="AI83" s="71"/>
+      <c r="AJ83" s="71"/>
+      <c r="AK83" s="71"/>
+      <c r="AL83" s="71"/>
+      <c r="AM83" s="71"/>
+      <c r="AN83" s="71"/>
+      <c r="AO83" s="71"/>
+      <c r="AP83" s="71"/>
+      <c r="AQ83" s="71"/>
+      <c r="AR83" s="71"/>
+      <c r="AS83" s="71"/>
+      <c r="AT83" s="71"/>
+      <c r="AU83" s="71"/>
+      <c r="AV83" s="71"/>
+      <c r="AW83" s="71"/>
+      <c r="AX83" s="71"/>
+      <c r="AY83" s="71"/>
+      <c r="AZ83" s="71"/>
+      <c r="BA83" s="71"/>
+      <c r="BB83" s="71"/>
+      <c r="BC83" s="71"/>
       <c r="BD83" s="49"/>
     </row>
     <row r="84" spans="26:56" ht="6" customHeight="1">
-      <c r="Z84" s="58"/>
-      <c r="AA84" s="58"/>
-      <c r="AB84" s="58"/>
-      <c r="AC84" s="58"/>
-      <c r="AD84" s="58"/>
-      <c r="AE84" s="58"/>
-      <c r="AF84" s="58"/>
-      <c r="AG84" s="58"/>
-      <c r="AH84" s="58"/>
-      <c r="AI84" s="58"/>
-      <c r="AJ84" s="58"/>
-      <c r="AK84" s="58"/>
-      <c r="AL84" s="58"/>
-      <c r="AM84" s="58"/>
-      <c r="AN84" s="58"/>
-      <c r="AO84" s="58"/>
-      <c r="AP84" s="58"/>
-      <c r="AQ84" s="58"/>
-      <c r="AR84" s="58"/>
-      <c r="AS84" s="58"/>
-      <c r="AT84" s="58"/>
-      <c r="AU84" s="58"/>
-      <c r="AV84" s="58"/>
-      <c r="AW84" s="58"/>
-      <c r="AX84" s="58"/>
-      <c r="AY84" s="58"/>
-      <c r="AZ84" s="58"/>
-      <c r="BA84" s="58"/>
-      <c r="BB84" s="58"/>
-      <c r="BC84" s="58"/>
+      <c r="Z84" s="71"/>
+      <c r="AA84" s="71"/>
+      <c r="AB84" s="71"/>
+      <c r="AC84" s="71"/>
+      <c r="AD84" s="71"/>
+      <c r="AE84" s="71"/>
+      <c r="AF84" s="71"/>
+      <c r="AG84" s="71"/>
+      <c r="AH84" s="71"/>
+      <c r="AI84" s="71"/>
+      <c r="AJ84" s="71"/>
+      <c r="AK84" s="71"/>
+      <c r="AL84" s="71"/>
+      <c r="AM84" s="71"/>
+      <c r="AN84" s="71"/>
+      <c r="AO84" s="71"/>
+      <c r="AP84" s="71"/>
+      <c r="AQ84" s="71"/>
+      <c r="AR84" s="71"/>
+      <c r="AS84" s="71"/>
+      <c r="AT84" s="71"/>
+      <c r="AU84" s="71"/>
+      <c r="AV84" s="71"/>
+      <c r="AW84" s="71"/>
+      <c r="AX84" s="71"/>
+      <c r="AY84" s="71"/>
+      <c r="AZ84" s="71"/>
+      <c r="BA84" s="71"/>
+      <c r="BB84" s="71"/>
+      <c r="BC84" s="71"/>
       <c r="BD84" s="49"/>
     </row>
     <row r="85" spans="26:56" ht="6" customHeight="1">
-      <c r="Z85" s="58"/>
-      <c r="AA85" s="58"/>
-      <c r="AB85" s="58"/>
-      <c r="AC85" s="58"/>
-      <c r="AD85" s="58"/>
-      <c r="AE85" s="58"/>
-      <c r="AF85" s="58"/>
-      <c r="AG85" s="58"/>
-      <c r="AH85" s="58"/>
-      <c r="AI85" s="58"/>
-      <c r="AJ85" s="58"/>
-      <c r="AK85" s="58"/>
-      <c r="AL85" s="58"/>
-      <c r="AM85" s="58"/>
-      <c r="AN85" s="58"/>
-      <c r="AO85" s="58"/>
-      <c r="AP85" s="58"/>
-      <c r="AQ85" s="58"/>
-      <c r="AR85" s="58"/>
-      <c r="AS85" s="58"/>
-      <c r="AT85" s="58"/>
-      <c r="AU85" s="58"/>
-      <c r="AV85" s="58"/>
-      <c r="AW85" s="58"/>
-      <c r="AX85" s="58"/>
-      <c r="AY85" s="58"/>
-      <c r="AZ85" s="58"/>
-      <c r="BA85" s="58"/>
-      <c r="BB85" s="58"/>
-      <c r="BC85" s="58"/>
+      <c r="Z85" s="71"/>
+      <c r="AA85" s="71"/>
+      <c r="AB85" s="71"/>
+      <c r="AC85" s="71"/>
+      <c r="AD85" s="71"/>
+      <c r="AE85" s="71"/>
+      <c r="AF85" s="71"/>
+      <c r="AG85" s="71"/>
+      <c r="AH85" s="71"/>
+      <c r="AI85" s="71"/>
+      <c r="AJ85" s="71"/>
+      <c r="AK85" s="71"/>
+      <c r="AL85" s="71"/>
+      <c r="AM85" s="71"/>
+      <c r="AN85" s="71"/>
+      <c r="AO85" s="71"/>
+      <c r="AP85" s="71"/>
+      <c r="AQ85" s="71"/>
+      <c r="AR85" s="71"/>
+      <c r="AS85" s="71"/>
+      <c r="AT85" s="71"/>
+      <c r="AU85" s="71"/>
+      <c r="AV85" s="71"/>
+      <c r="AW85" s="71"/>
+      <c r="AX85" s="71"/>
+      <c r="AY85" s="71"/>
+      <c r="AZ85" s="71"/>
+      <c r="BA85" s="71"/>
+      <c r="BB85" s="71"/>
+      <c r="BC85" s="71"/>
       <c r="BD85" s="49"/>
     </row>
     <row r="86" spans="26:56" ht="6" customHeight="1">
-      <c r="Z86" s="58"/>
-      <c r="AA86" s="58"/>
-      <c r="AB86" s="58"/>
-      <c r="AC86" s="58"/>
-      <c r="AD86" s="58"/>
-      <c r="AE86" s="58"/>
-      <c r="AF86" s="58"/>
-      <c r="AG86" s="58"/>
-      <c r="AH86" s="58"/>
-      <c r="AI86" s="58"/>
-      <c r="AJ86" s="58"/>
-      <c r="AK86" s="58"/>
-      <c r="AL86" s="58"/>
-      <c r="AM86" s="58"/>
-      <c r="AN86" s="58"/>
-      <c r="AO86" s="58"/>
-      <c r="AP86" s="58"/>
-      <c r="AQ86" s="58"/>
-      <c r="AR86" s="58"/>
-      <c r="AS86" s="58"/>
-      <c r="AT86" s="58"/>
-      <c r="AU86" s="58"/>
-      <c r="AV86" s="58"/>
-      <c r="AW86" s="58"/>
-      <c r="AX86" s="58"/>
-      <c r="AY86" s="58"/>
-      <c r="AZ86" s="58"/>
-      <c r="BA86" s="58"/>
-      <c r="BB86" s="58"/>
-      <c r="BC86" s="58"/>
+      <c r="Z86" s="71"/>
+      <c r="AA86" s="71"/>
+      <c r="AB86" s="71"/>
+      <c r="AC86" s="71"/>
+      <c r="AD86" s="71"/>
+      <c r="AE86" s="71"/>
+      <c r="AF86" s="71"/>
+      <c r="AG86" s="71"/>
+      <c r="AH86" s="71"/>
+      <c r="AI86" s="71"/>
+      <c r="AJ86" s="71"/>
+      <c r="AK86" s="71"/>
+      <c r="AL86" s="71"/>
+      <c r="AM86" s="71"/>
+      <c r="AN86" s="71"/>
+      <c r="AO86" s="71"/>
+      <c r="AP86" s="71"/>
+      <c r="AQ86" s="71"/>
+      <c r="AR86" s="71"/>
+      <c r="AS86" s="71"/>
+      <c r="AT86" s="71"/>
+      <c r="AU86" s="71"/>
+      <c r="AV86" s="71"/>
+      <c r="AW86" s="71"/>
+      <c r="AX86" s="71"/>
+      <c r="AY86" s="71"/>
+      <c r="AZ86" s="71"/>
+      <c r="BA86" s="71"/>
+      <c r="BB86" s="71"/>
+      <c r="BC86" s="71"/>
       <c r="BD86" s="49"/>
     </row>
     <row r="87" spans="26:56" ht="6" customHeight="1">
-      <c r="Z87" s="58"/>
-      <c r="AA87" s="58"/>
-      <c r="AB87" s="58"/>
-      <c r="AC87" s="58"/>
-      <c r="AD87" s="58"/>
-      <c r="AE87" s="58"/>
-      <c r="AF87" s="58"/>
-      <c r="AG87" s="58"/>
-      <c r="AH87" s="58"/>
-      <c r="AI87" s="58"/>
-      <c r="AJ87" s="58"/>
-      <c r="AK87" s="58"/>
-      <c r="AL87" s="58"/>
-      <c r="AM87" s="58"/>
-      <c r="AN87" s="58"/>
-      <c r="AO87" s="58"/>
-      <c r="AP87" s="58"/>
-      <c r="AQ87" s="58"/>
-      <c r="AR87" s="58"/>
-      <c r="AS87" s="58"/>
-      <c r="AT87" s="58"/>
-      <c r="AU87" s="58"/>
-      <c r="AV87" s="58"/>
-      <c r="AW87" s="58"/>
-      <c r="AX87" s="58"/>
-      <c r="AY87" s="58"/>
-      <c r="AZ87" s="58"/>
-      <c r="BA87" s="58"/>
-      <c r="BB87" s="58"/>
-      <c r="BC87" s="58"/>
+      <c r="Z87" s="71"/>
+      <c r="AA87" s="71"/>
+      <c r="AB87" s="71"/>
+      <c r="AC87" s="71"/>
+      <c r="AD87" s="71"/>
+      <c r="AE87" s="71"/>
+      <c r="AF87" s="71"/>
+      <c r="AG87" s="71"/>
+      <c r="AH87" s="71"/>
+      <c r="AI87" s="71"/>
+      <c r="AJ87" s="71"/>
+      <c r="AK87" s="71"/>
+      <c r="AL87" s="71"/>
+      <c r="AM87" s="71"/>
+      <c r="AN87" s="71"/>
+      <c r="AO87" s="71"/>
+      <c r="AP87" s="71"/>
+      <c r="AQ87" s="71"/>
+      <c r="AR87" s="71"/>
+      <c r="AS87" s="71"/>
+      <c r="AT87" s="71"/>
+      <c r="AU87" s="71"/>
+      <c r="AV87" s="71"/>
+      <c r="AW87" s="71"/>
+      <c r="AX87" s="71"/>
+      <c r="AY87" s="71"/>
+      <c r="AZ87" s="71"/>
+      <c r="BA87" s="71"/>
+      <c r="BB87" s="71"/>
+      <c r="BC87" s="71"/>
       <c r="BD87" s="49"/>
     </row>
     <row r="88" spans="26:56" ht="6" customHeight="1">
-      <c r="Z88" s="58"/>
-      <c r="AA88" s="58"/>
-      <c r="AB88" s="58"/>
-      <c r="AC88" s="58"/>
-      <c r="AD88" s="58"/>
-      <c r="AE88" s="58"/>
-      <c r="AF88" s="58"/>
-      <c r="AG88" s="58"/>
-      <c r="AH88" s="58"/>
-      <c r="AI88" s="58"/>
-      <c r="AJ88" s="58"/>
-      <c r="AK88" s="58"/>
-      <c r="AL88" s="58"/>
-      <c r="AM88" s="58"/>
-      <c r="AN88" s="58"/>
-      <c r="AO88" s="58"/>
-      <c r="AP88" s="58"/>
-      <c r="AQ88" s="58"/>
-      <c r="AR88" s="58"/>
-      <c r="AS88" s="58"/>
-      <c r="AT88" s="58"/>
-      <c r="AU88" s="58"/>
-      <c r="AV88" s="58"/>
-      <c r="AW88" s="58"/>
-      <c r="AX88" s="58"/>
-      <c r="AY88" s="58"/>
-      <c r="AZ88" s="58"/>
-      <c r="BA88" s="58"/>
-      <c r="BB88" s="58"/>
-      <c r="BC88" s="58"/>
+      <c r="Z88" s="71"/>
+      <c r="AA88" s="71"/>
+      <c r="AB88" s="71"/>
+      <c r="AC88" s="71"/>
+      <c r="AD88" s="71"/>
+      <c r="AE88" s="71"/>
+      <c r="AF88" s="71"/>
+      <c r="AG88" s="71"/>
+      <c r="AH88" s="71"/>
+      <c r="AI88" s="71"/>
+      <c r="AJ88" s="71"/>
+      <c r="AK88" s="71"/>
+      <c r="AL88" s="71"/>
+      <c r="AM88" s="71"/>
+      <c r="AN88" s="71"/>
+      <c r="AO88" s="71"/>
+      <c r="AP88" s="71"/>
+      <c r="AQ88" s="71"/>
+      <c r="AR88" s="71"/>
+      <c r="AS88" s="71"/>
+      <c r="AT88" s="71"/>
+      <c r="AU88" s="71"/>
+      <c r="AV88" s="71"/>
+      <c r="AW88" s="71"/>
+      <c r="AX88" s="71"/>
+      <c r="AY88" s="71"/>
+      <c r="AZ88" s="71"/>
+      <c r="BA88" s="71"/>
+      <c r="BB88" s="71"/>
+      <c r="BC88" s="71"/>
       <c r="BD88" s="49"/>
     </row>
     <row r="89" spans="26:56" ht="6" customHeight="1">
-      <c r="Z89" s="58"/>
-      <c r="AA89" s="58"/>
-      <c r="AB89" s="58"/>
-      <c r="AC89" s="58"/>
-      <c r="AD89" s="58"/>
-      <c r="AE89" s="58"/>
-      <c r="AF89" s="58"/>
-      <c r="AG89" s="58"/>
-      <c r="AH89" s="58"/>
-      <c r="AI89" s="58"/>
-      <c r="AJ89" s="58"/>
-      <c r="AK89" s="58"/>
-      <c r="AL89" s="58"/>
-      <c r="AM89" s="58"/>
-      <c r="AN89" s="58"/>
-      <c r="AO89" s="58"/>
-      <c r="AP89" s="58"/>
-      <c r="AQ89" s="58"/>
-      <c r="AR89" s="58"/>
-      <c r="AS89" s="58"/>
-      <c r="AT89" s="58"/>
-      <c r="AU89" s="58"/>
-      <c r="AV89" s="58"/>
-      <c r="AW89" s="58"/>
-      <c r="AX89" s="58"/>
-      <c r="AY89" s="58"/>
-      <c r="AZ89" s="58"/>
-      <c r="BA89" s="58"/>
-      <c r="BB89" s="58"/>
-      <c r="BC89" s="58"/>
+      <c r="Z89" s="71"/>
+      <c r="AA89" s="71"/>
+      <c r="AB89" s="71"/>
+      <c r="AC89" s="71"/>
+      <c r="AD89" s="71"/>
+      <c r="AE89" s="71"/>
+      <c r="AF89" s="71"/>
+      <c r="AG89" s="71"/>
+      <c r="AH89" s="71"/>
+      <c r="AI89" s="71"/>
+      <c r="AJ89" s="71"/>
+      <c r="AK89" s="71"/>
+      <c r="AL89" s="71"/>
+      <c r="AM89" s="71"/>
+      <c r="AN89" s="71"/>
+      <c r="AO89" s="71"/>
+      <c r="AP89" s="71"/>
+      <c r="AQ89" s="71"/>
+      <c r="AR89" s="71"/>
+      <c r="AS89" s="71"/>
+      <c r="AT89" s="71"/>
+      <c r="AU89" s="71"/>
+      <c r="AV89" s="71"/>
+      <c r="AW89" s="71"/>
+      <c r="AX89" s="71"/>
+      <c r="AY89" s="71"/>
+      <c r="AZ89" s="71"/>
+      <c r="BA89" s="71"/>
+      <c r="BB89" s="71"/>
+      <c r="BC89" s="71"/>
       <c r="BD89" s="49"/>
     </row>
     <row r="90" spans="26:56" ht="6" customHeight="1">
-      <c r="Z90" s="52" t="s">
+      <c r="Z90" s="70" t="s">
         <v>129</v>
       </c>
-      <c r="AA90" s="52"/>
-      <c r="AB90" s="52"/>
-      <c r="AC90" s="52"/>
-      <c r="AD90" s="52"/>
-      <c r="AE90" s="52"/>
-      <c r="AF90" s="52"/>
-      <c r="AG90" s="52"/>
-      <c r="AH90" s="52"/>
-      <c r="AI90" s="52"/>
-      <c r="AJ90" s="52"/>
-      <c r="AK90" s="52"/>
-      <c r="AL90" s="52"/>
-      <c r="AM90" s="52"/>
-      <c r="AN90" s="52"/>
-      <c r="AO90" s="52"/>
-      <c r="AP90" s="52"/>
-      <c r="AQ90" s="52"/>
-      <c r="AR90" s="52"/>
-      <c r="AS90" s="52"/>
-      <c r="AT90" s="52"/>
-      <c r="AU90" s="52"/>
-      <c r="AV90" s="52"/>
-      <c r="AW90" s="52"/>
-      <c r="AX90" s="52"/>
-      <c r="AY90" s="52"/>
-      <c r="AZ90" s="52"/>
-      <c r="BA90" s="52"/>
-      <c r="BB90" s="52"/>
-      <c r="BC90" s="52"/>
+      <c r="AA90" s="70"/>
+      <c r="AB90" s="70"/>
+      <c r="AC90" s="70"/>
+      <c r="AD90" s="70"/>
+      <c r="AE90" s="70"/>
+      <c r="AF90" s="70"/>
+      <c r="AG90" s="70"/>
+      <c r="AH90" s="70"/>
+      <c r="AI90" s="70"/>
+      <c r="AJ90" s="70"/>
+      <c r="AK90" s="70"/>
+      <c r="AL90" s="70"/>
+      <c r="AM90" s="70"/>
+      <c r="AN90" s="70"/>
+      <c r="AO90" s="70"/>
+      <c r="AP90" s="70"/>
+      <c r="AQ90" s="70"/>
+      <c r="AR90" s="70"/>
+      <c r="AS90" s="70"/>
+      <c r="AT90" s="70"/>
+      <c r="AU90" s="70"/>
+      <c r="AV90" s="70"/>
+      <c r="AW90" s="70"/>
+      <c r="AX90" s="70"/>
+      <c r="AY90" s="70"/>
+      <c r="AZ90" s="70"/>
+      <c r="BA90" s="70"/>
+      <c r="BB90" s="70"/>
+      <c r="BC90" s="70"/>
       <c r="BD90" s="50"/>
     </row>
     <row r="91" spans="26:56" ht="6" customHeight="1">
-      <c r="Z91" s="52"/>
-      <c r="AA91" s="52"/>
-      <c r="AB91" s="52"/>
-      <c r="AC91" s="52"/>
-      <c r="AD91" s="52"/>
-      <c r="AE91" s="52"/>
-      <c r="AF91" s="52"/>
-      <c r="AG91" s="52"/>
-      <c r="AH91" s="52"/>
-      <c r="AI91" s="52"/>
-      <c r="AJ91" s="52"/>
-      <c r="AK91" s="52"/>
-      <c r="AL91" s="52"/>
-      <c r="AM91" s="52"/>
-      <c r="AN91" s="52"/>
-      <c r="AO91" s="52"/>
-      <c r="AP91" s="52"/>
-      <c r="AQ91" s="52"/>
-      <c r="AR91" s="52"/>
-      <c r="AS91" s="52"/>
-      <c r="AT91" s="52"/>
-      <c r="AU91" s="52"/>
-      <c r="AV91" s="52"/>
-      <c r="AW91" s="52"/>
-      <c r="AX91" s="52"/>
-      <c r="AY91" s="52"/>
-      <c r="AZ91" s="52"/>
-      <c r="BA91" s="52"/>
-      <c r="BB91" s="52"/>
-      <c r="BC91" s="52"/>
+      <c r="Z91" s="70"/>
+      <c r="AA91" s="70"/>
+      <c r="AB91" s="70"/>
+      <c r="AC91" s="70"/>
+      <c r="AD91" s="70"/>
+      <c r="AE91" s="70"/>
+      <c r="AF91" s="70"/>
+      <c r="AG91" s="70"/>
+      <c r="AH91" s="70"/>
+      <c r="AI91" s="70"/>
+      <c r="AJ91" s="70"/>
+      <c r="AK91" s="70"/>
+      <c r="AL91" s="70"/>
+      <c r="AM91" s="70"/>
+      <c r="AN91" s="70"/>
+      <c r="AO91" s="70"/>
+      <c r="AP91" s="70"/>
+      <c r="AQ91" s="70"/>
+      <c r="AR91" s="70"/>
+      <c r="AS91" s="70"/>
+      <c r="AT91" s="70"/>
+      <c r="AU91" s="70"/>
+      <c r="AV91" s="70"/>
+      <c r="AW91" s="70"/>
+      <c r="AX91" s="70"/>
+      <c r="AY91" s="70"/>
+      <c r="AZ91" s="70"/>
+      <c r="BA91" s="70"/>
+      <c r="BB91" s="70"/>
+      <c r="BC91" s="70"/>
       <c r="BD91" s="50"/>
     </row>
     <row r="92" spans="26:56" ht="6" customHeight="1">
@@ -19317,13 +19312,25 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="BN9:CQ11"/>
-    <mergeCell ref="BN12:CQ13"/>
-    <mergeCell ref="Z2:BC3"/>
-    <mergeCell ref="Z4:BC6"/>
-    <mergeCell ref="R5:W7"/>
-    <mergeCell ref="BF5:BK7"/>
-    <mergeCell ref="Z9:BC13"/>
+    <mergeCell ref="Z90:BC91"/>
+    <mergeCell ref="Z65:BC69"/>
+    <mergeCell ref="BN65:CQ67"/>
+    <mergeCell ref="BN68:CQ69"/>
+    <mergeCell ref="Z71:BC72"/>
+    <mergeCell ref="Z77:BC81"/>
+    <mergeCell ref="Z82:BC89"/>
+    <mergeCell ref="Z59:BC61"/>
+    <mergeCell ref="BN59:CQ61"/>
+    <mergeCell ref="B60:P62"/>
+    <mergeCell ref="Z62:BC63"/>
+    <mergeCell ref="BN62:CQ63"/>
+    <mergeCell ref="B63:P64"/>
+    <mergeCell ref="Z48:BC50"/>
+    <mergeCell ref="B51:P52"/>
+    <mergeCell ref="Z51:BC52"/>
+    <mergeCell ref="B54:P56"/>
+    <mergeCell ref="Z54:BC58"/>
+    <mergeCell ref="B57:P58"/>
     <mergeCell ref="Z43:BC47"/>
     <mergeCell ref="BN43:CQ44"/>
     <mergeCell ref="Z14:BC16"/>
@@ -19337,25 +19344,13 @@
     <mergeCell ref="BN37:CQ38"/>
     <mergeCell ref="Z40:BC41"/>
     <mergeCell ref="BN40:CQ42"/>
-    <mergeCell ref="Z48:BC50"/>
-    <mergeCell ref="B51:P52"/>
-    <mergeCell ref="Z51:BC52"/>
-    <mergeCell ref="B54:P56"/>
-    <mergeCell ref="Z54:BC58"/>
-    <mergeCell ref="B57:P58"/>
-    <mergeCell ref="Z59:BC61"/>
-    <mergeCell ref="BN59:CQ61"/>
-    <mergeCell ref="B60:P62"/>
-    <mergeCell ref="Z62:BC63"/>
-    <mergeCell ref="BN62:CQ63"/>
-    <mergeCell ref="B63:P64"/>
-    <mergeCell ref="Z90:BC91"/>
-    <mergeCell ref="Z65:BC69"/>
-    <mergeCell ref="BN65:CQ67"/>
-    <mergeCell ref="BN68:CQ69"/>
-    <mergeCell ref="Z71:BC72"/>
-    <mergeCell ref="Z77:BC81"/>
-    <mergeCell ref="Z82:BC89"/>
+    <mergeCell ref="BN9:CQ11"/>
+    <mergeCell ref="BN12:CQ13"/>
+    <mergeCell ref="Z2:BC3"/>
+    <mergeCell ref="Z4:BC6"/>
+    <mergeCell ref="R5:W7"/>
+    <mergeCell ref="BF5:BK7"/>
+    <mergeCell ref="Z9:BC13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B63" r:id="rId1" xr:uid="{189F5753-E498-40D4-9164-AE23048F312F}"/>
@@ -19385,7 +19380,7 @@
   <sheetPr codeName="Arkusz14">
     <tabColor rgb="FF1E73BE"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="4" bestFit="1" customWidth="1"/>
@@ -19396,7 +19391,7 @@
     <col min="9" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:26">
       <c r="A1" s="13" t="s">
         <v>35</v>
       </c>
@@ -19405,12 +19400,12 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:26">
       <c r="A2" s="13" t="s">
         <v>49</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -19418,7 +19413,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:26">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -19427,7 +19422,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:26">
       <c r="A4" s="8" t="s">
         <v>51</v>
       </c>
@@ -19438,7 +19433,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:26">
       <c r="A5" s="13" t="s">
         <v>35</v>
       </c>
@@ -19461,7 +19456,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:26">
       <c r="A6" s="13" t="s">
         <v>56</v>
       </c>
@@ -19483,8 +19478,68 @@
       <c r="G6" s="15">
         <v>3004</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="K6" s="4" t="b">
+        <f>AND($A6=$B$1,B$5=$B$2)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="b">
+        <f t="shared" ref="L6:V13" si="0">$A6=$B$1</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="b">
+        <f>B$5=$B$2</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="4" t="b">
+        <f t="shared" ref="U6:Z6" si="1">C$5=$B$2</f>
+        <v>0</v>
+      </c>
+      <c r="V6" s="4" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W6" s="4" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X6" s="4" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y6" s="4" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="4" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" s="13" t="s">
         <v>48</v>
       </c>
@@ -19506,8 +19561,40 @@
       <c r="G7" s="17">
         <v>3196</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="K7" s="4" t="b">
+        <f t="shared" ref="K7:K13" si="2">$A7=$B$1</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R7" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8" s="13" t="s">
         <v>57</v>
       </c>
@@ -19529,8 +19616,40 @@
       <c r="G8" s="17">
         <v>3537</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="K8" s="4" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L8" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M8" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N8" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O8" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="P8" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q8" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="R8" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9" s="13" t="s">
         <v>58</v>
       </c>
@@ -19552,8 +19671,40 @@
       <c r="G9" s="17">
         <v>4732</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="K9" s="4" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" s="13" t="s">
         <v>59</v>
       </c>
@@ -19575,8 +19726,40 @@
       <c r="G10" s="17">
         <v>4206</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="K10" s="4" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R10" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="13" t="s">
         <v>60</v>
       </c>
@@ -19598,8 +19781,40 @@
       <c r="G11" s="17">
         <v>3689</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="K11" s="4" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R11" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="13" t="s">
         <v>61</v>
       </c>
@@ -19621,8 +19836,85 @@
       <c r="G12" s="17">
         <v>2816</v>
       </c>
+      <c r="K12" s="4" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="K13" s="4" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="4" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B6:G12">
+    <cfRule type="expression" dxfId="6" priority="3">
+      <formula>$A6=$B$1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>B$5=$B$2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>AND($A6=$B$1,B$5=$B$2)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{00000000-0002-0000-0800-000000000000}">
       <formula1>$B$5:$G$5</formula1>
@@ -19693,7 +19985,10 @@
       <c r="E3" s="11">
         <v>293</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="F3" s="12" t="b">
+        <f>OR(WEEKDAY($A3,2)=6,WEEKDAY($A3,2)=7)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="10">
@@ -19707,7 +20002,10 @@
       <c r="E4" s="11">
         <v>626</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="12" t="b">
+        <f t="shared" ref="F4:F32" si="0">OR(WEEKDAY($A4,2)=6,WEEKDAY($A4,2)=7)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="10">
@@ -19725,7 +20023,10 @@
       <c r="E5" s="11">
         <v>533</v>
       </c>
-      <c r="F5" s="12"/>
+      <c r="F5" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="10">
@@ -19743,7 +20044,10 @@
       <c r="E6" s="11">
         <v>670</v>
       </c>
-      <c r="F6" s="12"/>
+      <c r="F6" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="10">
@@ -19755,7 +20059,10 @@
       <c r="E7" s="11">
         <v>972</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="10">
@@ -19767,7 +20074,10 @@
       <c r="E8" s="11">
         <v>303</v>
       </c>
-      <c r="F8" s="12"/>
+      <c r="F8" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="10">
@@ -19785,7 +20095,10 @@
       <c r="E9" s="11">
         <v>526</v>
       </c>
-      <c r="F9" s="12"/>
+      <c r="F9" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="10">
@@ -19803,7 +20116,10 @@
       <c r="E10" s="11">
         <v>661</v>
       </c>
-      <c r="F10" s="12"/>
+      <c r="F10" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="10">
@@ -19817,7 +20133,10 @@
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
-      <c r="F11" s="12"/>
+      <c r="F11" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="10">
@@ -19831,7 +20150,10 @@
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
-      <c r="F12" s="12"/>
+      <c r="F12" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="10">
@@ -19849,7 +20171,10 @@
       <c r="E13" s="11">
         <v>987</v>
       </c>
-      <c r="F13" s="12"/>
+      <c r="F13" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="10">
@@ -19867,7 +20192,10 @@
       <c r="E14" s="11">
         <v>132</v>
       </c>
-      <c r="F14" s="12"/>
+      <c r="F14" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="10">
@@ -19881,7 +20209,10 @@
         <v>701</v>
       </c>
       <c r="E15" s="11"/>
-      <c r="F15" s="12"/>
+      <c r="F15" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="10">
@@ -19895,7 +20226,10 @@
         <v>611</v>
       </c>
       <c r="E16" s="11"/>
-      <c r="F16" s="12"/>
+      <c r="F16" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="10">
@@ -19913,7 +20247,10 @@
       <c r="E17" s="11">
         <v>710</v>
       </c>
-      <c r="F17" s="12"/>
+      <c r="F17" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="10">
@@ -19931,7 +20268,10 @@
       <c r="E18" s="11">
         <v>996</v>
       </c>
-      <c r="F18" s="12"/>
+      <c r="F18" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="10">
@@ -19949,7 +20289,10 @@
       <c r="E19" s="11">
         <v>597</v>
       </c>
-      <c r="F19" s="12"/>
+      <c r="F19" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="10">
@@ -19967,7 +20310,10 @@
       <c r="E20" s="11">
         <v>273</v>
       </c>
-      <c r="F20" s="12"/>
+      <c r="F20" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="10">
@@ -19981,7 +20327,10 @@
       <c r="E21" s="11">
         <v>683</v>
       </c>
-      <c r="F21" s="12"/>
+      <c r="F21" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="10">
@@ -19995,7 +20344,10 @@
       <c r="E22" s="11">
         <v>528</v>
       </c>
-      <c r="F22" s="12"/>
+      <c r="F22" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="10">
@@ -20013,7 +20365,10 @@
       <c r="E23" s="11">
         <v>896</v>
       </c>
-      <c r="F23" s="12"/>
+      <c r="F23" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="10">
@@ -20031,7 +20386,10 @@
       <c r="E24" s="11">
         <v>440</v>
       </c>
-      <c r="F24" s="12"/>
+      <c r="F24" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="10">
@@ -20049,7 +20407,10 @@
       <c r="E25" s="11">
         <v>287</v>
       </c>
-      <c r="F25" s="12"/>
+      <c r="F25" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="10">
@@ -20067,7 +20428,10 @@
       <c r="E26" s="11">
         <v>692</v>
       </c>
-      <c r="F26" s="12"/>
+      <c r="F26" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="10">
@@ -20085,7 +20449,10 @@
       <c r="E27" s="11">
         <v>122</v>
       </c>
-      <c r="F27" s="12"/>
+      <c r="F27" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="10">
@@ -20101,7 +20468,10 @@
       <c r="E28" s="11">
         <v>150</v>
       </c>
-      <c r="F28" s="12"/>
+      <c r="F28" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="10">
@@ -20117,7 +20487,10 @@
       <c r="E29" s="11">
         <v>934</v>
       </c>
-      <c r="F29" s="12"/>
+      <c r="F29" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="10">
@@ -20135,7 +20508,10 @@
       <c r="E30" s="11">
         <v>873</v>
       </c>
-      <c r="F30" s="12"/>
+      <c r="F30" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10">
@@ -20147,7 +20523,10 @@
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="12"/>
+      <c r="F31" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="10">
@@ -20159,9 +20538,20 @@
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="12" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A3:E32">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>OR(WEEKDAY(A3,2)=6,WEEKDAY(A3,2)=7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>OR(WEEKDAY($A3,2)=6,WEEKDAY($A3,2)=7)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -20628,13 +21018,13 @@
     <sortCondition ref="G3"/>
   </sortState>
   <conditionalFormatting sqref="A3:A14">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C14">
-    <cfRule type="aboveAverage" dxfId="12" priority="2"/>
+    <cfRule type="aboveAverage" dxfId="15" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F12">
-    <cfRule type="top10" dxfId="9" priority="1" percent="1" rank="30"/>
+    <cfRule type="top10" dxfId="14" priority="1" percent="1" rank="30"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21500,11 +21890,11 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:E7">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
+      <formula>8000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
       <formula>4000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="greaterThan">
-      <formula>8000</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21691,7 +22081,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G11">
-    <cfRule type="aboveAverage" dxfId="5" priority="5"/>
+    <cfRule type="aboveAverage" dxfId="11" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -28702,7 +29092,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:D435">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>$C3&gt;$F$1</formula>
     </cfRule>
   </conditionalFormatting>

--- a/excel/Pliki+Mistrz+Excela/początkowe/Rozdział 09 - Formatowanie warunkowe.xlsx
+++ b/excel/Pliki+Mistrz+Excela/początkowe/Rozdział 09 - Formatowanie warunkowe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huber\Desktop\portf\kursy\learning-practice-path\excel\Pliki+Mistrz+Excela\początkowe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D821D1D0-5C08-45F5-A8D3-CB8E4D47B11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CF90F2-E263-4962-8FBF-CEF82C721CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="777" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="777" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ExceliAdam" sheetId="44" r:id="rId1"/>
@@ -11121,17 +11121,49 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="34" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="36" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="35" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="34" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="37" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="36" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="36" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="35" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
@@ -11142,38 +11174,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="34" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="34" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="34" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="36" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="37" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="34" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="34" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="38">
@@ -11216,18 +11216,11 @@
     <cellStyle name="Wrap Text" xfId="29" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="ziel" xfId="30" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="6" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11241,21 +11234,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11276,14 +11255,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -12442,10 +12414,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="G1:G11" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18" dataCellStyle="Normalny 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="G1:G11" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14" dataCellStyle="Normalny 2">
   <autoFilter ref="G1:G11" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Punkty" dataDxfId="17" dataCellStyle="Normalny 2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Punkty" dataDxfId="13" dataCellStyle="Normalny 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12846,38 +12818,38 @@
       <c r="W2" s="35"/>
       <c r="X2" s="35"/>
       <c r="Y2" s="35"/>
-      <c r="Z2" s="55" t="s">
+      <c r="Z2" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="55"/>
-      <c r="AG2" s="55"/>
-      <c r="AH2" s="55"/>
-      <c r="AI2" s="55"/>
-      <c r="AJ2" s="55"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="55"/>
-      <c r="AR2" s="55"/>
-      <c r="AS2" s="55"/>
-      <c r="AT2" s="55"/>
-      <c r="AU2" s="55"/>
-      <c r="AV2" s="55"/>
-      <c r="AW2" s="55"/>
-      <c r="AX2" s="55"/>
-      <c r="AY2" s="55"/>
-      <c r="AZ2" s="55"/>
-      <c r="BA2" s="55"/>
-      <c r="BB2" s="55"/>
-      <c r="BC2" s="55"/>
+      <c r="AA2" s="68"/>
+      <c r="AB2" s="68"/>
+      <c r="AC2" s="68"/>
+      <c r="AD2" s="68"/>
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="68"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="68"/>
+      <c r="AI2" s="68"/>
+      <c r="AJ2" s="68"/>
+      <c r="AK2" s="68"/>
+      <c r="AL2" s="68"/>
+      <c r="AM2" s="68"/>
+      <c r="AN2" s="68"/>
+      <c r="AO2" s="68"/>
+      <c r="AP2" s="68"/>
+      <c r="AQ2" s="68"/>
+      <c r="AR2" s="68"/>
+      <c r="AS2" s="68"/>
+      <c r="AT2" s="68"/>
+      <c r="AU2" s="68"/>
+      <c r="AV2" s="68"/>
+      <c r="AW2" s="68"/>
+      <c r="AX2" s="68"/>
+      <c r="AY2" s="68"/>
+      <c r="AZ2" s="68"/>
+      <c r="BA2" s="68"/>
+      <c r="BB2" s="68"/>
+      <c r="BC2" s="68"/>
       <c r="BD2" s="36"/>
       <c r="BE2" s="35"/>
       <c r="BF2" s="35"/>
@@ -12932,36 +12904,36 @@
       <c r="W3" s="35"/>
       <c r="X3" s="35"/>
       <c r="Y3" s="35"/>
-      <c r="Z3" s="55"/>
-      <c r="AA3" s="55"/>
-      <c r="AB3" s="55"/>
-      <c r="AC3" s="55"/>
-      <c r="AD3" s="55"/>
-      <c r="AE3" s="55"/>
-      <c r="AF3" s="55"/>
-      <c r="AG3" s="55"/>
-      <c r="AH3" s="55"/>
-      <c r="AI3" s="55"/>
-      <c r="AJ3" s="55"/>
-      <c r="AK3" s="55"/>
-      <c r="AL3" s="55"/>
-      <c r="AM3" s="55"/>
-      <c r="AN3" s="55"/>
-      <c r="AO3" s="55"/>
-      <c r="AP3" s="55"/>
-      <c r="AQ3" s="55"/>
-      <c r="AR3" s="55"/>
-      <c r="AS3" s="55"/>
-      <c r="AT3" s="55"/>
-      <c r="AU3" s="55"/>
-      <c r="AV3" s="55"/>
-      <c r="AW3" s="55"/>
-      <c r="AX3" s="55"/>
-      <c r="AY3" s="55"/>
-      <c r="AZ3" s="55"/>
-      <c r="BA3" s="55"/>
-      <c r="BB3" s="55"/>
-      <c r="BC3" s="55"/>
+      <c r="Z3" s="68"/>
+      <c r="AA3" s="68"/>
+      <c r="AB3" s="68"/>
+      <c r="AC3" s="68"/>
+      <c r="AD3" s="68"/>
+      <c r="AE3" s="68"/>
+      <c r="AF3" s="68"/>
+      <c r="AG3" s="68"/>
+      <c r="AH3" s="68"/>
+      <c r="AI3" s="68"/>
+      <c r="AJ3" s="68"/>
+      <c r="AK3" s="68"/>
+      <c r="AL3" s="68"/>
+      <c r="AM3" s="68"/>
+      <c r="AN3" s="68"/>
+      <c r="AO3" s="68"/>
+      <c r="AP3" s="68"/>
+      <c r="AQ3" s="68"/>
+      <c r="AR3" s="68"/>
+      <c r="AS3" s="68"/>
+      <c r="AT3" s="68"/>
+      <c r="AU3" s="68"/>
+      <c r="AV3" s="68"/>
+      <c r="AW3" s="68"/>
+      <c r="AX3" s="68"/>
+      <c r="AY3" s="68"/>
+      <c r="AZ3" s="68"/>
+      <c r="BA3" s="68"/>
+      <c r="BB3" s="68"/>
+      <c r="BC3" s="68"/>
       <c r="BD3" s="36"/>
       <c r="BE3" s="35"/>
       <c r="BF3" s="35"/>
@@ -13016,38 +12988,38 @@
       <c r="W4" s="35"/>
       <c r="X4" s="35"/>
       <c r="Y4" s="35"/>
-      <c r="Z4" s="56" t="s">
+      <c r="Z4" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="56"/>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="56"/>
-      <c r="AG4" s="56"/>
-      <c r="AH4" s="56"/>
-      <c r="AI4" s="56"/>
-      <c r="AJ4" s="56"/>
-      <c r="AK4" s="56"/>
-      <c r="AL4" s="56"/>
-      <c r="AM4" s="56"/>
-      <c r="AN4" s="56"/>
-      <c r="AO4" s="56"/>
-      <c r="AP4" s="56"/>
-      <c r="AQ4" s="56"/>
-      <c r="AR4" s="56"/>
-      <c r="AS4" s="56"/>
-      <c r="AT4" s="56"/>
-      <c r="AU4" s="56"/>
-      <c r="AV4" s="56"/>
-      <c r="AW4" s="56"/>
-      <c r="AX4" s="56"/>
-      <c r="AY4" s="56"/>
-      <c r="AZ4" s="56"/>
-      <c r="BA4" s="56"/>
-      <c r="BB4" s="56"/>
-      <c r="BC4" s="56"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="63"/>
+      <c r="AD4" s="63"/>
+      <c r="AE4" s="63"/>
+      <c r="AF4" s="63"/>
+      <c r="AG4" s="63"/>
+      <c r="AH4" s="63"/>
+      <c r="AI4" s="63"/>
+      <c r="AJ4" s="63"/>
+      <c r="AK4" s="63"/>
+      <c r="AL4" s="63"/>
+      <c r="AM4" s="63"/>
+      <c r="AN4" s="63"/>
+      <c r="AO4" s="63"/>
+      <c r="AP4" s="63"/>
+      <c r="AQ4" s="63"/>
+      <c r="AR4" s="63"/>
+      <c r="AS4" s="63"/>
+      <c r="AT4" s="63"/>
+      <c r="AU4" s="63"/>
+      <c r="AV4" s="63"/>
+      <c r="AW4" s="63"/>
+      <c r="AX4" s="63"/>
+      <c r="AY4" s="63"/>
+      <c r="AZ4" s="63"/>
+      <c r="BA4" s="63"/>
+      <c r="BB4" s="63"/>
+      <c r="BC4" s="63"/>
       <c r="BD4" s="37"/>
       <c r="BE4" s="35"/>
       <c r="BF4" s="35"/>
@@ -13094,56 +13066,56 @@
       <c r="CU4" s="35"/>
     </row>
     <row r="5" spans="18:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="R5" s="57" t="s">
+      <c r="R5" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="S5" s="57"/>
-      <c r="T5" s="57"/>
-      <c r="U5" s="57"/>
-      <c r="V5" s="57"/>
-      <c r="W5" s="57"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
       <c r="X5" s="35"/>
       <c r="Y5" s="35"/>
-      <c r="Z5" s="56"/>
-      <c r="AA5" s="56"/>
-      <c r="AB5" s="56"/>
-      <c r="AC5" s="56"/>
-      <c r="AD5" s="56"/>
-      <c r="AE5" s="56"/>
-      <c r="AF5" s="56"/>
-      <c r="AG5" s="56"/>
-      <c r="AH5" s="56"/>
-      <c r="AI5" s="56"/>
-      <c r="AJ5" s="56"/>
-      <c r="AK5" s="56"/>
-      <c r="AL5" s="56"/>
-      <c r="AM5" s="56"/>
-      <c r="AN5" s="56"/>
-      <c r="AO5" s="56"/>
-      <c r="AP5" s="56"/>
-      <c r="AQ5" s="56"/>
-      <c r="AR5" s="56"/>
-      <c r="AS5" s="56"/>
-      <c r="AT5" s="56"/>
-      <c r="AU5" s="56"/>
-      <c r="AV5" s="56"/>
-      <c r="AW5" s="56"/>
-      <c r="AX5" s="56"/>
-      <c r="AY5" s="56"/>
-      <c r="AZ5" s="56"/>
-      <c r="BA5" s="56"/>
-      <c r="BB5" s="56"/>
-      <c r="BC5" s="56"/>
+      <c r="Z5" s="63"/>
+      <c r="AA5" s="63"/>
+      <c r="AB5" s="63"/>
+      <c r="AC5" s="63"/>
+      <c r="AD5" s="63"/>
+      <c r="AE5" s="63"/>
+      <c r="AF5" s="63"/>
+      <c r="AG5" s="63"/>
+      <c r="AH5" s="63"/>
+      <c r="AI5" s="63"/>
+      <c r="AJ5" s="63"/>
+      <c r="AK5" s="63"/>
+      <c r="AL5" s="63"/>
+      <c r="AM5" s="63"/>
+      <c r="AN5" s="63"/>
+      <c r="AO5" s="63"/>
+      <c r="AP5" s="63"/>
+      <c r="AQ5" s="63"/>
+      <c r="AR5" s="63"/>
+      <c r="AS5" s="63"/>
+      <c r="AT5" s="63"/>
+      <c r="AU5" s="63"/>
+      <c r="AV5" s="63"/>
+      <c r="AW5" s="63"/>
+      <c r="AX5" s="63"/>
+      <c r="AY5" s="63"/>
+      <c r="AZ5" s="63"/>
+      <c r="BA5" s="63"/>
+      <c r="BB5" s="63"/>
+      <c r="BC5" s="63"/>
       <c r="BD5" s="37"/>
       <c r="BE5" s="35"/>
-      <c r="BF5" s="57" t="s">
+      <c r="BF5" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="BG5" s="57"/>
-      <c r="BH5" s="57"/>
-      <c r="BI5" s="57"/>
-      <c r="BJ5" s="57"/>
-      <c r="BK5" s="57"/>
+      <c r="BG5" s="69"/>
+      <c r="BH5" s="69"/>
+      <c r="BI5" s="69"/>
+      <c r="BJ5" s="69"/>
+      <c r="BK5" s="69"/>
       <c r="BL5" s="35"/>
       <c r="BM5" s="35"/>
       <c r="BN5" s="35"/>
@@ -13182,52 +13154,52 @@
       <c r="CU5" s="35"/>
     </row>
     <row r="6" spans="18:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="R6" s="57"/>
-      <c r="S6" s="57"/>
-      <c r="T6" s="57"/>
-      <c r="U6" s="57"/>
-      <c r="V6" s="57"/>
-      <c r="W6" s="57"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="69"/>
+      <c r="V6" s="69"/>
+      <c r="W6" s="69"/>
       <c r="X6" s="35"/>
       <c r="Y6" s="35"/>
-      <c r="Z6" s="56"/>
-      <c r="AA6" s="56"/>
-      <c r="AB6" s="56"/>
-      <c r="AC6" s="56"/>
-      <c r="AD6" s="56"/>
-      <c r="AE6" s="56"/>
-      <c r="AF6" s="56"/>
-      <c r="AG6" s="56"/>
-      <c r="AH6" s="56"/>
-      <c r="AI6" s="56"/>
-      <c r="AJ6" s="56"/>
-      <c r="AK6" s="56"/>
-      <c r="AL6" s="56"/>
-      <c r="AM6" s="56"/>
-      <c r="AN6" s="56"/>
-      <c r="AO6" s="56"/>
-      <c r="AP6" s="56"/>
-      <c r="AQ6" s="56"/>
-      <c r="AR6" s="56"/>
-      <c r="AS6" s="56"/>
-      <c r="AT6" s="56"/>
-      <c r="AU6" s="56"/>
-      <c r="AV6" s="56"/>
-      <c r="AW6" s="56"/>
-      <c r="AX6" s="56"/>
-      <c r="AY6" s="56"/>
-      <c r="AZ6" s="56"/>
-      <c r="BA6" s="56"/>
-      <c r="BB6" s="56"/>
-      <c r="BC6" s="56"/>
+      <c r="Z6" s="63"/>
+      <c r="AA6" s="63"/>
+      <c r="AB6" s="63"/>
+      <c r="AC6" s="63"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="63"/>
+      <c r="AG6" s="63"/>
+      <c r="AH6" s="63"/>
+      <c r="AI6" s="63"/>
+      <c r="AJ6" s="63"/>
+      <c r="AK6" s="63"/>
+      <c r="AL6" s="63"/>
+      <c r="AM6" s="63"/>
+      <c r="AN6" s="63"/>
+      <c r="AO6" s="63"/>
+      <c r="AP6" s="63"/>
+      <c r="AQ6" s="63"/>
+      <c r="AR6" s="63"/>
+      <c r="AS6" s="63"/>
+      <c r="AT6" s="63"/>
+      <c r="AU6" s="63"/>
+      <c r="AV6" s="63"/>
+      <c r="AW6" s="63"/>
+      <c r="AX6" s="63"/>
+      <c r="AY6" s="63"/>
+      <c r="AZ6" s="63"/>
+      <c r="BA6" s="63"/>
+      <c r="BB6" s="63"/>
+      <c r="BC6" s="63"/>
       <c r="BD6" s="37"/>
       <c r="BE6" s="35"/>
-      <c r="BF6" s="57"/>
-      <c r="BG6" s="57"/>
-      <c r="BH6" s="57"/>
-      <c r="BI6" s="57"/>
-      <c r="BJ6" s="57"/>
-      <c r="BK6" s="57"/>
+      <c r="BF6" s="69"/>
+      <c r="BG6" s="69"/>
+      <c r="BH6" s="69"/>
+      <c r="BI6" s="69"/>
+      <c r="BJ6" s="69"/>
+      <c r="BK6" s="69"/>
       <c r="BL6" s="35"/>
       <c r="BM6" s="35"/>
       <c r="BN6" s="35"/>
@@ -13266,12 +13238,12 @@
       <c r="CU6" s="35"/>
     </row>
     <row r="7" spans="18:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="R7" s="57"/>
-      <c r="S7" s="57"/>
-      <c r="T7" s="57"/>
-      <c r="U7" s="57"/>
-      <c r="V7" s="57"/>
-      <c r="W7" s="57"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="69"/>
+      <c r="T7" s="69"/>
+      <c r="U7" s="69"/>
+      <c r="V7" s="69"/>
+      <c r="W7" s="69"/>
       <c r="X7" s="38"/>
       <c r="Y7" s="35"/>
       <c r="Z7" s="35"/>
@@ -13306,12 +13278,12 @@
       <c r="BC7" s="35"/>
       <c r="BD7" s="35"/>
       <c r="BE7" s="35"/>
-      <c r="BF7" s="57"/>
-      <c r="BG7" s="57"/>
-      <c r="BH7" s="57"/>
-      <c r="BI7" s="57"/>
-      <c r="BJ7" s="57"/>
-      <c r="BK7" s="57"/>
+      <c r="BF7" s="69"/>
+      <c r="BG7" s="69"/>
+      <c r="BH7" s="69"/>
+      <c r="BI7" s="69"/>
+      <c r="BJ7" s="69"/>
+      <c r="BK7" s="69"/>
       <c r="BL7" s="35"/>
       <c r="BM7" s="35"/>
       <c r="BN7" s="35"/>
@@ -13442,38 +13414,38 @@
       <c r="W9" s="39"/>
       <c r="X9" s="39"/>
       <c r="Y9" s="39"/>
-      <c r="Z9" s="58" t="s">
+      <c r="Z9" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="AA9" s="58"/>
-      <c r="AB9" s="58"/>
-      <c r="AC9" s="58"/>
-      <c r="AD9" s="58"/>
-      <c r="AE9" s="58"/>
-      <c r="AF9" s="58"/>
-      <c r="AG9" s="58"/>
-      <c r="AH9" s="58"/>
-      <c r="AI9" s="58"/>
-      <c r="AJ9" s="58"/>
-      <c r="AK9" s="58"/>
-      <c r="AL9" s="58"/>
-      <c r="AM9" s="58"/>
-      <c r="AN9" s="58"/>
-      <c r="AO9" s="58"/>
-      <c r="AP9" s="58"/>
-      <c r="AQ9" s="58"/>
-      <c r="AR9" s="58"/>
-      <c r="AS9" s="58"/>
-      <c r="AT9" s="58"/>
-      <c r="AU9" s="58"/>
-      <c r="AV9" s="58"/>
-      <c r="AW9" s="58"/>
-      <c r="AX9" s="58"/>
-      <c r="AY9" s="58"/>
-      <c r="AZ9" s="58"/>
-      <c r="BA9" s="58"/>
-      <c r="BB9" s="58"/>
-      <c r="BC9" s="58"/>
+      <c r="AA9" s="70"/>
+      <c r="AB9" s="70"/>
+      <c r="AC9" s="70"/>
+      <c r="AD9" s="70"/>
+      <c r="AE9" s="70"/>
+      <c r="AF9" s="70"/>
+      <c r="AG9" s="70"/>
+      <c r="AH9" s="70"/>
+      <c r="AI9" s="70"/>
+      <c r="AJ9" s="70"/>
+      <c r="AK9" s="70"/>
+      <c r="AL9" s="70"/>
+      <c r="AM9" s="70"/>
+      <c r="AN9" s="70"/>
+      <c r="AO9" s="70"/>
+      <c r="AP9" s="70"/>
+      <c r="AQ9" s="70"/>
+      <c r="AR9" s="70"/>
+      <c r="AS9" s="70"/>
+      <c r="AT9" s="70"/>
+      <c r="AU9" s="70"/>
+      <c r="AV9" s="70"/>
+      <c r="AW9" s="70"/>
+      <c r="AX9" s="70"/>
+      <c r="AY9" s="70"/>
+      <c r="AZ9" s="70"/>
+      <c r="BA9" s="70"/>
+      <c r="BB9" s="70"/>
+      <c r="BC9" s="70"/>
       <c r="BD9" s="40"/>
       <c r="BE9" s="35"/>
       <c r="BF9" s="39"/>
@@ -13484,38 +13456,38 @@
       <c r="BK9" s="39"/>
       <c r="BL9" s="39"/>
       <c r="BM9" s="39"/>
-      <c r="BN9" s="52" t="s">
+      <c r="BN9" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="BO9" s="52"/>
-      <c r="BP9" s="52"/>
-      <c r="BQ9" s="52"/>
-      <c r="BR9" s="52"/>
-      <c r="BS9" s="52"/>
-      <c r="BT9" s="52"/>
-      <c r="BU9" s="52"/>
-      <c r="BV9" s="52"/>
-      <c r="BW9" s="52"/>
-      <c r="BX9" s="52"/>
-      <c r="BY9" s="52"/>
-      <c r="BZ9" s="52"/>
-      <c r="CA9" s="52"/>
-      <c r="CB9" s="52"/>
-      <c r="CC9" s="52"/>
-      <c r="CD9" s="52"/>
-      <c r="CE9" s="52"/>
-      <c r="CF9" s="52"/>
-      <c r="CG9" s="52"/>
-      <c r="CH9" s="52"/>
-      <c r="CI9" s="52"/>
-      <c r="CJ9" s="52"/>
-      <c r="CK9" s="52"/>
-      <c r="CL9" s="52"/>
-      <c r="CM9" s="52"/>
-      <c r="CN9" s="52"/>
-      <c r="CO9" s="52"/>
-      <c r="CP9" s="52"/>
-      <c r="CQ9" s="52"/>
+      <c r="BO9" s="60"/>
+      <c r="BP9" s="60"/>
+      <c r="BQ9" s="60"/>
+      <c r="BR9" s="60"/>
+      <c r="BS9" s="60"/>
+      <c r="BT9" s="60"/>
+      <c r="BU9" s="60"/>
+      <c r="BV9" s="60"/>
+      <c r="BW9" s="60"/>
+      <c r="BX9" s="60"/>
+      <c r="BY9" s="60"/>
+      <c r="BZ9" s="60"/>
+      <c r="CA9" s="60"/>
+      <c r="CB9" s="60"/>
+      <c r="CC9" s="60"/>
+      <c r="CD9" s="60"/>
+      <c r="CE9" s="60"/>
+      <c r="CF9" s="60"/>
+      <c r="CG9" s="60"/>
+      <c r="CH9" s="60"/>
+      <c r="CI9" s="60"/>
+      <c r="CJ9" s="60"/>
+      <c r="CK9" s="60"/>
+      <c r="CL9" s="60"/>
+      <c r="CM9" s="60"/>
+      <c r="CN9" s="60"/>
+      <c r="CO9" s="60"/>
+      <c r="CP9" s="60"/>
+      <c r="CQ9" s="60"/>
       <c r="CR9" s="41"/>
       <c r="CS9" s="41"/>
       <c r="CT9" s="41"/>
@@ -13530,36 +13502,36 @@
       <c r="W10" s="35"/>
       <c r="X10" s="35"/>
       <c r="Y10" s="35"/>
-      <c r="Z10" s="59"/>
-      <c r="AA10" s="59"/>
-      <c r="AB10" s="59"/>
-      <c r="AC10" s="59"/>
-      <c r="AD10" s="59"/>
-      <c r="AE10" s="59"/>
-      <c r="AF10" s="59"/>
-      <c r="AG10" s="59"/>
-      <c r="AH10" s="59"/>
-      <c r="AI10" s="59"/>
-      <c r="AJ10" s="59"/>
-      <c r="AK10" s="59"/>
-      <c r="AL10" s="59"/>
-      <c r="AM10" s="59"/>
-      <c r="AN10" s="59"/>
-      <c r="AO10" s="59"/>
-      <c r="AP10" s="59"/>
-      <c r="AQ10" s="59"/>
-      <c r="AR10" s="59"/>
-      <c r="AS10" s="59"/>
-      <c r="AT10" s="59"/>
-      <c r="AU10" s="59"/>
-      <c r="AV10" s="59"/>
-      <c r="AW10" s="59"/>
-      <c r="AX10" s="59"/>
-      <c r="AY10" s="59"/>
-      <c r="AZ10" s="59"/>
-      <c r="BA10" s="59"/>
-      <c r="BB10" s="59"/>
-      <c r="BC10" s="59"/>
+      <c r="Z10" s="71"/>
+      <c r="AA10" s="71"/>
+      <c r="AB10" s="71"/>
+      <c r="AC10" s="71"/>
+      <c r="AD10" s="71"/>
+      <c r="AE10" s="71"/>
+      <c r="AF10" s="71"/>
+      <c r="AG10" s="71"/>
+      <c r="AH10" s="71"/>
+      <c r="AI10" s="71"/>
+      <c r="AJ10" s="71"/>
+      <c r="AK10" s="71"/>
+      <c r="AL10" s="71"/>
+      <c r="AM10" s="71"/>
+      <c r="AN10" s="71"/>
+      <c r="AO10" s="71"/>
+      <c r="AP10" s="71"/>
+      <c r="AQ10" s="71"/>
+      <c r="AR10" s="71"/>
+      <c r="AS10" s="71"/>
+      <c r="AT10" s="71"/>
+      <c r="AU10" s="71"/>
+      <c r="AV10" s="71"/>
+      <c r="AW10" s="71"/>
+      <c r="AX10" s="71"/>
+      <c r="AY10" s="71"/>
+      <c r="AZ10" s="71"/>
+      <c r="BA10" s="71"/>
+      <c r="BB10" s="71"/>
+      <c r="BC10" s="71"/>
       <c r="BD10" s="40"/>
       <c r="BE10" s="35"/>
       <c r="BF10" s="35"/>
@@ -13570,36 +13542,36 @@
       <c r="BK10" s="35"/>
       <c r="BL10" s="35"/>
       <c r="BM10" s="35"/>
-      <c r="BN10" s="53"/>
-      <c r="BO10" s="53"/>
-      <c r="BP10" s="53"/>
-      <c r="BQ10" s="53"/>
-      <c r="BR10" s="53"/>
-      <c r="BS10" s="53"/>
-      <c r="BT10" s="53"/>
-      <c r="BU10" s="53"/>
-      <c r="BV10" s="53"/>
-      <c r="BW10" s="53"/>
-      <c r="BX10" s="53"/>
-      <c r="BY10" s="53"/>
-      <c r="BZ10" s="53"/>
-      <c r="CA10" s="53"/>
-      <c r="CB10" s="53"/>
-      <c r="CC10" s="53"/>
-      <c r="CD10" s="53"/>
-      <c r="CE10" s="53"/>
-      <c r="CF10" s="53"/>
-      <c r="CG10" s="53"/>
-      <c r="CH10" s="53"/>
-      <c r="CI10" s="53"/>
-      <c r="CJ10" s="53"/>
-      <c r="CK10" s="53"/>
-      <c r="CL10" s="53"/>
-      <c r="CM10" s="53"/>
-      <c r="CN10" s="53"/>
-      <c r="CO10" s="53"/>
-      <c r="CP10" s="53"/>
-      <c r="CQ10" s="53"/>
+      <c r="BN10" s="55"/>
+      <c r="BO10" s="55"/>
+      <c r="BP10" s="55"/>
+      <c r="BQ10" s="55"/>
+      <c r="BR10" s="55"/>
+      <c r="BS10" s="55"/>
+      <c r="BT10" s="55"/>
+      <c r="BU10" s="55"/>
+      <c r="BV10" s="55"/>
+      <c r="BW10" s="55"/>
+      <c r="BX10" s="55"/>
+      <c r="BY10" s="55"/>
+      <c r="BZ10" s="55"/>
+      <c r="CA10" s="55"/>
+      <c r="CB10" s="55"/>
+      <c r="CC10" s="55"/>
+      <c r="CD10" s="55"/>
+      <c r="CE10" s="55"/>
+      <c r="CF10" s="55"/>
+      <c r="CG10" s="55"/>
+      <c r="CH10" s="55"/>
+      <c r="CI10" s="55"/>
+      <c r="CJ10" s="55"/>
+      <c r="CK10" s="55"/>
+      <c r="CL10" s="55"/>
+      <c r="CM10" s="55"/>
+      <c r="CN10" s="55"/>
+      <c r="CO10" s="55"/>
+      <c r="CP10" s="55"/>
+      <c r="CQ10" s="55"/>
       <c r="CR10" s="41"/>
       <c r="CS10" s="41"/>
       <c r="CT10" s="41"/>
@@ -13614,36 +13586,36 @@
       <c r="W11" s="35"/>
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
-      <c r="Z11" s="59"/>
-      <c r="AA11" s="59"/>
-      <c r="AB11" s="59"/>
-      <c r="AC11" s="59"/>
-      <c r="AD11" s="59"/>
-      <c r="AE11" s="59"/>
-      <c r="AF11" s="59"/>
-      <c r="AG11" s="59"/>
-      <c r="AH11" s="59"/>
-      <c r="AI11" s="59"/>
-      <c r="AJ11" s="59"/>
-      <c r="AK11" s="59"/>
-      <c r="AL11" s="59"/>
-      <c r="AM11" s="59"/>
-      <c r="AN11" s="59"/>
-      <c r="AO11" s="59"/>
-      <c r="AP11" s="59"/>
-      <c r="AQ11" s="59"/>
-      <c r="AR11" s="59"/>
-      <c r="AS11" s="59"/>
-      <c r="AT11" s="59"/>
-      <c r="AU11" s="59"/>
-      <c r="AV11" s="59"/>
-      <c r="AW11" s="59"/>
-      <c r="AX11" s="59"/>
-      <c r="AY11" s="59"/>
-      <c r="AZ11" s="59"/>
-      <c r="BA11" s="59"/>
-      <c r="BB11" s="59"/>
-      <c r="BC11" s="59"/>
+      <c r="Z11" s="71"/>
+      <c r="AA11" s="71"/>
+      <c r="AB11" s="71"/>
+      <c r="AC11" s="71"/>
+      <c r="AD11" s="71"/>
+      <c r="AE11" s="71"/>
+      <c r="AF11" s="71"/>
+      <c r="AG11" s="71"/>
+      <c r="AH11" s="71"/>
+      <c r="AI11" s="71"/>
+      <c r="AJ11" s="71"/>
+      <c r="AK11" s="71"/>
+      <c r="AL11" s="71"/>
+      <c r="AM11" s="71"/>
+      <c r="AN11" s="71"/>
+      <c r="AO11" s="71"/>
+      <c r="AP11" s="71"/>
+      <c r="AQ11" s="71"/>
+      <c r="AR11" s="71"/>
+      <c r="AS11" s="71"/>
+      <c r="AT11" s="71"/>
+      <c r="AU11" s="71"/>
+      <c r="AV11" s="71"/>
+      <c r="AW11" s="71"/>
+      <c r="AX11" s="71"/>
+      <c r="AY11" s="71"/>
+      <c r="AZ11" s="71"/>
+      <c r="BA11" s="71"/>
+      <c r="BB11" s="71"/>
+      <c r="BC11" s="71"/>
       <c r="BD11" s="40"/>
       <c r="BE11" s="35"/>
       <c r="BF11" s="35"/>
@@ -13654,36 +13626,36 @@
       <c r="BK11" s="35"/>
       <c r="BL11" s="35"/>
       <c r="BM11" s="35"/>
-      <c r="BN11" s="53"/>
-      <c r="BO11" s="53"/>
-      <c r="BP11" s="53"/>
-      <c r="BQ11" s="53"/>
-      <c r="BR11" s="53"/>
-      <c r="BS11" s="53"/>
-      <c r="BT11" s="53"/>
-      <c r="BU11" s="53"/>
-      <c r="BV11" s="53"/>
-      <c r="BW11" s="53"/>
-      <c r="BX11" s="53"/>
-      <c r="BY11" s="53"/>
-      <c r="BZ11" s="53"/>
-      <c r="CA11" s="53"/>
-      <c r="CB11" s="53"/>
-      <c r="CC11" s="53"/>
-      <c r="CD11" s="53"/>
-      <c r="CE11" s="53"/>
-      <c r="CF11" s="53"/>
-      <c r="CG11" s="53"/>
-      <c r="CH11" s="53"/>
-      <c r="CI11" s="53"/>
-      <c r="CJ11" s="53"/>
-      <c r="CK11" s="53"/>
-      <c r="CL11" s="53"/>
-      <c r="CM11" s="53"/>
-      <c r="CN11" s="53"/>
-      <c r="CO11" s="53"/>
-      <c r="CP11" s="53"/>
-      <c r="CQ11" s="53"/>
+      <c r="BN11" s="55"/>
+      <c r="BO11" s="55"/>
+      <c r="BP11" s="55"/>
+      <c r="BQ11" s="55"/>
+      <c r="BR11" s="55"/>
+      <c r="BS11" s="55"/>
+      <c r="BT11" s="55"/>
+      <c r="BU11" s="55"/>
+      <c r="BV11" s="55"/>
+      <c r="BW11" s="55"/>
+      <c r="BX11" s="55"/>
+      <c r="BY11" s="55"/>
+      <c r="BZ11" s="55"/>
+      <c r="CA11" s="55"/>
+      <c r="CB11" s="55"/>
+      <c r="CC11" s="55"/>
+      <c r="CD11" s="55"/>
+      <c r="CE11" s="55"/>
+      <c r="CF11" s="55"/>
+      <c r="CG11" s="55"/>
+      <c r="CH11" s="55"/>
+      <c r="CI11" s="55"/>
+      <c r="CJ11" s="55"/>
+      <c r="CK11" s="55"/>
+      <c r="CL11" s="55"/>
+      <c r="CM11" s="55"/>
+      <c r="CN11" s="55"/>
+      <c r="CO11" s="55"/>
+      <c r="CP11" s="55"/>
+      <c r="CQ11" s="55"/>
       <c r="CR11" s="41"/>
       <c r="CS11" s="41"/>
       <c r="CT11" s="41"/>
@@ -13698,36 +13670,36 @@
       <c r="W12" s="35"/>
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
-      <c r="Z12" s="59"/>
-      <c r="AA12" s="59"/>
-      <c r="AB12" s="59"/>
-      <c r="AC12" s="59"/>
-      <c r="AD12" s="59"/>
-      <c r="AE12" s="59"/>
-      <c r="AF12" s="59"/>
-      <c r="AG12" s="59"/>
-      <c r="AH12" s="59"/>
-      <c r="AI12" s="59"/>
-      <c r="AJ12" s="59"/>
-      <c r="AK12" s="59"/>
-      <c r="AL12" s="59"/>
-      <c r="AM12" s="59"/>
-      <c r="AN12" s="59"/>
-      <c r="AO12" s="59"/>
-      <c r="AP12" s="59"/>
-      <c r="AQ12" s="59"/>
-      <c r="AR12" s="59"/>
-      <c r="AS12" s="59"/>
-      <c r="AT12" s="59"/>
-      <c r="AU12" s="59"/>
-      <c r="AV12" s="59"/>
-      <c r="AW12" s="59"/>
-      <c r="AX12" s="59"/>
-      <c r="AY12" s="59"/>
-      <c r="AZ12" s="59"/>
-      <c r="BA12" s="59"/>
-      <c r="BB12" s="59"/>
-      <c r="BC12" s="59"/>
+      <c r="Z12" s="71"/>
+      <c r="AA12" s="71"/>
+      <c r="AB12" s="71"/>
+      <c r="AC12" s="71"/>
+      <c r="AD12" s="71"/>
+      <c r="AE12" s="71"/>
+      <c r="AF12" s="71"/>
+      <c r="AG12" s="71"/>
+      <c r="AH12" s="71"/>
+      <c r="AI12" s="71"/>
+      <c r="AJ12" s="71"/>
+      <c r="AK12" s="71"/>
+      <c r="AL12" s="71"/>
+      <c r="AM12" s="71"/>
+      <c r="AN12" s="71"/>
+      <c r="AO12" s="71"/>
+      <c r="AP12" s="71"/>
+      <c r="AQ12" s="71"/>
+      <c r="AR12" s="71"/>
+      <c r="AS12" s="71"/>
+      <c r="AT12" s="71"/>
+      <c r="AU12" s="71"/>
+      <c r="AV12" s="71"/>
+      <c r="AW12" s="71"/>
+      <c r="AX12" s="71"/>
+      <c r="AY12" s="71"/>
+      <c r="AZ12" s="71"/>
+      <c r="BA12" s="71"/>
+      <c r="BB12" s="71"/>
+      <c r="BC12" s="71"/>
       <c r="BD12" s="40"/>
       <c r="BE12" s="35"/>
       <c r="BF12" s="35"/>
@@ -13738,38 +13710,38 @@
       <c r="BK12" s="35"/>
       <c r="BL12" s="35"/>
       <c r="BM12" s="35"/>
-      <c r="BN12" s="54" t="s">
+      <c r="BN12" s="56" t="s">
         <v>99</v>
       </c>
-      <c r="BO12" s="54"/>
-      <c r="BP12" s="54"/>
-      <c r="BQ12" s="54"/>
-      <c r="BR12" s="54"/>
-      <c r="BS12" s="54"/>
-      <c r="BT12" s="54"/>
-      <c r="BU12" s="54"/>
-      <c r="BV12" s="54"/>
-      <c r="BW12" s="54"/>
-      <c r="BX12" s="54"/>
-      <c r="BY12" s="54"/>
-      <c r="BZ12" s="54"/>
-      <c r="CA12" s="54"/>
-      <c r="CB12" s="54"/>
-      <c r="CC12" s="54"/>
-      <c r="CD12" s="54"/>
-      <c r="CE12" s="54"/>
-      <c r="CF12" s="54"/>
-      <c r="CG12" s="54"/>
-      <c r="CH12" s="54"/>
-      <c r="CI12" s="54"/>
-      <c r="CJ12" s="54"/>
-      <c r="CK12" s="54"/>
-      <c r="CL12" s="54"/>
-      <c r="CM12" s="54"/>
-      <c r="CN12" s="54"/>
-      <c r="CO12" s="54"/>
-      <c r="CP12" s="54"/>
-      <c r="CQ12" s="54"/>
+      <c r="BO12" s="56"/>
+      <c r="BP12" s="56"/>
+      <c r="BQ12" s="56"/>
+      <c r="BR12" s="56"/>
+      <c r="BS12" s="56"/>
+      <c r="BT12" s="56"/>
+      <c r="BU12" s="56"/>
+      <c r="BV12" s="56"/>
+      <c r="BW12" s="56"/>
+      <c r="BX12" s="56"/>
+      <c r="BY12" s="56"/>
+      <c r="BZ12" s="56"/>
+      <c r="CA12" s="56"/>
+      <c r="CB12" s="56"/>
+      <c r="CC12" s="56"/>
+      <c r="CD12" s="56"/>
+      <c r="CE12" s="56"/>
+      <c r="CF12" s="56"/>
+      <c r="CG12" s="56"/>
+      <c r="CH12" s="56"/>
+      <c r="CI12" s="56"/>
+      <c r="CJ12" s="56"/>
+      <c r="CK12" s="56"/>
+      <c r="CL12" s="56"/>
+      <c r="CM12" s="56"/>
+      <c r="CN12" s="56"/>
+      <c r="CO12" s="56"/>
+      <c r="CP12" s="56"/>
+      <c r="CQ12" s="56"/>
       <c r="CR12" s="42"/>
       <c r="CS12" s="42"/>
       <c r="CT12" s="42"/>
@@ -13784,36 +13756,36 @@
       <c r="W13" s="35"/>
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
-      <c r="Z13" s="59"/>
-      <c r="AA13" s="59"/>
-      <c r="AB13" s="59"/>
-      <c r="AC13" s="59"/>
-      <c r="AD13" s="59"/>
-      <c r="AE13" s="59"/>
-      <c r="AF13" s="59"/>
-      <c r="AG13" s="59"/>
-      <c r="AH13" s="59"/>
-      <c r="AI13" s="59"/>
-      <c r="AJ13" s="59"/>
-      <c r="AK13" s="59"/>
-      <c r="AL13" s="59"/>
-      <c r="AM13" s="59"/>
-      <c r="AN13" s="59"/>
-      <c r="AO13" s="59"/>
-      <c r="AP13" s="59"/>
-      <c r="AQ13" s="59"/>
-      <c r="AR13" s="59"/>
-      <c r="AS13" s="59"/>
-      <c r="AT13" s="59"/>
-      <c r="AU13" s="59"/>
-      <c r="AV13" s="59"/>
-      <c r="AW13" s="59"/>
-      <c r="AX13" s="59"/>
-      <c r="AY13" s="59"/>
-      <c r="AZ13" s="59"/>
-      <c r="BA13" s="59"/>
-      <c r="BB13" s="59"/>
-      <c r="BC13" s="59"/>
+      <c r="Z13" s="71"/>
+      <c r="AA13" s="71"/>
+      <c r="AB13" s="71"/>
+      <c r="AC13" s="71"/>
+      <c r="AD13" s="71"/>
+      <c r="AE13" s="71"/>
+      <c r="AF13" s="71"/>
+      <c r="AG13" s="71"/>
+      <c r="AH13" s="71"/>
+      <c r="AI13" s="71"/>
+      <c r="AJ13" s="71"/>
+      <c r="AK13" s="71"/>
+      <c r="AL13" s="71"/>
+      <c r="AM13" s="71"/>
+      <c r="AN13" s="71"/>
+      <c r="AO13" s="71"/>
+      <c r="AP13" s="71"/>
+      <c r="AQ13" s="71"/>
+      <c r="AR13" s="71"/>
+      <c r="AS13" s="71"/>
+      <c r="AT13" s="71"/>
+      <c r="AU13" s="71"/>
+      <c r="AV13" s="71"/>
+      <c r="AW13" s="71"/>
+      <c r="AX13" s="71"/>
+      <c r="AY13" s="71"/>
+      <c r="AZ13" s="71"/>
+      <c r="BA13" s="71"/>
+      <c r="BB13" s="71"/>
+      <c r="BC13" s="71"/>
       <c r="BD13" s="40"/>
       <c r="BE13" s="35"/>
       <c r="BF13" s="35"/>
@@ -13824,36 +13796,36 @@
       <c r="BK13" s="35"/>
       <c r="BL13" s="35"/>
       <c r="BM13" s="35"/>
-      <c r="BN13" s="54"/>
-      <c r="BO13" s="54"/>
-      <c r="BP13" s="54"/>
-      <c r="BQ13" s="54"/>
-      <c r="BR13" s="54"/>
-      <c r="BS13" s="54"/>
-      <c r="BT13" s="54"/>
-      <c r="BU13" s="54"/>
-      <c r="BV13" s="54"/>
-      <c r="BW13" s="54"/>
-      <c r="BX13" s="54"/>
-      <c r="BY13" s="54"/>
-      <c r="BZ13" s="54"/>
-      <c r="CA13" s="54"/>
-      <c r="CB13" s="54"/>
-      <c r="CC13" s="54"/>
-      <c r="CD13" s="54"/>
-      <c r="CE13" s="54"/>
-      <c r="CF13" s="54"/>
-      <c r="CG13" s="54"/>
-      <c r="CH13" s="54"/>
-      <c r="CI13" s="54"/>
-      <c r="CJ13" s="54"/>
-      <c r="CK13" s="54"/>
-      <c r="CL13" s="54"/>
-      <c r="CM13" s="54"/>
-      <c r="CN13" s="54"/>
-      <c r="CO13" s="54"/>
-      <c r="CP13" s="54"/>
-      <c r="CQ13" s="54"/>
+      <c r="BN13" s="56"/>
+      <c r="BO13" s="56"/>
+      <c r="BP13" s="56"/>
+      <c r="BQ13" s="56"/>
+      <c r="BR13" s="56"/>
+      <c r="BS13" s="56"/>
+      <c r="BT13" s="56"/>
+      <c r="BU13" s="56"/>
+      <c r="BV13" s="56"/>
+      <c r="BW13" s="56"/>
+      <c r="BX13" s="56"/>
+      <c r="BY13" s="56"/>
+      <c r="BZ13" s="56"/>
+      <c r="CA13" s="56"/>
+      <c r="CB13" s="56"/>
+      <c r="CC13" s="56"/>
+      <c r="CD13" s="56"/>
+      <c r="CE13" s="56"/>
+      <c r="CF13" s="56"/>
+      <c r="CG13" s="56"/>
+      <c r="CH13" s="56"/>
+      <c r="CI13" s="56"/>
+      <c r="CJ13" s="56"/>
+      <c r="CK13" s="56"/>
+      <c r="CL13" s="56"/>
+      <c r="CM13" s="56"/>
+      <c r="CN13" s="56"/>
+      <c r="CO13" s="56"/>
+      <c r="CP13" s="56"/>
+      <c r="CQ13" s="56"/>
       <c r="CR13" s="42"/>
       <c r="CS13" s="42"/>
       <c r="CT13" s="42"/>
@@ -13868,38 +13840,38 @@
       <c r="W14" s="35"/>
       <c r="X14" s="35"/>
       <c r="Y14" s="35"/>
-      <c r="Z14" s="62" t="s">
+      <c r="Z14" s="59" t="s">
         <v>100</v>
       </c>
-      <c r="AA14" s="62"/>
-      <c r="AB14" s="62"/>
-      <c r="AC14" s="62"/>
-      <c r="AD14" s="62"/>
-      <c r="AE14" s="62"/>
-      <c r="AF14" s="62"/>
-      <c r="AG14" s="62"/>
-      <c r="AH14" s="62"/>
-      <c r="AI14" s="62"/>
-      <c r="AJ14" s="62"/>
-      <c r="AK14" s="62"/>
-      <c r="AL14" s="62"/>
-      <c r="AM14" s="62"/>
-      <c r="AN14" s="62"/>
-      <c r="AO14" s="62"/>
-      <c r="AP14" s="62"/>
-      <c r="AQ14" s="62"/>
-      <c r="AR14" s="62"/>
-      <c r="AS14" s="62"/>
-      <c r="AT14" s="62"/>
-      <c r="AU14" s="62"/>
-      <c r="AV14" s="62"/>
-      <c r="AW14" s="62"/>
-      <c r="AX14" s="62"/>
-      <c r="AY14" s="62"/>
-      <c r="AZ14" s="62"/>
-      <c r="BA14" s="62"/>
-      <c r="BB14" s="62"/>
-      <c r="BC14" s="62"/>
+      <c r="AA14" s="59"/>
+      <c r="AB14" s="59"/>
+      <c r="AC14" s="59"/>
+      <c r="AD14" s="59"/>
+      <c r="AE14" s="59"/>
+      <c r="AF14" s="59"/>
+      <c r="AG14" s="59"/>
+      <c r="AH14" s="59"/>
+      <c r="AI14" s="59"/>
+      <c r="AJ14" s="59"/>
+      <c r="AK14" s="59"/>
+      <c r="AL14" s="59"/>
+      <c r="AM14" s="59"/>
+      <c r="AN14" s="59"/>
+      <c r="AO14" s="59"/>
+      <c r="AP14" s="59"/>
+      <c r="AQ14" s="59"/>
+      <c r="AR14" s="59"/>
+      <c r="AS14" s="59"/>
+      <c r="AT14" s="59"/>
+      <c r="AU14" s="59"/>
+      <c r="AV14" s="59"/>
+      <c r="AW14" s="59"/>
+      <c r="AX14" s="59"/>
+      <c r="AY14" s="59"/>
+      <c r="AZ14" s="59"/>
+      <c r="BA14" s="59"/>
+      <c r="BB14" s="59"/>
+      <c r="BC14" s="59"/>
       <c r="BD14" s="43"/>
       <c r="BE14" s="35"/>
       <c r="BF14" s="35"/>
@@ -13954,36 +13926,36 @@
       <c r="W15" s="35"/>
       <c r="X15" s="35"/>
       <c r="Y15" s="35"/>
-      <c r="Z15" s="62"/>
-      <c r="AA15" s="62"/>
-      <c r="AB15" s="62"/>
-      <c r="AC15" s="62"/>
-      <c r="AD15" s="62"/>
-      <c r="AE15" s="62"/>
-      <c r="AF15" s="62"/>
-      <c r="AG15" s="62"/>
-      <c r="AH15" s="62"/>
-      <c r="AI15" s="62"/>
-      <c r="AJ15" s="62"/>
-      <c r="AK15" s="62"/>
-      <c r="AL15" s="62"/>
-      <c r="AM15" s="62"/>
-      <c r="AN15" s="62"/>
-      <c r="AO15" s="62"/>
-      <c r="AP15" s="62"/>
-      <c r="AQ15" s="62"/>
-      <c r="AR15" s="62"/>
-      <c r="AS15" s="62"/>
-      <c r="AT15" s="62"/>
-      <c r="AU15" s="62"/>
-      <c r="AV15" s="62"/>
-      <c r="AW15" s="62"/>
-      <c r="AX15" s="62"/>
-      <c r="AY15" s="62"/>
-      <c r="AZ15" s="62"/>
-      <c r="BA15" s="62"/>
-      <c r="BB15" s="62"/>
-      <c r="BC15" s="62"/>
+      <c r="Z15" s="59"/>
+      <c r="AA15" s="59"/>
+      <c r="AB15" s="59"/>
+      <c r="AC15" s="59"/>
+      <c r="AD15" s="59"/>
+      <c r="AE15" s="59"/>
+      <c r="AF15" s="59"/>
+      <c r="AG15" s="59"/>
+      <c r="AH15" s="59"/>
+      <c r="AI15" s="59"/>
+      <c r="AJ15" s="59"/>
+      <c r="AK15" s="59"/>
+      <c r="AL15" s="59"/>
+      <c r="AM15" s="59"/>
+      <c r="AN15" s="59"/>
+      <c r="AO15" s="59"/>
+      <c r="AP15" s="59"/>
+      <c r="AQ15" s="59"/>
+      <c r="AR15" s="59"/>
+      <c r="AS15" s="59"/>
+      <c r="AT15" s="59"/>
+      <c r="AU15" s="59"/>
+      <c r="AV15" s="59"/>
+      <c r="AW15" s="59"/>
+      <c r="AX15" s="59"/>
+      <c r="AY15" s="59"/>
+      <c r="AZ15" s="59"/>
+      <c r="BA15" s="59"/>
+      <c r="BB15" s="59"/>
+      <c r="BC15" s="59"/>
       <c r="BD15" s="43"/>
       <c r="BE15" s="35"/>
       <c r="BF15" s="35"/>
@@ -14038,36 +14010,36 @@
       <c r="W16" s="35"/>
       <c r="X16" s="35"/>
       <c r="Y16" s="35"/>
-      <c r="Z16" s="62"/>
-      <c r="AA16" s="62"/>
-      <c r="AB16" s="62"/>
-      <c r="AC16" s="62"/>
-      <c r="AD16" s="62"/>
-      <c r="AE16" s="62"/>
-      <c r="AF16" s="62"/>
-      <c r="AG16" s="62"/>
-      <c r="AH16" s="62"/>
-      <c r="AI16" s="62"/>
-      <c r="AJ16" s="62"/>
-      <c r="AK16" s="62"/>
-      <c r="AL16" s="62"/>
-      <c r="AM16" s="62"/>
-      <c r="AN16" s="62"/>
-      <c r="AO16" s="62"/>
-      <c r="AP16" s="62"/>
-      <c r="AQ16" s="62"/>
-      <c r="AR16" s="62"/>
-      <c r="AS16" s="62"/>
-      <c r="AT16" s="62"/>
-      <c r="AU16" s="62"/>
-      <c r="AV16" s="62"/>
-      <c r="AW16" s="62"/>
-      <c r="AX16" s="62"/>
-      <c r="AY16" s="62"/>
-      <c r="AZ16" s="62"/>
-      <c r="BA16" s="62"/>
-      <c r="BB16" s="62"/>
-      <c r="BC16" s="62"/>
+      <c r="Z16" s="59"/>
+      <c r="AA16" s="59"/>
+      <c r="AB16" s="59"/>
+      <c r="AC16" s="59"/>
+      <c r="AD16" s="59"/>
+      <c r="AE16" s="59"/>
+      <c r="AF16" s="59"/>
+      <c r="AG16" s="59"/>
+      <c r="AH16" s="59"/>
+      <c r="AI16" s="59"/>
+      <c r="AJ16" s="59"/>
+      <c r="AK16" s="59"/>
+      <c r="AL16" s="59"/>
+      <c r="AM16" s="59"/>
+      <c r="AN16" s="59"/>
+      <c r="AO16" s="59"/>
+      <c r="AP16" s="59"/>
+      <c r="AQ16" s="59"/>
+      <c r="AR16" s="59"/>
+      <c r="AS16" s="59"/>
+      <c r="AT16" s="59"/>
+      <c r="AU16" s="59"/>
+      <c r="AV16" s="59"/>
+      <c r="AW16" s="59"/>
+      <c r="AX16" s="59"/>
+      <c r="AY16" s="59"/>
+      <c r="AZ16" s="59"/>
+      <c r="BA16" s="59"/>
+      <c r="BB16" s="59"/>
+      <c r="BC16" s="59"/>
       <c r="BD16" s="43"/>
       <c r="BE16" s="35"/>
       <c r="BF16" s="35"/>
@@ -14114,71 +14086,71 @@
       <c r="CU16" s="35"/>
     </row>
     <row r="17" spans="18:56" ht="6" customHeight="1">
-      <c r="Z17" s="63" t="s">
+      <c r="Z17" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="AA17" s="63"/>
-      <c r="AB17" s="63"/>
-      <c r="AC17" s="63"/>
-      <c r="AD17" s="63"/>
-      <c r="AE17" s="63"/>
-      <c r="AF17" s="63"/>
-      <c r="AG17" s="63"/>
-      <c r="AH17" s="63"/>
-      <c r="AI17" s="63"/>
-      <c r="AJ17" s="63"/>
-      <c r="AK17" s="63"/>
-      <c r="AL17" s="63"/>
-      <c r="AM17" s="63"/>
-      <c r="AN17" s="63"/>
-      <c r="AO17" s="63"/>
-      <c r="AP17" s="63"/>
-      <c r="AQ17" s="63"/>
-      <c r="AR17" s="63"/>
-      <c r="AS17" s="63"/>
-      <c r="AT17" s="63"/>
-      <c r="AU17" s="63"/>
-      <c r="AV17" s="63"/>
-      <c r="AW17" s="63"/>
-      <c r="AX17" s="63"/>
-      <c r="AY17" s="63"/>
-      <c r="AZ17" s="63"/>
-      <c r="BA17" s="63"/>
-      <c r="BB17" s="63"/>
-      <c r="BC17" s="63"/>
+      <c r="AA17" s="57"/>
+      <c r="AB17" s="57"/>
+      <c r="AC17" s="57"/>
+      <c r="AD17" s="57"/>
+      <c r="AE17" s="57"/>
+      <c r="AF17" s="57"/>
+      <c r="AG17" s="57"/>
+      <c r="AH17" s="57"/>
+      <c r="AI17" s="57"/>
+      <c r="AJ17" s="57"/>
+      <c r="AK17" s="57"/>
+      <c r="AL17" s="57"/>
+      <c r="AM17" s="57"/>
+      <c r="AN17" s="57"/>
+      <c r="AO17" s="57"/>
+      <c r="AP17" s="57"/>
+      <c r="AQ17" s="57"/>
+      <c r="AR17" s="57"/>
+      <c r="AS17" s="57"/>
+      <c r="AT17" s="57"/>
+      <c r="AU17" s="57"/>
+      <c r="AV17" s="57"/>
+      <c r="AW17" s="57"/>
+      <c r="AX17" s="57"/>
+      <c r="AY17" s="57"/>
+      <c r="AZ17" s="57"/>
+      <c r="BA17" s="57"/>
+      <c r="BB17" s="57"/>
+      <c r="BC17" s="57"/>
       <c r="BD17" s="44"/>
     </row>
     <row r="18" spans="18:56" ht="6" customHeight="1">
-      <c r="Z18" s="63"/>
-      <c r="AA18" s="63"/>
-      <c r="AB18" s="63"/>
-      <c r="AC18" s="63"/>
-      <c r="AD18" s="63"/>
-      <c r="AE18" s="63"/>
-      <c r="AF18" s="63"/>
-      <c r="AG18" s="63"/>
-      <c r="AH18" s="63"/>
-      <c r="AI18" s="63"/>
-      <c r="AJ18" s="63"/>
-      <c r="AK18" s="63"/>
-      <c r="AL18" s="63"/>
-      <c r="AM18" s="63"/>
-      <c r="AN18" s="63"/>
-      <c r="AO18" s="63"/>
-      <c r="AP18" s="63"/>
-      <c r="AQ18" s="63"/>
-      <c r="AR18" s="63"/>
-      <c r="AS18" s="63"/>
-      <c r="AT18" s="63"/>
-      <c r="AU18" s="63"/>
-      <c r="AV18" s="63"/>
-      <c r="AW18" s="63"/>
-      <c r="AX18" s="63"/>
-      <c r="AY18" s="63"/>
-      <c r="AZ18" s="63"/>
-      <c r="BA18" s="63"/>
-      <c r="BB18" s="63"/>
-      <c r="BC18" s="63"/>
+      <c r="Z18" s="57"/>
+      <c r="AA18" s="57"/>
+      <c r="AB18" s="57"/>
+      <c r="AC18" s="57"/>
+      <c r="AD18" s="57"/>
+      <c r="AE18" s="57"/>
+      <c r="AF18" s="57"/>
+      <c r="AG18" s="57"/>
+      <c r="AH18" s="57"/>
+      <c r="AI18" s="57"/>
+      <c r="AJ18" s="57"/>
+      <c r="AK18" s="57"/>
+      <c r="AL18" s="57"/>
+      <c r="AM18" s="57"/>
+      <c r="AN18" s="57"/>
+      <c r="AO18" s="57"/>
+      <c r="AP18" s="57"/>
+      <c r="AQ18" s="57"/>
+      <c r="AR18" s="57"/>
+      <c r="AS18" s="57"/>
+      <c r="AT18" s="57"/>
+      <c r="AU18" s="57"/>
+      <c r="AV18" s="57"/>
+      <c r="AW18" s="57"/>
+      <c r="AX18" s="57"/>
+      <c r="AY18" s="57"/>
+      <c r="AZ18" s="57"/>
+      <c r="BA18" s="57"/>
+      <c r="BB18" s="57"/>
+      <c r="BC18" s="57"/>
       <c r="BD18" s="44"/>
     </row>
     <row r="19" spans="18:56" ht="6" customHeight="1"/>
@@ -14192,208 +14164,208 @@
       <c r="W21" s="39"/>
       <c r="X21" s="39"/>
       <c r="Y21" s="39"/>
-      <c r="Z21" s="64" t="s">
+      <c r="Z21" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="AA21" s="64"/>
-      <c r="AB21" s="64"/>
-      <c r="AC21" s="64"/>
-      <c r="AD21" s="64"/>
-      <c r="AE21" s="64"/>
-      <c r="AF21" s="64"/>
-      <c r="AG21" s="64"/>
-      <c r="AH21" s="64"/>
-      <c r="AI21" s="64"/>
-      <c r="AJ21" s="64"/>
-      <c r="AK21" s="64"/>
-      <c r="AL21" s="64"/>
-      <c r="AM21" s="64"/>
-      <c r="AN21" s="64"/>
-      <c r="AO21" s="64"/>
-      <c r="AP21" s="64"/>
-      <c r="AQ21" s="64"/>
-      <c r="AR21" s="64"/>
-      <c r="AS21" s="64"/>
-      <c r="AT21" s="64"/>
-      <c r="AU21" s="64"/>
-      <c r="AV21" s="64"/>
-      <c r="AW21" s="64"/>
-      <c r="AX21" s="64"/>
-      <c r="AY21" s="64"/>
-      <c r="AZ21" s="64"/>
-      <c r="BA21" s="64"/>
-      <c r="BB21" s="64"/>
-      <c r="BC21" s="64"/>
+      <c r="AA21" s="65"/>
+      <c r="AB21" s="65"/>
+      <c r="AC21" s="65"/>
+      <c r="AD21" s="65"/>
+      <c r="AE21" s="65"/>
+      <c r="AF21" s="65"/>
+      <c r="AG21" s="65"/>
+      <c r="AH21" s="65"/>
+      <c r="AI21" s="65"/>
+      <c r="AJ21" s="65"/>
+      <c r="AK21" s="65"/>
+      <c r="AL21" s="65"/>
+      <c r="AM21" s="65"/>
+      <c r="AN21" s="65"/>
+      <c r="AO21" s="65"/>
+      <c r="AP21" s="65"/>
+      <c r="AQ21" s="65"/>
+      <c r="AR21" s="65"/>
+      <c r="AS21" s="65"/>
+      <c r="AT21" s="65"/>
+      <c r="AU21" s="65"/>
+      <c r="AV21" s="65"/>
+      <c r="AW21" s="65"/>
+      <c r="AX21" s="65"/>
+      <c r="AY21" s="65"/>
+      <c r="AZ21" s="65"/>
+      <c r="BA21" s="65"/>
+      <c r="BB21" s="65"/>
+      <c r="BC21" s="65"/>
       <c r="BD21" s="45"/>
     </row>
     <row r="22" spans="18:56" ht="6" customHeight="1">
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="65"/>
-      <c r="AC22" s="65"/>
-      <c r="AD22" s="65"/>
-      <c r="AE22" s="65"/>
-      <c r="AF22" s="65"/>
-      <c r="AG22" s="65"/>
-      <c r="AH22" s="65"/>
-      <c r="AI22" s="65"/>
-      <c r="AJ22" s="65"/>
-      <c r="AK22" s="65"/>
-      <c r="AL22" s="65"/>
-      <c r="AM22" s="65"/>
-      <c r="AN22" s="65"/>
-      <c r="AO22" s="65"/>
-      <c r="AP22" s="65"/>
-      <c r="AQ22" s="65"/>
-      <c r="AR22" s="65"/>
-      <c r="AS22" s="65"/>
-      <c r="AT22" s="65"/>
-      <c r="AU22" s="65"/>
-      <c r="AV22" s="65"/>
-      <c r="AW22" s="65"/>
-      <c r="AX22" s="65"/>
-      <c r="AY22" s="65"/>
-      <c r="AZ22" s="65"/>
-      <c r="BA22" s="65"/>
-      <c r="BB22" s="65"/>
-      <c r="BC22" s="65"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="66"/>
+      <c r="AD22" s="66"/>
+      <c r="AE22" s="66"/>
+      <c r="AF22" s="66"/>
+      <c r="AG22" s="66"/>
+      <c r="AH22" s="66"/>
+      <c r="AI22" s="66"/>
+      <c r="AJ22" s="66"/>
+      <c r="AK22" s="66"/>
+      <c r="AL22" s="66"/>
+      <c r="AM22" s="66"/>
+      <c r="AN22" s="66"/>
+      <c r="AO22" s="66"/>
+      <c r="AP22" s="66"/>
+      <c r="AQ22" s="66"/>
+      <c r="AR22" s="66"/>
+      <c r="AS22" s="66"/>
+      <c r="AT22" s="66"/>
+      <c r="AU22" s="66"/>
+      <c r="AV22" s="66"/>
+      <c r="AW22" s="66"/>
+      <c r="AX22" s="66"/>
+      <c r="AY22" s="66"/>
+      <c r="AZ22" s="66"/>
+      <c r="BA22" s="66"/>
+      <c r="BB22" s="66"/>
+      <c r="BC22" s="66"/>
       <c r="BD22" s="45"/>
     </row>
     <row r="23" spans="18:56" ht="6" customHeight="1">
-      <c r="Z23" s="66" t="s">
+      <c r="Z23" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="AA23" s="66"/>
-      <c r="AB23" s="66"/>
-      <c r="AC23" s="66"/>
-      <c r="AD23" s="66"/>
-      <c r="AE23" s="66"/>
-      <c r="AF23" s="66"/>
-      <c r="AG23" s="66"/>
-      <c r="AH23" s="66"/>
-      <c r="AI23" s="66"/>
-      <c r="AJ23" s="66"/>
-      <c r="AK23" s="66"/>
-      <c r="AL23" s="66"/>
-      <c r="AM23" s="66"/>
-      <c r="AN23" s="66"/>
-      <c r="AO23" s="66"/>
-      <c r="AP23" s="66"/>
-      <c r="AQ23" s="66"/>
-      <c r="AR23" s="66"/>
-      <c r="AS23" s="66"/>
-      <c r="AT23" s="66"/>
-      <c r="AU23" s="66"/>
-      <c r="AV23" s="66"/>
-      <c r="AW23" s="66"/>
-      <c r="AX23" s="66"/>
-      <c r="AY23" s="66"/>
-      <c r="AZ23" s="66"/>
-      <c r="BA23" s="66"/>
-      <c r="BB23" s="66"/>
-      <c r="BC23" s="66"/>
+      <c r="AA23" s="67"/>
+      <c r="AB23" s="67"/>
+      <c r="AC23" s="67"/>
+      <c r="AD23" s="67"/>
+      <c r="AE23" s="67"/>
+      <c r="AF23" s="67"/>
+      <c r="AG23" s="67"/>
+      <c r="AH23" s="67"/>
+      <c r="AI23" s="67"/>
+      <c r="AJ23" s="67"/>
+      <c r="AK23" s="67"/>
+      <c r="AL23" s="67"/>
+      <c r="AM23" s="67"/>
+      <c r="AN23" s="67"/>
+      <c r="AO23" s="67"/>
+      <c r="AP23" s="67"/>
+      <c r="AQ23" s="67"/>
+      <c r="AR23" s="67"/>
+      <c r="AS23" s="67"/>
+      <c r="AT23" s="67"/>
+      <c r="AU23" s="67"/>
+      <c r="AV23" s="67"/>
+      <c r="AW23" s="67"/>
+      <c r="AX23" s="67"/>
+      <c r="AY23" s="67"/>
+      <c r="AZ23" s="67"/>
+      <c r="BA23" s="67"/>
+      <c r="BB23" s="67"/>
+      <c r="BC23" s="67"/>
       <c r="BD23" s="46"/>
     </row>
     <row r="24" spans="18:56" ht="6" customHeight="1">
-      <c r="Z24" s="66"/>
-      <c r="AA24" s="66"/>
-      <c r="AB24" s="66"/>
-      <c r="AC24" s="66"/>
-      <c r="AD24" s="66"/>
-      <c r="AE24" s="66"/>
-      <c r="AF24" s="66"/>
-      <c r="AG24" s="66"/>
-      <c r="AH24" s="66"/>
-      <c r="AI24" s="66"/>
-      <c r="AJ24" s="66"/>
-      <c r="AK24" s="66"/>
-      <c r="AL24" s="66"/>
-      <c r="AM24" s="66"/>
-      <c r="AN24" s="66"/>
-      <c r="AO24" s="66"/>
-      <c r="AP24" s="66"/>
-      <c r="AQ24" s="66"/>
-      <c r="AR24" s="66"/>
-      <c r="AS24" s="66"/>
-      <c r="AT24" s="66"/>
-      <c r="AU24" s="66"/>
-      <c r="AV24" s="66"/>
-      <c r="AW24" s="66"/>
-      <c r="AX24" s="66"/>
-      <c r="AY24" s="66"/>
-      <c r="AZ24" s="66"/>
-      <c r="BA24" s="66"/>
-      <c r="BB24" s="66"/>
-      <c r="BC24" s="66"/>
+      <c r="Z24" s="67"/>
+      <c r="AA24" s="67"/>
+      <c r="AB24" s="67"/>
+      <c r="AC24" s="67"/>
+      <c r="AD24" s="67"/>
+      <c r="AE24" s="67"/>
+      <c r="AF24" s="67"/>
+      <c r="AG24" s="67"/>
+      <c r="AH24" s="67"/>
+      <c r="AI24" s="67"/>
+      <c r="AJ24" s="67"/>
+      <c r="AK24" s="67"/>
+      <c r="AL24" s="67"/>
+      <c r="AM24" s="67"/>
+      <c r="AN24" s="67"/>
+      <c r="AO24" s="67"/>
+      <c r="AP24" s="67"/>
+      <c r="AQ24" s="67"/>
+      <c r="AR24" s="67"/>
+      <c r="AS24" s="67"/>
+      <c r="AT24" s="67"/>
+      <c r="AU24" s="67"/>
+      <c r="AV24" s="67"/>
+      <c r="AW24" s="67"/>
+      <c r="AX24" s="67"/>
+      <c r="AY24" s="67"/>
+      <c r="AZ24" s="67"/>
+      <c r="BA24" s="67"/>
+      <c r="BB24" s="67"/>
+      <c r="BC24" s="67"/>
       <c r="BD24" s="46"/>
     </row>
     <row r="25" spans="18:56" ht="6" customHeight="1"/>
     <row r="26" spans="18:56" ht="6" customHeight="1">
-      <c r="Z26" s="63" t="s">
+      <c r="Z26" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="AA26" s="63"/>
-      <c r="AB26" s="63"/>
-      <c r="AC26" s="63"/>
-      <c r="AD26" s="63"/>
-      <c r="AE26" s="63"/>
-      <c r="AF26" s="63"/>
-      <c r="AG26" s="63"/>
-      <c r="AH26" s="63"/>
-      <c r="AI26" s="63"/>
-      <c r="AJ26" s="63"/>
-      <c r="AK26" s="63"/>
-      <c r="AL26" s="63"/>
-      <c r="AM26" s="63"/>
-      <c r="AN26" s="63"/>
-      <c r="AO26" s="63"/>
-      <c r="AP26" s="63"/>
-      <c r="AQ26" s="63"/>
-      <c r="AR26" s="63"/>
-      <c r="AS26" s="63"/>
-      <c r="AT26" s="63"/>
-      <c r="AU26" s="63"/>
-      <c r="AV26" s="63"/>
-      <c r="AW26" s="63"/>
-      <c r="AX26" s="63"/>
-      <c r="AY26" s="63"/>
-      <c r="AZ26" s="63"/>
-      <c r="BA26" s="63"/>
-      <c r="BB26" s="63"/>
-      <c r="BC26" s="63"/>
+      <c r="AA26" s="57"/>
+      <c r="AB26" s="57"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="57"/>
+      <c r="AE26" s="57"/>
+      <c r="AF26" s="57"/>
+      <c r="AG26" s="57"/>
+      <c r="AH26" s="57"/>
+      <c r="AI26" s="57"/>
+      <c r="AJ26" s="57"/>
+      <c r="AK26" s="57"/>
+      <c r="AL26" s="57"/>
+      <c r="AM26" s="57"/>
+      <c r="AN26" s="57"/>
+      <c r="AO26" s="57"/>
+      <c r="AP26" s="57"/>
+      <c r="AQ26" s="57"/>
+      <c r="AR26" s="57"/>
+      <c r="AS26" s="57"/>
+      <c r="AT26" s="57"/>
+      <c r="AU26" s="57"/>
+      <c r="AV26" s="57"/>
+      <c r="AW26" s="57"/>
+      <c r="AX26" s="57"/>
+      <c r="AY26" s="57"/>
+      <c r="AZ26" s="57"/>
+      <c r="BA26" s="57"/>
+      <c r="BB26" s="57"/>
+      <c r="BC26" s="57"/>
       <c r="BD26" s="44"/>
     </row>
     <row r="27" spans="18:56" ht="6" customHeight="1">
-      <c r="Z27" s="63"/>
-      <c r="AA27" s="63"/>
-      <c r="AB27" s="63"/>
-      <c r="AC27" s="63"/>
-      <c r="AD27" s="63"/>
-      <c r="AE27" s="63"/>
-      <c r="AF27" s="63"/>
-      <c r="AG27" s="63"/>
-      <c r="AH27" s="63"/>
-      <c r="AI27" s="63"/>
-      <c r="AJ27" s="63"/>
-      <c r="AK27" s="63"/>
-      <c r="AL27" s="63"/>
-      <c r="AM27" s="63"/>
-      <c r="AN27" s="63"/>
-      <c r="AO27" s="63"/>
-      <c r="AP27" s="63"/>
-      <c r="AQ27" s="63"/>
-      <c r="AR27" s="63"/>
-      <c r="AS27" s="63"/>
-      <c r="AT27" s="63"/>
-      <c r="AU27" s="63"/>
-      <c r="AV27" s="63"/>
-      <c r="AW27" s="63"/>
-      <c r="AX27" s="63"/>
-      <c r="AY27" s="63"/>
-      <c r="AZ27" s="63"/>
-      <c r="BA27" s="63"/>
-      <c r="BB27" s="63"/>
-      <c r="BC27" s="63"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="57"/>
+      <c r="AB27" s="57"/>
+      <c r="AC27" s="57"/>
+      <c r="AD27" s="57"/>
+      <c r="AE27" s="57"/>
+      <c r="AF27" s="57"/>
+      <c r="AG27" s="57"/>
+      <c r="AH27" s="57"/>
+      <c r="AI27" s="57"/>
+      <c r="AJ27" s="57"/>
+      <c r="AK27" s="57"/>
+      <c r="AL27" s="57"/>
+      <c r="AM27" s="57"/>
+      <c r="AN27" s="57"/>
+      <c r="AO27" s="57"/>
+      <c r="AP27" s="57"/>
+      <c r="AQ27" s="57"/>
+      <c r="AR27" s="57"/>
+      <c r="AS27" s="57"/>
+      <c r="AT27" s="57"/>
+      <c r="AU27" s="57"/>
+      <c r="AV27" s="57"/>
+      <c r="AW27" s="57"/>
+      <c r="AX27" s="57"/>
+      <c r="AY27" s="57"/>
+      <c r="AZ27" s="57"/>
+      <c r="BA27" s="57"/>
+      <c r="BB27" s="57"/>
+      <c r="BC27" s="57"/>
       <c r="BD27" s="44"/>
     </row>
     <row r="28" spans="18:56" ht="6" customHeight="1">
@@ -14441,38 +14413,38 @@
       <c r="W32" s="39"/>
       <c r="X32" s="39"/>
       <c r="Y32" s="39"/>
-      <c r="Z32" s="60" t="s">
+      <c r="Z32" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="AA32" s="60"/>
-      <c r="AB32" s="60"/>
-      <c r="AC32" s="60"/>
-      <c r="AD32" s="60"/>
-      <c r="AE32" s="60"/>
-      <c r="AF32" s="60"/>
-      <c r="AG32" s="60"/>
-      <c r="AH32" s="60"/>
-      <c r="AI32" s="60"/>
-      <c r="AJ32" s="60"/>
-      <c r="AK32" s="60"/>
-      <c r="AL32" s="60"/>
-      <c r="AM32" s="60"/>
-      <c r="AN32" s="60"/>
-      <c r="AO32" s="60"/>
-      <c r="AP32" s="60"/>
-      <c r="AQ32" s="60"/>
-      <c r="AR32" s="60"/>
-      <c r="AS32" s="60"/>
-      <c r="AT32" s="60"/>
-      <c r="AU32" s="60"/>
-      <c r="AV32" s="60"/>
-      <c r="AW32" s="60"/>
-      <c r="AX32" s="60"/>
-      <c r="AY32" s="60"/>
-      <c r="AZ32" s="60"/>
-      <c r="BA32" s="60"/>
-      <c r="BB32" s="60"/>
-      <c r="BC32" s="60"/>
+      <c r="AA32" s="53"/>
+      <c r="AB32" s="53"/>
+      <c r="AC32" s="53"/>
+      <c r="AD32" s="53"/>
+      <c r="AE32" s="53"/>
+      <c r="AF32" s="53"/>
+      <c r="AG32" s="53"/>
+      <c r="AH32" s="53"/>
+      <c r="AI32" s="53"/>
+      <c r="AJ32" s="53"/>
+      <c r="AK32" s="53"/>
+      <c r="AL32" s="53"/>
+      <c r="AM32" s="53"/>
+      <c r="AN32" s="53"/>
+      <c r="AO32" s="53"/>
+      <c r="AP32" s="53"/>
+      <c r="AQ32" s="53"/>
+      <c r="AR32" s="53"/>
+      <c r="AS32" s="53"/>
+      <c r="AT32" s="53"/>
+      <c r="AU32" s="53"/>
+      <c r="AV32" s="53"/>
+      <c r="AW32" s="53"/>
+      <c r="AX32" s="53"/>
+      <c r="AY32" s="53"/>
+      <c r="AZ32" s="53"/>
+      <c r="BA32" s="53"/>
+      <c r="BB32" s="53"/>
+      <c r="BC32" s="53"/>
       <c r="BD32" s="48"/>
     </row>
     <row r="33" spans="18:99" s="1" customFormat="1" ht="6" customHeight="1">
@@ -14484,36 +14456,36 @@
       <c r="W33" s="35"/>
       <c r="X33" s="35"/>
       <c r="Y33" s="35"/>
-      <c r="Z33" s="61"/>
-      <c r="AA33" s="61"/>
-      <c r="AB33" s="61"/>
-      <c r="AC33" s="61"/>
-      <c r="AD33" s="61"/>
-      <c r="AE33" s="61"/>
-      <c r="AF33" s="61"/>
-      <c r="AG33" s="61"/>
-      <c r="AH33" s="61"/>
-      <c r="AI33" s="61"/>
-      <c r="AJ33" s="61"/>
-      <c r="AK33" s="61"/>
-      <c r="AL33" s="61"/>
-      <c r="AM33" s="61"/>
-      <c r="AN33" s="61"/>
-      <c r="AO33" s="61"/>
-      <c r="AP33" s="61"/>
-      <c r="AQ33" s="61"/>
-      <c r="AR33" s="61"/>
-      <c r="AS33" s="61"/>
-      <c r="AT33" s="61"/>
-      <c r="AU33" s="61"/>
-      <c r="AV33" s="61"/>
-      <c r="AW33" s="61"/>
-      <c r="AX33" s="61"/>
-      <c r="AY33" s="61"/>
-      <c r="AZ33" s="61"/>
-      <c r="BA33" s="61"/>
-      <c r="BB33" s="61"/>
-      <c r="BC33" s="61"/>
+      <c r="Z33" s="54"/>
+      <c r="AA33" s="54"/>
+      <c r="AB33" s="54"/>
+      <c r="AC33" s="54"/>
+      <c r="AD33" s="54"/>
+      <c r="AE33" s="54"/>
+      <c r="AF33" s="54"/>
+      <c r="AG33" s="54"/>
+      <c r="AH33" s="54"/>
+      <c r="AI33" s="54"/>
+      <c r="AJ33" s="54"/>
+      <c r="AK33" s="54"/>
+      <c r="AL33" s="54"/>
+      <c r="AM33" s="54"/>
+      <c r="AN33" s="54"/>
+      <c r="AO33" s="54"/>
+      <c r="AP33" s="54"/>
+      <c r="AQ33" s="54"/>
+      <c r="AR33" s="54"/>
+      <c r="AS33" s="54"/>
+      <c r="AT33" s="54"/>
+      <c r="AU33" s="54"/>
+      <c r="AV33" s="54"/>
+      <c r="AW33" s="54"/>
+      <c r="AX33" s="54"/>
+      <c r="AY33" s="54"/>
+      <c r="AZ33" s="54"/>
+      <c r="BA33" s="54"/>
+      <c r="BB33" s="54"/>
+      <c r="BC33" s="54"/>
       <c r="BD33" s="48"/>
       <c r="BE33" s="35"/>
       <c r="BF33" s="35"/>
@@ -14568,36 +14540,36 @@
       <c r="W34" s="35"/>
       <c r="X34" s="35"/>
       <c r="Y34" s="35"/>
-      <c r="Z34" s="61"/>
-      <c r="AA34" s="61"/>
-      <c r="AB34" s="61"/>
-      <c r="AC34" s="61"/>
-      <c r="AD34" s="61"/>
-      <c r="AE34" s="61"/>
-      <c r="AF34" s="61"/>
-      <c r="AG34" s="61"/>
-      <c r="AH34" s="61"/>
-      <c r="AI34" s="61"/>
-      <c r="AJ34" s="61"/>
-      <c r="AK34" s="61"/>
-      <c r="AL34" s="61"/>
-      <c r="AM34" s="61"/>
-      <c r="AN34" s="61"/>
-      <c r="AO34" s="61"/>
-      <c r="AP34" s="61"/>
-      <c r="AQ34" s="61"/>
-      <c r="AR34" s="61"/>
-      <c r="AS34" s="61"/>
-      <c r="AT34" s="61"/>
-      <c r="AU34" s="61"/>
-      <c r="AV34" s="61"/>
-      <c r="AW34" s="61"/>
-      <c r="AX34" s="61"/>
-      <c r="AY34" s="61"/>
-      <c r="AZ34" s="61"/>
-      <c r="BA34" s="61"/>
-      <c r="BB34" s="61"/>
-      <c r="BC34" s="61"/>
+      <c r="Z34" s="54"/>
+      <c r="AA34" s="54"/>
+      <c r="AB34" s="54"/>
+      <c r="AC34" s="54"/>
+      <c r="AD34" s="54"/>
+      <c r="AE34" s="54"/>
+      <c r="AF34" s="54"/>
+      <c r="AG34" s="54"/>
+      <c r="AH34" s="54"/>
+      <c r="AI34" s="54"/>
+      <c r="AJ34" s="54"/>
+      <c r="AK34" s="54"/>
+      <c r="AL34" s="54"/>
+      <c r="AM34" s="54"/>
+      <c r="AN34" s="54"/>
+      <c r="AO34" s="54"/>
+      <c r="AP34" s="54"/>
+      <c r="AQ34" s="54"/>
+      <c r="AR34" s="54"/>
+      <c r="AS34" s="54"/>
+      <c r="AT34" s="54"/>
+      <c r="AU34" s="54"/>
+      <c r="AV34" s="54"/>
+      <c r="AW34" s="54"/>
+      <c r="AX34" s="54"/>
+      <c r="AY34" s="54"/>
+      <c r="AZ34" s="54"/>
+      <c r="BA34" s="54"/>
+      <c r="BB34" s="54"/>
+      <c r="BC34" s="54"/>
       <c r="BD34" s="48"/>
       <c r="BE34" s="35"/>
       <c r="BF34" s="39"/>
@@ -14608,38 +14580,38 @@
       <c r="BK34" s="39"/>
       <c r="BL34" s="39"/>
       <c r="BM34" s="39"/>
-      <c r="BN34" s="52" t="s">
+      <c r="BN34" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="BO34" s="52"/>
-      <c r="BP34" s="52"/>
-      <c r="BQ34" s="52"/>
-      <c r="BR34" s="52"/>
-      <c r="BS34" s="52"/>
-      <c r="BT34" s="52"/>
-      <c r="BU34" s="52"/>
-      <c r="BV34" s="52"/>
-      <c r="BW34" s="52"/>
-      <c r="BX34" s="52"/>
-      <c r="BY34" s="52"/>
-      <c r="BZ34" s="52"/>
-      <c r="CA34" s="52"/>
-      <c r="CB34" s="52"/>
-      <c r="CC34" s="52"/>
-      <c r="CD34" s="52"/>
-      <c r="CE34" s="52"/>
-      <c r="CF34" s="52"/>
-      <c r="CG34" s="52"/>
-      <c r="CH34" s="52"/>
-      <c r="CI34" s="52"/>
-      <c r="CJ34" s="52"/>
-      <c r="CK34" s="52"/>
-      <c r="CL34" s="52"/>
-      <c r="CM34" s="52"/>
-      <c r="CN34" s="52"/>
-      <c r="CO34" s="52"/>
-      <c r="CP34" s="52"/>
-      <c r="CQ34" s="52"/>
+      <c r="BO34" s="60"/>
+      <c r="BP34" s="60"/>
+      <c r="BQ34" s="60"/>
+      <c r="BR34" s="60"/>
+      <c r="BS34" s="60"/>
+      <c r="BT34" s="60"/>
+      <c r="BU34" s="60"/>
+      <c r="BV34" s="60"/>
+      <c r="BW34" s="60"/>
+      <c r="BX34" s="60"/>
+      <c r="BY34" s="60"/>
+      <c r="BZ34" s="60"/>
+      <c r="CA34" s="60"/>
+      <c r="CB34" s="60"/>
+      <c r="CC34" s="60"/>
+      <c r="CD34" s="60"/>
+      <c r="CE34" s="60"/>
+      <c r="CF34" s="60"/>
+      <c r="CG34" s="60"/>
+      <c r="CH34" s="60"/>
+      <c r="CI34" s="60"/>
+      <c r="CJ34" s="60"/>
+      <c r="CK34" s="60"/>
+      <c r="CL34" s="60"/>
+      <c r="CM34" s="60"/>
+      <c r="CN34" s="60"/>
+      <c r="CO34" s="60"/>
+      <c r="CP34" s="60"/>
+      <c r="CQ34" s="60"/>
       <c r="CR34" s="41"/>
       <c r="CS34" s="41"/>
       <c r="CT34" s="41"/>
@@ -14654,36 +14626,36 @@
       <c r="W35" s="35"/>
       <c r="X35" s="35"/>
       <c r="Y35" s="35"/>
-      <c r="Z35" s="61"/>
-      <c r="AA35" s="61"/>
-      <c r="AB35" s="61"/>
-      <c r="AC35" s="61"/>
-      <c r="AD35" s="61"/>
-      <c r="AE35" s="61"/>
-      <c r="AF35" s="61"/>
-      <c r="AG35" s="61"/>
-      <c r="AH35" s="61"/>
-      <c r="AI35" s="61"/>
-      <c r="AJ35" s="61"/>
-      <c r="AK35" s="61"/>
-      <c r="AL35" s="61"/>
-      <c r="AM35" s="61"/>
-      <c r="AN35" s="61"/>
-      <c r="AO35" s="61"/>
-      <c r="AP35" s="61"/>
-      <c r="AQ35" s="61"/>
-      <c r="AR35" s="61"/>
-      <c r="AS35" s="61"/>
-      <c r="AT35" s="61"/>
-      <c r="AU35" s="61"/>
-      <c r="AV35" s="61"/>
-      <c r="AW35" s="61"/>
-      <c r="AX35" s="61"/>
-      <c r="AY35" s="61"/>
-      <c r="AZ35" s="61"/>
-      <c r="BA35" s="61"/>
-      <c r="BB35" s="61"/>
-      <c r="BC35" s="61"/>
+      <c r="Z35" s="54"/>
+      <c r="AA35" s="54"/>
+      <c r="AB35" s="54"/>
+      <c r="AC35" s="54"/>
+      <c r="AD35" s="54"/>
+      <c r="AE35" s="54"/>
+      <c r="AF35" s="54"/>
+      <c r="AG35" s="54"/>
+      <c r="AH35" s="54"/>
+      <c r="AI35" s="54"/>
+      <c r="AJ35" s="54"/>
+      <c r="AK35" s="54"/>
+      <c r="AL35" s="54"/>
+      <c r="AM35" s="54"/>
+      <c r="AN35" s="54"/>
+      <c r="AO35" s="54"/>
+      <c r="AP35" s="54"/>
+      <c r="AQ35" s="54"/>
+      <c r="AR35" s="54"/>
+      <c r="AS35" s="54"/>
+      <c r="AT35" s="54"/>
+      <c r="AU35" s="54"/>
+      <c r="AV35" s="54"/>
+      <c r="AW35" s="54"/>
+      <c r="AX35" s="54"/>
+      <c r="AY35" s="54"/>
+      <c r="AZ35" s="54"/>
+      <c r="BA35" s="54"/>
+      <c r="BB35" s="54"/>
+      <c r="BC35" s="54"/>
       <c r="BD35" s="48"/>
       <c r="BE35" s="35"/>
       <c r="BF35" s="35"/>
@@ -14694,36 +14666,36 @@
       <c r="BK35" s="35"/>
       <c r="BL35" s="35"/>
       <c r="BM35" s="35"/>
-      <c r="BN35" s="53"/>
-      <c r="BO35" s="53"/>
-      <c r="BP35" s="53"/>
-      <c r="BQ35" s="53"/>
-      <c r="BR35" s="53"/>
-      <c r="BS35" s="53"/>
-      <c r="BT35" s="53"/>
-      <c r="BU35" s="53"/>
-      <c r="BV35" s="53"/>
-      <c r="BW35" s="53"/>
-      <c r="BX35" s="53"/>
-      <c r="BY35" s="53"/>
-      <c r="BZ35" s="53"/>
-      <c r="CA35" s="53"/>
-      <c r="CB35" s="53"/>
-      <c r="CC35" s="53"/>
-      <c r="CD35" s="53"/>
-      <c r="CE35" s="53"/>
-      <c r="CF35" s="53"/>
-      <c r="CG35" s="53"/>
-      <c r="CH35" s="53"/>
-      <c r="CI35" s="53"/>
-      <c r="CJ35" s="53"/>
-      <c r="CK35" s="53"/>
-      <c r="CL35" s="53"/>
-      <c r="CM35" s="53"/>
-      <c r="CN35" s="53"/>
-      <c r="CO35" s="53"/>
-      <c r="CP35" s="53"/>
-      <c r="CQ35" s="53"/>
+      <c r="BN35" s="55"/>
+      <c r="BO35" s="55"/>
+      <c r="BP35" s="55"/>
+      <c r="BQ35" s="55"/>
+      <c r="BR35" s="55"/>
+      <c r="BS35" s="55"/>
+      <c r="BT35" s="55"/>
+      <c r="BU35" s="55"/>
+      <c r="BV35" s="55"/>
+      <c r="BW35" s="55"/>
+      <c r="BX35" s="55"/>
+      <c r="BY35" s="55"/>
+      <c r="BZ35" s="55"/>
+      <c r="CA35" s="55"/>
+      <c r="CB35" s="55"/>
+      <c r="CC35" s="55"/>
+      <c r="CD35" s="55"/>
+      <c r="CE35" s="55"/>
+      <c r="CF35" s="55"/>
+      <c r="CG35" s="55"/>
+      <c r="CH35" s="55"/>
+      <c r="CI35" s="55"/>
+      <c r="CJ35" s="55"/>
+      <c r="CK35" s="55"/>
+      <c r="CL35" s="55"/>
+      <c r="CM35" s="55"/>
+      <c r="CN35" s="55"/>
+      <c r="CO35" s="55"/>
+      <c r="CP35" s="55"/>
+      <c r="CQ35" s="55"/>
       <c r="CR35" s="41"/>
       <c r="CS35" s="41"/>
       <c r="CT35" s="41"/>
@@ -14738,36 +14710,36 @@
       <c r="W36" s="35"/>
       <c r="X36" s="35"/>
       <c r="Y36" s="35"/>
-      <c r="Z36" s="61"/>
-      <c r="AA36" s="61"/>
-      <c r="AB36" s="61"/>
-      <c r="AC36" s="61"/>
-      <c r="AD36" s="61"/>
-      <c r="AE36" s="61"/>
-      <c r="AF36" s="61"/>
-      <c r="AG36" s="61"/>
-      <c r="AH36" s="61"/>
-      <c r="AI36" s="61"/>
-      <c r="AJ36" s="61"/>
-      <c r="AK36" s="61"/>
-      <c r="AL36" s="61"/>
-      <c r="AM36" s="61"/>
-      <c r="AN36" s="61"/>
-      <c r="AO36" s="61"/>
-      <c r="AP36" s="61"/>
-      <c r="AQ36" s="61"/>
-      <c r="AR36" s="61"/>
-      <c r="AS36" s="61"/>
-      <c r="AT36" s="61"/>
-      <c r="AU36" s="61"/>
-      <c r="AV36" s="61"/>
-      <c r="AW36" s="61"/>
-      <c r="AX36" s="61"/>
-      <c r="AY36" s="61"/>
-      <c r="AZ36" s="61"/>
-      <c r="BA36" s="61"/>
-      <c r="BB36" s="61"/>
-      <c r="BC36" s="61"/>
+      <c r="Z36" s="54"/>
+      <c r="AA36" s="54"/>
+      <c r="AB36" s="54"/>
+      <c r="AC36" s="54"/>
+      <c r="AD36" s="54"/>
+      <c r="AE36" s="54"/>
+      <c r="AF36" s="54"/>
+      <c r="AG36" s="54"/>
+      <c r="AH36" s="54"/>
+      <c r="AI36" s="54"/>
+      <c r="AJ36" s="54"/>
+      <c r="AK36" s="54"/>
+      <c r="AL36" s="54"/>
+      <c r="AM36" s="54"/>
+      <c r="AN36" s="54"/>
+      <c r="AO36" s="54"/>
+      <c r="AP36" s="54"/>
+      <c r="AQ36" s="54"/>
+      <c r="AR36" s="54"/>
+      <c r="AS36" s="54"/>
+      <c r="AT36" s="54"/>
+      <c r="AU36" s="54"/>
+      <c r="AV36" s="54"/>
+      <c r="AW36" s="54"/>
+      <c r="AX36" s="54"/>
+      <c r="AY36" s="54"/>
+      <c r="AZ36" s="54"/>
+      <c r="BA36" s="54"/>
+      <c r="BB36" s="54"/>
+      <c r="BC36" s="54"/>
       <c r="BD36" s="48"/>
       <c r="BE36" s="35"/>
       <c r="BF36" s="35"/>
@@ -14778,36 +14750,36 @@
       <c r="BK36" s="35"/>
       <c r="BL36" s="35"/>
       <c r="BM36" s="35"/>
-      <c r="BN36" s="53"/>
-      <c r="BO36" s="53"/>
-      <c r="BP36" s="53"/>
-      <c r="BQ36" s="53"/>
-      <c r="BR36" s="53"/>
-      <c r="BS36" s="53"/>
-      <c r="BT36" s="53"/>
-      <c r="BU36" s="53"/>
-      <c r="BV36" s="53"/>
-      <c r="BW36" s="53"/>
-      <c r="BX36" s="53"/>
-      <c r="BY36" s="53"/>
-      <c r="BZ36" s="53"/>
-      <c r="CA36" s="53"/>
-      <c r="CB36" s="53"/>
-      <c r="CC36" s="53"/>
-      <c r="CD36" s="53"/>
-      <c r="CE36" s="53"/>
-      <c r="CF36" s="53"/>
-      <c r="CG36" s="53"/>
-      <c r="CH36" s="53"/>
-      <c r="CI36" s="53"/>
-      <c r="CJ36" s="53"/>
-      <c r="CK36" s="53"/>
-      <c r="CL36" s="53"/>
-      <c r="CM36" s="53"/>
-      <c r="CN36" s="53"/>
-      <c r="CO36" s="53"/>
-      <c r="CP36" s="53"/>
-      <c r="CQ36" s="53"/>
+      <c r="BN36" s="55"/>
+      <c r="BO36" s="55"/>
+      <c r="BP36" s="55"/>
+      <c r="BQ36" s="55"/>
+      <c r="BR36" s="55"/>
+      <c r="BS36" s="55"/>
+      <c r="BT36" s="55"/>
+      <c r="BU36" s="55"/>
+      <c r="BV36" s="55"/>
+      <c r="BW36" s="55"/>
+      <c r="BX36" s="55"/>
+      <c r="BY36" s="55"/>
+      <c r="BZ36" s="55"/>
+      <c r="CA36" s="55"/>
+      <c r="CB36" s="55"/>
+      <c r="CC36" s="55"/>
+      <c r="CD36" s="55"/>
+      <c r="CE36" s="55"/>
+      <c r="CF36" s="55"/>
+      <c r="CG36" s="55"/>
+      <c r="CH36" s="55"/>
+      <c r="CI36" s="55"/>
+      <c r="CJ36" s="55"/>
+      <c r="CK36" s="55"/>
+      <c r="CL36" s="55"/>
+      <c r="CM36" s="55"/>
+      <c r="CN36" s="55"/>
+      <c r="CO36" s="55"/>
+      <c r="CP36" s="55"/>
+      <c r="CQ36" s="55"/>
       <c r="CR36" s="41"/>
       <c r="CS36" s="41"/>
       <c r="CT36" s="41"/>
@@ -14822,38 +14794,38 @@
       <c r="W37" s="35"/>
       <c r="X37" s="35"/>
       <c r="Y37" s="35"/>
-      <c r="Z37" s="62" t="s">
+      <c r="Z37" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="AA37" s="62"/>
-      <c r="AB37" s="62"/>
-      <c r="AC37" s="62"/>
-      <c r="AD37" s="62"/>
-      <c r="AE37" s="62"/>
-      <c r="AF37" s="62"/>
-      <c r="AG37" s="62"/>
-      <c r="AH37" s="62"/>
-      <c r="AI37" s="62"/>
-      <c r="AJ37" s="62"/>
-      <c r="AK37" s="62"/>
-      <c r="AL37" s="62"/>
-      <c r="AM37" s="62"/>
-      <c r="AN37" s="62"/>
-      <c r="AO37" s="62"/>
-      <c r="AP37" s="62"/>
-      <c r="AQ37" s="62"/>
-      <c r="AR37" s="62"/>
-      <c r="AS37" s="62"/>
-      <c r="AT37" s="62"/>
-      <c r="AU37" s="62"/>
-      <c r="AV37" s="62"/>
-      <c r="AW37" s="62"/>
-      <c r="AX37" s="62"/>
-      <c r="AY37" s="62"/>
-      <c r="AZ37" s="62"/>
-      <c r="BA37" s="62"/>
-      <c r="BB37" s="62"/>
-      <c r="BC37" s="62"/>
+      <c r="AA37" s="59"/>
+      <c r="AB37" s="59"/>
+      <c r="AC37" s="59"/>
+      <c r="AD37" s="59"/>
+      <c r="AE37" s="59"/>
+      <c r="AF37" s="59"/>
+      <c r="AG37" s="59"/>
+      <c r="AH37" s="59"/>
+      <c r="AI37" s="59"/>
+      <c r="AJ37" s="59"/>
+      <c r="AK37" s="59"/>
+      <c r="AL37" s="59"/>
+      <c r="AM37" s="59"/>
+      <c r="AN37" s="59"/>
+      <c r="AO37" s="59"/>
+      <c r="AP37" s="59"/>
+      <c r="AQ37" s="59"/>
+      <c r="AR37" s="59"/>
+      <c r="AS37" s="59"/>
+      <c r="AT37" s="59"/>
+      <c r="AU37" s="59"/>
+      <c r="AV37" s="59"/>
+      <c r="AW37" s="59"/>
+      <c r="AX37" s="59"/>
+      <c r="AY37" s="59"/>
+      <c r="AZ37" s="59"/>
+      <c r="BA37" s="59"/>
+      <c r="BB37" s="59"/>
+      <c r="BC37" s="59"/>
       <c r="BD37" s="43"/>
       <c r="BE37" s="35"/>
       <c r="BF37" s="35"/>
@@ -14864,38 +14836,38 @@
       <c r="BK37" s="35"/>
       <c r="BL37" s="35"/>
       <c r="BM37" s="35"/>
-      <c r="BN37" s="54" t="s">
+      <c r="BN37" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="BO37" s="54"/>
-      <c r="BP37" s="54"/>
-      <c r="BQ37" s="54"/>
-      <c r="BR37" s="54"/>
-      <c r="BS37" s="54"/>
-      <c r="BT37" s="54"/>
-      <c r="BU37" s="54"/>
-      <c r="BV37" s="54"/>
-      <c r="BW37" s="54"/>
-      <c r="BX37" s="54"/>
-      <c r="BY37" s="54"/>
-      <c r="BZ37" s="54"/>
-      <c r="CA37" s="54"/>
-      <c r="CB37" s="54"/>
-      <c r="CC37" s="54"/>
-      <c r="CD37" s="54"/>
-      <c r="CE37" s="54"/>
-      <c r="CF37" s="54"/>
-      <c r="CG37" s="54"/>
-      <c r="CH37" s="54"/>
-      <c r="CI37" s="54"/>
-      <c r="CJ37" s="54"/>
-      <c r="CK37" s="54"/>
-      <c r="CL37" s="54"/>
-      <c r="CM37" s="54"/>
-      <c r="CN37" s="54"/>
-      <c r="CO37" s="54"/>
-      <c r="CP37" s="54"/>
-      <c r="CQ37" s="54"/>
+      <c r="BO37" s="56"/>
+      <c r="BP37" s="56"/>
+      <c r="BQ37" s="56"/>
+      <c r="BR37" s="56"/>
+      <c r="BS37" s="56"/>
+      <c r="BT37" s="56"/>
+      <c r="BU37" s="56"/>
+      <c r="BV37" s="56"/>
+      <c r="BW37" s="56"/>
+      <c r="BX37" s="56"/>
+      <c r="BY37" s="56"/>
+      <c r="BZ37" s="56"/>
+      <c r="CA37" s="56"/>
+      <c r="CB37" s="56"/>
+      <c r="CC37" s="56"/>
+      <c r="CD37" s="56"/>
+      <c r="CE37" s="56"/>
+      <c r="CF37" s="56"/>
+      <c r="CG37" s="56"/>
+      <c r="CH37" s="56"/>
+      <c r="CI37" s="56"/>
+      <c r="CJ37" s="56"/>
+      <c r="CK37" s="56"/>
+      <c r="CL37" s="56"/>
+      <c r="CM37" s="56"/>
+      <c r="CN37" s="56"/>
+      <c r="CO37" s="56"/>
+      <c r="CP37" s="56"/>
+      <c r="CQ37" s="56"/>
       <c r="CR37" s="42"/>
       <c r="CS37" s="42"/>
       <c r="CT37" s="42"/>
@@ -14910,36 +14882,36 @@
       <c r="W38" s="35"/>
       <c r="X38" s="35"/>
       <c r="Y38" s="35"/>
-      <c r="Z38" s="62"/>
-      <c r="AA38" s="62"/>
-      <c r="AB38" s="62"/>
-      <c r="AC38" s="62"/>
-      <c r="AD38" s="62"/>
-      <c r="AE38" s="62"/>
-      <c r="AF38" s="62"/>
-      <c r="AG38" s="62"/>
-      <c r="AH38" s="62"/>
-      <c r="AI38" s="62"/>
-      <c r="AJ38" s="62"/>
-      <c r="AK38" s="62"/>
-      <c r="AL38" s="62"/>
-      <c r="AM38" s="62"/>
-      <c r="AN38" s="62"/>
-      <c r="AO38" s="62"/>
-      <c r="AP38" s="62"/>
-      <c r="AQ38" s="62"/>
-      <c r="AR38" s="62"/>
-      <c r="AS38" s="62"/>
-      <c r="AT38" s="62"/>
-      <c r="AU38" s="62"/>
-      <c r="AV38" s="62"/>
-      <c r="AW38" s="62"/>
-      <c r="AX38" s="62"/>
-      <c r="AY38" s="62"/>
-      <c r="AZ38" s="62"/>
-      <c r="BA38" s="62"/>
-      <c r="BB38" s="62"/>
-      <c r="BC38" s="62"/>
+      <c r="Z38" s="59"/>
+      <c r="AA38" s="59"/>
+      <c r="AB38" s="59"/>
+      <c r="AC38" s="59"/>
+      <c r="AD38" s="59"/>
+      <c r="AE38" s="59"/>
+      <c r="AF38" s="59"/>
+      <c r="AG38" s="59"/>
+      <c r="AH38" s="59"/>
+      <c r="AI38" s="59"/>
+      <c r="AJ38" s="59"/>
+      <c r="AK38" s="59"/>
+      <c r="AL38" s="59"/>
+      <c r="AM38" s="59"/>
+      <c r="AN38" s="59"/>
+      <c r="AO38" s="59"/>
+      <c r="AP38" s="59"/>
+      <c r="AQ38" s="59"/>
+      <c r="AR38" s="59"/>
+      <c r="AS38" s="59"/>
+      <c r="AT38" s="59"/>
+      <c r="AU38" s="59"/>
+      <c r="AV38" s="59"/>
+      <c r="AW38" s="59"/>
+      <c r="AX38" s="59"/>
+      <c r="AY38" s="59"/>
+      <c r="AZ38" s="59"/>
+      <c r="BA38" s="59"/>
+      <c r="BB38" s="59"/>
+      <c r="BC38" s="59"/>
       <c r="BD38" s="43"/>
       <c r="BE38" s="35"/>
       <c r="BF38" s="35"/>
@@ -14950,36 +14922,36 @@
       <c r="BK38" s="35"/>
       <c r="BL38" s="35"/>
       <c r="BM38" s="35"/>
-      <c r="BN38" s="54"/>
-      <c r="BO38" s="54"/>
-      <c r="BP38" s="54"/>
-      <c r="BQ38" s="54"/>
-      <c r="BR38" s="54"/>
-      <c r="BS38" s="54"/>
-      <c r="BT38" s="54"/>
-      <c r="BU38" s="54"/>
-      <c r="BV38" s="54"/>
-      <c r="BW38" s="54"/>
-      <c r="BX38" s="54"/>
-      <c r="BY38" s="54"/>
-      <c r="BZ38" s="54"/>
-      <c r="CA38" s="54"/>
-      <c r="CB38" s="54"/>
-      <c r="CC38" s="54"/>
-      <c r="CD38" s="54"/>
-      <c r="CE38" s="54"/>
-      <c r="CF38" s="54"/>
-      <c r="CG38" s="54"/>
-      <c r="CH38" s="54"/>
-      <c r="CI38" s="54"/>
-      <c r="CJ38" s="54"/>
-      <c r="CK38" s="54"/>
-      <c r="CL38" s="54"/>
-      <c r="CM38" s="54"/>
-      <c r="CN38" s="54"/>
-      <c r="CO38" s="54"/>
-      <c r="CP38" s="54"/>
-      <c r="CQ38" s="54"/>
+      <c r="BN38" s="56"/>
+      <c r="BO38" s="56"/>
+      <c r="BP38" s="56"/>
+      <c r="BQ38" s="56"/>
+      <c r="BR38" s="56"/>
+      <c r="BS38" s="56"/>
+      <c r="BT38" s="56"/>
+      <c r="BU38" s="56"/>
+      <c r="BV38" s="56"/>
+      <c r="BW38" s="56"/>
+      <c r="BX38" s="56"/>
+      <c r="BY38" s="56"/>
+      <c r="BZ38" s="56"/>
+      <c r="CA38" s="56"/>
+      <c r="CB38" s="56"/>
+      <c r="CC38" s="56"/>
+      <c r="CD38" s="56"/>
+      <c r="CE38" s="56"/>
+      <c r="CF38" s="56"/>
+      <c r="CG38" s="56"/>
+      <c r="CH38" s="56"/>
+      <c r="CI38" s="56"/>
+      <c r="CJ38" s="56"/>
+      <c r="CK38" s="56"/>
+      <c r="CL38" s="56"/>
+      <c r="CM38" s="56"/>
+      <c r="CN38" s="56"/>
+      <c r="CO38" s="56"/>
+      <c r="CP38" s="56"/>
+      <c r="CQ38" s="56"/>
       <c r="CR38" s="42"/>
       <c r="CS38" s="42"/>
       <c r="CT38" s="42"/>
@@ -14994,36 +14966,36 @@
       <c r="W39" s="35"/>
       <c r="X39" s="35"/>
       <c r="Y39" s="35"/>
-      <c r="Z39" s="62"/>
-      <c r="AA39" s="62"/>
-      <c r="AB39" s="62"/>
-      <c r="AC39" s="62"/>
-      <c r="AD39" s="62"/>
-      <c r="AE39" s="62"/>
-      <c r="AF39" s="62"/>
-      <c r="AG39" s="62"/>
-      <c r="AH39" s="62"/>
-      <c r="AI39" s="62"/>
-      <c r="AJ39" s="62"/>
-      <c r="AK39" s="62"/>
-      <c r="AL39" s="62"/>
-      <c r="AM39" s="62"/>
-      <c r="AN39" s="62"/>
-      <c r="AO39" s="62"/>
-      <c r="AP39" s="62"/>
-      <c r="AQ39" s="62"/>
-      <c r="AR39" s="62"/>
-      <c r="AS39" s="62"/>
-      <c r="AT39" s="62"/>
-      <c r="AU39" s="62"/>
-      <c r="AV39" s="62"/>
-      <c r="AW39" s="62"/>
-      <c r="AX39" s="62"/>
-      <c r="AY39" s="62"/>
-      <c r="AZ39" s="62"/>
-      <c r="BA39" s="62"/>
-      <c r="BB39" s="62"/>
-      <c r="BC39" s="62"/>
+      <c r="Z39" s="59"/>
+      <c r="AA39" s="59"/>
+      <c r="AB39" s="59"/>
+      <c r="AC39" s="59"/>
+      <c r="AD39" s="59"/>
+      <c r="AE39" s="59"/>
+      <c r="AF39" s="59"/>
+      <c r="AG39" s="59"/>
+      <c r="AH39" s="59"/>
+      <c r="AI39" s="59"/>
+      <c r="AJ39" s="59"/>
+      <c r="AK39" s="59"/>
+      <c r="AL39" s="59"/>
+      <c r="AM39" s="59"/>
+      <c r="AN39" s="59"/>
+      <c r="AO39" s="59"/>
+      <c r="AP39" s="59"/>
+      <c r="AQ39" s="59"/>
+      <c r="AR39" s="59"/>
+      <c r="AS39" s="59"/>
+      <c r="AT39" s="59"/>
+      <c r="AU39" s="59"/>
+      <c r="AV39" s="59"/>
+      <c r="AW39" s="59"/>
+      <c r="AX39" s="59"/>
+      <c r="AY39" s="59"/>
+      <c r="AZ39" s="59"/>
+      <c r="BA39" s="59"/>
+      <c r="BB39" s="59"/>
+      <c r="BC39" s="59"/>
       <c r="BD39" s="43"/>
       <c r="BE39" s="35"/>
       <c r="BF39" s="35"/>
@@ -15078,38 +15050,38 @@
       <c r="W40" s="35"/>
       <c r="X40" s="35"/>
       <c r="Y40" s="35"/>
-      <c r="Z40" s="63" t="s">
+      <c r="Z40" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="AA40" s="63"/>
-      <c r="AB40" s="63"/>
-      <c r="AC40" s="63"/>
-      <c r="AD40" s="63"/>
-      <c r="AE40" s="63"/>
-      <c r="AF40" s="63"/>
-      <c r="AG40" s="63"/>
-      <c r="AH40" s="63"/>
-      <c r="AI40" s="63"/>
-      <c r="AJ40" s="63"/>
-      <c r="AK40" s="63"/>
-      <c r="AL40" s="63"/>
-      <c r="AM40" s="63"/>
-      <c r="AN40" s="63"/>
-      <c r="AO40" s="63"/>
-      <c r="AP40" s="63"/>
-      <c r="AQ40" s="63"/>
-      <c r="AR40" s="63"/>
-      <c r="AS40" s="63"/>
-      <c r="AT40" s="63"/>
-      <c r="AU40" s="63"/>
-      <c r="AV40" s="63"/>
-      <c r="AW40" s="63"/>
-      <c r="AX40" s="63"/>
-      <c r="AY40" s="63"/>
-      <c r="AZ40" s="63"/>
-      <c r="BA40" s="63"/>
-      <c r="BB40" s="63"/>
-      <c r="BC40" s="63"/>
+      <c r="AA40" s="57"/>
+      <c r="AB40" s="57"/>
+      <c r="AC40" s="57"/>
+      <c r="AD40" s="57"/>
+      <c r="AE40" s="57"/>
+      <c r="AF40" s="57"/>
+      <c r="AG40" s="57"/>
+      <c r="AH40" s="57"/>
+      <c r="AI40" s="57"/>
+      <c r="AJ40" s="57"/>
+      <c r="AK40" s="57"/>
+      <c r="AL40" s="57"/>
+      <c r="AM40" s="57"/>
+      <c r="AN40" s="57"/>
+      <c r="AO40" s="57"/>
+      <c r="AP40" s="57"/>
+      <c r="AQ40" s="57"/>
+      <c r="AR40" s="57"/>
+      <c r="AS40" s="57"/>
+      <c r="AT40" s="57"/>
+      <c r="AU40" s="57"/>
+      <c r="AV40" s="57"/>
+      <c r="AW40" s="57"/>
+      <c r="AX40" s="57"/>
+      <c r="AY40" s="57"/>
+      <c r="AZ40" s="57"/>
+      <c r="BA40" s="57"/>
+      <c r="BB40" s="57"/>
+      <c r="BC40" s="57"/>
       <c r="BD40" s="44"/>
       <c r="BE40" s="35"/>
       <c r="BF40" s="35"/>
@@ -15120,38 +15092,38 @@
       <c r="BK40" s="35"/>
       <c r="BL40" s="35"/>
       <c r="BM40" s="35"/>
-      <c r="BN40" s="53" t="s">
+      <c r="BN40" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="BO40" s="53"/>
-      <c r="BP40" s="53"/>
-      <c r="BQ40" s="53"/>
-      <c r="BR40" s="53"/>
-      <c r="BS40" s="53"/>
-      <c r="BT40" s="53"/>
-      <c r="BU40" s="53"/>
-      <c r="BV40" s="53"/>
-      <c r="BW40" s="53"/>
-      <c r="BX40" s="53"/>
-      <c r="BY40" s="53"/>
-      <c r="BZ40" s="53"/>
-      <c r="CA40" s="53"/>
-      <c r="CB40" s="53"/>
-      <c r="CC40" s="53"/>
-      <c r="CD40" s="53"/>
-      <c r="CE40" s="53"/>
-      <c r="CF40" s="53"/>
-      <c r="CG40" s="53"/>
-      <c r="CH40" s="53"/>
-      <c r="CI40" s="53"/>
-      <c r="CJ40" s="53"/>
-      <c r="CK40" s="53"/>
-      <c r="CL40" s="53"/>
-      <c r="CM40" s="53"/>
-      <c r="CN40" s="53"/>
-      <c r="CO40" s="53"/>
-      <c r="CP40" s="53"/>
-      <c r="CQ40" s="53"/>
+      <c r="BO40" s="55"/>
+      <c r="BP40" s="55"/>
+      <c r="BQ40" s="55"/>
+      <c r="BR40" s="55"/>
+      <c r="BS40" s="55"/>
+      <c r="BT40" s="55"/>
+      <c r="BU40" s="55"/>
+      <c r="BV40" s="55"/>
+      <c r="BW40" s="55"/>
+      <c r="BX40" s="55"/>
+      <c r="BY40" s="55"/>
+      <c r="BZ40" s="55"/>
+      <c r="CA40" s="55"/>
+      <c r="CB40" s="55"/>
+      <c r="CC40" s="55"/>
+      <c r="CD40" s="55"/>
+      <c r="CE40" s="55"/>
+      <c r="CF40" s="55"/>
+      <c r="CG40" s="55"/>
+      <c r="CH40" s="55"/>
+      <c r="CI40" s="55"/>
+      <c r="CJ40" s="55"/>
+      <c r="CK40" s="55"/>
+      <c r="CL40" s="55"/>
+      <c r="CM40" s="55"/>
+      <c r="CN40" s="55"/>
+      <c r="CO40" s="55"/>
+      <c r="CP40" s="55"/>
+      <c r="CQ40" s="55"/>
       <c r="CR40" s="41"/>
       <c r="CS40" s="41"/>
       <c r="CT40" s="41"/>
@@ -15166,36 +15138,36 @@
       <c r="W41" s="35"/>
       <c r="X41" s="35"/>
       <c r="Y41" s="35"/>
-      <c r="Z41" s="63"/>
-      <c r="AA41" s="63"/>
-      <c r="AB41" s="63"/>
-      <c r="AC41" s="63"/>
-      <c r="AD41" s="63"/>
-      <c r="AE41" s="63"/>
-      <c r="AF41" s="63"/>
-      <c r="AG41" s="63"/>
-      <c r="AH41" s="63"/>
-      <c r="AI41" s="63"/>
-      <c r="AJ41" s="63"/>
-      <c r="AK41" s="63"/>
-      <c r="AL41" s="63"/>
-      <c r="AM41" s="63"/>
-      <c r="AN41" s="63"/>
-      <c r="AO41" s="63"/>
-      <c r="AP41" s="63"/>
-      <c r="AQ41" s="63"/>
-      <c r="AR41" s="63"/>
-      <c r="AS41" s="63"/>
-      <c r="AT41" s="63"/>
-      <c r="AU41" s="63"/>
-      <c r="AV41" s="63"/>
-      <c r="AW41" s="63"/>
-      <c r="AX41" s="63"/>
-      <c r="AY41" s="63"/>
-      <c r="AZ41" s="63"/>
-      <c r="BA41" s="63"/>
-      <c r="BB41" s="63"/>
-      <c r="BC41" s="63"/>
+      <c r="Z41" s="57"/>
+      <c r="AA41" s="57"/>
+      <c r="AB41" s="57"/>
+      <c r="AC41" s="57"/>
+      <c r="AD41" s="57"/>
+      <c r="AE41" s="57"/>
+      <c r="AF41" s="57"/>
+      <c r="AG41" s="57"/>
+      <c r="AH41" s="57"/>
+      <c r="AI41" s="57"/>
+      <c r="AJ41" s="57"/>
+      <c r="AK41" s="57"/>
+      <c r="AL41" s="57"/>
+      <c r="AM41" s="57"/>
+      <c r="AN41" s="57"/>
+      <c r="AO41" s="57"/>
+      <c r="AP41" s="57"/>
+      <c r="AQ41" s="57"/>
+      <c r="AR41" s="57"/>
+      <c r="AS41" s="57"/>
+      <c r="AT41" s="57"/>
+      <c r="AU41" s="57"/>
+      <c r="AV41" s="57"/>
+      <c r="AW41" s="57"/>
+      <c r="AX41" s="57"/>
+      <c r="AY41" s="57"/>
+      <c r="AZ41" s="57"/>
+      <c r="BA41" s="57"/>
+      <c r="BB41" s="57"/>
+      <c r="BC41" s="57"/>
       <c r="BD41" s="44"/>
       <c r="BE41" s="35"/>
       <c r="BF41" s="35"/>
@@ -15206,36 +15178,36 @@
       <c r="BK41" s="35"/>
       <c r="BL41" s="35"/>
       <c r="BM41" s="35"/>
-      <c r="BN41" s="53"/>
-      <c r="BO41" s="53"/>
-      <c r="BP41" s="53"/>
-      <c r="BQ41" s="53"/>
-      <c r="BR41" s="53"/>
-      <c r="BS41" s="53"/>
-      <c r="BT41" s="53"/>
-      <c r="BU41" s="53"/>
-      <c r="BV41" s="53"/>
-      <c r="BW41" s="53"/>
-      <c r="BX41" s="53"/>
-      <c r="BY41" s="53"/>
-      <c r="BZ41" s="53"/>
-      <c r="CA41" s="53"/>
-      <c r="CB41" s="53"/>
-      <c r="CC41" s="53"/>
-      <c r="CD41" s="53"/>
-      <c r="CE41" s="53"/>
-      <c r="CF41" s="53"/>
-      <c r="CG41" s="53"/>
-      <c r="CH41" s="53"/>
-      <c r="CI41" s="53"/>
-      <c r="CJ41" s="53"/>
-      <c r="CK41" s="53"/>
-      <c r="CL41" s="53"/>
-      <c r="CM41" s="53"/>
-      <c r="CN41" s="53"/>
-      <c r="CO41" s="53"/>
-      <c r="CP41" s="53"/>
-      <c r="CQ41" s="53"/>
+      <c r="BN41" s="55"/>
+      <c r="BO41" s="55"/>
+      <c r="BP41" s="55"/>
+      <c r="BQ41" s="55"/>
+      <c r="BR41" s="55"/>
+      <c r="BS41" s="55"/>
+      <c r="BT41" s="55"/>
+      <c r="BU41" s="55"/>
+      <c r="BV41" s="55"/>
+      <c r="BW41" s="55"/>
+      <c r="BX41" s="55"/>
+      <c r="BY41" s="55"/>
+      <c r="BZ41" s="55"/>
+      <c r="CA41" s="55"/>
+      <c r="CB41" s="55"/>
+      <c r="CC41" s="55"/>
+      <c r="CD41" s="55"/>
+      <c r="CE41" s="55"/>
+      <c r="CF41" s="55"/>
+      <c r="CG41" s="55"/>
+      <c r="CH41" s="55"/>
+      <c r="CI41" s="55"/>
+      <c r="CJ41" s="55"/>
+      <c r="CK41" s="55"/>
+      <c r="CL41" s="55"/>
+      <c r="CM41" s="55"/>
+      <c r="CN41" s="55"/>
+      <c r="CO41" s="55"/>
+      <c r="CP41" s="55"/>
+      <c r="CQ41" s="55"/>
       <c r="CR41" s="41"/>
       <c r="CS41" s="41"/>
       <c r="CT41" s="41"/>
@@ -15290,36 +15262,36 @@
       <c r="BK42" s="35"/>
       <c r="BL42" s="35"/>
       <c r="BM42" s="35"/>
-      <c r="BN42" s="53"/>
-      <c r="BO42" s="53"/>
-      <c r="BP42" s="53"/>
-      <c r="BQ42" s="53"/>
-      <c r="BR42" s="53"/>
-      <c r="BS42" s="53"/>
-      <c r="BT42" s="53"/>
-      <c r="BU42" s="53"/>
-      <c r="BV42" s="53"/>
-      <c r="BW42" s="53"/>
-      <c r="BX42" s="53"/>
-      <c r="BY42" s="53"/>
-      <c r="BZ42" s="53"/>
-      <c r="CA42" s="53"/>
-      <c r="CB42" s="53"/>
-      <c r="CC42" s="53"/>
-      <c r="CD42" s="53"/>
-      <c r="CE42" s="53"/>
-      <c r="CF42" s="53"/>
-      <c r="CG42" s="53"/>
-      <c r="CH42" s="53"/>
-      <c r="CI42" s="53"/>
-      <c r="CJ42" s="53"/>
-      <c r="CK42" s="53"/>
-      <c r="CL42" s="53"/>
-      <c r="CM42" s="53"/>
-      <c r="CN42" s="53"/>
-      <c r="CO42" s="53"/>
-      <c r="CP42" s="53"/>
-      <c r="CQ42" s="53"/>
+      <c r="BN42" s="55"/>
+      <c r="BO42" s="55"/>
+      <c r="BP42" s="55"/>
+      <c r="BQ42" s="55"/>
+      <c r="BR42" s="55"/>
+      <c r="BS42" s="55"/>
+      <c r="BT42" s="55"/>
+      <c r="BU42" s="55"/>
+      <c r="BV42" s="55"/>
+      <c r="BW42" s="55"/>
+      <c r="BX42" s="55"/>
+      <c r="BY42" s="55"/>
+      <c r="BZ42" s="55"/>
+      <c r="CA42" s="55"/>
+      <c r="CB42" s="55"/>
+      <c r="CC42" s="55"/>
+      <c r="CD42" s="55"/>
+      <c r="CE42" s="55"/>
+      <c r="CF42" s="55"/>
+      <c r="CG42" s="55"/>
+      <c r="CH42" s="55"/>
+      <c r="CI42" s="55"/>
+      <c r="CJ42" s="55"/>
+      <c r="CK42" s="55"/>
+      <c r="CL42" s="55"/>
+      <c r="CM42" s="55"/>
+      <c r="CN42" s="55"/>
+      <c r="CO42" s="55"/>
+      <c r="CP42" s="55"/>
+      <c r="CQ42" s="55"/>
       <c r="CR42" s="41"/>
       <c r="CS42" s="41"/>
       <c r="CT42" s="41"/>
@@ -15334,38 +15306,38 @@
       <c r="W43" s="39"/>
       <c r="X43" s="39"/>
       <c r="Y43" s="39"/>
-      <c r="Z43" s="60" t="s">
+      <c r="Z43" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="AA43" s="60"/>
-      <c r="AB43" s="60"/>
-      <c r="AC43" s="60"/>
-      <c r="AD43" s="60"/>
-      <c r="AE43" s="60"/>
-      <c r="AF43" s="60"/>
-      <c r="AG43" s="60"/>
-      <c r="AH43" s="60"/>
-      <c r="AI43" s="60"/>
-      <c r="AJ43" s="60"/>
-      <c r="AK43" s="60"/>
-      <c r="AL43" s="60"/>
-      <c r="AM43" s="60"/>
-      <c r="AN43" s="60"/>
-      <c r="AO43" s="60"/>
-      <c r="AP43" s="60"/>
-      <c r="AQ43" s="60"/>
-      <c r="AR43" s="60"/>
-      <c r="AS43" s="60"/>
-      <c r="AT43" s="60"/>
-      <c r="AU43" s="60"/>
-      <c r="AV43" s="60"/>
-      <c r="AW43" s="60"/>
-      <c r="AX43" s="60"/>
-      <c r="AY43" s="60"/>
-      <c r="AZ43" s="60"/>
-      <c r="BA43" s="60"/>
-      <c r="BB43" s="60"/>
-      <c r="BC43" s="60"/>
+      <c r="AA43" s="53"/>
+      <c r="AB43" s="53"/>
+      <c r="AC43" s="53"/>
+      <c r="AD43" s="53"/>
+      <c r="AE43" s="53"/>
+      <c r="AF43" s="53"/>
+      <c r="AG43" s="53"/>
+      <c r="AH43" s="53"/>
+      <c r="AI43" s="53"/>
+      <c r="AJ43" s="53"/>
+      <c r="AK43" s="53"/>
+      <c r="AL43" s="53"/>
+      <c r="AM43" s="53"/>
+      <c r="AN43" s="53"/>
+      <c r="AO43" s="53"/>
+      <c r="AP43" s="53"/>
+      <c r="AQ43" s="53"/>
+      <c r="AR43" s="53"/>
+      <c r="AS43" s="53"/>
+      <c r="AT43" s="53"/>
+      <c r="AU43" s="53"/>
+      <c r="AV43" s="53"/>
+      <c r="AW43" s="53"/>
+      <c r="AX43" s="53"/>
+      <c r="AY43" s="53"/>
+      <c r="AZ43" s="53"/>
+      <c r="BA43" s="53"/>
+      <c r="BB43" s="53"/>
+      <c r="BC43" s="53"/>
       <c r="BD43" s="48"/>
       <c r="BE43" s="35"/>
       <c r="BF43" s="35"/>
@@ -15376,38 +15348,38 @@
       <c r="BK43" s="35"/>
       <c r="BL43" s="35"/>
       <c r="BM43" s="35"/>
-      <c r="BN43" s="54" t="s">
+      <c r="BN43" s="56" t="s">
         <v>112</v>
       </c>
-      <c r="BO43" s="54"/>
-      <c r="BP43" s="54"/>
-      <c r="BQ43" s="54"/>
-      <c r="BR43" s="54"/>
-      <c r="BS43" s="54"/>
-      <c r="BT43" s="54"/>
-      <c r="BU43" s="54"/>
-      <c r="BV43" s="54"/>
-      <c r="BW43" s="54"/>
-      <c r="BX43" s="54"/>
-      <c r="BY43" s="54"/>
-      <c r="BZ43" s="54"/>
-      <c r="CA43" s="54"/>
-      <c r="CB43" s="54"/>
-      <c r="CC43" s="54"/>
-      <c r="CD43" s="54"/>
-      <c r="CE43" s="54"/>
-      <c r="CF43" s="54"/>
-      <c r="CG43" s="54"/>
-      <c r="CH43" s="54"/>
-      <c r="CI43" s="54"/>
-      <c r="CJ43" s="54"/>
-      <c r="CK43" s="54"/>
-      <c r="CL43" s="54"/>
-      <c r="CM43" s="54"/>
-      <c r="CN43" s="54"/>
-      <c r="CO43" s="54"/>
-      <c r="CP43" s="54"/>
-      <c r="CQ43" s="54"/>
+      <c r="BO43" s="56"/>
+      <c r="BP43" s="56"/>
+      <c r="BQ43" s="56"/>
+      <c r="BR43" s="56"/>
+      <c r="BS43" s="56"/>
+      <c r="BT43" s="56"/>
+      <c r="BU43" s="56"/>
+      <c r="BV43" s="56"/>
+      <c r="BW43" s="56"/>
+      <c r="BX43" s="56"/>
+      <c r="BY43" s="56"/>
+      <c r="BZ43" s="56"/>
+      <c r="CA43" s="56"/>
+      <c r="CB43" s="56"/>
+      <c r="CC43" s="56"/>
+      <c r="CD43" s="56"/>
+      <c r="CE43" s="56"/>
+      <c r="CF43" s="56"/>
+      <c r="CG43" s="56"/>
+      <c r="CH43" s="56"/>
+      <c r="CI43" s="56"/>
+      <c r="CJ43" s="56"/>
+      <c r="CK43" s="56"/>
+      <c r="CL43" s="56"/>
+      <c r="CM43" s="56"/>
+      <c r="CN43" s="56"/>
+      <c r="CO43" s="56"/>
+      <c r="CP43" s="56"/>
+      <c r="CQ43" s="56"/>
       <c r="CR43" s="42"/>
       <c r="CS43" s="42"/>
       <c r="CT43" s="42"/>
@@ -15422,36 +15394,36 @@
       <c r="W44" s="35"/>
       <c r="X44" s="35"/>
       <c r="Y44" s="35"/>
-      <c r="Z44" s="61"/>
-      <c r="AA44" s="61"/>
-      <c r="AB44" s="61"/>
-      <c r="AC44" s="61"/>
-      <c r="AD44" s="61"/>
-      <c r="AE44" s="61"/>
-      <c r="AF44" s="61"/>
-      <c r="AG44" s="61"/>
-      <c r="AH44" s="61"/>
-      <c r="AI44" s="61"/>
-      <c r="AJ44" s="61"/>
-      <c r="AK44" s="61"/>
-      <c r="AL44" s="61"/>
-      <c r="AM44" s="61"/>
-      <c r="AN44" s="61"/>
-      <c r="AO44" s="61"/>
-      <c r="AP44" s="61"/>
-      <c r="AQ44" s="61"/>
-      <c r="AR44" s="61"/>
-      <c r="AS44" s="61"/>
-      <c r="AT44" s="61"/>
-      <c r="AU44" s="61"/>
-      <c r="AV44" s="61"/>
-      <c r="AW44" s="61"/>
-      <c r="AX44" s="61"/>
-      <c r="AY44" s="61"/>
-      <c r="AZ44" s="61"/>
-      <c r="BA44" s="61"/>
-      <c r="BB44" s="61"/>
-      <c r="BC44" s="61"/>
+      <c r="Z44" s="54"/>
+      <c r="AA44" s="54"/>
+      <c r="AB44" s="54"/>
+      <c r="AC44" s="54"/>
+      <c r="AD44" s="54"/>
+      <c r="AE44" s="54"/>
+      <c r="AF44" s="54"/>
+      <c r="AG44" s="54"/>
+      <c r="AH44" s="54"/>
+      <c r="AI44" s="54"/>
+      <c r="AJ44" s="54"/>
+      <c r="AK44" s="54"/>
+      <c r="AL44" s="54"/>
+      <c r="AM44" s="54"/>
+      <c r="AN44" s="54"/>
+      <c r="AO44" s="54"/>
+      <c r="AP44" s="54"/>
+      <c r="AQ44" s="54"/>
+      <c r="AR44" s="54"/>
+      <c r="AS44" s="54"/>
+      <c r="AT44" s="54"/>
+      <c r="AU44" s="54"/>
+      <c r="AV44" s="54"/>
+      <c r="AW44" s="54"/>
+      <c r="AX44" s="54"/>
+      <c r="AY44" s="54"/>
+      <c r="AZ44" s="54"/>
+      <c r="BA44" s="54"/>
+      <c r="BB44" s="54"/>
+      <c r="BC44" s="54"/>
       <c r="BD44" s="48"/>
       <c r="BE44" s="35"/>
       <c r="BF44" s="35"/>
@@ -15462,36 +15434,36 @@
       <c r="BK44" s="35"/>
       <c r="BL44" s="35"/>
       <c r="BM44" s="35"/>
-      <c r="BN44" s="54"/>
-      <c r="BO44" s="54"/>
-      <c r="BP44" s="54"/>
-      <c r="BQ44" s="54"/>
-      <c r="BR44" s="54"/>
-      <c r="BS44" s="54"/>
-      <c r="BT44" s="54"/>
-      <c r="BU44" s="54"/>
-      <c r="BV44" s="54"/>
-      <c r="BW44" s="54"/>
-      <c r="BX44" s="54"/>
-      <c r="BY44" s="54"/>
-      <c r="BZ44" s="54"/>
-      <c r="CA44" s="54"/>
-      <c r="CB44" s="54"/>
-      <c r="CC44" s="54"/>
-      <c r="CD44" s="54"/>
-      <c r="CE44" s="54"/>
-      <c r="CF44" s="54"/>
-      <c r="CG44" s="54"/>
-      <c r="CH44" s="54"/>
-      <c r="CI44" s="54"/>
-      <c r="CJ44" s="54"/>
-      <c r="CK44" s="54"/>
-      <c r="CL44" s="54"/>
-      <c r="CM44" s="54"/>
-      <c r="CN44" s="54"/>
-      <c r="CO44" s="54"/>
-      <c r="CP44" s="54"/>
-      <c r="CQ44" s="54"/>
+      <c r="BN44" s="56"/>
+      <c r="BO44" s="56"/>
+      <c r="BP44" s="56"/>
+      <c r="BQ44" s="56"/>
+      <c r="BR44" s="56"/>
+      <c r="BS44" s="56"/>
+      <c r="BT44" s="56"/>
+      <c r="BU44" s="56"/>
+      <c r="BV44" s="56"/>
+      <c r="BW44" s="56"/>
+      <c r="BX44" s="56"/>
+      <c r="BY44" s="56"/>
+      <c r="BZ44" s="56"/>
+      <c r="CA44" s="56"/>
+      <c r="CB44" s="56"/>
+      <c r="CC44" s="56"/>
+      <c r="CD44" s="56"/>
+      <c r="CE44" s="56"/>
+      <c r="CF44" s="56"/>
+      <c r="CG44" s="56"/>
+      <c r="CH44" s="56"/>
+      <c r="CI44" s="56"/>
+      <c r="CJ44" s="56"/>
+      <c r="CK44" s="56"/>
+      <c r="CL44" s="56"/>
+      <c r="CM44" s="56"/>
+      <c r="CN44" s="56"/>
+      <c r="CO44" s="56"/>
+      <c r="CP44" s="56"/>
+      <c r="CQ44" s="56"/>
       <c r="CR44" s="42"/>
       <c r="CS44" s="42"/>
       <c r="CT44" s="42"/>
@@ -15506,36 +15478,36 @@
       <c r="W45" s="35"/>
       <c r="X45" s="35"/>
       <c r="Y45" s="35"/>
-      <c r="Z45" s="61"/>
-      <c r="AA45" s="61"/>
-      <c r="AB45" s="61"/>
-      <c r="AC45" s="61"/>
-      <c r="AD45" s="61"/>
-      <c r="AE45" s="61"/>
-      <c r="AF45" s="61"/>
-      <c r="AG45" s="61"/>
-      <c r="AH45" s="61"/>
-      <c r="AI45" s="61"/>
-      <c r="AJ45" s="61"/>
-      <c r="AK45" s="61"/>
-      <c r="AL45" s="61"/>
-      <c r="AM45" s="61"/>
-      <c r="AN45" s="61"/>
-      <c r="AO45" s="61"/>
-      <c r="AP45" s="61"/>
-      <c r="AQ45" s="61"/>
-      <c r="AR45" s="61"/>
-      <c r="AS45" s="61"/>
-      <c r="AT45" s="61"/>
-      <c r="AU45" s="61"/>
-      <c r="AV45" s="61"/>
-      <c r="AW45" s="61"/>
-      <c r="AX45" s="61"/>
-      <c r="AY45" s="61"/>
-      <c r="AZ45" s="61"/>
-      <c r="BA45" s="61"/>
-      <c r="BB45" s="61"/>
-      <c r="BC45" s="61"/>
+      <c r="Z45" s="54"/>
+      <c r="AA45" s="54"/>
+      <c r="AB45" s="54"/>
+      <c r="AC45" s="54"/>
+      <c r="AD45" s="54"/>
+      <c r="AE45" s="54"/>
+      <c r="AF45" s="54"/>
+      <c r="AG45" s="54"/>
+      <c r="AH45" s="54"/>
+      <c r="AI45" s="54"/>
+      <c r="AJ45" s="54"/>
+      <c r="AK45" s="54"/>
+      <c r="AL45" s="54"/>
+      <c r="AM45" s="54"/>
+      <c r="AN45" s="54"/>
+      <c r="AO45" s="54"/>
+      <c r="AP45" s="54"/>
+      <c r="AQ45" s="54"/>
+      <c r="AR45" s="54"/>
+      <c r="AS45" s="54"/>
+      <c r="AT45" s="54"/>
+      <c r="AU45" s="54"/>
+      <c r="AV45" s="54"/>
+      <c r="AW45" s="54"/>
+      <c r="AX45" s="54"/>
+      <c r="AY45" s="54"/>
+      <c r="AZ45" s="54"/>
+      <c r="BA45" s="54"/>
+      <c r="BB45" s="54"/>
+      <c r="BC45" s="54"/>
       <c r="BD45" s="48"/>
       <c r="BE45" s="35"/>
       <c r="BF45" s="35"/>
@@ -15590,36 +15562,36 @@
       <c r="W46" s="35"/>
       <c r="X46" s="35"/>
       <c r="Y46" s="35"/>
-      <c r="Z46" s="61"/>
-      <c r="AA46" s="61"/>
-      <c r="AB46" s="61"/>
-      <c r="AC46" s="61"/>
-      <c r="AD46" s="61"/>
-      <c r="AE46" s="61"/>
-      <c r="AF46" s="61"/>
-      <c r="AG46" s="61"/>
-      <c r="AH46" s="61"/>
-      <c r="AI46" s="61"/>
-      <c r="AJ46" s="61"/>
-      <c r="AK46" s="61"/>
-      <c r="AL46" s="61"/>
-      <c r="AM46" s="61"/>
-      <c r="AN46" s="61"/>
-      <c r="AO46" s="61"/>
-      <c r="AP46" s="61"/>
-      <c r="AQ46" s="61"/>
-      <c r="AR46" s="61"/>
-      <c r="AS46" s="61"/>
-      <c r="AT46" s="61"/>
-      <c r="AU46" s="61"/>
-      <c r="AV46" s="61"/>
-      <c r="AW46" s="61"/>
-      <c r="AX46" s="61"/>
-      <c r="AY46" s="61"/>
-      <c r="AZ46" s="61"/>
-      <c r="BA46" s="61"/>
-      <c r="BB46" s="61"/>
-      <c r="BC46" s="61"/>
+      <c r="Z46" s="54"/>
+      <c r="AA46" s="54"/>
+      <c r="AB46" s="54"/>
+      <c r="AC46" s="54"/>
+      <c r="AD46" s="54"/>
+      <c r="AE46" s="54"/>
+      <c r="AF46" s="54"/>
+      <c r="AG46" s="54"/>
+      <c r="AH46" s="54"/>
+      <c r="AI46" s="54"/>
+      <c r="AJ46" s="54"/>
+      <c r="AK46" s="54"/>
+      <c r="AL46" s="54"/>
+      <c r="AM46" s="54"/>
+      <c r="AN46" s="54"/>
+      <c r="AO46" s="54"/>
+      <c r="AP46" s="54"/>
+      <c r="AQ46" s="54"/>
+      <c r="AR46" s="54"/>
+      <c r="AS46" s="54"/>
+      <c r="AT46" s="54"/>
+      <c r="AU46" s="54"/>
+      <c r="AV46" s="54"/>
+      <c r="AW46" s="54"/>
+      <c r="AX46" s="54"/>
+      <c r="AY46" s="54"/>
+      <c r="AZ46" s="54"/>
+      <c r="BA46" s="54"/>
+      <c r="BB46" s="54"/>
+      <c r="BC46" s="54"/>
       <c r="BD46" s="48"/>
       <c r="BE46" s="35"/>
       <c r="BF46" s="35"/>
@@ -15674,36 +15646,36 @@
       <c r="W47" s="35"/>
       <c r="X47" s="35"/>
       <c r="Y47" s="35"/>
-      <c r="Z47" s="61"/>
-      <c r="AA47" s="61"/>
-      <c r="AB47" s="61"/>
-      <c r="AC47" s="61"/>
-      <c r="AD47" s="61"/>
-      <c r="AE47" s="61"/>
-      <c r="AF47" s="61"/>
-      <c r="AG47" s="61"/>
-      <c r="AH47" s="61"/>
-      <c r="AI47" s="61"/>
-      <c r="AJ47" s="61"/>
-      <c r="AK47" s="61"/>
-      <c r="AL47" s="61"/>
-      <c r="AM47" s="61"/>
-      <c r="AN47" s="61"/>
-      <c r="AO47" s="61"/>
-      <c r="AP47" s="61"/>
-      <c r="AQ47" s="61"/>
-      <c r="AR47" s="61"/>
-      <c r="AS47" s="61"/>
-      <c r="AT47" s="61"/>
-      <c r="AU47" s="61"/>
-      <c r="AV47" s="61"/>
-      <c r="AW47" s="61"/>
-      <c r="AX47" s="61"/>
-      <c r="AY47" s="61"/>
-      <c r="AZ47" s="61"/>
-      <c r="BA47" s="61"/>
-      <c r="BB47" s="61"/>
-      <c r="BC47" s="61"/>
+      <c r="Z47" s="54"/>
+      <c r="AA47" s="54"/>
+      <c r="AB47" s="54"/>
+      <c r="AC47" s="54"/>
+      <c r="AD47" s="54"/>
+      <c r="AE47" s="54"/>
+      <c r="AF47" s="54"/>
+      <c r="AG47" s="54"/>
+      <c r="AH47" s="54"/>
+      <c r="AI47" s="54"/>
+      <c r="AJ47" s="54"/>
+      <c r="AK47" s="54"/>
+      <c r="AL47" s="54"/>
+      <c r="AM47" s="54"/>
+      <c r="AN47" s="54"/>
+      <c r="AO47" s="54"/>
+      <c r="AP47" s="54"/>
+      <c r="AQ47" s="54"/>
+      <c r="AR47" s="54"/>
+      <c r="AS47" s="54"/>
+      <c r="AT47" s="54"/>
+      <c r="AU47" s="54"/>
+      <c r="AV47" s="54"/>
+      <c r="AW47" s="54"/>
+      <c r="AX47" s="54"/>
+      <c r="AY47" s="54"/>
+      <c r="AZ47" s="54"/>
+      <c r="BA47" s="54"/>
+      <c r="BB47" s="54"/>
+      <c r="BC47" s="54"/>
       <c r="BD47" s="48"/>
       <c r="BE47" s="35"/>
       <c r="BF47" s="35"/>
@@ -15758,38 +15730,38 @@
       <c r="W48" s="35"/>
       <c r="X48" s="35"/>
       <c r="Y48" s="35"/>
-      <c r="Z48" s="62" t="s">
+      <c r="Z48" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="AA48" s="62"/>
-      <c r="AB48" s="62"/>
-      <c r="AC48" s="62"/>
-      <c r="AD48" s="62"/>
-      <c r="AE48" s="62"/>
-      <c r="AF48" s="62"/>
-      <c r="AG48" s="62"/>
-      <c r="AH48" s="62"/>
-      <c r="AI48" s="62"/>
-      <c r="AJ48" s="62"/>
-      <c r="AK48" s="62"/>
-      <c r="AL48" s="62"/>
-      <c r="AM48" s="62"/>
-      <c r="AN48" s="62"/>
-      <c r="AO48" s="62"/>
-      <c r="AP48" s="62"/>
-      <c r="AQ48" s="62"/>
-      <c r="AR48" s="62"/>
-      <c r="AS48" s="62"/>
-      <c r="AT48" s="62"/>
-      <c r="AU48" s="62"/>
-      <c r="AV48" s="62"/>
-      <c r="AW48" s="62"/>
-      <c r="AX48" s="62"/>
-      <c r="AY48" s="62"/>
-      <c r="AZ48" s="62"/>
-      <c r="BA48" s="62"/>
-      <c r="BB48" s="62"/>
-      <c r="BC48" s="62"/>
+      <c r="AA48" s="59"/>
+      <c r="AB48" s="59"/>
+      <c r="AC48" s="59"/>
+      <c r="AD48" s="59"/>
+      <c r="AE48" s="59"/>
+      <c r="AF48" s="59"/>
+      <c r="AG48" s="59"/>
+      <c r="AH48" s="59"/>
+      <c r="AI48" s="59"/>
+      <c r="AJ48" s="59"/>
+      <c r="AK48" s="59"/>
+      <c r="AL48" s="59"/>
+      <c r="AM48" s="59"/>
+      <c r="AN48" s="59"/>
+      <c r="AO48" s="59"/>
+      <c r="AP48" s="59"/>
+      <c r="AQ48" s="59"/>
+      <c r="AR48" s="59"/>
+      <c r="AS48" s="59"/>
+      <c r="AT48" s="59"/>
+      <c r="AU48" s="59"/>
+      <c r="AV48" s="59"/>
+      <c r="AW48" s="59"/>
+      <c r="AX48" s="59"/>
+      <c r="AY48" s="59"/>
+      <c r="AZ48" s="59"/>
+      <c r="BA48" s="59"/>
+      <c r="BB48" s="59"/>
+      <c r="BC48" s="59"/>
       <c r="BD48" s="43"/>
       <c r="BE48" s="35"/>
       <c r="BF48" s="35"/>
@@ -15860,36 +15832,36 @@
       <c r="W49" s="35"/>
       <c r="X49" s="35"/>
       <c r="Y49" s="35"/>
-      <c r="Z49" s="62"/>
-      <c r="AA49" s="62"/>
-      <c r="AB49" s="62"/>
-      <c r="AC49" s="62"/>
-      <c r="AD49" s="62"/>
-      <c r="AE49" s="62"/>
-      <c r="AF49" s="62"/>
-      <c r="AG49" s="62"/>
-      <c r="AH49" s="62"/>
-      <c r="AI49" s="62"/>
-      <c r="AJ49" s="62"/>
-      <c r="AK49" s="62"/>
-      <c r="AL49" s="62"/>
-      <c r="AM49" s="62"/>
-      <c r="AN49" s="62"/>
-      <c r="AO49" s="62"/>
-      <c r="AP49" s="62"/>
-      <c r="AQ49" s="62"/>
-      <c r="AR49" s="62"/>
-      <c r="AS49" s="62"/>
-      <c r="AT49" s="62"/>
-      <c r="AU49" s="62"/>
-      <c r="AV49" s="62"/>
-      <c r="AW49" s="62"/>
-      <c r="AX49" s="62"/>
-      <c r="AY49" s="62"/>
-      <c r="AZ49" s="62"/>
-      <c r="BA49" s="62"/>
-      <c r="BB49" s="62"/>
-      <c r="BC49" s="62"/>
+      <c r="Z49" s="59"/>
+      <c r="AA49" s="59"/>
+      <c r="AB49" s="59"/>
+      <c r="AC49" s="59"/>
+      <c r="AD49" s="59"/>
+      <c r="AE49" s="59"/>
+      <c r="AF49" s="59"/>
+      <c r="AG49" s="59"/>
+      <c r="AH49" s="59"/>
+      <c r="AI49" s="59"/>
+      <c r="AJ49" s="59"/>
+      <c r="AK49" s="59"/>
+      <c r="AL49" s="59"/>
+      <c r="AM49" s="59"/>
+      <c r="AN49" s="59"/>
+      <c r="AO49" s="59"/>
+      <c r="AP49" s="59"/>
+      <c r="AQ49" s="59"/>
+      <c r="AR49" s="59"/>
+      <c r="AS49" s="59"/>
+      <c r="AT49" s="59"/>
+      <c r="AU49" s="59"/>
+      <c r="AV49" s="59"/>
+      <c r="AW49" s="59"/>
+      <c r="AX49" s="59"/>
+      <c r="AY49" s="59"/>
+      <c r="AZ49" s="59"/>
+      <c r="BA49" s="59"/>
+      <c r="BB49" s="59"/>
+      <c r="BC49" s="59"/>
       <c r="BD49" s="43"/>
       <c r="BE49" s="35"/>
       <c r="BF49" s="35"/>
@@ -15960,36 +15932,36 @@
       <c r="W50" s="35"/>
       <c r="X50" s="35"/>
       <c r="Y50" s="35"/>
-      <c r="Z50" s="62"/>
-      <c r="AA50" s="62"/>
-      <c r="AB50" s="62"/>
-      <c r="AC50" s="62"/>
-      <c r="AD50" s="62"/>
-      <c r="AE50" s="62"/>
-      <c r="AF50" s="62"/>
-      <c r="AG50" s="62"/>
-      <c r="AH50" s="62"/>
-      <c r="AI50" s="62"/>
-      <c r="AJ50" s="62"/>
-      <c r="AK50" s="62"/>
-      <c r="AL50" s="62"/>
-      <c r="AM50" s="62"/>
-      <c r="AN50" s="62"/>
-      <c r="AO50" s="62"/>
-      <c r="AP50" s="62"/>
-      <c r="AQ50" s="62"/>
-      <c r="AR50" s="62"/>
-      <c r="AS50" s="62"/>
-      <c r="AT50" s="62"/>
-      <c r="AU50" s="62"/>
-      <c r="AV50" s="62"/>
-      <c r="AW50" s="62"/>
-      <c r="AX50" s="62"/>
-      <c r="AY50" s="62"/>
-      <c r="AZ50" s="62"/>
-      <c r="BA50" s="62"/>
-      <c r="BB50" s="62"/>
-      <c r="BC50" s="62"/>
+      <c r="Z50" s="59"/>
+      <c r="AA50" s="59"/>
+      <c r="AB50" s="59"/>
+      <c r="AC50" s="59"/>
+      <c r="AD50" s="59"/>
+      <c r="AE50" s="59"/>
+      <c r="AF50" s="59"/>
+      <c r="AG50" s="59"/>
+      <c r="AH50" s="59"/>
+      <c r="AI50" s="59"/>
+      <c r="AJ50" s="59"/>
+      <c r="AK50" s="59"/>
+      <c r="AL50" s="59"/>
+      <c r="AM50" s="59"/>
+      <c r="AN50" s="59"/>
+      <c r="AO50" s="59"/>
+      <c r="AP50" s="59"/>
+      <c r="AQ50" s="59"/>
+      <c r="AR50" s="59"/>
+      <c r="AS50" s="59"/>
+      <c r="AT50" s="59"/>
+      <c r="AU50" s="59"/>
+      <c r="AV50" s="59"/>
+      <c r="AW50" s="59"/>
+      <c r="AX50" s="59"/>
+      <c r="AY50" s="59"/>
+      <c r="AZ50" s="59"/>
+      <c r="BA50" s="59"/>
+      <c r="BB50" s="59"/>
+      <c r="BC50" s="59"/>
       <c r="BD50" s="43"/>
       <c r="BE50" s="35"/>
       <c r="BF50" s="35"/>
@@ -16036,23 +16008,23 @@
       <c r="CU50" s="35"/>
     </row>
     <row r="51" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B51" s="56" t="s">
+      <c r="B51" s="63" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="56"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
-      <c r="H51" s="56"/>
-      <c r="I51" s="56"/>
-      <c r="J51" s="56"/>
-      <c r="K51" s="56"/>
-      <c r="L51" s="56"/>
-      <c r="M51" s="56"/>
-      <c r="N51" s="56"/>
-      <c r="O51" s="56"/>
-      <c r="P51" s="56"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="63"/>
+      <c r="I51" s="63"/>
+      <c r="J51" s="63"/>
+      <c r="K51" s="63"/>
+      <c r="L51" s="63"/>
+      <c r="M51" s="63"/>
+      <c r="N51" s="63"/>
+      <c r="O51" s="63"/>
+      <c r="P51" s="63"/>
       <c r="Q51" s="35"/>
       <c r="R51" s="35"/>
       <c r="S51" s="35"/>
@@ -16062,38 +16034,38 @@
       <c r="W51" s="35"/>
       <c r="X51" s="35"/>
       <c r="Y51" s="35"/>
-      <c r="Z51" s="63" t="s">
+      <c r="Z51" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="AA51" s="63"/>
-      <c r="AB51" s="63"/>
-      <c r="AC51" s="63"/>
-      <c r="AD51" s="63"/>
-      <c r="AE51" s="63"/>
-      <c r="AF51" s="63"/>
-      <c r="AG51" s="63"/>
-      <c r="AH51" s="63"/>
-      <c r="AI51" s="63"/>
-      <c r="AJ51" s="63"/>
-      <c r="AK51" s="63"/>
-      <c r="AL51" s="63"/>
-      <c r="AM51" s="63"/>
-      <c r="AN51" s="63"/>
-      <c r="AO51" s="63"/>
-      <c r="AP51" s="63"/>
-      <c r="AQ51" s="63"/>
-      <c r="AR51" s="63"/>
-      <c r="AS51" s="63"/>
-      <c r="AT51" s="63"/>
-      <c r="AU51" s="63"/>
-      <c r="AV51" s="63"/>
-      <c r="AW51" s="63"/>
-      <c r="AX51" s="63"/>
-      <c r="AY51" s="63"/>
-      <c r="AZ51" s="63"/>
-      <c r="BA51" s="63"/>
-      <c r="BB51" s="63"/>
-      <c r="BC51" s="63"/>
+      <c r="AA51" s="57"/>
+      <c r="AB51" s="57"/>
+      <c r="AC51" s="57"/>
+      <c r="AD51" s="57"/>
+      <c r="AE51" s="57"/>
+      <c r="AF51" s="57"/>
+      <c r="AG51" s="57"/>
+      <c r="AH51" s="57"/>
+      <c r="AI51" s="57"/>
+      <c r="AJ51" s="57"/>
+      <c r="AK51" s="57"/>
+      <c r="AL51" s="57"/>
+      <c r="AM51" s="57"/>
+      <c r="AN51" s="57"/>
+      <c r="AO51" s="57"/>
+      <c r="AP51" s="57"/>
+      <c r="AQ51" s="57"/>
+      <c r="AR51" s="57"/>
+      <c r="AS51" s="57"/>
+      <c r="AT51" s="57"/>
+      <c r="AU51" s="57"/>
+      <c r="AV51" s="57"/>
+      <c r="AW51" s="57"/>
+      <c r="AX51" s="57"/>
+      <c r="AY51" s="57"/>
+      <c r="AZ51" s="57"/>
+      <c r="BA51" s="57"/>
+      <c r="BB51" s="57"/>
+      <c r="BC51" s="57"/>
       <c r="BD51" s="44"/>
       <c r="BE51" s="35"/>
       <c r="BF51" s="35"/>
@@ -16140,21 +16112,21 @@
       <c r="CU51" s="35"/>
     </row>
     <row r="52" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B52" s="56"/>
-      <c r="C52" s="56"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="56"/>
-      <c r="G52" s="56"/>
-      <c r="H52" s="56"/>
-      <c r="I52" s="56"/>
-      <c r="J52" s="56"/>
-      <c r="K52" s="56"/>
-      <c r="L52" s="56"/>
-      <c r="M52" s="56"/>
-      <c r="N52" s="56"/>
-      <c r="O52" s="56"/>
-      <c r="P52" s="56"/>
+      <c r="B52" s="63"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="63"/>
+      <c r="I52" s="63"/>
+      <c r="J52" s="63"/>
+      <c r="K52" s="63"/>
+      <c r="L52" s="63"/>
+      <c r="M52" s="63"/>
+      <c r="N52" s="63"/>
+      <c r="O52" s="63"/>
+      <c r="P52" s="63"/>
       <c r="Q52" s="35"/>
       <c r="R52" s="35"/>
       <c r="S52" s="35"/>
@@ -16164,36 +16136,36 @@
       <c r="W52" s="35"/>
       <c r="X52" s="35"/>
       <c r="Y52" s="35"/>
-      <c r="Z52" s="63"/>
-      <c r="AA52" s="63"/>
-      <c r="AB52" s="63"/>
-      <c r="AC52" s="63"/>
-      <c r="AD52" s="63"/>
-      <c r="AE52" s="63"/>
-      <c r="AF52" s="63"/>
-      <c r="AG52" s="63"/>
-      <c r="AH52" s="63"/>
-      <c r="AI52" s="63"/>
-      <c r="AJ52" s="63"/>
-      <c r="AK52" s="63"/>
-      <c r="AL52" s="63"/>
-      <c r="AM52" s="63"/>
-      <c r="AN52" s="63"/>
-      <c r="AO52" s="63"/>
-      <c r="AP52" s="63"/>
-      <c r="AQ52" s="63"/>
-      <c r="AR52" s="63"/>
-      <c r="AS52" s="63"/>
-      <c r="AT52" s="63"/>
-      <c r="AU52" s="63"/>
-      <c r="AV52" s="63"/>
-      <c r="AW52" s="63"/>
-      <c r="AX52" s="63"/>
-      <c r="AY52" s="63"/>
-      <c r="AZ52" s="63"/>
-      <c r="BA52" s="63"/>
-      <c r="BB52" s="63"/>
-      <c r="BC52" s="63"/>
+      <c r="Z52" s="57"/>
+      <c r="AA52" s="57"/>
+      <c r="AB52" s="57"/>
+      <c r="AC52" s="57"/>
+      <c r="AD52" s="57"/>
+      <c r="AE52" s="57"/>
+      <c r="AF52" s="57"/>
+      <c r="AG52" s="57"/>
+      <c r="AH52" s="57"/>
+      <c r="AI52" s="57"/>
+      <c r="AJ52" s="57"/>
+      <c r="AK52" s="57"/>
+      <c r="AL52" s="57"/>
+      <c r="AM52" s="57"/>
+      <c r="AN52" s="57"/>
+      <c r="AO52" s="57"/>
+      <c r="AP52" s="57"/>
+      <c r="AQ52" s="57"/>
+      <c r="AR52" s="57"/>
+      <c r="AS52" s="57"/>
+      <c r="AT52" s="57"/>
+      <c r="AU52" s="57"/>
+      <c r="AV52" s="57"/>
+      <c r="AW52" s="57"/>
+      <c r="AX52" s="57"/>
+      <c r="AY52" s="57"/>
+      <c r="AZ52" s="57"/>
+      <c r="BA52" s="57"/>
+      <c r="BB52" s="57"/>
+      <c r="BC52" s="57"/>
       <c r="BD52" s="44"/>
       <c r="BE52" s="35"/>
       <c r="BF52" s="35"/>
@@ -16340,23 +16312,23 @@
       <c r="CU53" s="35"/>
     </row>
     <row r="54" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B54" s="67" t="s">
+      <c r="B54" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="67"/>
-      <c r="D54" s="67"/>
-      <c r="E54" s="67"/>
-      <c r="F54" s="67"/>
-      <c r="G54" s="67"/>
-      <c r="H54" s="67"/>
-      <c r="I54" s="67"/>
-      <c r="J54" s="67"/>
-      <c r="K54" s="67"/>
-      <c r="L54" s="67"/>
-      <c r="M54" s="67"/>
-      <c r="N54" s="67"/>
-      <c r="O54" s="67"/>
-      <c r="P54" s="67"/>
+      <c r="C54" s="61"/>
+      <c r="D54" s="61"/>
+      <c r="E54" s="61"/>
+      <c r="F54" s="61"/>
+      <c r="G54" s="61"/>
+      <c r="H54" s="61"/>
+      <c r="I54" s="61"/>
+      <c r="J54" s="61"/>
+      <c r="K54" s="61"/>
+      <c r="L54" s="61"/>
+      <c r="M54" s="61"/>
+      <c r="N54" s="61"/>
+      <c r="O54" s="61"/>
+      <c r="P54" s="61"/>
       <c r="Q54" s="35"/>
       <c r="R54" s="39"/>
       <c r="S54" s="39"/>
@@ -16366,38 +16338,38 @@
       <c r="W54" s="39"/>
       <c r="X54" s="39"/>
       <c r="Y54" s="39"/>
-      <c r="Z54" s="60" t="s">
+      <c r="Z54" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="AA54" s="60"/>
-      <c r="AB54" s="60"/>
-      <c r="AC54" s="60"/>
-      <c r="AD54" s="60"/>
-      <c r="AE54" s="60"/>
-      <c r="AF54" s="60"/>
-      <c r="AG54" s="60"/>
-      <c r="AH54" s="60"/>
-      <c r="AI54" s="60"/>
-      <c r="AJ54" s="60"/>
-      <c r="AK54" s="60"/>
-      <c r="AL54" s="60"/>
-      <c r="AM54" s="60"/>
-      <c r="AN54" s="60"/>
-      <c r="AO54" s="60"/>
-      <c r="AP54" s="60"/>
-      <c r="AQ54" s="60"/>
-      <c r="AR54" s="60"/>
-      <c r="AS54" s="60"/>
-      <c r="AT54" s="60"/>
-      <c r="AU54" s="60"/>
-      <c r="AV54" s="60"/>
-      <c r="AW54" s="60"/>
-      <c r="AX54" s="60"/>
-      <c r="AY54" s="60"/>
-      <c r="AZ54" s="60"/>
-      <c r="BA54" s="60"/>
-      <c r="BB54" s="60"/>
-      <c r="BC54" s="60"/>
+      <c r="AA54" s="53"/>
+      <c r="AB54" s="53"/>
+      <c r="AC54" s="53"/>
+      <c r="AD54" s="53"/>
+      <c r="AE54" s="53"/>
+      <c r="AF54" s="53"/>
+      <c r="AG54" s="53"/>
+      <c r="AH54" s="53"/>
+      <c r="AI54" s="53"/>
+      <c r="AJ54" s="53"/>
+      <c r="AK54" s="53"/>
+      <c r="AL54" s="53"/>
+      <c r="AM54" s="53"/>
+      <c r="AN54" s="53"/>
+      <c r="AO54" s="53"/>
+      <c r="AP54" s="53"/>
+      <c r="AQ54" s="53"/>
+      <c r="AR54" s="53"/>
+      <c r="AS54" s="53"/>
+      <c r="AT54" s="53"/>
+      <c r="AU54" s="53"/>
+      <c r="AV54" s="53"/>
+      <c r="AW54" s="53"/>
+      <c r="AX54" s="53"/>
+      <c r="AY54" s="53"/>
+      <c r="AZ54" s="53"/>
+      <c r="BA54" s="53"/>
+      <c r="BB54" s="53"/>
+      <c r="BC54" s="53"/>
       <c r="BD54" s="48"/>
       <c r="BE54" s="35"/>
       <c r="BF54" s="35"/>
@@ -16444,21 +16416,21 @@
       <c r="CU54" s="35"/>
     </row>
     <row r="55" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B55" s="67"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="67"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="67"/>
-      <c r="J55" s="67"/>
-      <c r="K55" s="67"/>
-      <c r="L55" s="67"/>
-      <c r="M55" s="67"/>
-      <c r="N55" s="67"/>
-      <c r="O55" s="67"/>
-      <c r="P55" s="67"/>
+      <c r="B55" s="61"/>
+      <c r="C55" s="61"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="61"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="61"/>
+      <c r="I55" s="61"/>
+      <c r="J55" s="61"/>
+      <c r="K55" s="61"/>
+      <c r="L55" s="61"/>
+      <c r="M55" s="61"/>
+      <c r="N55" s="61"/>
+      <c r="O55" s="61"/>
+      <c r="P55" s="61"/>
       <c r="Q55" s="35"/>
       <c r="R55" s="35"/>
       <c r="S55" s="35"/>
@@ -16468,36 +16440,36 @@
       <c r="W55" s="35"/>
       <c r="X55" s="35"/>
       <c r="Y55" s="35"/>
-      <c r="Z55" s="61"/>
-      <c r="AA55" s="61"/>
-      <c r="AB55" s="61"/>
-      <c r="AC55" s="61"/>
-      <c r="AD55" s="61"/>
-      <c r="AE55" s="61"/>
-      <c r="AF55" s="61"/>
-      <c r="AG55" s="61"/>
-      <c r="AH55" s="61"/>
-      <c r="AI55" s="61"/>
-      <c r="AJ55" s="61"/>
-      <c r="AK55" s="61"/>
-      <c r="AL55" s="61"/>
-      <c r="AM55" s="61"/>
-      <c r="AN55" s="61"/>
-      <c r="AO55" s="61"/>
-      <c r="AP55" s="61"/>
-      <c r="AQ55" s="61"/>
-      <c r="AR55" s="61"/>
-      <c r="AS55" s="61"/>
-      <c r="AT55" s="61"/>
-      <c r="AU55" s="61"/>
-      <c r="AV55" s="61"/>
-      <c r="AW55" s="61"/>
-      <c r="AX55" s="61"/>
-      <c r="AY55" s="61"/>
-      <c r="AZ55" s="61"/>
-      <c r="BA55" s="61"/>
-      <c r="BB55" s="61"/>
-      <c r="BC55" s="61"/>
+      <c r="Z55" s="54"/>
+      <c r="AA55" s="54"/>
+      <c r="AB55" s="54"/>
+      <c r="AC55" s="54"/>
+      <c r="AD55" s="54"/>
+      <c r="AE55" s="54"/>
+      <c r="AF55" s="54"/>
+      <c r="AG55" s="54"/>
+      <c r="AH55" s="54"/>
+      <c r="AI55" s="54"/>
+      <c r="AJ55" s="54"/>
+      <c r="AK55" s="54"/>
+      <c r="AL55" s="54"/>
+      <c r="AM55" s="54"/>
+      <c r="AN55" s="54"/>
+      <c r="AO55" s="54"/>
+      <c r="AP55" s="54"/>
+      <c r="AQ55" s="54"/>
+      <c r="AR55" s="54"/>
+      <c r="AS55" s="54"/>
+      <c r="AT55" s="54"/>
+      <c r="AU55" s="54"/>
+      <c r="AV55" s="54"/>
+      <c r="AW55" s="54"/>
+      <c r="AX55" s="54"/>
+      <c r="AY55" s="54"/>
+      <c r="AZ55" s="54"/>
+      <c r="BA55" s="54"/>
+      <c r="BB55" s="54"/>
+      <c r="BC55" s="54"/>
       <c r="BD55" s="48"/>
       <c r="BE55" s="35"/>
       <c r="BF55" s="35"/>
@@ -16544,21 +16516,21 @@
       <c r="CU55" s="35"/>
     </row>
     <row r="56" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B56" s="67"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="67"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="67"/>
-      <c r="H56" s="67"/>
-      <c r="I56" s="67"/>
-      <c r="J56" s="67"/>
-      <c r="K56" s="67"/>
-      <c r="L56" s="67"/>
-      <c r="M56" s="67"/>
-      <c r="N56" s="67"/>
-      <c r="O56" s="67"/>
-      <c r="P56" s="67"/>
+      <c r="B56" s="61"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="61"/>
+      <c r="E56" s="61"/>
+      <c r="F56" s="61"/>
+      <c r="G56" s="61"/>
+      <c r="H56" s="61"/>
+      <c r="I56" s="61"/>
+      <c r="J56" s="61"/>
+      <c r="K56" s="61"/>
+      <c r="L56" s="61"/>
+      <c r="M56" s="61"/>
+      <c r="N56" s="61"/>
+      <c r="O56" s="61"/>
+      <c r="P56" s="61"/>
       <c r="Q56" s="35"/>
       <c r="R56" s="35"/>
       <c r="S56" s="35"/>
@@ -16568,36 +16540,36 @@
       <c r="W56" s="35"/>
       <c r="X56" s="35"/>
       <c r="Y56" s="35"/>
-      <c r="Z56" s="61"/>
-      <c r="AA56" s="61"/>
-      <c r="AB56" s="61"/>
-      <c r="AC56" s="61"/>
-      <c r="AD56" s="61"/>
-      <c r="AE56" s="61"/>
-      <c r="AF56" s="61"/>
-      <c r="AG56" s="61"/>
-      <c r="AH56" s="61"/>
-      <c r="AI56" s="61"/>
-      <c r="AJ56" s="61"/>
-      <c r="AK56" s="61"/>
-      <c r="AL56" s="61"/>
-      <c r="AM56" s="61"/>
-      <c r="AN56" s="61"/>
-      <c r="AO56" s="61"/>
-      <c r="AP56" s="61"/>
-      <c r="AQ56" s="61"/>
-      <c r="AR56" s="61"/>
-      <c r="AS56" s="61"/>
-      <c r="AT56" s="61"/>
-      <c r="AU56" s="61"/>
-      <c r="AV56" s="61"/>
-      <c r="AW56" s="61"/>
-      <c r="AX56" s="61"/>
-      <c r="AY56" s="61"/>
-      <c r="AZ56" s="61"/>
-      <c r="BA56" s="61"/>
-      <c r="BB56" s="61"/>
-      <c r="BC56" s="61"/>
+      <c r="Z56" s="54"/>
+      <c r="AA56" s="54"/>
+      <c r="AB56" s="54"/>
+      <c r="AC56" s="54"/>
+      <c r="AD56" s="54"/>
+      <c r="AE56" s="54"/>
+      <c r="AF56" s="54"/>
+      <c r="AG56" s="54"/>
+      <c r="AH56" s="54"/>
+      <c r="AI56" s="54"/>
+      <c r="AJ56" s="54"/>
+      <c r="AK56" s="54"/>
+      <c r="AL56" s="54"/>
+      <c r="AM56" s="54"/>
+      <c r="AN56" s="54"/>
+      <c r="AO56" s="54"/>
+      <c r="AP56" s="54"/>
+      <c r="AQ56" s="54"/>
+      <c r="AR56" s="54"/>
+      <c r="AS56" s="54"/>
+      <c r="AT56" s="54"/>
+      <c r="AU56" s="54"/>
+      <c r="AV56" s="54"/>
+      <c r="AW56" s="54"/>
+      <c r="AX56" s="54"/>
+      <c r="AY56" s="54"/>
+      <c r="AZ56" s="54"/>
+      <c r="BA56" s="54"/>
+      <c r="BB56" s="54"/>
+      <c r="BC56" s="54"/>
       <c r="BD56" s="48"/>
       <c r="BE56" s="35"/>
       <c r="BF56" s="35"/>
@@ -16644,23 +16616,23 @@
       <c r="CU56" s="35"/>
     </row>
     <row r="57" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B57" s="68" t="s">
+      <c r="B57" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="68"/>
-      <c r="D57" s="68"/>
-      <c r="E57" s="68"/>
-      <c r="F57" s="68"/>
-      <c r="G57" s="68"/>
-      <c r="H57" s="68"/>
-      <c r="I57" s="68"/>
-      <c r="J57" s="68"/>
-      <c r="K57" s="68"/>
-      <c r="L57" s="68"/>
-      <c r="M57" s="68"/>
-      <c r="N57" s="68"/>
-      <c r="O57" s="68"/>
-      <c r="P57" s="68"/>
+      <c r="C57" s="64"/>
+      <c r="D57" s="64"/>
+      <c r="E57" s="64"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
+      <c r="H57" s="64"/>
+      <c r="I57" s="64"/>
+      <c r="J57" s="64"/>
+      <c r="K57" s="64"/>
+      <c r="L57" s="64"/>
+      <c r="M57" s="64"/>
+      <c r="N57" s="64"/>
+      <c r="O57" s="64"/>
+      <c r="P57" s="64"/>
       <c r="Q57" s="35"/>
       <c r="R57" s="35"/>
       <c r="S57" s="35"/>
@@ -16670,36 +16642,36 @@
       <c r="W57" s="35"/>
       <c r="X57" s="35"/>
       <c r="Y57" s="35"/>
-      <c r="Z57" s="61"/>
-      <c r="AA57" s="61"/>
-      <c r="AB57" s="61"/>
-      <c r="AC57" s="61"/>
-      <c r="AD57" s="61"/>
-      <c r="AE57" s="61"/>
-      <c r="AF57" s="61"/>
-      <c r="AG57" s="61"/>
-      <c r="AH57" s="61"/>
-      <c r="AI57" s="61"/>
-      <c r="AJ57" s="61"/>
-      <c r="AK57" s="61"/>
-      <c r="AL57" s="61"/>
-      <c r="AM57" s="61"/>
-      <c r="AN57" s="61"/>
-      <c r="AO57" s="61"/>
-      <c r="AP57" s="61"/>
-      <c r="AQ57" s="61"/>
-      <c r="AR57" s="61"/>
-      <c r="AS57" s="61"/>
-      <c r="AT57" s="61"/>
-      <c r="AU57" s="61"/>
-      <c r="AV57" s="61"/>
-      <c r="AW57" s="61"/>
-      <c r="AX57" s="61"/>
-      <c r="AY57" s="61"/>
-      <c r="AZ57" s="61"/>
-      <c r="BA57" s="61"/>
-      <c r="BB57" s="61"/>
-      <c r="BC57" s="61"/>
+      <c r="Z57" s="54"/>
+      <c r="AA57" s="54"/>
+      <c r="AB57" s="54"/>
+      <c r="AC57" s="54"/>
+      <c r="AD57" s="54"/>
+      <c r="AE57" s="54"/>
+      <c r="AF57" s="54"/>
+      <c r="AG57" s="54"/>
+      <c r="AH57" s="54"/>
+      <c r="AI57" s="54"/>
+      <c r="AJ57" s="54"/>
+      <c r="AK57" s="54"/>
+      <c r="AL57" s="54"/>
+      <c r="AM57" s="54"/>
+      <c r="AN57" s="54"/>
+      <c r="AO57" s="54"/>
+      <c r="AP57" s="54"/>
+      <c r="AQ57" s="54"/>
+      <c r="AR57" s="54"/>
+      <c r="AS57" s="54"/>
+      <c r="AT57" s="54"/>
+      <c r="AU57" s="54"/>
+      <c r="AV57" s="54"/>
+      <c r="AW57" s="54"/>
+      <c r="AX57" s="54"/>
+      <c r="AY57" s="54"/>
+      <c r="AZ57" s="54"/>
+      <c r="BA57" s="54"/>
+      <c r="BB57" s="54"/>
+      <c r="BC57" s="54"/>
       <c r="BD57" s="48"/>
       <c r="BE57" s="35"/>
       <c r="BF57" s="35"/>
@@ -16746,21 +16718,21 @@
       <c r="CU57" s="35"/>
     </row>
     <row r="58" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B58" s="68"/>
-      <c r="C58" s="68"/>
-      <c r="D58" s="68"/>
-      <c r="E58" s="68"/>
-      <c r="F58" s="68"/>
-      <c r="G58" s="68"/>
-      <c r="H58" s="68"/>
-      <c r="I58" s="68"/>
-      <c r="J58" s="68"/>
-      <c r="K58" s="68"/>
-      <c r="L58" s="68"/>
-      <c r="M58" s="68"/>
-      <c r="N58" s="68"/>
-      <c r="O58" s="68"/>
-      <c r="P58" s="68"/>
+      <c r="B58" s="64"/>
+      <c r="C58" s="64"/>
+      <c r="D58" s="64"/>
+      <c r="E58" s="64"/>
+      <c r="F58" s="64"/>
+      <c r="G58" s="64"/>
+      <c r="H58" s="64"/>
+      <c r="I58" s="64"/>
+      <c r="J58" s="64"/>
+      <c r="K58" s="64"/>
+      <c r="L58" s="64"/>
+      <c r="M58" s="64"/>
+      <c r="N58" s="64"/>
+      <c r="O58" s="64"/>
+      <c r="P58" s="64"/>
       <c r="Q58" s="35"/>
       <c r="R58" s="35"/>
       <c r="S58" s="35"/>
@@ -16770,36 +16742,36 @@
       <c r="W58" s="35"/>
       <c r="X58" s="35"/>
       <c r="Y58" s="35"/>
-      <c r="Z58" s="61"/>
-      <c r="AA58" s="61"/>
-      <c r="AB58" s="61"/>
-      <c r="AC58" s="61"/>
-      <c r="AD58" s="61"/>
-      <c r="AE58" s="61"/>
-      <c r="AF58" s="61"/>
-      <c r="AG58" s="61"/>
-      <c r="AH58" s="61"/>
-      <c r="AI58" s="61"/>
-      <c r="AJ58" s="61"/>
-      <c r="AK58" s="61"/>
-      <c r="AL58" s="61"/>
-      <c r="AM58" s="61"/>
-      <c r="AN58" s="61"/>
-      <c r="AO58" s="61"/>
-      <c r="AP58" s="61"/>
-      <c r="AQ58" s="61"/>
-      <c r="AR58" s="61"/>
-      <c r="AS58" s="61"/>
-      <c r="AT58" s="61"/>
-      <c r="AU58" s="61"/>
-      <c r="AV58" s="61"/>
-      <c r="AW58" s="61"/>
-      <c r="AX58" s="61"/>
-      <c r="AY58" s="61"/>
-      <c r="AZ58" s="61"/>
-      <c r="BA58" s="61"/>
-      <c r="BB58" s="61"/>
-      <c r="BC58" s="61"/>
+      <c r="Z58" s="54"/>
+      <c r="AA58" s="54"/>
+      <c r="AB58" s="54"/>
+      <c r="AC58" s="54"/>
+      <c r="AD58" s="54"/>
+      <c r="AE58" s="54"/>
+      <c r="AF58" s="54"/>
+      <c r="AG58" s="54"/>
+      <c r="AH58" s="54"/>
+      <c r="AI58" s="54"/>
+      <c r="AJ58" s="54"/>
+      <c r="AK58" s="54"/>
+      <c r="AL58" s="54"/>
+      <c r="AM58" s="54"/>
+      <c r="AN58" s="54"/>
+      <c r="AO58" s="54"/>
+      <c r="AP58" s="54"/>
+      <c r="AQ58" s="54"/>
+      <c r="AR58" s="54"/>
+      <c r="AS58" s="54"/>
+      <c r="AT58" s="54"/>
+      <c r="AU58" s="54"/>
+      <c r="AV58" s="54"/>
+      <c r="AW58" s="54"/>
+      <c r="AX58" s="54"/>
+      <c r="AY58" s="54"/>
+      <c r="AZ58" s="54"/>
+      <c r="BA58" s="54"/>
+      <c r="BB58" s="54"/>
+      <c r="BC58" s="54"/>
       <c r="BD58" s="48"/>
       <c r="BE58" s="35"/>
       <c r="BF58" s="35"/>
@@ -16870,38 +16842,38 @@
       <c r="W59" s="35"/>
       <c r="X59" s="35"/>
       <c r="Y59" s="35"/>
-      <c r="Z59" s="62" t="s">
+      <c r="Z59" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="AA59" s="62"/>
-      <c r="AB59" s="62"/>
-      <c r="AC59" s="62"/>
-      <c r="AD59" s="62"/>
-      <c r="AE59" s="62"/>
-      <c r="AF59" s="62"/>
-      <c r="AG59" s="62"/>
-      <c r="AH59" s="62"/>
-      <c r="AI59" s="62"/>
-      <c r="AJ59" s="62"/>
-      <c r="AK59" s="62"/>
-      <c r="AL59" s="62"/>
-      <c r="AM59" s="62"/>
-      <c r="AN59" s="62"/>
-      <c r="AO59" s="62"/>
-      <c r="AP59" s="62"/>
-      <c r="AQ59" s="62"/>
-      <c r="AR59" s="62"/>
-      <c r="AS59" s="62"/>
-      <c r="AT59" s="62"/>
-      <c r="AU59" s="62"/>
-      <c r="AV59" s="62"/>
-      <c r="AW59" s="62"/>
-      <c r="AX59" s="62"/>
-      <c r="AY59" s="62"/>
-      <c r="AZ59" s="62"/>
-      <c r="BA59" s="62"/>
-      <c r="BB59" s="62"/>
-      <c r="BC59" s="62"/>
+      <c r="AA59" s="59"/>
+      <c r="AB59" s="59"/>
+      <c r="AC59" s="59"/>
+      <c r="AD59" s="59"/>
+      <c r="AE59" s="59"/>
+      <c r="AF59" s="59"/>
+      <c r="AG59" s="59"/>
+      <c r="AH59" s="59"/>
+      <c r="AI59" s="59"/>
+      <c r="AJ59" s="59"/>
+      <c r="AK59" s="59"/>
+      <c r="AL59" s="59"/>
+      <c r="AM59" s="59"/>
+      <c r="AN59" s="59"/>
+      <c r="AO59" s="59"/>
+      <c r="AP59" s="59"/>
+      <c r="AQ59" s="59"/>
+      <c r="AR59" s="59"/>
+      <c r="AS59" s="59"/>
+      <c r="AT59" s="59"/>
+      <c r="AU59" s="59"/>
+      <c r="AV59" s="59"/>
+      <c r="AW59" s="59"/>
+      <c r="AX59" s="59"/>
+      <c r="AY59" s="59"/>
+      <c r="AZ59" s="59"/>
+      <c r="BA59" s="59"/>
+      <c r="BB59" s="59"/>
+      <c r="BC59" s="59"/>
       <c r="BD59" s="43"/>
       <c r="BE59" s="35"/>
       <c r="BF59" s="39"/>
@@ -16912,61 +16884,61 @@
       <c r="BK59" s="39"/>
       <c r="BL59" s="39"/>
       <c r="BM59" s="39"/>
-      <c r="BN59" s="52" t="s">
+      <c r="BN59" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="BO59" s="52"/>
-      <c r="BP59" s="52"/>
-      <c r="BQ59" s="52"/>
-      <c r="BR59" s="52"/>
-      <c r="BS59" s="52"/>
-      <c r="BT59" s="52"/>
-      <c r="BU59" s="52"/>
-      <c r="BV59" s="52"/>
-      <c r="BW59" s="52"/>
-      <c r="BX59" s="52"/>
-      <c r="BY59" s="52"/>
-      <c r="BZ59" s="52"/>
-      <c r="CA59" s="52"/>
-      <c r="CB59" s="52"/>
-      <c r="CC59" s="52"/>
-      <c r="CD59" s="52"/>
-      <c r="CE59" s="52"/>
-      <c r="CF59" s="52"/>
-      <c r="CG59" s="52"/>
-      <c r="CH59" s="52"/>
-      <c r="CI59" s="52"/>
-      <c r="CJ59" s="52"/>
-      <c r="CK59" s="52"/>
-      <c r="CL59" s="52"/>
-      <c r="CM59" s="52"/>
-      <c r="CN59" s="52"/>
-      <c r="CO59" s="52"/>
-      <c r="CP59" s="52"/>
-      <c r="CQ59" s="52"/>
+      <c r="BO59" s="60"/>
+      <c r="BP59" s="60"/>
+      <c r="BQ59" s="60"/>
+      <c r="BR59" s="60"/>
+      <c r="BS59" s="60"/>
+      <c r="BT59" s="60"/>
+      <c r="BU59" s="60"/>
+      <c r="BV59" s="60"/>
+      <c r="BW59" s="60"/>
+      <c r="BX59" s="60"/>
+      <c r="BY59" s="60"/>
+      <c r="BZ59" s="60"/>
+      <c r="CA59" s="60"/>
+      <c r="CB59" s="60"/>
+      <c r="CC59" s="60"/>
+      <c r="CD59" s="60"/>
+      <c r="CE59" s="60"/>
+      <c r="CF59" s="60"/>
+      <c r="CG59" s="60"/>
+      <c r="CH59" s="60"/>
+      <c r="CI59" s="60"/>
+      <c r="CJ59" s="60"/>
+      <c r="CK59" s="60"/>
+      <c r="CL59" s="60"/>
+      <c r="CM59" s="60"/>
+      <c r="CN59" s="60"/>
+      <c r="CO59" s="60"/>
+      <c r="CP59" s="60"/>
+      <c r="CQ59" s="60"/>
       <c r="CR59" s="41"/>
       <c r="CS59" s="41"/>
       <c r="CT59" s="41"/>
       <c r="CU59" s="41"/>
     </row>
     <row r="60" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B60" s="67" t="s">
+      <c r="B60" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="C60" s="67"/>
-      <c r="D60" s="67"/>
-      <c r="E60" s="67"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="67"/>
-      <c r="H60" s="67"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="67"/>
-      <c r="K60" s="67"/>
-      <c r="L60" s="67"/>
-      <c r="M60" s="67"/>
-      <c r="N60" s="67"/>
-      <c r="O60" s="67"/>
-      <c r="P60" s="67"/>
+      <c r="C60" s="61"/>
+      <c r="D60" s="61"/>
+      <c r="E60" s="61"/>
+      <c r="F60" s="61"/>
+      <c r="G60" s="61"/>
+      <c r="H60" s="61"/>
+      <c r="I60" s="61"/>
+      <c r="J60" s="61"/>
+      <c r="K60" s="61"/>
+      <c r="L60" s="61"/>
+      <c r="M60" s="61"/>
+      <c r="N60" s="61"/>
+      <c r="O60" s="61"/>
+      <c r="P60" s="61"/>
       <c r="Q60" s="35"/>
       <c r="R60" s="35"/>
       <c r="S60" s="35"/>
@@ -16976,36 +16948,36 @@
       <c r="W60" s="35"/>
       <c r="X60" s="35"/>
       <c r="Y60" s="35"/>
-      <c r="Z60" s="62"/>
-      <c r="AA60" s="62"/>
-      <c r="AB60" s="62"/>
-      <c r="AC60" s="62"/>
-      <c r="AD60" s="62"/>
-      <c r="AE60" s="62"/>
-      <c r="AF60" s="62"/>
-      <c r="AG60" s="62"/>
-      <c r="AH60" s="62"/>
-      <c r="AI60" s="62"/>
-      <c r="AJ60" s="62"/>
-      <c r="AK60" s="62"/>
-      <c r="AL60" s="62"/>
-      <c r="AM60" s="62"/>
-      <c r="AN60" s="62"/>
-      <c r="AO60" s="62"/>
-      <c r="AP60" s="62"/>
-      <c r="AQ60" s="62"/>
-      <c r="AR60" s="62"/>
-      <c r="AS60" s="62"/>
-      <c r="AT60" s="62"/>
-      <c r="AU60" s="62"/>
-      <c r="AV60" s="62"/>
-      <c r="AW60" s="62"/>
-      <c r="AX60" s="62"/>
-      <c r="AY60" s="62"/>
-      <c r="AZ60" s="62"/>
-      <c r="BA60" s="62"/>
-      <c r="BB60" s="62"/>
-      <c r="BC60" s="62"/>
+      <c r="Z60" s="59"/>
+      <c r="AA60" s="59"/>
+      <c r="AB60" s="59"/>
+      <c r="AC60" s="59"/>
+      <c r="AD60" s="59"/>
+      <c r="AE60" s="59"/>
+      <c r="AF60" s="59"/>
+      <c r="AG60" s="59"/>
+      <c r="AH60" s="59"/>
+      <c r="AI60" s="59"/>
+      <c r="AJ60" s="59"/>
+      <c r="AK60" s="59"/>
+      <c r="AL60" s="59"/>
+      <c r="AM60" s="59"/>
+      <c r="AN60" s="59"/>
+      <c r="AO60" s="59"/>
+      <c r="AP60" s="59"/>
+      <c r="AQ60" s="59"/>
+      <c r="AR60" s="59"/>
+      <c r="AS60" s="59"/>
+      <c r="AT60" s="59"/>
+      <c r="AU60" s="59"/>
+      <c r="AV60" s="59"/>
+      <c r="AW60" s="59"/>
+      <c r="AX60" s="59"/>
+      <c r="AY60" s="59"/>
+      <c r="AZ60" s="59"/>
+      <c r="BA60" s="59"/>
+      <c r="BB60" s="59"/>
+      <c r="BC60" s="59"/>
       <c r="BD60" s="43"/>
       <c r="BE60" s="35"/>
       <c r="BF60" s="35"/>
@@ -17016,57 +16988,57 @@
       <c r="BK60" s="35"/>
       <c r="BL60" s="35"/>
       <c r="BM60" s="35"/>
-      <c r="BN60" s="53"/>
-      <c r="BO60" s="53"/>
-      <c r="BP60" s="53"/>
-      <c r="BQ60" s="53"/>
-      <c r="BR60" s="53"/>
-      <c r="BS60" s="53"/>
-      <c r="BT60" s="53"/>
-      <c r="BU60" s="53"/>
-      <c r="BV60" s="53"/>
-      <c r="BW60" s="53"/>
-      <c r="BX60" s="53"/>
-      <c r="BY60" s="53"/>
-      <c r="BZ60" s="53"/>
-      <c r="CA60" s="53"/>
-      <c r="CB60" s="53"/>
-      <c r="CC60" s="53"/>
-      <c r="CD60" s="53"/>
-      <c r="CE60" s="53"/>
-      <c r="CF60" s="53"/>
-      <c r="CG60" s="53"/>
-      <c r="CH60" s="53"/>
-      <c r="CI60" s="53"/>
-      <c r="CJ60" s="53"/>
-      <c r="CK60" s="53"/>
-      <c r="CL60" s="53"/>
-      <c r="CM60" s="53"/>
-      <c r="CN60" s="53"/>
-      <c r="CO60" s="53"/>
-      <c r="CP60" s="53"/>
-      <c r="CQ60" s="53"/>
+      <c r="BN60" s="55"/>
+      <c r="BO60" s="55"/>
+      <c r="BP60" s="55"/>
+      <c r="BQ60" s="55"/>
+      <c r="BR60" s="55"/>
+      <c r="BS60" s="55"/>
+      <c r="BT60" s="55"/>
+      <c r="BU60" s="55"/>
+      <c r="BV60" s="55"/>
+      <c r="BW60" s="55"/>
+      <c r="BX60" s="55"/>
+      <c r="BY60" s="55"/>
+      <c r="BZ60" s="55"/>
+      <c r="CA60" s="55"/>
+      <c r="CB60" s="55"/>
+      <c r="CC60" s="55"/>
+      <c r="CD60" s="55"/>
+      <c r="CE60" s="55"/>
+      <c r="CF60" s="55"/>
+      <c r="CG60" s="55"/>
+      <c r="CH60" s="55"/>
+      <c r="CI60" s="55"/>
+      <c r="CJ60" s="55"/>
+      <c r="CK60" s="55"/>
+      <c r="CL60" s="55"/>
+      <c r="CM60" s="55"/>
+      <c r="CN60" s="55"/>
+      <c r="CO60" s="55"/>
+      <c r="CP60" s="55"/>
+      <c r="CQ60" s="55"/>
       <c r="CR60" s="41"/>
       <c r="CS60" s="41"/>
       <c r="CT60" s="41"/>
       <c r="CU60" s="41"/>
     </row>
     <row r="61" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B61" s="67"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="67"/>
-      <c r="J61" s="67"/>
-      <c r="K61" s="67"/>
-      <c r="L61" s="67"/>
-      <c r="M61" s="67"/>
-      <c r="N61" s="67"/>
-      <c r="O61" s="67"/>
-      <c r="P61" s="67"/>
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="61"/>
+      <c r="I61" s="61"/>
+      <c r="J61" s="61"/>
+      <c r="K61" s="61"/>
+      <c r="L61" s="61"/>
+      <c r="M61" s="61"/>
+      <c r="N61" s="61"/>
+      <c r="O61" s="61"/>
+      <c r="P61" s="61"/>
       <c r="Q61" s="35"/>
       <c r="R61" s="35"/>
       <c r="S61" s="35"/>
@@ -17076,36 +17048,36 @@
       <c r="W61" s="35"/>
       <c r="X61" s="35"/>
       <c r="Y61" s="35"/>
-      <c r="Z61" s="62"/>
-      <c r="AA61" s="62"/>
-      <c r="AB61" s="62"/>
-      <c r="AC61" s="62"/>
-      <c r="AD61" s="62"/>
-      <c r="AE61" s="62"/>
-      <c r="AF61" s="62"/>
-      <c r="AG61" s="62"/>
-      <c r="AH61" s="62"/>
-      <c r="AI61" s="62"/>
-      <c r="AJ61" s="62"/>
-      <c r="AK61" s="62"/>
-      <c r="AL61" s="62"/>
-      <c r="AM61" s="62"/>
-      <c r="AN61" s="62"/>
-      <c r="AO61" s="62"/>
-      <c r="AP61" s="62"/>
-      <c r="AQ61" s="62"/>
-      <c r="AR61" s="62"/>
-      <c r="AS61" s="62"/>
-      <c r="AT61" s="62"/>
-      <c r="AU61" s="62"/>
-      <c r="AV61" s="62"/>
-      <c r="AW61" s="62"/>
-      <c r="AX61" s="62"/>
-      <c r="AY61" s="62"/>
-      <c r="AZ61" s="62"/>
-      <c r="BA61" s="62"/>
-      <c r="BB61" s="62"/>
-      <c r="BC61" s="62"/>
+      <c r="Z61" s="59"/>
+      <c r="AA61" s="59"/>
+      <c r="AB61" s="59"/>
+      <c r="AC61" s="59"/>
+      <c r="AD61" s="59"/>
+      <c r="AE61" s="59"/>
+      <c r="AF61" s="59"/>
+      <c r="AG61" s="59"/>
+      <c r="AH61" s="59"/>
+      <c r="AI61" s="59"/>
+      <c r="AJ61" s="59"/>
+      <c r="AK61" s="59"/>
+      <c r="AL61" s="59"/>
+      <c r="AM61" s="59"/>
+      <c r="AN61" s="59"/>
+      <c r="AO61" s="59"/>
+      <c r="AP61" s="59"/>
+      <c r="AQ61" s="59"/>
+      <c r="AR61" s="59"/>
+      <c r="AS61" s="59"/>
+      <c r="AT61" s="59"/>
+      <c r="AU61" s="59"/>
+      <c r="AV61" s="59"/>
+      <c r="AW61" s="59"/>
+      <c r="AX61" s="59"/>
+      <c r="AY61" s="59"/>
+      <c r="AZ61" s="59"/>
+      <c r="BA61" s="59"/>
+      <c r="BB61" s="59"/>
+      <c r="BC61" s="59"/>
       <c r="BD61" s="43"/>
       <c r="BE61" s="35"/>
       <c r="BF61" s="35"/>
@@ -17116,57 +17088,57 @@
       <c r="BK61" s="35"/>
       <c r="BL61" s="35"/>
       <c r="BM61" s="35"/>
-      <c r="BN61" s="53"/>
-      <c r="BO61" s="53"/>
-      <c r="BP61" s="53"/>
-      <c r="BQ61" s="53"/>
-      <c r="BR61" s="53"/>
-      <c r="BS61" s="53"/>
-      <c r="BT61" s="53"/>
-      <c r="BU61" s="53"/>
-      <c r="BV61" s="53"/>
-      <c r="BW61" s="53"/>
-      <c r="BX61" s="53"/>
-      <c r="BY61" s="53"/>
-      <c r="BZ61" s="53"/>
-      <c r="CA61" s="53"/>
-      <c r="CB61" s="53"/>
-      <c r="CC61" s="53"/>
-      <c r="CD61" s="53"/>
-      <c r="CE61" s="53"/>
-      <c r="CF61" s="53"/>
-      <c r="CG61" s="53"/>
-      <c r="CH61" s="53"/>
-      <c r="CI61" s="53"/>
-      <c r="CJ61" s="53"/>
-      <c r="CK61" s="53"/>
-      <c r="CL61" s="53"/>
-      <c r="CM61" s="53"/>
-      <c r="CN61" s="53"/>
-      <c r="CO61" s="53"/>
-      <c r="CP61" s="53"/>
-      <c r="CQ61" s="53"/>
+      <c r="BN61" s="55"/>
+      <c r="BO61" s="55"/>
+      <c r="BP61" s="55"/>
+      <c r="BQ61" s="55"/>
+      <c r="BR61" s="55"/>
+      <c r="BS61" s="55"/>
+      <c r="BT61" s="55"/>
+      <c r="BU61" s="55"/>
+      <c r="BV61" s="55"/>
+      <c r="BW61" s="55"/>
+      <c r="BX61" s="55"/>
+      <c r="BY61" s="55"/>
+      <c r="BZ61" s="55"/>
+      <c r="CA61" s="55"/>
+      <c r="CB61" s="55"/>
+      <c r="CC61" s="55"/>
+      <c r="CD61" s="55"/>
+      <c r="CE61" s="55"/>
+      <c r="CF61" s="55"/>
+      <c r="CG61" s="55"/>
+      <c r="CH61" s="55"/>
+      <c r="CI61" s="55"/>
+      <c r="CJ61" s="55"/>
+      <c r="CK61" s="55"/>
+      <c r="CL61" s="55"/>
+      <c r="CM61" s="55"/>
+      <c r="CN61" s="55"/>
+      <c r="CO61" s="55"/>
+      <c r="CP61" s="55"/>
+      <c r="CQ61" s="55"/>
       <c r="CR61" s="41"/>
       <c r="CS61" s="41"/>
       <c r="CT61" s="41"/>
       <c r="CU61" s="41"/>
     </row>
     <row r="62" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B62" s="67"/>
-      <c r="C62" s="67"/>
-      <c r="D62" s="67"/>
-      <c r="E62" s="67"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="67"/>
-      <c r="H62" s="67"/>
-      <c r="I62" s="67"/>
-      <c r="J62" s="67"/>
-      <c r="K62" s="67"/>
-      <c r="L62" s="67"/>
-      <c r="M62" s="67"/>
-      <c r="N62" s="67"/>
-      <c r="O62" s="67"/>
-      <c r="P62" s="67"/>
+      <c r="B62" s="61"/>
+      <c r="C62" s="61"/>
+      <c r="D62" s="61"/>
+      <c r="E62" s="61"/>
+      <c r="F62" s="61"/>
+      <c r="G62" s="61"/>
+      <c r="H62" s="61"/>
+      <c r="I62" s="61"/>
+      <c r="J62" s="61"/>
+      <c r="K62" s="61"/>
+      <c r="L62" s="61"/>
+      <c r="M62" s="61"/>
+      <c r="N62" s="61"/>
+      <c r="O62" s="61"/>
+      <c r="P62" s="61"/>
       <c r="Q62" s="35"/>
       <c r="R62" s="35"/>
       <c r="S62" s="35"/>
@@ -17176,38 +17148,38 @@
       <c r="W62" s="35"/>
       <c r="X62" s="35"/>
       <c r="Y62" s="35"/>
-      <c r="Z62" s="63" t="s">
+      <c r="Z62" s="57" t="s">
         <v>121</v>
       </c>
-      <c r="AA62" s="63"/>
-      <c r="AB62" s="63"/>
-      <c r="AC62" s="63"/>
-      <c r="AD62" s="63"/>
-      <c r="AE62" s="63"/>
-      <c r="AF62" s="63"/>
-      <c r="AG62" s="63"/>
-      <c r="AH62" s="63"/>
-      <c r="AI62" s="63"/>
-      <c r="AJ62" s="63"/>
-      <c r="AK62" s="63"/>
-      <c r="AL62" s="63"/>
-      <c r="AM62" s="63"/>
-      <c r="AN62" s="63"/>
-      <c r="AO62" s="63"/>
-      <c r="AP62" s="63"/>
-      <c r="AQ62" s="63"/>
-      <c r="AR62" s="63"/>
-      <c r="AS62" s="63"/>
-      <c r="AT62" s="63"/>
-      <c r="AU62" s="63"/>
-      <c r="AV62" s="63"/>
-      <c r="AW62" s="63"/>
-      <c r="AX62" s="63"/>
-      <c r="AY62" s="63"/>
-      <c r="AZ62" s="63"/>
-      <c r="BA62" s="63"/>
-      <c r="BB62" s="63"/>
-      <c r="BC62" s="63"/>
+      <c r="AA62" s="57"/>
+      <c r="AB62" s="57"/>
+      <c r="AC62" s="57"/>
+      <c r="AD62" s="57"/>
+      <c r="AE62" s="57"/>
+      <c r="AF62" s="57"/>
+      <c r="AG62" s="57"/>
+      <c r="AH62" s="57"/>
+      <c r="AI62" s="57"/>
+      <c r="AJ62" s="57"/>
+      <c r="AK62" s="57"/>
+      <c r="AL62" s="57"/>
+      <c r="AM62" s="57"/>
+      <c r="AN62" s="57"/>
+      <c r="AO62" s="57"/>
+      <c r="AP62" s="57"/>
+      <c r="AQ62" s="57"/>
+      <c r="AR62" s="57"/>
+      <c r="AS62" s="57"/>
+      <c r="AT62" s="57"/>
+      <c r="AU62" s="57"/>
+      <c r="AV62" s="57"/>
+      <c r="AW62" s="57"/>
+      <c r="AX62" s="57"/>
+      <c r="AY62" s="57"/>
+      <c r="AZ62" s="57"/>
+      <c r="BA62" s="57"/>
+      <c r="BB62" s="57"/>
+      <c r="BC62" s="57"/>
       <c r="BD62" s="44"/>
       <c r="BE62" s="35"/>
       <c r="BF62" s="35"/>
@@ -17218,61 +17190,61 @@
       <c r="BK62" s="35"/>
       <c r="BL62" s="35"/>
       <c r="BM62" s="35"/>
-      <c r="BN62" s="54" t="s">
+      <c r="BN62" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="BO62" s="54"/>
-      <c r="BP62" s="54"/>
-      <c r="BQ62" s="54"/>
-      <c r="BR62" s="54"/>
-      <c r="BS62" s="54"/>
-      <c r="BT62" s="54"/>
-      <c r="BU62" s="54"/>
-      <c r="BV62" s="54"/>
-      <c r="BW62" s="54"/>
-      <c r="BX62" s="54"/>
-      <c r="BY62" s="54"/>
-      <c r="BZ62" s="54"/>
-      <c r="CA62" s="54"/>
-      <c r="CB62" s="54"/>
-      <c r="CC62" s="54"/>
-      <c r="CD62" s="54"/>
-      <c r="CE62" s="54"/>
-      <c r="CF62" s="54"/>
-      <c r="CG62" s="54"/>
-      <c r="CH62" s="54"/>
-      <c r="CI62" s="54"/>
-      <c r="CJ62" s="54"/>
-      <c r="CK62" s="54"/>
-      <c r="CL62" s="54"/>
-      <c r="CM62" s="54"/>
-      <c r="CN62" s="54"/>
-      <c r="CO62" s="54"/>
-      <c r="CP62" s="54"/>
-      <c r="CQ62" s="54"/>
+      <c r="BO62" s="56"/>
+      <c r="BP62" s="56"/>
+      <c r="BQ62" s="56"/>
+      <c r="BR62" s="56"/>
+      <c r="BS62" s="56"/>
+      <c r="BT62" s="56"/>
+      <c r="BU62" s="56"/>
+      <c r="BV62" s="56"/>
+      <c r="BW62" s="56"/>
+      <c r="BX62" s="56"/>
+      <c r="BY62" s="56"/>
+      <c r="BZ62" s="56"/>
+      <c r="CA62" s="56"/>
+      <c r="CB62" s="56"/>
+      <c r="CC62" s="56"/>
+      <c r="CD62" s="56"/>
+      <c r="CE62" s="56"/>
+      <c r="CF62" s="56"/>
+      <c r="CG62" s="56"/>
+      <c r="CH62" s="56"/>
+      <c r="CI62" s="56"/>
+      <c r="CJ62" s="56"/>
+      <c r="CK62" s="56"/>
+      <c r="CL62" s="56"/>
+      <c r="CM62" s="56"/>
+      <c r="CN62" s="56"/>
+      <c r="CO62" s="56"/>
+      <c r="CP62" s="56"/>
+      <c r="CQ62" s="56"/>
       <c r="CR62" s="42"/>
       <c r="CS62" s="42"/>
       <c r="CT62" s="42"/>
       <c r="CU62" s="42"/>
     </row>
     <row r="63" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B63" s="69" t="s">
+      <c r="B63" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="69"/>
-      <c r="D63" s="69"/>
-      <c r="E63" s="69"/>
-      <c r="F63" s="69"/>
-      <c r="G63" s="69"/>
-      <c r="H63" s="69"/>
-      <c r="I63" s="69"/>
-      <c r="J63" s="69"/>
-      <c r="K63" s="69"/>
-      <c r="L63" s="69"/>
-      <c r="M63" s="69"/>
-      <c r="N63" s="69"/>
-      <c r="O63" s="69"/>
-      <c r="P63" s="69"/>
+      <c r="C63" s="62"/>
+      <c r="D63" s="62"/>
+      <c r="E63" s="62"/>
+      <c r="F63" s="62"/>
+      <c r="G63" s="62"/>
+      <c r="H63" s="62"/>
+      <c r="I63" s="62"/>
+      <c r="J63" s="62"/>
+      <c r="K63" s="62"/>
+      <c r="L63" s="62"/>
+      <c r="M63" s="62"/>
+      <c r="N63" s="62"/>
+      <c r="O63" s="62"/>
+      <c r="P63" s="62"/>
       <c r="Q63" s="35"/>
       <c r="R63" s="35"/>
       <c r="S63" s="35"/>
@@ -17282,36 +17254,36 @@
       <c r="W63" s="35"/>
       <c r="X63" s="35"/>
       <c r="Y63" s="35"/>
-      <c r="Z63" s="63"/>
-      <c r="AA63" s="63"/>
-      <c r="AB63" s="63"/>
-      <c r="AC63" s="63"/>
-      <c r="AD63" s="63"/>
-      <c r="AE63" s="63"/>
-      <c r="AF63" s="63"/>
-      <c r="AG63" s="63"/>
-      <c r="AH63" s="63"/>
-      <c r="AI63" s="63"/>
-      <c r="AJ63" s="63"/>
-      <c r="AK63" s="63"/>
-      <c r="AL63" s="63"/>
-      <c r="AM63" s="63"/>
-      <c r="AN63" s="63"/>
-      <c r="AO63" s="63"/>
-      <c r="AP63" s="63"/>
-      <c r="AQ63" s="63"/>
-      <c r="AR63" s="63"/>
-      <c r="AS63" s="63"/>
-      <c r="AT63" s="63"/>
-      <c r="AU63" s="63"/>
-      <c r="AV63" s="63"/>
-      <c r="AW63" s="63"/>
-      <c r="AX63" s="63"/>
-      <c r="AY63" s="63"/>
-      <c r="AZ63" s="63"/>
-      <c r="BA63" s="63"/>
-      <c r="BB63" s="63"/>
-      <c r="BC63" s="63"/>
+      <c r="Z63" s="57"/>
+      <c r="AA63" s="57"/>
+      <c r="AB63" s="57"/>
+      <c r="AC63" s="57"/>
+      <c r="AD63" s="57"/>
+      <c r="AE63" s="57"/>
+      <c r="AF63" s="57"/>
+      <c r="AG63" s="57"/>
+      <c r="AH63" s="57"/>
+      <c r="AI63" s="57"/>
+      <c r="AJ63" s="57"/>
+      <c r="AK63" s="57"/>
+      <c r="AL63" s="57"/>
+      <c r="AM63" s="57"/>
+      <c r="AN63" s="57"/>
+      <c r="AO63" s="57"/>
+      <c r="AP63" s="57"/>
+      <c r="AQ63" s="57"/>
+      <c r="AR63" s="57"/>
+      <c r="AS63" s="57"/>
+      <c r="AT63" s="57"/>
+      <c r="AU63" s="57"/>
+      <c r="AV63" s="57"/>
+      <c r="AW63" s="57"/>
+      <c r="AX63" s="57"/>
+      <c r="AY63" s="57"/>
+      <c r="AZ63" s="57"/>
+      <c r="BA63" s="57"/>
+      <c r="BB63" s="57"/>
+      <c r="BC63" s="57"/>
       <c r="BD63" s="44"/>
       <c r="BE63" s="35"/>
       <c r="BF63" s="35"/>
@@ -17322,57 +17294,57 @@
       <c r="BK63" s="35"/>
       <c r="BL63" s="35"/>
       <c r="BM63" s="35"/>
-      <c r="BN63" s="54"/>
-      <c r="BO63" s="54"/>
-      <c r="BP63" s="54"/>
-      <c r="BQ63" s="54"/>
-      <c r="BR63" s="54"/>
-      <c r="BS63" s="54"/>
-      <c r="BT63" s="54"/>
-      <c r="BU63" s="54"/>
-      <c r="BV63" s="54"/>
-      <c r="BW63" s="54"/>
-      <c r="BX63" s="54"/>
-      <c r="BY63" s="54"/>
-      <c r="BZ63" s="54"/>
-      <c r="CA63" s="54"/>
-      <c r="CB63" s="54"/>
-      <c r="CC63" s="54"/>
-      <c r="CD63" s="54"/>
-      <c r="CE63" s="54"/>
-      <c r="CF63" s="54"/>
-      <c r="CG63" s="54"/>
-      <c r="CH63" s="54"/>
-      <c r="CI63" s="54"/>
-      <c r="CJ63" s="54"/>
-      <c r="CK63" s="54"/>
-      <c r="CL63" s="54"/>
-      <c r="CM63" s="54"/>
-      <c r="CN63" s="54"/>
-      <c r="CO63" s="54"/>
-      <c r="CP63" s="54"/>
-      <c r="CQ63" s="54"/>
+      <c r="BN63" s="56"/>
+      <c r="BO63" s="56"/>
+      <c r="BP63" s="56"/>
+      <c r="BQ63" s="56"/>
+      <c r="BR63" s="56"/>
+      <c r="BS63" s="56"/>
+      <c r="BT63" s="56"/>
+      <c r="BU63" s="56"/>
+      <c r="BV63" s="56"/>
+      <c r="BW63" s="56"/>
+      <c r="BX63" s="56"/>
+      <c r="BY63" s="56"/>
+      <c r="BZ63" s="56"/>
+      <c r="CA63" s="56"/>
+      <c r="CB63" s="56"/>
+      <c r="CC63" s="56"/>
+      <c r="CD63" s="56"/>
+      <c r="CE63" s="56"/>
+      <c r="CF63" s="56"/>
+      <c r="CG63" s="56"/>
+      <c r="CH63" s="56"/>
+      <c r="CI63" s="56"/>
+      <c r="CJ63" s="56"/>
+      <c r="CK63" s="56"/>
+      <c r="CL63" s="56"/>
+      <c r="CM63" s="56"/>
+      <c r="CN63" s="56"/>
+      <c r="CO63" s="56"/>
+      <c r="CP63" s="56"/>
+      <c r="CQ63" s="56"/>
       <c r="CR63" s="42"/>
       <c r="CS63" s="42"/>
       <c r="CT63" s="42"/>
       <c r="CU63" s="42"/>
     </row>
     <row r="64" spans="2:99" s="1" customFormat="1" ht="6" customHeight="1">
-      <c r="B64" s="69"/>
-      <c r="C64" s="69"/>
-      <c r="D64" s="69"/>
-      <c r="E64" s="69"/>
-      <c r="F64" s="69"/>
-      <c r="G64" s="69"/>
-      <c r="H64" s="69"/>
-      <c r="I64" s="69"/>
-      <c r="J64" s="69"/>
-      <c r="K64" s="69"/>
-      <c r="L64" s="69"/>
-      <c r="M64" s="69"/>
-      <c r="N64" s="69"/>
-      <c r="O64" s="69"/>
-      <c r="P64" s="69"/>
+      <c r="B64" s="62"/>
+      <c r="C64" s="62"/>
+      <c r="D64" s="62"/>
+      <c r="E64" s="62"/>
+      <c r="F64" s="62"/>
+      <c r="G64" s="62"/>
+      <c r="H64" s="62"/>
+      <c r="I64" s="62"/>
+      <c r="J64" s="62"/>
+      <c r="K64" s="62"/>
+      <c r="L64" s="62"/>
+      <c r="M64" s="62"/>
+      <c r="N64" s="62"/>
+      <c r="O64" s="62"/>
+      <c r="P64" s="62"/>
       <c r="Q64" s="35"/>
       <c r="R64" s="35"/>
       <c r="S64" s="35"/>
@@ -17466,38 +17438,38 @@
       <c r="W65" s="39"/>
       <c r="X65" s="39"/>
       <c r="Y65" s="39"/>
-      <c r="Z65" s="60" t="s">
+      <c r="Z65" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="AA65" s="60"/>
-      <c r="AB65" s="60"/>
-      <c r="AC65" s="60"/>
-      <c r="AD65" s="60"/>
-      <c r="AE65" s="60"/>
-      <c r="AF65" s="60"/>
-      <c r="AG65" s="60"/>
-      <c r="AH65" s="60"/>
-      <c r="AI65" s="60"/>
-      <c r="AJ65" s="60"/>
-      <c r="AK65" s="60"/>
-      <c r="AL65" s="60"/>
-      <c r="AM65" s="60"/>
-      <c r="AN65" s="60"/>
-      <c r="AO65" s="60"/>
-      <c r="AP65" s="60"/>
-      <c r="AQ65" s="60"/>
-      <c r="AR65" s="60"/>
-      <c r="AS65" s="60"/>
-      <c r="AT65" s="60"/>
-      <c r="AU65" s="60"/>
-      <c r="AV65" s="60"/>
-      <c r="AW65" s="60"/>
-      <c r="AX65" s="60"/>
-      <c r="AY65" s="60"/>
-      <c r="AZ65" s="60"/>
-      <c r="BA65" s="60"/>
-      <c r="BB65" s="60"/>
-      <c r="BC65" s="60"/>
+      <c r="AA65" s="53"/>
+      <c r="AB65" s="53"/>
+      <c r="AC65" s="53"/>
+      <c r="AD65" s="53"/>
+      <c r="AE65" s="53"/>
+      <c r="AF65" s="53"/>
+      <c r="AG65" s="53"/>
+      <c r="AH65" s="53"/>
+      <c r="AI65" s="53"/>
+      <c r="AJ65" s="53"/>
+      <c r="AK65" s="53"/>
+      <c r="AL65" s="53"/>
+      <c r="AM65" s="53"/>
+      <c r="AN65" s="53"/>
+      <c r="AO65" s="53"/>
+      <c r="AP65" s="53"/>
+      <c r="AQ65" s="53"/>
+      <c r="AR65" s="53"/>
+      <c r="AS65" s="53"/>
+      <c r="AT65" s="53"/>
+      <c r="AU65" s="53"/>
+      <c r="AV65" s="53"/>
+      <c r="AW65" s="53"/>
+      <c r="AX65" s="53"/>
+      <c r="AY65" s="53"/>
+      <c r="AZ65" s="53"/>
+      <c r="BA65" s="53"/>
+      <c r="BB65" s="53"/>
+      <c r="BC65" s="53"/>
       <c r="BD65" s="48"/>
       <c r="BE65" s="35"/>
       <c r="BF65" s="35"/>
@@ -17508,38 +17480,38 @@
       <c r="BK65" s="35"/>
       <c r="BL65" s="35"/>
       <c r="BM65" s="35"/>
-      <c r="BN65" s="53" t="s">
+      <c r="BN65" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="BO65" s="53"/>
-      <c r="BP65" s="53"/>
-      <c r="BQ65" s="53"/>
-      <c r="BR65" s="53"/>
-      <c r="BS65" s="53"/>
-      <c r="BT65" s="53"/>
-      <c r="BU65" s="53"/>
-      <c r="BV65" s="53"/>
-      <c r="BW65" s="53"/>
-      <c r="BX65" s="53"/>
-      <c r="BY65" s="53"/>
-      <c r="BZ65" s="53"/>
-      <c r="CA65" s="53"/>
-      <c r="CB65" s="53"/>
-      <c r="CC65" s="53"/>
-      <c r="CD65" s="53"/>
-      <c r="CE65" s="53"/>
-      <c r="CF65" s="53"/>
-      <c r="CG65" s="53"/>
-      <c r="CH65" s="53"/>
-      <c r="CI65" s="53"/>
-      <c r="CJ65" s="53"/>
-      <c r="CK65" s="53"/>
-      <c r="CL65" s="53"/>
-      <c r="CM65" s="53"/>
-      <c r="CN65" s="53"/>
-      <c r="CO65" s="53"/>
-      <c r="CP65" s="53"/>
-      <c r="CQ65" s="53"/>
+      <c r="BO65" s="55"/>
+      <c r="BP65" s="55"/>
+      <c r="BQ65" s="55"/>
+      <c r="BR65" s="55"/>
+      <c r="BS65" s="55"/>
+      <c r="BT65" s="55"/>
+      <c r="BU65" s="55"/>
+      <c r="BV65" s="55"/>
+      <c r="BW65" s="55"/>
+      <c r="BX65" s="55"/>
+      <c r="BY65" s="55"/>
+      <c r="BZ65" s="55"/>
+      <c r="CA65" s="55"/>
+      <c r="CB65" s="55"/>
+      <c r="CC65" s="55"/>
+      <c r="CD65" s="55"/>
+      <c r="CE65" s="55"/>
+      <c r="CF65" s="55"/>
+      <c r="CG65" s="55"/>
+      <c r="CH65" s="55"/>
+      <c r="CI65" s="55"/>
+      <c r="CJ65" s="55"/>
+      <c r="CK65" s="55"/>
+      <c r="CL65" s="55"/>
+      <c r="CM65" s="55"/>
+      <c r="CN65" s="55"/>
+      <c r="CO65" s="55"/>
+      <c r="CP65" s="55"/>
+      <c r="CQ65" s="55"/>
       <c r="CR65" s="41"/>
       <c r="CS65" s="41"/>
       <c r="CT65" s="41"/>
@@ -17554,36 +17526,36 @@
       <c r="W66" s="35"/>
       <c r="X66" s="35"/>
       <c r="Y66" s="35"/>
-      <c r="Z66" s="61"/>
-      <c r="AA66" s="61"/>
-      <c r="AB66" s="61"/>
-      <c r="AC66" s="61"/>
-      <c r="AD66" s="61"/>
-      <c r="AE66" s="61"/>
-      <c r="AF66" s="61"/>
-      <c r="AG66" s="61"/>
-      <c r="AH66" s="61"/>
-      <c r="AI66" s="61"/>
-      <c r="AJ66" s="61"/>
-      <c r="AK66" s="61"/>
-      <c r="AL66" s="61"/>
-      <c r="AM66" s="61"/>
-      <c r="AN66" s="61"/>
-      <c r="AO66" s="61"/>
-      <c r="AP66" s="61"/>
-      <c r="AQ66" s="61"/>
-      <c r="AR66" s="61"/>
-      <c r="AS66" s="61"/>
-      <c r="AT66" s="61"/>
-      <c r="AU66" s="61"/>
-      <c r="AV66" s="61"/>
-      <c r="AW66" s="61"/>
-      <c r="AX66" s="61"/>
-      <c r="AY66" s="61"/>
-      <c r="AZ66" s="61"/>
-      <c r="BA66" s="61"/>
-      <c r="BB66" s="61"/>
-      <c r="BC66" s="61"/>
+      <c r="Z66" s="54"/>
+      <c r="AA66" s="54"/>
+      <c r="AB66" s="54"/>
+      <c r="AC66" s="54"/>
+      <c r="AD66" s="54"/>
+      <c r="AE66" s="54"/>
+      <c r="AF66" s="54"/>
+      <c r="AG66" s="54"/>
+      <c r="AH66" s="54"/>
+      <c r="AI66" s="54"/>
+      <c r="AJ66" s="54"/>
+      <c r="AK66" s="54"/>
+      <c r="AL66" s="54"/>
+      <c r="AM66" s="54"/>
+      <c r="AN66" s="54"/>
+      <c r="AO66" s="54"/>
+      <c r="AP66" s="54"/>
+      <c r="AQ66" s="54"/>
+      <c r="AR66" s="54"/>
+      <c r="AS66" s="54"/>
+      <c r="AT66" s="54"/>
+      <c r="AU66" s="54"/>
+      <c r="AV66" s="54"/>
+      <c r="AW66" s="54"/>
+      <c r="AX66" s="54"/>
+      <c r="AY66" s="54"/>
+      <c r="AZ66" s="54"/>
+      <c r="BA66" s="54"/>
+      <c r="BB66" s="54"/>
+      <c r="BC66" s="54"/>
       <c r="BD66" s="48"/>
       <c r="BE66" s="35"/>
       <c r="BF66" s="35"/>
@@ -17594,36 +17566,36 @@
       <c r="BK66" s="35"/>
       <c r="BL66" s="35"/>
       <c r="BM66" s="35"/>
-      <c r="BN66" s="53"/>
-      <c r="BO66" s="53"/>
-      <c r="BP66" s="53"/>
-      <c r="BQ66" s="53"/>
-      <c r="BR66" s="53"/>
-      <c r="BS66" s="53"/>
-      <c r="BT66" s="53"/>
-      <c r="BU66" s="53"/>
-      <c r="BV66" s="53"/>
-      <c r="BW66" s="53"/>
-      <c r="BX66" s="53"/>
-      <c r="BY66" s="53"/>
-      <c r="BZ66" s="53"/>
-      <c r="CA66" s="53"/>
-      <c r="CB66" s="53"/>
-      <c r="CC66" s="53"/>
-      <c r="CD66" s="53"/>
-      <c r="CE66" s="53"/>
-      <c r="CF66" s="53"/>
-      <c r="CG66" s="53"/>
-      <c r="CH66" s="53"/>
-      <c r="CI66" s="53"/>
-      <c r="CJ66" s="53"/>
-      <c r="CK66" s="53"/>
-      <c r="CL66" s="53"/>
-      <c r="CM66" s="53"/>
-      <c r="CN66" s="53"/>
-      <c r="CO66" s="53"/>
-      <c r="CP66" s="53"/>
-      <c r="CQ66" s="53"/>
+      <c r="BN66" s="55"/>
+      <c r="BO66" s="55"/>
+      <c r="BP66" s="55"/>
+      <c r="BQ66" s="55"/>
+      <c r="BR66" s="55"/>
+      <c r="BS66" s="55"/>
+      <c r="BT66" s="55"/>
+      <c r="BU66" s="55"/>
+      <c r="BV66" s="55"/>
+      <c r="BW66" s="55"/>
+      <c r="BX66" s="55"/>
+      <c r="BY66" s="55"/>
+      <c r="BZ66" s="55"/>
+      <c r="CA66" s="55"/>
+      <c r="CB66" s="55"/>
+      <c r="CC66" s="55"/>
+      <c r="CD66" s="55"/>
+      <c r="CE66" s="55"/>
+      <c r="CF66" s="55"/>
+      <c r="CG66" s="55"/>
+      <c r="CH66" s="55"/>
+      <c r="CI66" s="55"/>
+      <c r="CJ66" s="55"/>
+      <c r="CK66" s="55"/>
+      <c r="CL66" s="55"/>
+      <c r="CM66" s="55"/>
+      <c r="CN66" s="55"/>
+      <c r="CO66" s="55"/>
+      <c r="CP66" s="55"/>
+      <c r="CQ66" s="55"/>
       <c r="CR66" s="41"/>
       <c r="CS66" s="41"/>
       <c r="CT66" s="41"/>
@@ -17638,36 +17610,36 @@
       <c r="W67" s="35"/>
       <c r="X67" s="35"/>
       <c r="Y67" s="35"/>
-      <c r="Z67" s="61"/>
-      <c r="AA67" s="61"/>
-      <c r="AB67" s="61"/>
-      <c r="AC67" s="61"/>
-      <c r="AD67" s="61"/>
-      <c r="AE67" s="61"/>
-      <c r="AF67" s="61"/>
-      <c r="AG67" s="61"/>
-      <c r="AH67" s="61"/>
-      <c r="AI67" s="61"/>
-      <c r="AJ67" s="61"/>
-      <c r="AK67" s="61"/>
-      <c r="AL67" s="61"/>
-      <c r="AM67" s="61"/>
-      <c r="AN67" s="61"/>
-      <c r="AO67" s="61"/>
-      <c r="AP67" s="61"/>
-      <c r="AQ67" s="61"/>
-      <c r="AR67" s="61"/>
-      <c r="AS67" s="61"/>
-      <c r="AT67" s="61"/>
-      <c r="AU67" s="61"/>
-      <c r="AV67" s="61"/>
-      <c r="AW67" s="61"/>
-      <c r="AX67" s="61"/>
-      <c r="AY67" s="61"/>
-      <c r="AZ67" s="61"/>
-      <c r="BA67" s="61"/>
-      <c r="BB67" s="61"/>
-      <c r="BC67" s="61"/>
+      <c r="Z67" s="54"/>
+      <c r="AA67" s="54"/>
+      <c r="AB67" s="54"/>
+      <c r="AC67" s="54"/>
+      <c r="AD67" s="54"/>
+      <c r="AE67" s="54"/>
+      <c r="AF67" s="54"/>
+      <c r="AG67" s="54"/>
+      <c r="AH67" s="54"/>
+      <c r="AI67" s="54"/>
+      <c r="AJ67" s="54"/>
+      <c r="AK67" s="54"/>
+      <c r="AL67" s="54"/>
+      <c r="AM67" s="54"/>
+      <c r="AN67" s="54"/>
+      <c r="AO67" s="54"/>
+      <c r="AP67" s="54"/>
+      <c r="AQ67" s="54"/>
+      <c r="AR67" s="54"/>
+      <c r="AS67" s="54"/>
+      <c r="AT67" s="54"/>
+      <c r="AU67" s="54"/>
+      <c r="AV67" s="54"/>
+      <c r="AW67" s="54"/>
+      <c r="AX67" s="54"/>
+      <c r="AY67" s="54"/>
+      <c r="AZ67" s="54"/>
+      <c r="BA67" s="54"/>
+      <c r="BB67" s="54"/>
+      <c r="BC67" s="54"/>
       <c r="BD67" s="48"/>
       <c r="BE67" s="35"/>
       <c r="BF67" s="35"/>
@@ -17678,36 +17650,36 @@
       <c r="BK67" s="35"/>
       <c r="BL67" s="35"/>
       <c r="BM67" s="35"/>
-      <c r="BN67" s="53"/>
-      <c r="BO67" s="53"/>
-      <c r="BP67" s="53"/>
-      <c r="BQ67" s="53"/>
-      <c r="BR67" s="53"/>
-      <c r="BS67" s="53"/>
-      <c r="BT67" s="53"/>
-      <c r="BU67" s="53"/>
-      <c r="BV67" s="53"/>
-      <c r="BW67" s="53"/>
-      <c r="BX67" s="53"/>
-      <c r="BY67" s="53"/>
-      <c r="BZ67" s="53"/>
-      <c r="CA67" s="53"/>
-      <c r="CB67" s="53"/>
-      <c r="CC67" s="53"/>
-      <c r="CD67" s="53"/>
-      <c r="CE67" s="53"/>
-      <c r="CF67" s="53"/>
-      <c r="CG67" s="53"/>
-      <c r="CH67" s="53"/>
-      <c r="CI67" s="53"/>
-      <c r="CJ67" s="53"/>
-      <c r="CK67" s="53"/>
-      <c r="CL67" s="53"/>
-      <c r="CM67" s="53"/>
-      <c r="CN67" s="53"/>
-      <c r="CO67" s="53"/>
-      <c r="CP67" s="53"/>
-      <c r="CQ67" s="53"/>
+      <c r="BN67" s="55"/>
+      <c r="BO67" s="55"/>
+      <c r="BP67" s="55"/>
+      <c r="BQ67" s="55"/>
+      <c r="BR67" s="55"/>
+      <c r="BS67" s="55"/>
+      <c r="BT67" s="55"/>
+      <c r="BU67" s="55"/>
+      <c r="BV67" s="55"/>
+      <c r="BW67" s="55"/>
+      <c r="BX67" s="55"/>
+      <c r="BY67" s="55"/>
+      <c r="BZ67" s="55"/>
+      <c r="CA67" s="55"/>
+      <c r="CB67" s="55"/>
+      <c r="CC67" s="55"/>
+      <c r="CD67" s="55"/>
+      <c r="CE67" s="55"/>
+      <c r="CF67" s="55"/>
+      <c r="CG67" s="55"/>
+      <c r="CH67" s="55"/>
+      <c r="CI67" s="55"/>
+      <c r="CJ67" s="55"/>
+      <c r="CK67" s="55"/>
+      <c r="CL67" s="55"/>
+      <c r="CM67" s="55"/>
+      <c r="CN67" s="55"/>
+      <c r="CO67" s="55"/>
+      <c r="CP67" s="55"/>
+      <c r="CQ67" s="55"/>
       <c r="CR67" s="41"/>
       <c r="CS67" s="41"/>
       <c r="CT67" s="41"/>
@@ -17722,36 +17694,36 @@
       <c r="W68" s="35"/>
       <c r="X68" s="35"/>
       <c r="Y68" s="35"/>
-      <c r="Z68" s="61"/>
-      <c r="AA68" s="61"/>
-      <c r="AB68" s="61"/>
-      <c r="AC68" s="61"/>
-      <c r="AD68" s="61"/>
-      <c r="AE68" s="61"/>
-      <c r="AF68" s="61"/>
-      <c r="AG68" s="61"/>
-      <c r="AH68" s="61"/>
-      <c r="AI68" s="61"/>
-      <c r="AJ68" s="61"/>
-      <c r="AK68" s="61"/>
-      <c r="AL68" s="61"/>
-      <c r="AM68" s="61"/>
-      <c r="AN68" s="61"/>
-      <c r="AO68" s="61"/>
-      <c r="AP68" s="61"/>
-      <c r="AQ68" s="61"/>
-      <c r="AR68" s="61"/>
-      <c r="AS68" s="61"/>
-      <c r="AT68" s="61"/>
-      <c r="AU68" s="61"/>
-      <c r="AV68" s="61"/>
-      <c r="AW68" s="61"/>
-      <c r="AX68" s="61"/>
-      <c r="AY68" s="61"/>
-      <c r="AZ68" s="61"/>
-      <c r="BA68" s="61"/>
-      <c r="BB68" s="61"/>
-      <c r="BC68" s="61"/>
+      <c r="Z68" s="54"/>
+      <c r="AA68" s="54"/>
+      <c r="AB68" s="54"/>
+      <c r="AC68" s="54"/>
+      <c r="AD68" s="54"/>
+      <c r="AE68" s="54"/>
+      <c r="AF68" s="54"/>
+      <c r="AG68" s="54"/>
+      <c r="AH68" s="54"/>
+      <c r="AI68" s="54"/>
+      <c r="AJ68" s="54"/>
+      <c r="AK68" s="54"/>
+      <c r="AL68" s="54"/>
+      <c r="AM68" s="54"/>
+      <c r="AN68" s="54"/>
+      <c r="AO68" s="54"/>
+      <c r="AP68" s="54"/>
+      <c r="AQ68" s="54"/>
+      <c r="AR68" s="54"/>
+      <c r="AS68" s="54"/>
+      <c r="AT68" s="54"/>
+      <c r="AU68" s="54"/>
+      <c r="AV68" s="54"/>
+      <c r="AW68" s="54"/>
+      <c r="AX68" s="54"/>
+      <c r="AY68" s="54"/>
+      <c r="AZ68" s="54"/>
+      <c r="BA68" s="54"/>
+      <c r="BB68" s="54"/>
+      <c r="BC68" s="54"/>
       <c r="BD68" s="48"/>
       <c r="BE68" s="35"/>
       <c r="BF68" s="35"/>
@@ -17762,38 +17734,38 @@
       <c r="BK68" s="35"/>
       <c r="BL68" s="35"/>
       <c r="BM68" s="35"/>
-      <c r="BN68" s="54" t="s">
+      <c r="BN68" s="56" t="s">
         <v>125</v>
       </c>
-      <c r="BO68" s="54"/>
-      <c r="BP68" s="54"/>
-      <c r="BQ68" s="54"/>
-      <c r="BR68" s="54"/>
-      <c r="BS68" s="54"/>
-      <c r="BT68" s="54"/>
-      <c r="BU68" s="54"/>
-      <c r="BV68" s="54"/>
-      <c r="BW68" s="54"/>
-      <c r="BX68" s="54"/>
-      <c r="BY68" s="54"/>
-      <c r="BZ68" s="54"/>
-      <c r="CA68" s="54"/>
-      <c r="CB68" s="54"/>
-      <c r="CC68" s="54"/>
-      <c r="CD68" s="54"/>
-      <c r="CE68" s="54"/>
-      <c r="CF68" s="54"/>
-      <c r="CG68" s="54"/>
-      <c r="CH68" s="54"/>
-      <c r="CI68" s="54"/>
-      <c r="CJ68" s="54"/>
-      <c r="CK68" s="54"/>
-      <c r="CL68" s="54"/>
-      <c r="CM68" s="54"/>
-      <c r="CN68" s="54"/>
-      <c r="CO68" s="54"/>
-      <c r="CP68" s="54"/>
-      <c r="CQ68" s="54"/>
+      <c r="BO68" s="56"/>
+      <c r="BP68" s="56"/>
+      <c r="BQ68" s="56"/>
+      <c r="BR68" s="56"/>
+      <c r="BS68" s="56"/>
+      <c r="BT68" s="56"/>
+      <c r="BU68" s="56"/>
+      <c r="BV68" s="56"/>
+      <c r="BW68" s="56"/>
+      <c r="BX68" s="56"/>
+      <c r="BY68" s="56"/>
+      <c r="BZ68" s="56"/>
+      <c r="CA68" s="56"/>
+      <c r="CB68" s="56"/>
+      <c r="CC68" s="56"/>
+      <c r="CD68" s="56"/>
+      <c r="CE68" s="56"/>
+      <c r="CF68" s="56"/>
+      <c r="CG68" s="56"/>
+      <c r="CH68" s="56"/>
+      <c r="CI68" s="56"/>
+      <c r="CJ68" s="56"/>
+      <c r="CK68" s="56"/>
+      <c r="CL68" s="56"/>
+      <c r="CM68" s="56"/>
+      <c r="CN68" s="56"/>
+      <c r="CO68" s="56"/>
+      <c r="CP68" s="56"/>
+      <c r="CQ68" s="56"/>
       <c r="CR68" s="42"/>
       <c r="CS68" s="42"/>
       <c r="CT68" s="42"/>
@@ -17808,36 +17780,36 @@
       <c r="W69" s="35"/>
       <c r="X69" s="35"/>
       <c r="Y69" s="35"/>
-      <c r="Z69" s="61"/>
-      <c r="AA69" s="61"/>
-      <c r="AB69" s="61"/>
-      <c r="AC69" s="61"/>
-      <c r="AD69" s="61"/>
-      <c r="AE69" s="61"/>
-      <c r="AF69" s="61"/>
-      <c r="AG69" s="61"/>
-      <c r="AH69" s="61"/>
-      <c r="AI69" s="61"/>
-      <c r="AJ69" s="61"/>
-      <c r="AK69" s="61"/>
-      <c r="AL69" s="61"/>
-      <c r="AM69" s="61"/>
-      <c r="AN69" s="61"/>
-      <c r="AO69" s="61"/>
-      <c r="AP69" s="61"/>
-      <c r="AQ69" s="61"/>
-      <c r="AR69" s="61"/>
-      <c r="AS69" s="61"/>
-      <c r="AT69" s="61"/>
-      <c r="AU69" s="61"/>
-      <c r="AV69" s="61"/>
-      <c r="AW69" s="61"/>
-      <c r="AX69" s="61"/>
-      <c r="AY69" s="61"/>
-      <c r="AZ69" s="61"/>
-      <c r="BA69" s="61"/>
-      <c r="BB69" s="61"/>
-      <c r="BC69" s="61"/>
+      <c r="Z69" s="54"/>
+      <c r="AA69" s="54"/>
+      <c r="AB69" s="54"/>
+      <c r="AC69" s="54"/>
+      <c r="AD69" s="54"/>
+      <c r="AE69" s="54"/>
+      <c r="AF69" s="54"/>
+      <c r="AG69" s="54"/>
+      <c r="AH69" s="54"/>
+      <c r="AI69" s="54"/>
+      <c r="AJ69" s="54"/>
+      <c r="AK69" s="54"/>
+      <c r="AL69" s="54"/>
+      <c r="AM69" s="54"/>
+      <c r="AN69" s="54"/>
+      <c r="AO69" s="54"/>
+      <c r="AP69" s="54"/>
+      <c r="AQ69" s="54"/>
+      <c r="AR69" s="54"/>
+      <c r="AS69" s="54"/>
+      <c r="AT69" s="54"/>
+      <c r="AU69" s="54"/>
+      <c r="AV69" s="54"/>
+      <c r="AW69" s="54"/>
+      <c r="AX69" s="54"/>
+      <c r="AY69" s="54"/>
+      <c r="AZ69" s="54"/>
+      <c r="BA69" s="54"/>
+      <c r="BB69" s="54"/>
+      <c r="BC69" s="54"/>
       <c r="BD69" s="48"/>
       <c r="BE69" s="35"/>
       <c r="BF69" s="35"/>
@@ -17848,36 +17820,36 @@
       <c r="BK69" s="35"/>
       <c r="BL69" s="35"/>
       <c r="BM69" s="35"/>
-      <c r="BN69" s="54"/>
-      <c r="BO69" s="54"/>
-      <c r="BP69" s="54"/>
-      <c r="BQ69" s="54"/>
-      <c r="BR69" s="54"/>
-      <c r="BS69" s="54"/>
-      <c r="BT69" s="54"/>
-      <c r="BU69" s="54"/>
-      <c r="BV69" s="54"/>
-      <c r="BW69" s="54"/>
-      <c r="BX69" s="54"/>
-      <c r="BY69" s="54"/>
-      <c r="BZ69" s="54"/>
-      <c r="CA69" s="54"/>
-      <c r="CB69" s="54"/>
-      <c r="CC69" s="54"/>
-      <c r="CD69" s="54"/>
-      <c r="CE69" s="54"/>
-      <c r="CF69" s="54"/>
-      <c r="CG69" s="54"/>
-      <c r="CH69" s="54"/>
-      <c r="CI69" s="54"/>
-      <c r="CJ69" s="54"/>
-      <c r="CK69" s="54"/>
-      <c r="CL69" s="54"/>
-      <c r="CM69" s="54"/>
-      <c r="CN69" s="54"/>
-      <c r="CO69" s="54"/>
-      <c r="CP69" s="54"/>
-      <c r="CQ69" s="54"/>
+      <c r="BN69" s="56"/>
+      <c r="BO69" s="56"/>
+      <c r="BP69" s="56"/>
+      <c r="BQ69" s="56"/>
+      <c r="BR69" s="56"/>
+      <c r="BS69" s="56"/>
+      <c r="BT69" s="56"/>
+      <c r="BU69" s="56"/>
+      <c r="BV69" s="56"/>
+      <c r="BW69" s="56"/>
+      <c r="BX69" s="56"/>
+      <c r="BY69" s="56"/>
+      <c r="BZ69" s="56"/>
+      <c r="CA69" s="56"/>
+      <c r="CB69" s="56"/>
+      <c r="CC69" s="56"/>
+      <c r="CD69" s="56"/>
+      <c r="CE69" s="56"/>
+      <c r="CF69" s="56"/>
+      <c r="CG69" s="56"/>
+      <c r="CH69" s="56"/>
+      <c r="CI69" s="56"/>
+      <c r="CJ69" s="56"/>
+      <c r="CK69" s="56"/>
+      <c r="CL69" s="56"/>
+      <c r="CM69" s="56"/>
+      <c r="CN69" s="56"/>
+      <c r="CO69" s="56"/>
+      <c r="CP69" s="56"/>
+      <c r="CQ69" s="56"/>
       <c r="CR69" s="42"/>
       <c r="CS69" s="42"/>
       <c r="CT69" s="42"/>
@@ -17976,38 +17948,38 @@
       <c r="W71" s="35"/>
       <c r="X71" s="35"/>
       <c r="Y71" s="35"/>
-      <c r="Z71" s="63" t="s">
+      <c r="Z71" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="AA71" s="63"/>
-      <c r="AB71" s="63"/>
-      <c r="AC71" s="63"/>
-      <c r="AD71" s="63"/>
-      <c r="AE71" s="63"/>
-      <c r="AF71" s="63"/>
-      <c r="AG71" s="63"/>
-      <c r="AH71" s="63"/>
-      <c r="AI71" s="63"/>
-      <c r="AJ71" s="63"/>
-      <c r="AK71" s="63"/>
-      <c r="AL71" s="63"/>
-      <c r="AM71" s="63"/>
-      <c r="AN71" s="63"/>
-      <c r="AO71" s="63"/>
-      <c r="AP71" s="63"/>
-      <c r="AQ71" s="63"/>
-      <c r="AR71" s="63"/>
-      <c r="AS71" s="63"/>
-      <c r="AT71" s="63"/>
-      <c r="AU71" s="63"/>
-      <c r="AV71" s="63"/>
-      <c r="AW71" s="63"/>
-      <c r="AX71" s="63"/>
-      <c r="AY71" s="63"/>
-      <c r="AZ71" s="63"/>
-      <c r="BA71" s="63"/>
-      <c r="BB71" s="63"/>
-      <c r="BC71" s="63"/>
+      <c r="AA71" s="57"/>
+      <c r="AB71" s="57"/>
+      <c r="AC71" s="57"/>
+      <c r="AD71" s="57"/>
+      <c r="AE71" s="57"/>
+      <c r="AF71" s="57"/>
+      <c r="AG71" s="57"/>
+      <c r="AH71" s="57"/>
+      <c r="AI71" s="57"/>
+      <c r="AJ71" s="57"/>
+      <c r="AK71" s="57"/>
+      <c r="AL71" s="57"/>
+      <c r="AM71" s="57"/>
+      <c r="AN71" s="57"/>
+      <c r="AO71" s="57"/>
+      <c r="AP71" s="57"/>
+      <c r="AQ71" s="57"/>
+      <c r="AR71" s="57"/>
+      <c r="AS71" s="57"/>
+      <c r="AT71" s="57"/>
+      <c r="AU71" s="57"/>
+      <c r="AV71" s="57"/>
+      <c r="AW71" s="57"/>
+      <c r="AX71" s="57"/>
+      <c r="AY71" s="57"/>
+      <c r="AZ71" s="57"/>
+      <c r="BA71" s="57"/>
+      <c r="BB71" s="57"/>
+      <c r="BC71" s="57"/>
       <c r="BD71" s="47"/>
       <c r="BE71" s="35"/>
       <c r="BF71" s="35"/>
@@ -18062,36 +18034,36 @@
       <c r="W72" s="35"/>
       <c r="X72" s="35"/>
       <c r="Y72" s="35"/>
-      <c r="Z72" s="63"/>
-      <c r="AA72" s="63"/>
-      <c r="AB72" s="63"/>
-      <c r="AC72" s="63"/>
-      <c r="AD72" s="63"/>
-      <c r="AE72" s="63"/>
-      <c r="AF72" s="63"/>
-      <c r="AG72" s="63"/>
-      <c r="AH72" s="63"/>
-      <c r="AI72" s="63"/>
-      <c r="AJ72" s="63"/>
-      <c r="AK72" s="63"/>
-      <c r="AL72" s="63"/>
-      <c r="AM72" s="63"/>
-      <c r="AN72" s="63"/>
-      <c r="AO72" s="63"/>
-      <c r="AP72" s="63"/>
-      <c r="AQ72" s="63"/>
-      <c r="AR72" s="63"/>
-      <c r="AS72" s="63"/>
-      <c r="AT72" s="63"/>
-      <c r="AU72" s="63"/>
-      <c r="AV72" s="63"/>
-      <c r="AW72" s="63"/>
-      <c r="AX72" s="63"/>
-      <c r="AY72" s="63"/>
-      <c r="AZ72" s="63"/>
-      <c r="BA72" s="63"/>
-      <c r="BB72" s="63"/>
-      <c r="BC72" s="63"/>
+      <c r="Z72" s="57"/>
+      <c r="AA72" s="57"/>
+      <c r="AB72" s="57"/>
+      <c r="AC72" s="57"/>
+      <c r="AD72" s="57"/>
+      <c r="AE72" s="57"/>
+      <c r="AF72" s="57"/>
+      <c r="AG72" s="57"/>
+      <c r="AH72" s="57"/>
+      <c r="AI72" s="57"/>
+      <c r="AJ72" s="57"/>
+      <c r="AK72" s="57"/>
+      <c r="AL72" s="57"/>
+      <c r="AM72" s="57"/>
+      <c r="AN72" s="57"/>
+      <c r="AO72" s="57"/>
+      <c r="AP72" s="57"/>
+      <c r="AQ72" s="57"/>
+      <c r="AR72" s="57"/>
+      <c r="AS72" s="57"/>
+      <c r="AT72" s="57"/>
+      <c r="AU72" s="57"/>
+      <c r="AV72" s="57"/>
+      <c r="AW72" s="57"/>
+      <c r="AX72" s="57"/>
+      <c r="AY72" s="57"/>
+      <c r="AZ72" s="57"/>
+      <c r="BA72" s="57"/>
+      <c r="BB72" s="57"/>
+      <c r="BC72" s="57"/>
       <c r="BD72" s="47"/>
       <c r="BE72" s="35"/>
       <c r="BF72" s="35"/>
@@ -18482,38 +18454,38 @@
       <c r="W77" s="35"/>
       <c r="X77" s="35"/>
       <c r="Y77" s="35"/>
-      <c r="Z77" s="71" t="s">
+      <c r="Z77" s="58" t="s">
         <v>127</v>
       </c>
-      <c r="AA77" s="71"/>
-      <c r="AB77" s="71"/>
-      <c r="AC77" s="71"/>
-      <c r="AD77" s="71"/>
-      <c r="AE77" s="71"/>
-      <c r="AF77" s="71"/>
-      <c r="AG77" s="71"/>
-      <c r="AH77" s="71"/>
-      <c r="AI77" s="71"/>
-      <c r="AJ77" s="71"/>
-      <c r="AK77" s="71"/>
-      <c r="AL77" s="71"/>
-      <c r="AM77" s="71"/>
-      <c r="AN77" s="71"/>
-      <c r="AO77" s="71"/>
-      <c r="AP77" s="71"/>
-      <c r="AQ77" s="71"/>
-      <c r="AR77" s="71"/>
-      <c r="AS77" s="71"/>
-      <c r="AT77" s="71"/>
-      <c r="AU77" s="71"/>
-      <c r="AV77" s="71"/>
-      <c r="AW77" s="71"/>
-      <c r="AX77" s="71"/>
-      <c r="AY77" s="71"/>
-      <c r="AZ77" s="71"/>
-      <c r="BA77" s="71"/>
-      <c r="BB77" s="71"/>
-      <c r="BC77" s="71"/>
+      <c r="AA77" s="58"/>
+      <c r="AB77" s="58"/>
+      <c r="AC77" s="58"/>
+      <c r="AD77" s="58"/>
+      <c r="AE77" s="58"/>
+      <c r="AF77" s="58"/>
+      <c r="AG77" s="58"/>
+      <c r="AH77" s="58"/>
+      <c r="AI77" s="58"/>
+      <c r="AJ77" s="58"/>
+      <c r="AK77" s="58"/>
+      <c r="AL77" s="58"/>
+      <c r="AM77" s="58"/>
+      <c r="AN77" s="58"/>
+      <c r="AO77" s="58"/>
+      <c r="AP77" s="58"/>
+      <c r="AQ77" s="58"/>
+      <c r="AR77" s="58"/>
+      <c r="AS77" s="58"/>
+      <c r="AT77" s="58"/>
+      <c r="AU77" s="58"/>
+      <c r="AV77" s="58"/>
+      <c r="AW77" s="58"/>
+      <c r="AX77" s="58"/>
+      <c r="AY77" s="58"/>
+      <c r="AZ77" s="58"/>
+      <c r="BA77" s="58"/>
+      <c r="BB77" s="58"/>
+      <c r="BC77" s="58"/>
       <c r="BD77" s="49"/>
       <c r="BE77" s="35"/>
       <c r="BF77" s="35"/>
@@ -18568,36 +18540,36 @@
       <c r="W78" s="35"/>
       <c r="X78" s="35"/>
       <c r="Y78" s="35"/>
-      <c r="Z78" s="71"/>
-      <c r="AA78" s="71"/>
-      <c r="AB78" s="71"/>
-      <c r="AC78" s="71"/>
-      <c r="AD78" s="71"/>
-      <c r="AE78" s="71"/>
-      <c r="AF78" s="71"/>
-      <c r="AG78" s="71"/>
-      <c r="AH78" s="71"/>
-      <c r="AI78" s="71"/>
-      <c r="AJ78" s="71"/>
-      <c r="AK78" s="71"/>
-      <c r="AL78" s="71"/>
-      <c r="AM78" s="71"/>
-      <c r="AN78" s="71"/>
-      <c r="AO78" s="71"/>
-      <c r="AP78" s="71"/>
-      <c r="AQ78" s="71"/>
-      <c r="AR78" s="71"/>
-      <c r="AS78" s="71"/>
-      <c r="AT78" s="71"/>
-      <c r="AU78" s="71"/>
-      <c r="AV78" s="71"/>
-      <c r="AW78" s="71"/>
-      <c r="AX78" s="71"/>
-      <c r="AY78" s="71"/>
-      <c r="AZ78" s="71"/>
-      <c r="BA78" s="71"/>
-      <c r="BB78" s="71"/>
-      <c r="BC78" s="71"/>
+      <c r="Z78" s="58"/>
+      <c r="AA78" s="58"/>
+      <c r="AB78" s="58"/>
+      <c r="AC78" s="58"/>
+      <c r="AD78" s="58"/>
+      <c r="AE78" s="58"/>
+      <c r="AF78" s="58"/>
+      <c r="AG78" s="58"/>
+      <c r="AH78" s="58"/>
+      <c r="AI78" s="58"/>
+      <c r="AJ78" s="58"/>
+      <c r="AK78" s="58"/>
+      <c r="AL78" s="58"/>
+      <c r="AM78" s="58"/>
+      <c r="AN78" s="58"/>
+      <c r="AO78" s="58"/>
+      <c r="AP78" s="58"/>
+      <c r="AQ78" s="58"/>
+      <c r="AR78" s="58"/>
+      <c r="AS78" s="58"/>
+      <c r="AT78" s="58"/>
+      <c r="AU78" s="58"/>
+      <c r="AV78" s="58"/>
+      <c r="AW78" s="58"/>
+      <c r="AX78" s="58"/>
+      <c r="AY78" s="58"/>
+      <c r="AZ78" s="58"/>
+      <c r="BA78" s="58"/>
+      <c r="BB78" s="58"/>
+      <c r="BC78" s="58"/>
       <c r="BD78" s="49"/>
       <c r="BE78" s="35"/>
       <c r="BF78" s="35"/>
@@ -18652,36 +18624,36 @@
       <c r="W79" s="35"/>
       <c r="X79" s="35"/>
       <c r="Y79" s="35"/>
-      <c r="Z79" s="71"/>
-      <c r="AA79" s="71"/>
-      <c r="AB79" s="71"/>
-      <c r="AC79" s="71"/>
-      <c r="AD79" s="71"/>
-      <c r="AE79" s="71"/>
-      <c r="AF79" s="71"/>
-      <c r="AG79" s="71"/>
-      <c r="AH79" s="71"/>
-      <c r="AI79" s="71"/>
-      <c r="AJ79" s="71"/>
-      <c r="AK79" s="71"/>
-      <c r="AL79" s="71"/>
-      <c r="AM79" s="71"/>
-      <c r="AN79" s="71"/>
-      <c r="AO79" s="71"/>
-      <c r="AP79" s="71"/>
-      <c r="AQ79" s="71"/>
-      <c r="AR79" s="71"/>
-      <c r="AS79" s="71"/>
-      <c r="AT79" s="71"/>
-      <c r="AU79" s="71"/>
-      <c r="AV79" s="71"/>
-      <c r="AW79" s="71"/>
-      <c r="AX79" s="71"/>
-      <c r="AY79" s="71"/>
-      <c r="AZ79" s="71"/>
-      <c r="BA79" s="71"/>
-      <c r="BB79" s="71"/>
-      <c r="BC79" s="71"/>
+      <c r="Z79" s="58"/>
+      <c r="AA79" s="58"/>
+      <c r="AB79" s="58"/>
+      <c r="AC79" s="58"/>
+      <c r="AD79" s="58"/>
+      <c r="AE79" s="58"/>
+      <c r="AF79" s="58"/>
+      <c r="AG79" s="58"/>
+      <c r="AH79" s="58"/>
+      <c r="AI79" s="58"/>
+      <c r="AJ79" s="58"/>
+      <c r="AK79" s="58"/>
+      <c r="AL79" s="58"/>
+      <c r="AM79" s="58"/>
+      <c r="AN79" s="58"/>
+      <c r="AO79" s="58"/>
+      <c r="AP79" s="58"/>
+      <c r="AQ79" s="58"/>
+      <c r="AR79" s="58"/>
+      <c r="AS79" s="58"/>
+      <c r="AT79" s="58"/>
+      <c r="AU79" s="58"/>
+      <c r="AV79" s="58"/>
+      <c r="AW79" s="58"/>
+      <c r="AX79" s="58"/>
+      <c r="AY79" s="58"/>
+      <c r="AZ79" s="58"/>
+      <c r="BA79" s="58"/>
+      <c r="BB79" s="58"/>
+      <c r="BC79" s="58"/>
       <c r="BD79" s="49"/>
       <c r="BE79" s="35"/>
       <c r="BF79" s="35"/>
@@ -18736,36 +18708,36 @@
       <c r="W80" s="35"/>
       <c r="X80" s="35"/>
       <c r="Y80" s="35"/>
-      <c r="Z80" s="71"/>
-      <c r="AA80" s="71"/>
-      <c r="AB80" s="71"/>
-      <c r="AC80" s="71"/>
-      <c r="AD80" s="71"/>
-      <c r="AE80" s="71"/>
-      <c r="AF80" s="71"/>
-      <c r="AG80" s="71"/>
-      <c r="AH80" s="71"/>
-      <c r="AI80" s="71"/>
-      <c r="AJ80" s="71"/>
-      <c r="AK80" s="71"/>
-      <c r="AL80" s="71"/>
-      <c r="AM80" s="71"/>
-      <c r="AN80" s="71"/>
-      <c r="AO80" s="71"/>
-      <c r="AP80" s="71"/>
-      <c r="AQ80" s="71"/>
-      <c r="AR80" s="71"/>
-      <c r="AS80" s="71"/>
-      <c r="AT80" s="71"/>
-      <c r="AU80" s="71"/>
-      <c r="AV80" s="71"/>
-      <c r="AW80" s="71"/>
-      <c r="AX80" s="71"/>
-      <c r="AY80" s="71"/>
-      <c r="AZ80" s="71"/>
-      <c r="BA80" s="71"/>
-      <c r="BB80" s="71"/>
-      <c r="BC80" s="71"/>
+      <c r="Z80" s="58"/>
+      <c r="AA80" s="58"/>
+      <c r="AB80" s="58"/>
+      <c r="AC80" s="58"/>
+      <c r="AD80" s="58"/>
+      <c r="AE80" s="58"/>
+      <c r="AF80" s="58"/>
+      <c r="AG80" s="58"/>
+      <c r="AH80" s="58"/>
+      <c r="AI80" s="58"/>
+      <c r="AJ80" s="58"/>
+      <c r="AK80" s="58"/>
+      <c r="AL80" s="58"/>
+      <c r="AM80" s="58"/>
+      <c r="AN80" s="58"/>
+      <c r="AO80" s="58"/>
+      <c r="AP80" s="58"/>
+      <c r="AQ80" s="58"/>
+      <c r="AR80" s="58"/>
+      <c r="AS80" s="58"/>
+      <c r="AT80" s="58"/>
+      <c r="AU80" s="58"/>
+      <c r="AV80" s="58"/>
+      <c r="AW80" s="58"/>
+      <c r="AX80" s="58"/>
+      <c r="AY80" s="58"/>
+      <c r="AZ80" s="58"/>
+      <c r="BA80" s="58"/>
+      <c r="BB80" s="58"/>
+      <c r="BC80" s="58"/>
       <c r="BD80" s="49"/>
       <c r="BE80" s="35"/>
       <c r="BF80" s="35"/>
@@ -18812,370 +18784,370 @@
       <c r="CU80" s="35"/>
     </row>
     <row r="81" spans="26:56" ht="6" customHeight="1">
-      <c r="Z81" s="71"/>
-      <c r="AA81" s="71"/>
-      <c r="AB81" s="71"/>
-      <c r="AC81" s="71"/>
-      <c r="AD81" s="71"/>
-      <c r="AE81" s="71"/>
-      <c r="AF81" s="71"/>
-      <c r="AG81" s="71"/>
-      <c r="AH81" s="71"/>
-      <c r="AI81" s="71"/>
-      <c r="AJ81" s="71"/>
-      <c r="AK81" s="71"/>
-      <c r="AL81" s="71"/>
-      <c r="AM81" s="71"/>
-      <c r="AN81" s="71"/>
-      <c r="AO81" s="71"/>
-      <c r="AP81" s="71"/>
-      <c r="AQ81" s="71"/>
-      <c r="AR81" s="71"/>
-      <c r="AS81" s="71"/>
-      <c r="AT81" s="71"/>
-      <c r="AU81" s="71"/>
-      <c r="AV81" s="71"/>
-      <c r="AW81" s="71"/>
-      <c r="AX81" s="71"/>
-      <c r="AY81" s="71"/>
-      <c r="AZ81" s="71"/>
-      <c r="BA81" s="71"/>
-      <c r="BB81" s="71"/>
-      <c r="BC81" s="71"/>
+      <c r="Z81" s="58"/>
+      <c r="AA81" s="58"/>
+      <c r="AB81" s="58"/>
+      <c r="AC81" s="58"/>
+      <c r="AD81" s="58"/>
+      <c r="AE81" s="58"/>
+      <c r="AF81" s="58"/>
+      <c r="AG81" s="58"/>
+      <c r="AH81" s="58"/>
+      <c r="AI81" s="58"/>
+      <c r="AJ81" s="58"/>
+      <c r="AK81" s="58"/>
+      <c r="AL81" s="58"/>
+      <c r="AM81" s="58"/>
+      <c r="AN81" s="58"/>
+      <c r="AO81" s="58"/>
+      <c r="AP81" s="58"/>
+      <c r="AQ81" s="58"/>
+      <c r="AR81" s="58"/>
+      <c r="AS81" s="58"/>
+      <c r="AT81" s="58"/>
+      <c r="AU81" s="58"/>
+      <c r="AV81" s="58"/>
+      <c r="AW81" s="58"/>
+      <c r="AX81" s="58"/>
+      <c r="AY81" s="58"/>
+      <c r="AZ81" s="58"/>
+      <c r="BA81" s="58"/>
+      <c r="BB81" s="58"/>
+      <c r="BC81" s="58"/>
       <c r="BD81" s="49"/>
     </row>
     <row r="82" spans="26:56" ht="6" customHeight="1">
-      <c r="Z82" s="71" t="s">
+      <c r="Z82" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="AA82" s="71"/>
-      <c r="AB82" s="71"/>
-      <c r="AC82" s="71"/>
-      <c r="AD82" s="71"/>
-      <c r="AE82" s="71"/>
-      <c r="AF82" s="71"/>
-      <c r="AG82" s="71"/>
-      <c r="AH82" s="71"/>
-      <c r="AI82" s="71"/>
-      <c r="AJ82" s="71"/>
-      <c r="AK82" s="71"/>
-      <c r="AL82" s="71"/>
-      <c r="AM82" s="71"/>
-      <c r="AN82" s="71"/>
-      <c r="AO82" s="71"/>
-      <c r="AP82" s="71"/>
-      <c r="AQ82" s="71"/>
-      <c r="AR82" s="71"/>
-      <c r="AS82" s="71"/>
-      <c r="AT82" s="71"/>
-      <c r="AU82" s="71"/>
-      <c r="AV82" s="71"/>
-      <c r="AW82" s="71"/>
-      <c r="AX82" s="71"/>
-      <c r="AY82" s="71"/>
-      <c r="AZ82" s="71"/>
-      <c r="BA82" s="71"/>
-      <c r="BB82" s="71"/>
-      <c r="BC82" s="71"/>
+      <c r="AA82" s="58"/>
+      <c r="AB82" s="58"/>
+      <c r="AC82" s="58"/>
+      <c r="AD82" s="58"/>
+      <c r="AE82" s="58"/>
+      <c r="AF82" s="58"/>
+      <c r="AG82" s="58"/>
+      <c r="AH82" s="58"/>
+      <c r="AI82" s="58"/>
+      <c r="AJ82" s="58"/>
+      <c r="AK82" s="58"/>
+      <c r="AL82" s="58"/>
+      <c r="AM82" s="58"/>
+      <c r="AN82" s="58"/>
+      <c r="AO82" s="58"/>
+      <c r="AP82" s="58"/>
+      <c r="AQ82" s="58"/>
+      <c r="AR82" s="58"/>
+      <c r="AS82" s="58"/>
+      <c r="AT82" s="58"/>
+      <c r="AU82" s="58"/>
+      <c r="AV82" s="58"/>
+      <c r="AW82" s="58"/>
+      <c r="AX82" s="58"/>
+      <c r="AY82" s="58"/>
+      <c r="AZ82" s="58"/>
+      <c r="BA82" s="58"/>
+      <c r="BB82" s="58"/>
+      <c r="BC82" s="58"/>
       <c r="BD82" s="49"/>
     </row>
     <row r="83" spans="26:56" ht="6" customHeight="1">
-      <c r="Z83" s="71"/>
-      <c r="AA83" s="71"/>
-      <c r="AB83" s="71"/>
-      <c r="AC83" s="71"/>
-      <c r="AD83" s="71"/>
-      <c r="AE83" s="71"/>
-      <c r="AF83" s="71"/>
-      <c r="AG83" s="71"/>
-      <c r="AH83" s="71"/>
-      <c r="AI83" s="71"/>
-      <c r="AJ83" s="71"/>
-      <c r="AK83" s="71"/>
-      <c r="AL83" s="71"/>
-      <c r="AM83" s="71"/>
-      <c r="AN83" s="71"/>
-      <c r="AO83" s="71"/>
-      <c r="AP83" s="71"/>
-      <c r="AQ83" s="71"/>
-      <c r="AR83" s="71"/>
-      <c r="AS83" s="71"/>
-      <c r="AT83" s="71"/>
-      <c r="AU83" s="71"/>
-      <c r="AV83" s="71"/>
-      <c r="AW83" s="71"/>
-      <c r="AX83" s="71"/>
-      <c r="AY83" s="71"/>
-      <c r="AZ83" s="71"/>
-      <c r="BA83" s="71"/>
-      <c r="BB83" s="71"/>
-      <c r="BC83" s="71"/>
+      <c r="Z83" s="58"/>
+      <c r="AA83" s="58"/>
+      <c r="AB83" s="58"/>
+      <c r="AC83" s="58"/>
+      <c r="AD83" s="58"/>
+      <c r="AE83" s="58"/>
+      <c r="AF83" s="58"/>
+      <c r="AG83" s="58"/>
+      <c r="AH83" s="58"/>
+      <c r="AI83" s="58"/>
+      <c r="AJ83" s="58"/>
+      <c r="AK83" s="58"/>
+      <c r="AL83" s="58"/>
+      <c r="AM83" s="58"/>
+      <c r="AN83" s="58"/>
+      <c r="AO83" s="58"/>
+      <c r="AP83" s="58"/>
+      <c r="AQ83" s="58"/>
+      <c r="AR83" s="58"/>
+      <c r="AS83" s="58"/>
+      <c r="AT83" s="58"/>
+      <c r="AU83" s="58"/>
+      <c r="AV83" s="58"/>
+      <c r="AW83" s="58"/>
+      <c r="AX83" s="58"/>
+      <c r="AY83" s="58"/>
+      <c r="AZ83" s="58"/>
+      <c r="BA83" s="58"/>
+      <c r="BB83" s="58"/>
+      <c r="BC83" s="58"/>
       <c r="BD83" s="49"/>
     </row>
     <row r="84" spans="26:56" ht="6" customHeight="1">
-      <c r="Z84" s="71"/>
-      <c r="AA84" s="71"/>
-      <c r="AB84" s="71"/>
-      <c r="AC84" s="71"/>
-      <c r="AD84" s="71"/>
-      <c r="AE84" s="71"/>
-      <c r="AF84" s="71"/>
-      <c r="AG84" s="71"/>
-      <c r="AH84" s="71"/>
-      <c r="AI84" s="71"/>
-      <c r="AJ84" s="71"/>
-      <c r="AK84" s="71"/>
-      <c r="AL84" s="71"/>
-      <c r="AM84" s="71"/>
-      <c r="AN84" s="71"/>
-      <c r="AO84" s="71"/>
-      <c r="AP84" s="71"/>
-      <c r="AQ84" s="71"/>
-      <c r="AR84" s="71"/>
-      <c r="AS84" s="71"/>
-      <c r="AT84" s="71"/>
-      <c r="AU84" s="71"/>
-      <c r="AV84" s="71"/>
-      <c r="AW84" s="71"/>
-      <c r="AX84" s="71"/>
-      <c r="AY84" s="71"/>
-      <c r="AZ84" s="71"/>
-      <c r="BA84" s="71"/>
-      <c r="BB84" s="71"/>
-      <c r="BC84" s="71"/>
+      <c r="Z84" s="58"/>
+      <c r="AA84" s="58"/>
+      <c r="AB84" s="58"/>
+      <c r="AC84" s="58"/>
+      <c r="AD84" s="58"/>
+      <c r="AE84" s="58"/>
+      <c r="AF84" s="58"/>
+      <c r="AG84" s="58"/>
+      <c r="AH84" s="58"/>
+      <c r="AI84" s="58"/>
+      <c r="AJ84" s="58"/>
+      <c r="AK84" s="58"/>
+      <c r="AL84" s="58"/>
+      <c r="AM84" s="58"/>
+      <c r="AN84" s="58"/>
+      <c r="AO84" s="58"/>
+      <c r="AP84" s="58"/>
+      <c r="AQ84" s="58"/>
+      <c r="AR84" s="58"/>
+      <c r="AS84" s="58"/>
+      <c r="AT84" s="58"/>
+      <c r="AU84" s="58"/>
+      <c r="AV84" s="58"/>
+      <c r="AW84" s="58"/>
+      <c r="AX84" s="58"/>
+      <c r="AY84" s="58"/>
+      <c r="AZ84" s="58"/>
+      <c r="BA84" s="58"/>
+      <c r="BB84" s="58"/>
+      <c r="BC84" s="58"/>
       <c r="BD84" s="49"/>
     </row>
     <row r="85" spans="26:56" ht="6" customHeight="1">
-      <c r="Z85" s="71"/>
-      <c r="AA85" s="71"/>
-      <c r="AB85" s="71"/>
-      <c r="AC85" s="71"/>
-      <c r="AD85" s="71"/>
-      <c r="AE85" s="71"/>
-      <c r="AF85" s="71"/>
-      <c r="AG85" s="71"/>
-      <c r="AH85" s="71"/>
-      <c r="AI85" s="71"/>
-      <c r="AJ85" s="71"/>
-      <c r="AK85" s="71"/>
-      <c r="AL85" s="71"/>
-      <c r="AM85" s="71"/>
-      <c r="AN85" s="71"/>
-      <c r="AO85" s="71"/>
-      <c r="AP85" s="71"/>
-      <c r="AQ85" s="71"/>
-      <c r="AR85" s="71"/>
-      <c r="AS85" s="71"/>
-      <c r="AT85" s="71"/>
-      <c r="AU85" s="71"/>
-      <c r="AV85" s="71"/>
-      <c r="AW85" s="71"/>
-      <c r="AX85" s="71"/>
-      <c r="AY85" s="71"/>
-      <c r="AZ85" s="71"/>
-      <c r="BA85" s="71"/>
-      <c r="BB85" s="71"/>
-      <c r="BC85" s="71"/>
+      <c r="Z85" s="58"/>
+      <c r="AA85" s="58"/>
+      <c r="AB85" s="58"/>
+      <c r="AC85" s="58"/>
+      <c r="AD85" s="58"/>
+      <c r="AE85" s="58"/>
+      <c r="AF85" s="58"/>
+      <c r="AG85" s="58"/>
+      <c r="AH85" s="58"/>
+      <c r="AI85" s="58"/>
+      <c r="AJ85" s="58"/>
+      <c r="AK85" s="58"/>
+      <c r="AL85" s="58"/>
+      <c r="AM85" s="58"/>
+      <c r="AN85" s="58"/>
+      <c r="AO85" s="58"/>
+      <c r="AP85" s="58"/>
+      <c r="AQ85" s="58"/>
+      <c r="AR85" s="58"/>
+      <c r="AS85" s="58"/>
+      <c r="AT85" s="58"/>
+      <c r="AU85" s="58"/>
+      <c r="AV85" s="58"/>
+      <c r="AW85" s="58"/>
+      <c r="AX85" s="58"/>
+      <c r="AY85" s="58"/>
+      <c r="AZ85" s="58"/>
+      <c r="BA85" s="58"/>
+      <c r="BB85" s="58"/>
+      <c r="BC85" s="58"/>
       <c r="BD85" s="49"/>
     </row>
     <row r="86" spans="26:56" ht="6" customHeight="1">
-      <c r="Z86" s="71"/>
-      <c r="AA86" s="71"/>
-      <c r="AB86" s="71"/>
-      <c r="AC86" s="71"/>
-      <c r="AD86" s="71"/>
-      <c r="AE86" s="71"/>
-      <c r="AF86" s="71"/>
-      <c r="AG86" s="71"/>
-      <c r="AH86" s="71"/>
-      <c r="AI86" s="71"/>
-      <c r="AJ86" s="71"/>
-      <c r="AK86" s="71"/>
-      <c r="AL86" s="71"/>
-      <c r="AM86" s="71"/>
-      <c r="AN86" s="71"/>
-      <c r="AO86" s="71"/>
-      <c r="AP86" s="71"/>
-      <c r="AQ86" s="71"/>
-      <c r="AR86" s="71"/>
-      <c r="AS86" s="71"/>
-      <c r="AT86" s="71"/>
-      <c r="AU86" s="71"/>
-      <c r="AV86" s="71"/>
-      <c r="AW86" s="71"/>
-      <c r="AX86" s="71"/>
-      <c r="AY86" s="71"/>
-      <c r="AZ86" s="71"/>
-      <c r="BA86" s="71"/>
-      <c r="BB86" s="71"/>
-      <c r="BC86" s="71"/>
+      <c r="Z86" s="58"/>
+      <c r="AA86" s="58"/>
+      <c r="AB86" s="58"/>
+      <c r="AC86" s="58"/>
+      <c r="AD86" s="58"/>
+      <c r="AE86" s="58"/>
+      <c r="AF86" s="58"/>
+      <c r="AG86" s="58"/>
+      <c r="AH86" s="58"/>
+      <c r="AI86" s="58"/>
+      <c r="AJ86" s="58"/>
+      <c r="AK86" s="58"/>
+      <c r="AL86" s="58"/>
+      <c r="AM86" s="58"/>
+      <c r="AN86" s="58"/>
+      <c r="AO86" s="58"/>
+      <c r="AP86" s="58"/>
+      <c r="AQ86" s="58"/>
+      <c r="AR86" s="58"/>
+      <c r="AS86" s="58"/>
+      <c r="AT86" s="58"/>
+      <c r="AU86" s="58"/>
+      <c r="AV86" s="58"/>
+      <c r="AW86" s="58"/>
+      <c r="AX86" s="58"/>
+      <c r="AY86" s="58"/>
+      <c r="AZ86" s="58"/>
+      <c r="BA86" s="58"/>
+      <c r="BB86" s="58"/>
+      <c r="BC86" s="58"/>
       <c r="BD86" s="49"/>
     </row>
     <row r="87" spans="26:56" ht="6" customHeight="1">
-      <c r="Z87" s="71"/>
-      <c r="AA87" s="71"/>
-      <c r="AB87" s="71"/>
-      <c r="AC87" s="71"/>
-      <c r="AD87" s="71"/>
-      <c r="AE87" s="71"/>
-      <c r="AF87" s="71"/>
-      <c r="AG87" s="71"/>
-      <c r="AH87" s="71"/>
-      <c r="AI87" s="71"/>
-      <c r="AJ87" s="71"/>
-      <c r="AK87" s="71"/>
-      <c r="AL87" s="71"/>
-      <c r="AM87" s="71"/>
-      <c r="AN87" s="71"/>
-      <c r="AO87" s="71"/>
-      <c r="AP87" s="71"/>
-      <c r="AQ87" s="71"/>
-      <c r="AR87" s="71"/>
-      <c r="AS87" s="71"/>
-      <c r="AT87" s="71"/>
-      <c r="AU87" s="71"/>
-      <c r="AV87" s="71"/>
-      <c r="AW87" s="71"/>
-      <c r="AX87" s="71"/>
-      <c r="AY87" s="71"/>
-      <c r="AZ87" s="71"/>
-      <c r="BA87" s="71"/>
-      <c r="BB87" s="71"/>
-      <c r="BC87" s="71"/>
+      <c r="Z87" s="58"/>
+      <c r="AA87" s="58"/>
+      <c r="AB87" s="58"/>
+      <c r="AC87" s="58"/>
+      <c r="AD87" s="58"/>
+      <c r="AE87" s="58"/>
+      <c r="AF87" s="58"/>
+      <c r="AG87" s="58"/>
+      <c r="AH87" s="58"/>
+      <c r="AI87" s="58"/>
+      <c r="AJ87" s="58"/>
+      <c r="AK87" s="58"/>
+      <c r="AL87" s="58"/>
+      <c r="AM87" s="58"/>
+      <c r="AN87" s="58"/>
+      <c r="AO87" s="58"/>
+      <c r="AP87" s="58"/>
+      <c r="AQ87" s="58"/>
+      <c r="AR87" s="58"/>
+      <c r="AS87" s="58"/>
+      <c r="AT87" s="58"/>
+      <c r="AU87" s="58"/>
+      <c r="AV87" s="58"/>
+      <c r="AW87" s="58"/>
+      <c r="AX87" s="58"/>
+      <c r="AY87" s="58"/>
+      <c r="AZ87" s="58"/>
+      <c r="BA87" s="58"/>
+      <c r="BB87" s="58"/>
+      <c r="BC87" s="58"/>
       <c r="BD87" s="49"/>
     </row>
     <row r="88" spans="26:56" ht="6" customHeight="1">
-      <c r="Z88" s="71"/>
-      <c r="AA88" s="71"/>
-      <c r="AB88" s="71"/>
-      <c r="AC88" s="71"/>
-      <c r="AD88" s="71"/>
-      <c r="AE88" s="71"/>
-      <c r="AF88" s="71"/>
-      <c r="AG88" s="71"/>
-      <c r="AH88" s="71"/>
-      <c r="AI88" s="71"/>
-      <c r="AJ88" s="71"/>
-      <c r="AK88" s="71"/>
-      <c r="AL88" s="71"/>
-      <c r="AM88" s="71"/>
-      <c r="AN88" s="71"/>
-      <c r="AO88" s="71"/>
-      <c r="AP88" s="71"/>
-      <c r="AQ88" s="71"/>
-      <c r="AR88" s="71"/>
-      <c r="AS88" s="71"/>
-      <c r="AT88" s="71"/>
-      <c r="AU88" s="71"/>
-      <c r="AV88" s="71"/>
-      <c r="AW88" s="71"/>
-      <c r="AX88" s="71"/>
-      <c r="AY88" s="71"/>
-      <c r="AZ88" s="71"/>
-      <c r="BA88" s="71"/>
-      <c r="BB88" s="71"/>
-      <c r="BC88" s="71"/>
+      <c r="Z88" s="58"/>
+      <c r="AA88" s="58"/>
+      <c r="AB88" s="58"/>
+      <c r="AC88" s="58"/>
+      <c r="AD88" s="58"/>
+      <c r="AE88" s="58"/>
+      <c r="AF88" s="58"/>
+      <c r="AG88" s="58"/>
+      <c r="AH88" s="58"/>
+      <c r="AI88" s="58"/>
+      <c r="AJ88" s="58"/>
+      <c r="AK88" s="58"/>
+      <c r="AL88" s="58"/>
+      <c r="AM88" s="58"/>
+      <c r="AN88" s="58"/>
+      <c r="AO88" s="58"/>
+      <c r="AP88" s="58"/>
+      <c r="AQ88" s="58"/>
+      <c r="AR88" s="58"/>
+      <c r="AS88" s="58"/>
+      <c r="AT88" s="58"/>
+      <c r="AU88" s="58"/>
+      <c r="AV88" s="58"/>
+      <c r="AW88" s="58"/>
+      <c r="AX88" s="58"/>
+      <c r="AY88" s="58"/>
+      <c r="AZ88" s="58"/>
+      <c r="BA88" s="58"/>
+      <c r="BB88" s="58"/>
+      <c r="BC88" s="58"/>
       <c r="BD88" s="49"/>
     </row>
     <row r="89" spans="26:56" ht="6" customHeight="1">
-      <c r="Z89" s="71"/>
-      <c r="AA89" s="71"/>
-      <c r="AB89" s="71"/>
-      <c r="AC89" s="71"/>
-      <c r="AD89" s="71"/>
-      <c r="AE89" s="71"/>
-      <c r="AF89" s="71"/>
-      <c r="AG89" s="71"/>
-      <c r="AH89" s="71"/>
-      <c r="AI89" s="71"/>
-      <c r="AJ89" s="71"/>
-      <c r="AK89" s="71"/>
-      <c r="AL89" s="71"/>
-      <c r="AM89" s="71"/>
-      <c r="AN89" s="71"/>
-      <c r="AO89" s="71"/>
-      <c r="AP89" s="71"/>
-      <c r="AQ89" s="71"/>
-      <c r="AR89" s="71"/>
-      <c r="AS89" s="71"/>
-      <c r="AT89" s="71"/>
-      <c r="AU89" s="71"/>
-      <c r="AV89" s="71"/>
-      <c r="AW89" s="71"/>
-      <c r="AX89" s="71"/>
-      <c r="AY89" s="71"/>
-      <c r="AZ89" s="71"/>
-      <c r="BA89" s="71"/>
-      <c r="BB89" s="71"/>
-      <c r="BC89" s="71"/>
+      <c r="Z89" s="58"/>
+      <c r="AA89" s="58"/>
+      <c r="AB89" s="58"/>
+      <c r="AC89" s="58"/>
+      <c r="AD89" s="58"/>
+      <c r="AE89" s="58"/>
+      <c r="AF89" s="58"/>
+      <c r="AG89" s="58"/>
+      <c r="AH89" s="58"/>
+      <c r="AI89" s="58"/>
+      <c r="AJ89" s="58"/>
+      <c r="AK89" s="58"/>
+      <c r="AL89" s="58"/>
+      <c r="AM89" s="58"/>
+      <c r="AN89" s="58"/>
+      <c r="AO89" s="58"/>
+      <c r="AP89" s="58"/>
+      <c r="AQ89" s="58"/>
+      <c r="AR89" s="58"/>
+      <c r="AS89" s="58"/>
+      <c r="AT89" s="58"/>
+      <c r="AU89" s="58"/>
+      <c r="AV89" s="58"/>
+      <c r="AW89" s="58"/>
+      <c r="AX89" s="58"/>
+      <c r="AY89" s="58"/>
+      <c r="AZ89" s="58"/>
+      <c r="BA89" s="58"/>
+      <c r="BB89" s="58"/>
+      <c r="BC89" s="58"/>
       <c r="BD89" s="49"/>
     </row>
     <row r="90" spans="26:56" ht="6" customHeight="1">
-      <c r="Z90" s="70" t="s">
+      <c r="Z90" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="AA90" s="70"/>
-      <c r="AB90" s="70"/>
-      <c r="AC90" s="70"/>
-      <c r="AD90" s="70"/>
-      <c r="AE90" s="70"/>
-      <c r="AF90" s="70"/>
-      <c r="AG90" s="70"/>
-      <c r="AH90" s="70"/>
-      <c r="AI90" s="70"/>
-      <c r="AJ90" s="70"/>
-      <c r="AK90" s="70"/>
-      <c r="AL90" s="70"/>
-      <c r="AM90" s="70"/>
-      <c r="AN90" s="70"/>
-      <c r="AO90" s="70"/>
-      <c r="AP90" s="70"/>
-      <c r="AQ90" s="70"/>
-      <c r="AR90" s="70"/>
-      <c r="AS90" s="70"/>
-      <c r="AT90" s="70"/>
-      <c r="AU90" s="70"/>
-      <c r="AV90" s="70"/>
-      <c r="AW90" s="70"/>
-      <c r="AX90" s="70"/>
-      <c r="AY90" s="70"/>
-      <c r="AZ90" s="70"/>
-      <c r="BA90" s="70"/>
-      <c r="BB90" s="70"/>
-      <c r="BC90" s="70"/>
+      <c r="AA90" s="52"/>
+      <c r="AB90" s="52"/>
+      <c r="AC90" s="52"/>
+      <c r="AD90" s="52"/>
+      <c r="AE90" s="52"/>
+      <c r="AF90" s="52"/>
+      <c r="AG90" s="52"/>
+      <c r="AH90" s="52"/>
+      <c r="AI90" s="52"/>
+      <c r="AJ90" s="52"/>
+      <c r="AK90" s="52"/>
+      <c r="AL90" s="52"/>
+      <c r="AM90" s="52"/>
+      <c r="AN90" s="52"/>
+      <c r="AO90" s="52"/>
+      <c r="AP90" s="52"/>
+      <c r="AQ90" s="52"/>
+      <c r="AR90" s="52"/>
+      <c r="AS90" s="52"/>
+      <c r="AT90" s="52"/>
+      <c r="AU90" s="52"/>
+      <c r="AV90" s="52"/>
+      <c r="AW90" s="52"/>
+      <c r="AX90" s="52"/>
+      <c r="AY90" s="52"/>
+      <c r="AZ90" s="52"/>
+      <c r="BA90" s="52"/>
+      <c r="BB90" s="52"/>
+      <c r="BC90" s="52"/>
       <c r="BD90" s="50"/>
     </row>
     <row r="91" spans="26:56" ht="6" customHeight="1">
-      <c r="Z91" s="70"/>
-      <c r="AA91" s="70"/>
-      <c r="AB91" s="70"/>
-      <c r="AC91" s="70"/>
-      <c r="AD91" s="70"/>
-      <c r="AE91" s="70"/>
-      <c r="AF91" s="70"/>
-      <c r="AG91" s="70"/>
-      <c r="AH91" s="70"/>
-      <c r="AI91" s="70"/>
-      <c r="AJ91" s="70"/>
-      <c r="AK91" s="70"/>
-      <c r="AL91" s="70"/>
-      <c r="AM91" s="70"/>
-      <c r="AN91" s="70"/>
-      <c r="AO91" s="70"/>
-      <c r="AP91" s="70"/>
-      <c r="AQ91" s="70"/>
-      <c r="AR91" s="70"/>
-      <c r="AS91" s="70"/>
-      <c r="AT91" s="70"/>
-      <c r="AU91" s="70"/>
-      <c r="AV91" s="70"/>
-      <c r="AW91" s="70"/>
-      <c r="AX91" s="70"/>
-      <c r="AY91" s="70"/>
-      <c r="AZ91" s="70"/>
-      <c r="BA91" s="70"/>
-      <c r="BB91" s="70"/>
-      <c r="BC91" s="70"/>
+      <c r="Z91" s="52"/>
+      <c r="AA91" s="52"/>
+      <c r="AB91" s="52"/>
+      <c r="AC91" s="52"/>
+      <c r="AD91" s="52"/>
+      <c r="AE91" s="52"/>
+      <c r="AF91" s="52"/>
+      <c r="AG91" s="52"/>
+      <c r="AH91" s="52"/>
+      <c r="AI91" s="52"/>
+      <c r="AJ91" s="52"/>
+      <c r="AK91" s="52"/>
+      <c r="AL91" s="52"/>
+      <c r="AM91" s="52"/>
+      <c r="AN91" s="52"/>
+      <c r="AO91" s="52"/>
+      <c r="AP91" s="52"/>
+      <c r="AQ91" s="52"/>
+      <c r="AR91" s="52"/>
+      <c r="AS91" s="52"/>
+      <c r="AT91" s="52"/>
+      <c r="AU91" s="52"/>
+      <c r="AV91" s="52"/>
+      <c r="AW91" s="52"/>
+      <c r="AX91" s="52"/>
+      <c r="AY91" s="52"/>
+      <c r="AZ91" s="52"/>
+      <c r="BA91" s="52"/>
+      <c r="BB91" s="52"/>
+      <c r="BC91" s="52"/>
       <c r="BD91" s="50"/>
     </row>
     <row r="92" spans="26:56" ht="6" customHeight="1">
@@ -19312,25 +19284,13 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="Z90:BC91"/>
-    <mergeCell ref="Z65:BC69"/>
-    <mergeCell ref="BN65:CQ67"/>
-    <mergeCell ref="BN68:CQ69"/>
-    <mergeCell ref="Z71:BC72"/>
-    <mergeCell ref="Z77:BC81"/>
-    <mergeCell ref="Z82:BC89"/>
-    <mergeCell ref="Z59:BC61"/>
-    <mergeCell ref="BN59:CQ61"/>
-    <mergeCell ref="B60:P62"/>
-    <mergeCell ref="Z62:BC63"/>
-    <mergeCell ref="BN62:CQ63"/>
-    <mergeCell ref="B63:P64"/>
-    <mergeCell ref="Z48:BC50"/>
-    <mergeCell ref="B51:P52"/>
-    <mergeCell ref="Z51:BC52"/>
-    <mergeCell ref="B54:P56"/>
-    <mergeCell ref="Z54:BC58"/>
-    <mergeCell ref="B57:P58"/>
+    <mergeCell ref="BN9:CQ11"/>
+    <mergeCell ref="BN12:CQ13"/>
+    <mergeCell ref="Z2:BC3"/>
+    <mergeCell ref="Z4:BC6"/>
+    <mergeCell ref="R5:W7"/>
+    <mergeCell ref="BF5:BK7"/>
+    <mergeCell ref="Z9:BC13"/>
     <mergeCell ref="Z43:BC47"/>
     <mergeCell ref="BN43:CQ44"/>
     <mergeCell ref="Z14:BC16"/>
@@ -19344,13 +19304,25 @@
     <mergeCell ref="BN37:CQ38"/>
     <mergeCell ref="Z40:BC41"/>
     <mergeCell ref="BN40:CQ42"/>
-    <mergeCell ref="BN9:CQ11"/>
-    <mergeCell ref="BN12:CQ13"/>
-    <mergeCell ref="Z2:BC3"/>
-    <mergeCell ref="Z4:BC6"/>
-    <mergeCell ref="R5:W7"/>
-    <mergeCell ref="BF5:BK7"/>
-    <mergeCell ref="Z9:BC13"/>
+    <mergeCell ref="Z48:BC50"/>
+    <mergeCell ref="B51:P52"/>
+    <mergeCell ref="Z51:BC52"/>
+    <mergeCell ref="B54:P56"/>
+    <mergeCell ref="Z54:BC58"/>
+    <mergeCell ref="B57:P58"/>
+    <mergeCell ref="Z59:BC61"/>
+    <mergeCell ref="BN59:CQ61"/>
+    <mergeCell ref="B60:P62"/>
+    <mergeCell ref="Z62:BC63"/>
+    <mergeCell ref="BN62:CQ63"/>
+    <mergeCell ref="B63:P64"/>
+    <mergeCell ref="Z90:BC91"/>
+    <mergeCell ref="Z65:BC69"/>
+    <mergeCell ref="BN65:CQ67"/>
+    <mergeCell ref="BN68:CQ69"/>
+    <mergeCell ref="Z71:BC72"/>
+    <mergeCell ref="Z77:BC81"/>
+    <mergeCell ref="Z82:BC89"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B63" r:id="rId1" xr:uid="{189F5753-E498-40D4-9164-AE23048F312F}"/>
@@ -19483,7 +19455,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="4" t="b">
-        <f t="shared" ref="L6:V13" si="0">$A6=$B$1</f>
+        <f t="shared" ref="L6:R13" si="0">$A6=$B$1</f>
         <v>0</v>
       </c>
       <c r="M6" s="4" t="b">
@@ -19905,14 +19877,14 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B6:G12">
-    <cfRule type="expression" dxfId="6" priority="3">
-      <formula>$A6=$B$1</formula>
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>AND($A6=$B$1,B$5=$B$2)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>B$5=$B$2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>AND($A6=$B$1,B$5=$B$2)</formula>
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>$A6=$B$1</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -20545,11 +20517,11 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:E32">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>OR(WEEKDAY($A3,2)=6,WEEKDAY($A3,2)=7)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>OR(WEEKDAY(A3,2)=6,WEEKDAY(A3,2)=7)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>OR(WEEKDAY($A3,2)=6,WEEKDAY($A3,2)=7)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20563,79 +20535,132 @@
     <tabColor rgb="FF1E73BE"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:2">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="B2" s="4">
+        <f>COUNTIF($A$2:A2,A2)-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="B3" s="4">
+        <f>COUNTIF($A$2:A3,A3)-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="B4" s="4">
+        <f>COUNTIF($A$2:A4,A4)-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
+      <c r="B5" s="4">
+        <f>COUNTIF($A$2:A5,A5)-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
+      <c r="B6" s="4">
+        <f>COUNTIF($A$2:A6,A6)-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
+      <c r="B7" s="4">
+        <f>COUNTIF($A$2:A7,A7)-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
+      <c r="B8" s="4">
+        <f>COUNTIF($A$2:A8,A8)-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
+      <c r="B9" s="4">
+        <f>COUNTIF($A$2:A9,A9)-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
+      <c r="B10" s="4">
+        <f>COUNTIF($A$2:A10,A10)-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
+      <c r="B11" s="4">
+        <f>COUNTIF($A$2:A11,A11)-1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
+      <c r="B12" s="4">
+        <f>COUNTIF($A$2:A12,A12)-1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
+      <c r="B13" s="4">
+        <f>COUNTIF($A$2:A13,A13)-1</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2:A13">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>COUNTIF($A$2:A2,A2)-1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -20646,7 +20671,7 @@
   <sheetPr codeName="Arkusz16">
     <tabColor rgb="FF1E73BE"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="4" bestFit="1" customWidth="1"/>
@@ -20657,7 +20682,7 @@
     <col min="6" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -20669,7 +20694,7 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -20679,9 +20704,16 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2" s="3">
+        <f>COUNTIF($C$2:$C$15,A2)</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="e">
+        <f>MATCH(A2,$C$2:$C$15,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -20691,9 +20723,16 @@
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="F3" s="3">
+        <f t="shared" ref="F3:F15" si="0">COUNTIF($C$2:$C$15,A3)</f>
+        <v>1</v>
+      </c>
+      <c r="G3" s="4">
+        <f t="shared" ref="G3:G15" si="1">MATCH(A3,$C$2:$C$15,0)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
@@ -20703,9 +20742,16 @@
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
@@ -20715,9 +20761,16 @@
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
         <v>74</v>
       </c>
@@ -20727,9 +20780,16 @@
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
@@ -20739,9 +20799,16 @@
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="6" t="s">
         <v>77</v>
       </c>
@@ -20751,9 +20818,16 @@
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
@@ -20763,9 +20837,16 @@
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="5" t="s">
         <v>80</v>
       </c>
@@ -20775,9 +20856,16 @@
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
@@ -20787,9 +20875,16 @@
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F11" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="6" t="s">
         <v>15</v>
       </c>
@@ -20799,9 +20894,16 @@
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="F12" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
@@ -20811,9 +20913,16 @@
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="F13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="6" t="s">
@@ -20821,9 +20930,16 @@
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="F14" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="6" t="s">
@@ -20831,7 +20947,14 @@
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -21018,13 +21141,13 @@
     <sortCondition ref="G3"/>
   </sortState>
   <conditionalFormatting sqref="A3:A14">
-    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:C14">
-    <cfRule type="aboveAverage" dxfId="15" priority="2"/>
+    <cfRule type="aboveAverage" dxfId="11" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F12">
-    <cfRule type="top10" dxfId="14" priority="1" percent="1" rank="30"/>
+    <cfRule type="top10" dxfId="10" priority="1" percent="1" rank="30"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21890,10 +22013,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:E7">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="greaterThan">
       <formula>8000</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="greaterThan">
       <formula>4000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22081,7 +22204,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G11">
-    <cfRule type="aboveAverage" dxfId="11" priority="5"/>
+    <cfRule type="aboveAverage" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -29092,7 +29215,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:D435">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>$C3&gt;$F$1</formula>
     </cfRule>
   </conditionalFormatting>
